--- a/data/italy/p6_deployment/data_preparation/construct_data/df_matches_to_construct_historic_values.xlsx
+++ b/data/italy/p6_deployment/data_preparation/construct_data/df_matches_to_construct_historic_values.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -55,11 +58,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:BN1"/>
+  <dimension ref="A1:BN5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -754,6 +758,466 @@
           <t>sum_pot_player_miss_away</t>
         </is>
       </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>WlhYT07d</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>45508.65625</v>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio partenio adriano lombardi
+  avellino </t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>26000</v>
+      </c>
+      <c r="F2" t="n">
+        <v>5050</v>
+      </c>
+      <c r="G2" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>A332L1f5</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>hKSfjtsQ</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="n">
+        <v>77</v>
+      </c>
+      <c r="X2" t="n">
+        <v>773</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>182.8333333333333</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>67.16666666666667</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>1137500</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>69</v>
+      </c>
+      <c r="AU2" t="inlineStr"/>
+      <c r="AV2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr"/>
+      <c r="AX2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr"/>
+      <c r="BA2" t="inlineStr"/>
+      <c r="BB2" t="inlineStr"/>
+      <c r="BC2" t="inlineStr"/>
+      <c r="BD2" t="inlineStr"/>
+      <c r="BE2" t="inlineStr"/>
+      <c r="BF2" t="inlineStr"/>
+      <c r="BG2" t="inlineStr"/>
+      <c r="BH2" t="inlineStr"/>
+      <c r="BI2" t="inlineStr"/>
+      <c r="BJ2" t="inlineStr"/>
+      <c r="BK2" t="inlineStr"/>
+      <c r="BL2" t="inlineStr"/>
+      <c r="BM2" t="inlineStr"/>
+      <c r="BN2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>SzxylMbS</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>45508.64583333334</v>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio dino manuzzi
+  cesena </t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>23860</v>
+      </c>
+      <c r="F3" t="n">
+        <v>4468</v>
+      </c>
+      <c r="G3" t="n">
+        <v>3</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>xddf1qfh</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>2gUwEtrE</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="n">
+        <v>77</v>
+      </c>
+      <c r="X3" t="n">
+        <v>773</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA3" t="inlineStr"/>
+      <c r="AB3" t="inlineStr"/>
+      <c r="AC3" t="inlineStr"/>
+      <c r="AD3" t="inlineStr"/>
+      <c r="AE3" t="inlineStr"/>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="inlineStr"/>
+      <c r="AH3" t="inlineStr"/>
+      <c r="AI3" t="inlineStr"/>
+      <c r="AJ3" t="inlineStr"/>
+      <c r="AK3" t="inlineStr"/>
+      <c r="AL3" t="inlineStr"/>
+      <c r="AM3" t="inlineStr"/>
+      <c r="AN3" t="inlineStr"/>
+      <c r="AO3" t="inlineStr"/>
+      <c r="AP3" t="inlineStr"/>
+      <c r="AQ3" t="inlineStr"/>
+      <c r="AR3" t="inlineStr"/>
+      <c r="AS3" t="inlineStr"/>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AU3" t="inlineStr"/>
+      <c r="AV3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr"/>
+      <c r="AX3" t="inlineStr"/>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr"/>
+      <c r="BA3" t="inlineStr"/>
+      <c r="BB3" t="inlineStr"/>
+      <c r="BC3" t="inlineStr"/>
+      <c r="BD3" t="inlineStr"/>
+      <c r="BE3" t="inlineStr"/>
+      <c r="BF3" t="inlineStr"/>
+      <c r="BG3" t="inlineStr"/>
+      <c r="BH3" t="inlineStr"/>
+      <c r="BI3" t="inlineStr"/>
+      <c r="BJ3" t="inlineStr"/>
+      <c r="BK3" t="inlineStr"/>
+      <c r="BL3" t="inlineStr"/>
+      <c r="BM3" t="inlineStr"/>
+      <c r="BN3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>bHLf4sq9</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>45507.64583333334</v>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vanni sanna
+  sassari </t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>12000</v>
+      </c>
+      <c r="F4" t="n">
+        <v>2955</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>UiGfvfvT</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>z7WK5Pwb</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="n">
+        <v>77</v>
+      </c>
+      <c r="X4" t="n">
+        <v>773</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="inlineStr"/>
+      <c r="AC4" t="inlineStr"/>
+      <c r="AD4" t="inlineStr"/>
+      <c r="AE4" t="inlineStr"/>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="inlineStr"/>
+      <c r="AH4" t="inlineStr"/>
+      <c r="AI4" t="inlineStr"/>
+      <c r="AJ4" t="inlineStr"/>
+      <c r="AK4" t="inlineStr"/>
+      <c r="AL4" t="inlineStr"/>
+      <c r="AM4" t="inlineStr"/>
+      <c r="AN4" t="inlineStr"/>
+      <c r="AO4" t="n">
+        <v>28</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>176</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>64</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>587500</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>64.5</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>29</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>181.6</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>70.2</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>1820000</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>70.2</v>
+      </c>
+      <c r="BA4" t="inlineStr"/>
+      <c r="BB4" t="inlineStr"/>
+      <c r="BC4" t="inlineStr"/>
+      <c r="BD4" t="inlineStr"/>
+      <c r="BE4" t="inlineStr"/>
+      <c r="BF4" t="inlineStr"/>
+      <c r="BG4" t="inlineStr"/>
+      <c r="BH4" t="inlineStr"/>
+      <c r="BI4" t="inlineStr"/>
+      <c r="BJ4" t="inlineStr"/>
+      <c r="BK4" t="inlineStr"/>
+      <c r="BL4" t="inlineStr"/>
+      <c r="BM4" t="inlineStr"/>
+      <c r="BN4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>f9bfyqFM</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>45507.54166666666</v>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio dei marmi
+  carrara </t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>5280</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1707</v>
+      </c>
+      <c r="G5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>hG4fg4z3</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>4rwnnbnB</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="n">
+        <v>77</v>
+      </c>
+      <c r="X5" t="n">
+        <v>773</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr"/>
+      <c r="AE5" t="inlineStr"/>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="inlineStr"/>
+      <c r="AH5" t="inlineStr"/>
+      <c r="AI5" t="inlineStr"/>
+      <c r="AJ5" t="inlineStr"/>
+      <c r="AK5" t="inlineStr"/>
+      <c r="AL5" t="inlineStr"/>
+      <c r="AM5" t="inlineStr"/>
+      <c r="AN5" t="inlineStr"/>
+      <c r="AO5" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>179.8</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>61.6</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>775000</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>70.8</v>
+      </c>
+      <c r="AU5" t="inlineStr"/>
+      <c r="AV5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr"/>
+      <c r="AX5" t="inlineStr"/>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr"/>
+      <c r="BA5" t="inlineStr"/>
+      <c r="BB5" t="inlineStr"/>
+      <c r="BC5" t="inlineStr"/>
+      <c r="BD5" t="inlineStr"/>
+      <c r="BE5" t="inlineStr"/>
+      <c r="BF5" t="inlineStr"/>
+      <c r="BG5" t="inlineStr"/>
+      <c r="BH5" t="inlineStr"/>
+      <c r="BI5" t="inlineStr"/>
+      <c r="BJ5" t="inlineStr"/>
+      <c r="BK5" t="inlineStr"/>
+      <c r="BL5" t="inlineStr"/>
+      <c r="BM5" t="inlineStr"/>
+      <c r="BN5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/italy/p6_deployment/data_preparation/construct_data/df_matches_to_construct_historic_values.xlsx
+++ b/data/italy/p6_deployment/data_preparation/construct_data/df_matches_to_construct_historic_values.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BN5"/>
+  <dimension ref="A1:BN9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -762,53 +762,82 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>WlhYT07d</t>
+          <t>AZ3PVMxp</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45508.65625</v>
-      </c>
-      <c r="C2" t="inlineStr"/>
+        <v>45513.67708333334</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cosso f 
+  ita </t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio partenio adriano lombardi
-  avellino </t>
+          <t xml:space="preserve">brianteo
+  monza </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>26000</v>
+        <v>16917</v>
       </c>
       <c r="F2" t="n">
-        <v>5050</v>
+        <v>7139</v>
       </c>
       <c r="G2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>A332L1f5</t>
+          <t>4YSMlwj7</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>hKSfjtsQ</t>
+          <t>W02MZDnp</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
+      <c r="M2" t="n">
+        <v>57</v>
+      </c>
+      <c r="N2" t="n">
+        <v>43</v>
+      </c>
+      <c r="O2" t="n">
+        <v>10</v>
+      </c>
+      <c r="P2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>4</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" t="n">
+        <v>15</v>
+      </c>
+      <c r="T2" t="n">
+        <v>9</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>CEv2hvmq</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>bmzifXwb</t>
+        </is>
+      </c>
       <c r="W2" t="n">
         <v>77</v>
       </c>
@@ -821,44 +850,88 @@
       <c r="Z2" t="n">
         <v>20242025</v>
       </c>
-      <c r="AA2" t="inlineStr"/>
-      <c r="AB2" t="inlineStr"/>
-      <c r="AC2" t="inlineStr"/>
-      <c r="AD2" t="inlineStr"/>
-      <c r="AE2" t="inlineStr"/>
-      <c r="AF2" t="inlineStr"/>
-      <c r="AG2" t="inlineStr"/>
-      <c r="AH2" t="inlineStr"/>
-      <c r="AI2" t="inlineStr"/>
-      <c r="AJ2" t="inlineStr"/>
-      <c r="AK2" t="inlineStr"/>
-      <c r="AL2" t="inlineStr"/>
-      <c r="AM2" t="inlineStr"/>
-      <c r="AN2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>ttyLthOA</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>rXw8YKDE</t>
+        </is>
+      </c>
+      <c r="AC2" t="n">
+        <v>25.63636363636364</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>183.9090909090909</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>1.454545454545455</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>72.27272727272727</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>4727272.727272728</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>76.54545454545455</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>182.6</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>68</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>983500</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>70</v>
+      </c>
       <c r="AO2" t="n">
-        <v>27.5</v>
+        <v>26.29166666666667</v>
       </c>
       <c r="AP2" t="n">
-        <v>182.8333333333333</v>
+        <v>180.875</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="AR2" t="n">
-        <v>67.16666666666667</v>
+        <v>72.29166666666667</v>
       </c>
       <c r="AS2" t="n">
-        <v>1137500</v>
+        <v>5370833.333333333</v>
       </c>
       <c r="AT2" t="n">
-        <v>69</v>
-      </c>
-      <c r="AU2" t="inlineStr"/>
-      <c r="AV2" t="inlineStr"/>
-      <c r="AW2" t="inlineStr"/>
-      <c r="AX2" t="inlineStr"/>
-      <c r="AY2" t="inlineStr"/>
-      <c r="AZ2" t="inlineStr"/>
+        <v>75.375</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>23.57894736842105</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>185.3157894736842</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>65.26315789473684</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>1278947.368421053</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>71.36842105263158</v>
+      </c>
       <c r="BA2" t="inlineStr"/>
       <c r="BB2" t="inlineStr"/>
       <c r="BC2" t="inlineStr"/>
@@ -877,53 +950,82 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>SzxylMbS</t>
+          <t>hvcjgHz8</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45508.64583333334</v>
-      </c>
-      <c r="C3" t="inlineStr"/>
+        <v>45513.65625</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">di marco d 
+  ita </t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio dino manuzzi
-  cesena </t>
+          <t xml:space="preserve">stadio luigi ferraris
+  genoa </t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>23860</v>
+        <v>36599</v>
       </c>
       <c r="F3" t="n">
-        <v>4468</v>
+        <v>22000</v>
       </c>
       <c r="G3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>xddf1qfh</t>
+          <t>d0PJxeie</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2gUwEtrE</t>
+          <t>6ulJbMCe</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr"/>
+      <c r="M3" t="n">
+        <v>54</v>
+      </c>
+      <c r="N3" t="n">
+        <v>46</v>
+      </c>
+      <c r="O3" t="n">
+        <v>19</v>
+      </c>
+      <c r="P3" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>13</v>
+      </c>
+      <c r="R3" t="n">
+        <v>5</v>
+      </c>
+      <c r="S3" t="n">
+        <v>16</v>
+      </c>
+      <c r="T3" t="n">
+        <v>11</v>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>tSiEeKvS</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Gfur2NmR</t>
+        </is>
+      </c>
       <c r="W3" t="n">
         <v>77</v>
       </c>
@@ -936,32 +1038,84 @@
       <c r="Z3" t="n">
         <v>20242025</v>
       </c>
-      <c r="AA3" t="inlineStr"/>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>nJbCGx2U</t>
+        </is>
+      </c>
       <c r="AB3" t="inlineStr"/>
-      <c r="AC3" t="inlineStr"/>
-      <c r="AD3" t="inlineStr"/>
-      <c r="AE3" t="inlineStr"/>
-      <c r="AF3" t="inlineStr"/>
-      <c r="AG3" t="inlineStr"/>
-      <c r="AH3" t="inlineStr"/>
-      <c r="AI3" t="inlineStr"/>
-      <c r="AJ3" t="inlineStr"/>
-      <c r="AK3" t="inlineStr"/>
-      <c r="AL3" t="inlineStr"/>
-      <c r="AM3" t="inlineStr"/>
-      <c r="AN3" t="inlineStr"/>
-      <c r="AO3" t="inlineStr"/>
-      <c r="AP3" t="inlineStr"/>
-      <c r="AQ3" t="inlineStr"/>
-      <c r="AR3" t="inlineStr"/>
-      <c r="AS3" t="inlineStr"/>
-      <c r="AT3" t="inlineStr"/>
-      <c r="AU3" t="inlineStr"/>
-      <c r="AV3" t="inlineStr"/>
-      <c r="AW3" t="inlineStr"/>
-      <c r="AX3" t="inlineStr"/>
-      <c r="AY3" t="inlineStr"/>
-      <c r="AZ3" t="inlineStr"/>
+      <c r="AC3" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>183.9</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>72.3</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>4072500</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>75.8</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>26</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>183.875</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>63.375</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>781250</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>68.875</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>26.53333333333333</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>184.0666666666667</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>1.533333333333333</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>72.26666666666667</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>5316666.666666667</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>75.93333333333334</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>25.4375</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>179.875</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>62.1875</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>718125</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>65.75</v>
+      </c>
       <c r="BA3" t="inlineStr"/>
       <c r="BB3" t="inlineStr"/>
       <c r="BC3" t="inlineStr"/>
@@ -980,53 +1134,82 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>bHLf4sq9</t>
+          <t>dnnqk0iD</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45507.64583333334</v>
-      </c>
-      <c r="C4" t="inlineStr"/>
+        <v>45513.5625</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">scatena g 
+  ita </t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">vanni sanna
-  sassari </t>
+          <t xml:space="preserve">bluenergy stadium   stadio friuli
+  udine </t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>12000</v>
+        <v>25144</v>
       </c>
       <c r="F4" t="n">
-        <v>2955</v>
+        <v>5850</v>
       </c>
       <c r="G4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>UiGfvfvT</t>
+          <t>rXw8YKDE</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>z7WK5Pwb</t>
+          <t>A332L1f5</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr"/>
+      <c r="M4" t="n">
+        <v>62</v>
+      </c>
+      <c r="N4" t="n">
+        <v>38</v>
+      </c>
+      <c r="O4" t="n">
+        <v>16</v>
+      </c>
+      <c r="P4" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>7</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1</v>
+      </c>
+      <c r="S4" t="n">
+        <v>15</v>
+      </c>
+      <c r="T4" t="n">
+        <v>10</v>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>ncu4OLs5</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>WE57Jh0D</t>
+        </is>
+      </c>
       <c r="W4" t="n">
         <v>77</v>
       </c>
@@ -1039,14 +1222,30 @@
       <c r="Z4" t="n">
         <v>20242025</v>
       </c>
-      <c r="AA4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>69Dxbc61</t>
+        </is>
+      </c>
       <c r="AB4" t="inlineStr"/>
-      <c r="AC4" t="inlineStr"/>
-      <c r="AD4" t="inlineStr"/>
-      <c r="AE4" t="inlineStr"/>
-      <c r="AF4" t="inlineStr"/>
-      <c r="AG4" t="inlineStr"/>
-      <c r="AH4" t="inlineStr"/>
+      <c r="AC4" t="n">
+        <v>25.45454545454545</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>184.8181818181818</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>73.45454545454545</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>4663636.363636363</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>76.27272727272727</v>
+      </c>
       <c r="AI4" t="inlineStr"/>
       <c r="AJ4" t="inlineStr"/>
       <c r="AK4" t="inlineStr"/>
@@ -1054,41 +1253,29 @@
       <c r="AM4" t="inlineStr"/>
       <c r="AN4" t="inlineStr"/>
       <c r="AO4" t="n">
-        <v>28</v>
+        <v>25.40909090909091</v>
       </c>
       <c r="AP4" t="n">
-        <v>176</v>
+        <v>183.8636363636364</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1</v>
+        <v>1.045454545454545</v>
       </c>
       <c r="AR4" t="n">
-        <v>64</v>
+        <v>71.81818181818181</v>
       </c>
       <c r="AS4" t="n">
-        <v>587500</v>
+        <v>4140909.090909091</v>
       </c>
       <c r="AT4" t="n">
-        <v>64.5</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>29</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>181.6</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>70.2</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>1820000</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>70.2</v>
-      </c>
+        <v>75.90909090909091</v>
+      </c>
+      <c r="AU4" t="inlineStr"/>
+      <c r="AV4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr"/>
+      <c r="AX4" t="inlineStr"/>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr"/>
       <c r="BA4" t="inlineStr"/>
       <c r="BB4" t="inlineStr"/>
       <c r="BC4" t="inlineStr"/>
@@ -1107,24 +1294,29 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>f9bfyqFM</t>
+          <t>QT6wuRFc</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45507.54166666666</v>
-      </c>
-      <c r="C5" t="inlineStr"/>
+        <v>45513.54166666666</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">prontera a 
+  ita </t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio dei marmi
-  carrara </t>
+          <t xml:space="preserve">mapei stadium – citta del tricolore
+  reggio emilia </t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5280</v>
+        <v>21525</v>
       </c>
       <c r="F5" t="n">
-        <v>1707</v>
+        <v>2000</v>
       </c>
       <c r="G5" t="n">
         <v>2</v>
@@ -1134,26 +1326,50 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>hG4fg4z3</t>
+          <t>QDdvI0zl</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>4rwnnbnB</t>
+          <t>C0yUqo8c</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr"/>
+      <c r="M5" t="n">
+        <v>49</v>
+      </c>
+      <c r="N5" t="n">
+        <v>51</v>
+      </c>
+      <c r="O5" t="n">
+        <v>15</v>
+      </c>
+      <c r="P5" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>9</v>
+      </c>
+      <c r="R5" t="n">
+        <v>2</v>
+      </c>
+      <c r="S5" t="n">
+        <v>15</v>
+      </c>
+      <c r="T5" t="n">
+        <v>9</v>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>bPHSQi9q</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>8dDPzPa7</t>
+        </is>
+      </c>
       <c r="W5" t="n">
         <v>77</v>
       </c>
@@ -1166,14 +1382,34 @@
       <c r="Z5" t="n">
         <v>20242025</v>
       </c>
-      <c r="AA5" t="inlineStr"/>
-      <c r="AB5" t="inlineStr"/>
-      <c r="AC5" t="inlineStr"/>
-      <c r="AD5" t="inlineStr"/>
-      <c r="AE5" t="inlineStr"/>
-      <c r="AF5" t="inlineStr"/>
-      <c r="AG5" t="inlineStr"/>
-      <c r="AH5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>0M9xNN8N</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>MkPmVv50</t>
+        </is>
+      </c>
+      <c r="AC5" t="n">
+        <v>24.54545454545455</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>185.1818181818182</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1.181818181818182</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>71.36363636363636</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>5297727.272727272</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>75.27272727272727</v>
+      </c>
       <c r="AI5" t="inlineStr"/>
       <c r="AJ5" t="inlineStr"/>
       <c r="AK5" t="inlineStr"/>
@@ -1181,29 +1417,41 @@
       <c r="AM5" t="inlineStr"/>
       <c r="AN5" t="inlineStr"/>
       <c r="AO5" t="n">
-        <v>21.4</v>
+        <v>21.60869565217391</v>
       </c>
       <c r="AP5" t="n">
-        <v>179.8</v>
+        <v>184.2608695652174</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1</v>
+        <v>1.043478260869565</v>
       </c>
       <c r="AR5" t="n">
-        <v>61.6</v>
+        <v>68.08695652173913</v>
       </c>
       <c r="AS5" t="n">
-        <v>775000</v>
+        <v>3495652.173913043</v>
       </c>
       <c r="AT5" t="n">
-        <v>70.8</v>
-      </c>
-      <c r="AU5" t="inlineStr"/>
-      <c r="AV5" t="inlineStr"/>
-      <c r="AW5" t="inlineStr"/>
-      <c r="AX5" t="inlineStr"/>
-      <c r="AY5" t="inlineStr"/>
-      <c r="AZ5" t="inlineStr"/>
+        <v>78.26086956521739</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>26.22727272727273</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>184.7727272727273</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>65.31818181818181</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>1042954.545454545</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>69.13636363636364</v>
+      </c>
       <c r="BA5" t="inlineStr"/>
       <c r="BB5" t="inlineStr"/>
       <c r="BC5" t="inlineStr"/>
@@ -1219,6 +1467,466 @@
       <c r="BM5" t="inlineStr"/>
       <c r="BN5" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>WlhYT07d</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>45508.65625</v>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio partenio adriano lombardi
+  avellino </t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>26000</v>
+      </c>
+      <c r="F6" t="n">
+        <v>5050</v>
+      </c>
+      <c r="G6" t="n">
+        <v>3</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>A332L1f5</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>hKSfjtsQ</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="n">
+        <v>77</v>
+      </c>
+      <c r="X6" t="n">
+        <v>773</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="inlineStr"/>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="inlineStr"/>
+      <c r="AH6" t="inlineStr"/>
+      <c r="AI6" t="inlineStr"/>
+      <c r="AJ6" t="inlineStr"/>
+      <c r="AK6" t="inlineStr"/>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="inlineStr"/>
+      <c r="AN6" t="inlineStr"/>
+      <c r="AO6" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>182.8333333333333</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>67.16666666666667</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>1137500</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>69</v>
+      </c>
+      <c r="AU6" t="inlineStr"/>
+      <c r="AV6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr"/>
+      <c r="AX6" t="inlineStr"/>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr"/>
+      <c r="BA6" t="inlineStr"/>
+      <c r="BB6" t="inlineStr"/>
+      <c r="BC6" t="inlineStr"/>
+      <c r="BD6" t="inlineStr"/>
+      <c r="BE6" t="inlineStr"/>
+      <c r="BF6" t="inlineStr"/>
+      <c r="BG6" t="inlineStr"/>
+      <c r="BH6" t="inlineStr"/>
+      <c r="BI6" t="inlineStr"/>
+      <c r="BJ6" t="inlineStr"/>
+      <c r="BK6" t="inlineStr"/>
+      <c r="BL6" t="inlineStr"/>
+      <c r="BM6" t="inlineStr"/>
+      <c r="BN6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>SzxylMbS</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>45508.64583333334</v>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio dino manuzzi
+  cesena </t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>23860</v>
+      </c>
+      <c r="F7" t="n">
+        <v>4468</v>
+      </c>
+      <c r="G7" t="n">
+        <v>3</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>xddf1qfh</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>2gUwEtrE</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="n">
+        <v>77</v>
+      </c>
+      <c r="X7" t="n">
+        <v>773</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA7" t="inlineStr"/>
+      <c r="AB7" t="inlineStr"/>
+      <c r="AC7" t="inlineStr"/>
+      <c r="AD7" t="inlineStr"/>
+      <c r="AE7" t="inlineStr"/>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="inlineStr"/>
+      <c r="AH7" t="inlineStr"/>
+      <c r="AI7" t="inlineStr"/>
+      <c r="AJ7" t="inlineStr"/>
+      <c r="AK7" t="inlineStr"/>
+      <c r="AL7" t="inlineStr"/>
+      <c r="AM7" t="inlineStr"/>
+      <c r="AN7" t="inlineStr"/>
+      <c r="AO7" t="inlineStr"/>
+      <c r="AP7" t="inlineStr"/>
+      <c r="AQ7" t="inlineStr"/>
+      <c r="AR7" t="inlineStr"/>
+      <c r="AS7" t="inlineStr"/>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AU7" t="inlineStr"/>
+      <c r="AV7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr"/>
+      <c r="AX7" t="inlineStr"/>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr"/>
+      <c r="BA7" t="inlineStr"/>
+      <c r="BB7" t="inlineStr"/>
+      <c r="BC7" t="inlineStr"/>
+      <c r="BD7" t="inlineStr"/>
+      <c r="BE7" t="inlineStr"/>
+      <c r="BF7" t="inlineStr"/>
+      <c r="BG7" t="inlineStr"/>
+      <c r="BH7" t="inlineStr"/>
+      <c r="BI7" t="inlineStr"/>
+      <c r="BJ7" t="inlineStr"/>
+      <c r="BK7" t="inlineStr"/>
+      <c r="BL7" t="inlineStr"/>
+      <c r="BM7" t="inlineStr"/>
+      <c r="BN7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>bHLf4sq9</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>45507.64583333334</v>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vanni sanna
+  sassari </t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>12000</v>
+      </c>
+      <c r="F8" t="n">
+        <v>2955</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>UiGfvfvT</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>z7WK5Pwb</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="n">
+        <v>77</v>
+      </c>
+      <c r="X8" t="n">
+        <v>773</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA8" t="inlineStr"/>
+      <c r="AB8" t="inlineStr"/>
+      <c r="AC8" t="inlineStr"/>
+      <c r="AD8" t="inlineStr"/>
+      <c r="AE8" t="inlineStr"/>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="inlineStr"/>
+      <c r="AH8" t="inlineStr"/>
+      <c r="AI8" t="inlineStr"/>
+      <c r="AJ8" t="inlineStr"/>
+      <c r="AK8" t="inlineStr"/>
+      <c r="AL8" t="inlineStr"/>
+      <c r="AM8" t="inlineStr"/>
+      <c r="AN8" t="inlineStr"/>
+      <c r="AO8" t="n">
+        <v>28</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>176</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>64</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>587500</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>64.5</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>29</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>181.6</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>70.2</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>1820000</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>70.2</v>
+      </c>
+      <c r="BA8" t="inlineStr"/>
+      <c r="BB8" t="inlineStr"/>
+      <c r="BC8" t="inlineStr"/>
+      <c r="BD8" t="inlineStr"/>
+      <c r="BE8" t="inlineStr"/>
+      <c r="BF8" t="inlineStr"/>
+      <c r="BG8" t="inlineStr"/>
+      <c r="BH8" t="inlineStr"/>
+      <c r="BI8" t="inlineStr"/>
+      <c r="BJ8" t="inlineStr"/>
+      <c r="BK8" t="inlineStr"/>
+      <c r="BL8" t="inlineStr"/>
+      <c r="BM8" t="inlineStr"/>
+      <c r="BN8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>f9bfyqFM</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45507.54166666666</v>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio dei marmi
+  carrara </t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>5280</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1707</v>
+      </c>
+      <c r="G9" t="n">
+        <v>2</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>hG4fg4z3</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>4rwnnbnB</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="n">
+        <v>77</v>
+      </c>
+      <c r="X9" t="n">
+        <v>773</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr"/>
+      <c r="AC9" t="inlineStr"/>
+      <c r="AD9" t="inlineStr"/>
+      <c r="AE9" t="inlineStr"/>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="inlineStr"/>
+      <c r="AH9" t="inlineStr"/>
+      <c r="AI9" t="inlineStr"/>
+      <c r="AJ9" t="inlineStr"/>
+      <c r="AK9" t="inlineStr"/>
+      <c r="AL9" t="inlineStr"/>
+      <c r="AM9" t="inlineStr"/>
+      <c r="AN9" t="inlineStr"/>
+      <c r="AO9" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>179.8</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>61.6</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>775000</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>70.8</v>
+      </c>
+      <c r="AU9" t="inlineStr"/>
+      <c r="AV9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr"/>
+      <c r="AX9" t="inlineStr"/>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr"/>
+      <c r="BA9" t="inlineStr"/>
+      <c r="BB9" t="inlineStr"/>
+      <c r="BC9" t="inlineStr"/>
+      <c r="BD9" t="inlineStr"/>
+      <c r="BE9" t="inlineStr"/>
+      <c r="BF9" t="inlineStr"/>
+      <c r="BG9" t="inlineStr"/>
+      <c r="BH9" t="inlineStr"/>
+      <c r="BI9" t="inlineStr"/>
+      <c r="BJ9" t="inlineStr"/>
+      <c r="BK9" t="inlineStr"/>
+      <c r="BL9" t="inlineStr"/>
+      <c r="BM9" t="inlineStr"/>
+      <c r="BN9" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/italy/p6_deployment/data_preparation/construct_data/df_matches_to_construct_historic_values.xlsx
+++ b/data/italy/p6_deployment/data_preparation/construct_data/df_matches_to_construct_historic_values.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BN9"/>
+  <dimension ref="A1:BN39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -762,490 +762,538 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>AZ3PVMxp</t>
+          <t>YH892O2B</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45513.67708333334</v>
+        <v>45522.65625</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">cosso f 
+          <t xml:space="preserve">la penna f 
   ita </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">brianteo
-  monza </t>
+          <t xml:space="preserve">unipol domus
+  cagliari </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>16917</v>
-      </c>
-      <c r="F2" t="n">
-        <v>7139</v>
-      </c>
+        <v>16416</v>
+      </c>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>4YSMlwj7</t>
+          <t>SCGVmKHb</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>W02MZDnp</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
+          <t>zVqqL0ma</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1.25</v>
+      </c>
       <c r="M2" t="n">
+        <v>43</v>
+      </c>
+      <c r="N2" t="n">
         <v>57</v>
       </c>
-      <c r="N2" t="n">
-        <v>43</v>
-      </c>
       <c r="O2" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="P2" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>2</v>
+      </c>
+      <c r="R2" t="n">
         <v>3</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>4</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
       </c>
       <c r="T2" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>CEv2hvmq</t>
+          <t>MLVBCoYg</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>bmzifXwb</t>
+          <t>xjigzK81</t>
         </is>
       </c>
       <c r="W2" t="n">
         <v>77</v>
       </c>
       <c r="X2" t="n">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="Y2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
         <v>20242025</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>ttyLthOA</t>
+          <t>69Dxbc61</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>rXw8YKDE</t>
+          <t>URcSl02h</t>
         </is>
       </c>
       <c r="AC2" t="n">
-        <v>25.63636363636364</v>
+        <v>24.90909090909091</v>
       </c>
       <c r="AD2" t="n">
-        <v>183.9090909090909</v>
+        <v>185</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.454545454545455</v>
+        <v>1</v>
       </c>
       <c r="AF2" t="n">
         <v>72.27272727272727</v>
       </c>
       <c r="AG2" t="n">
-        <v>4727272.727272728</v>
+        <v>4581818.181818182</v>
       </c>
       <c r="AH2" t="n">
-        <v>76.54545454545455</v>
+        <v>76.09090909090909</v>
       </c>
       <c r="AI2" t="n">
-        <v>29.8</v>
+        <v>24.75</v>
       </c>
       <c r="AJ2" t="n">
-        <v>182.6</v>
+        <v>181.625</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.2</v>
+        <v>1.75</v>
       </c>
       <c r="AL2" t="n">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="AM2" t="n">
-        <v>983500</v>
+        <v>19037500</v>
       </c>
       <c r="AN2" t="n">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="AO2" t="n">
-        <v>26.29166666666667</v>
+        <v>26.25</v>
       </c>
       <c r="AP2" t="n">
-        <v>180.875</v>
+        <v>184</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AR2" t="n">
-        <v>72.29166666666667</v>
+        <v>68.95</v>
       </c>
       <c r="AS2" t="n">
-        <v>5370833.333333333</v>
+        <v>2293750</v>
       </c>
       <c r="AT2" t="n">
-        <v>75.375</v>
+        <v>73.7</v>
       </c>
       <c r="AU2" t="n">
-        <v>23.57894736842105</v>
+        <v>24.78947368421053</v>
       </c>
       <c r="AV2" t="n">
-        <v>185.3157894736842</v>
+        <v>180.421052631579</v>
       </c>
       <c r="AW2" t="n">
-        <v>1</v>
+        <v>1.894736842105263</v>
       </c>
       <c r="AX2" t="n">
-        <v>65.26315789473684</v>
+        <v>77.21052631578948</v>
       </c>
       <c r="AY2" t="n">
-        <v>1278947.368421053</v>
+        <v>24271052.63157895</v>
       </c>
       <c r="AZ2" t="n">
-        <v>71.36842105263158</v>
-      </c>
-      <c r="BA2" t="inlineStr"/>
-      <c r="BB2" t="inlineStr"/>
-      <c r="BC2" t="inlineStr"/>
-      <c r="BD2" t="inlineStr"/>
-      <c r="BE2" t="inlineStr"/>
-      <c r="BF2" t="inlineStr"/>
-      <c r="BG2" t="inlineStr"/>
-      <c r="BH2" t="inlineStr"/>
-      <c r="BI2" t="inlineStr"/>
-      <c r="BJ2" t="inlineStr"/>
-      <c r="BK2" t="inlineStr"/>
-      <c r="BL2" t="inlineStr"/>
-      <c r="BM2" t="inlineStr"/>
-      <c r="BN2" t="inlineStr"/>
+        <v>82.21052631578948</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>28</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>183.5</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>288</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>12300000</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>292</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>29</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>180</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>78</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>13500000</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>78</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hvcjgHz8</t>
+          <t>8jyraADG</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45513.65625</v>
+        <v>45522.65625</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">di marco d 
+          <t xml:space="preserve">tremolada p 
   ita </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio luigi ferraris
-  genoa </t>
+          <t xml:space="preserve">stadio olimpico
+  rome </t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>36599</v>
-      </c>
-      <c r="F3" t="n">
-        <v>22000</v>
-      </c>
+        <v>70634</v>
+      </c>
+      <c r="F3" t="inlineStr"/>
       <c r="G3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>d0PJxeie</t>
+          <t>URcSl02h</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>6ulJbMCe</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
+          <t>MkPmVv50</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.55</v>
+      </c>
       <c r="M3" t="n">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="N3" t="n">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="O3" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="P3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Q3" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="R3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S3" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="T3" t="n">
         <v>11</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>tSiEeKvS</t>
+          <t>S8Ygn9ME</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>Gfur2NmR</t>
+          <t>n10g3KfJ</t>
         </is>
       </c>
       <c r="W3" t="n">
         <v>77</v>
       </c>
       <c r="X3" t="n">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="Y3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
         <v>20242025</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>nJbCGx2U</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr"/>
+          <t>zVqqL0ma</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>rJVAIaHo</t>
+        </is>
+      </c>
       <c r="AC3" t="n">
-        <v>27.2</v>
+        <v>26.1</v>
       </c>
       <c r="AD3" t="n">
-        <v>183.9</v>
+        <v>182.4</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="AF3" t="n">
-        <v>72.3</v>
+        <v>79</v>
       </c>
       <c r="AG3" t="n">
-        <v>4072500</v>
+        <v>20770000</v>
       </c>
       <c r="AH3" t="n">
-        <v>75.8</v>
+        <v>81.5</v>
       </c>
       <c r="AI3" t="n">
         <v>26</v>
       </c>
       <c r="AJ3" t="n">
-        <v>183.875</v>
+        <v>183.5</v>
       </c>
       <c r="AK3" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="AL3" t="n">
-        <v>63.375</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="AM3" t="n">
-        <v>781250</v>
+        <v>2240000</v>
       </c>
       <c r="AN3" t="n">
-        <v>68.875</v>
+        <v>74.2</v>
       </c>
       <c r="AO3" t="n">
-        <v>26.53333333333333</v>
+        <v>24.70833333333333</v>
       </c>
       <c r="AP3" t="n">
-        <v>184.0666666666667</v>
+        <v>182.375</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.533333333333333</v>
+        <v>1.458333333333333</v>
       </c>
       <c r="AR3" t="n">
-        <v>72.26666666666667</v>
+        <v>74.45833333333333</v>
       </c>
       <c r="AS3" t="n">
-        <v>5316666.666666667</v>
+        <v>11406250</v>
       </c>
       <c r="AT3" t="n">
-        <v>75.93333333333334</v>
+        <v>79</v>
       </c>
       <c r="AU3" t="n">
-        <v>25.4375</v>
+        <v>24.47619047619047</v>
       </c>
       <c r="AV3" t="n">
-        <v>179.875</v>
+        <v>181.7619047619048</v>
       </c>
       <c r="AW3" t="n">
         <v>1</v>
       </c>
       <c r="AX3" t="n">
-        <v>62.1875</v>
+        <v>66.52380952380952</v>
       </c>
       <c r="AY3" t="n">
-        <v>718125</v>
+        <v>1505714.285714286</v>
       </c>
       <c r="AZ3" t="n">
-        <v>65.75</v>
-      </c>
-      <c r="BA3" t="inlineStr"/>
-      <c r="BB3" t="inlineStr"/>
-      <c r="BC3" t="inlineStr"/>
-      <c r="BD3" t="inlineStr"/>
-      <c r="BE3" t="inlineStr"/>
-      <c r="BF3" t="inlineStr"/>
-      <c r="BG3" t="inlineStr"/>
-      <c r="BH3" t="inlineStr"/>
-      <c r="BI3" t="inlineStr"/>
-      <c r="BJ3" t="inlineStr"/>
-      <c r="BK3" t="inlineStr"/>
-      <c r="BL3" t="inlineStr"/>
-      <c r="BM3" t="inlineStr"/>
-      <c r="BN3" t="inlineStr"/>
+        <v>72.42857142857143</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>22</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>185</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>1</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>66</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>1200000</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>72</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>181.5</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK3" t="n">
+        <v>6</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>423</v>
+      </c>
+      <c r="BM3" t="n">
+        <v>19125000</v>
+      </c>
+      <c r="BN3" t="n">
+        <v>450</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>dnnqk0iD</t>
+          <t>x0nkeyzP</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45513.5625</v>
+        <v>45522.64583333334</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">scatena g 
+          <t xml:space="preserve">prontera a 
   ita </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">bluenergy stadium   stadio friuli
-  udine </t>
+          <t xml:space="preserve">stadio dino manuzzi
+  cesena </t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>25144</v>
+        <v>23860</v>
       </c>
       <c r="F4" t="n">
-        <v>5850</v>
+        <v>11382</v>
       </c>
       <c r="G4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>rXw8YKDE</t>
+          <t>xddf1qfh</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>A332L1f5</t>
+          <t>hG4fg4z3</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="N4" t="n">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="O4" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="P4" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>8</v>
+      </c>
+      <c r="R4" t="n">
         <v>4</v>
       </c>
-      <c r="Q4" t="n">
-        <v>7</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1</v>
-      </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="T4" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>ncu4OLs5</t>
+          <t>vD8aDRIm</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>WE57Jh0D</t>
+          <t>lSb6U6l0</t>
         </is>
       </c>
       <c r="W4" t="n">
         <v>77</v>
       </c>
       <c r="X4" t="n">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="Y4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
         <v>20242025</v>
       </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>69Dxbc61</t>
-        </is>
-      </c>
+      <c r="AA4" t="inlineStr"/>
       <c r="AB4" t="inlineStr"/>
-      <c r="AC4" t="n">
-        <v>25.45454545454545</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>184.8181818181818</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>73.45454545454545</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>4663636.363636363</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>76.27272727272727</v>
-      </c>
+      <c r="AC4" t="inlineStr"/>
+      <c r="AD4" t="inlineStr"/>
+      <c r="AE4" t="inlineStr"/>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="inlineStr"/>
+      <c r="AH4" t="inlineStr"/>
       <c r="AI4" t="inlineStr"/>
       <c r="AJ4" t="inlineStr"/>
       <c r="AK4" t="inlineStr"/>
@@ -1253,29 +1301,41 @@
       <c r="AM4" t="inlineStr"/>
       <c r="AN4" t="inlineStr"/>
       <c r="AO4" t="n">
-        <v>25.40909090909091</v>
+        <v>23.375</v>
       </c>
       <c r="AP4" t="n">
-        <v>183.8636363636364</v>
+        <v>183.75</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.045454545454545</v>
+        <v>1</v>
       </c>
       <c r="AR4" t="n">
-        <v>71.81818181818181</v>
+        <v>69.625</v>
       </c>
       <c r="AS4" t="n">
-        <v>4140909.090909091</v>
+        <v>3056250</v>
       </c>
       <c r="AT4" t="n">
-        <v>75.90909090909091</v>
-      </c>
-      <c r="AU4" t="inlineStr"/>
-      <c r="AV4" t="inlineStr"/>
-      <c r="AW4" t="inlineStr"/>
-      <c r="AX4" t="inlineStr"/>
-      <c r="AY4" t="inlineStr"/>
-      <c r="AZ4" t="inlineStr"/>
+        <v>75.75</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>23.375</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>181.5</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>62.875</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>871875</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>70.25</v>
+      </c>
       <c r="BA4" t="inlineStr"/>
       <c r="BB4" t="inlineStr"/>
       <c r="BC4" t="inlineStr"/>
@@ -1294,163 +1354,175 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>QT6wuRFc</t>
+          <t>SORbFvLt</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45513.54166666666</v>
+        <v>45522.64583333334</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">prontera a 
+          <t xml:space="preserve">bonacina k 
   ita </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapei stadium – citta del tricolore
-  reggio emilia </t>
+          <t xml:space="preserve">stadio san vito luigi marulla
+  cosenza </t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>21525</v>
+        <v>20987</v>
       </c>
       <c r="F5" t="n">
-        <v>2000</v>
+        <v>6840</v>
       </c>
       <c r="G5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>QDdvI0zl</t>
+          <t>p84TeBhA</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>C0yUqo8c</t>
+          <t>KUzfp5N3</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="N5" t="n">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="O5" t="n">
         <v>15</v>
       </c>
       <c r="P5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Q5" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="R5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="T5" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>bPHSQi9q</t>
+          <t>Yika9O16</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>8dDPzPa7</t>
+          <t>YgLhKnOo</t>
         </is>
       </c>
       <c r="W5" t="n">
         <v>77</v>
       </c>
       <c r="X5" t="n">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="Y5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
         <v>20242025</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0M9xNN8N</t>
+          <t>GnizyMB7</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>MkPmVv50</t>
+          <t>ttyLthOA</t>
         </is>
       </c>
       <c r="AC5" t="n">
-        <v>24.54545454545455</v>
+        <v>24.3</v>
       </c>
       <c r="AD5" t="n">
-        <v>185.1818181818182</v>
+        <v>184.7</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.181818181818182</v>
+        <v>1</v>
       </c>
       <c r="AF5" t="n">
-        <v>71.36363636363636</v>
+        <v>65.7</v>
       </c>
       <c r="AG5" t="n">
-        <v>5297727.272727272</v>
+        <v>1165000</v>
       </c>
       <c r="AH5" t="n">
-        <v>75.27272727272727</v>
-      </c>
-      <c r="AI5" t="inlineStr"/>
-      <c r="AJ5" t="inlineStr"/>
-      <c r="AK5" t="inlineStr"/>
-      <c r="AL5" t="inlineStr"/>
-      <c r="AM5" t="inlineStr"/>
-      <c r="AN5" t="inlineStr"/>
+        <v>71.59999999999999</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>25.81818181818182</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>186.0909090909091</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>69.45454545454545</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>1909090.909090909</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>73</v>
+      </c>
       <c r="AO5" t="n">
-        <v>21.60869565217391</v>
+        <v>22.25</v>
       </c>
       <c r="AP5" t="n">
-        <v>184.2608695652174</v>
+        <v>181.125</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.043478260869565</v>
+        <v>1</v>
       </c>
       <c r="AR5" t="n">
-        <v>68.08695652173913</v>
+        <v>64.375</v>
       </c>
       <c r="AS5" t="n">
-        <v>3495652.173913043</v>
+        <v>1179687.5</v>
       </c>
       <c r="AT5" t="n">
-        <v>78.26086956521739</v>
+        <v>71.875</v>
       </c>
       <c r="AU5" t="n">
-        <v>26.22727272727273</v>
+        <v>23.91666666666667</v>
       </c>
       <c r="AV5" t="n">
-        <v>184.7727272727273</v>
+        <v>182.5</v>
       </c>
       <c r="AW5" t="n">
         <v>1</v>
       </c>
       <c r="AX5" t="n">
-        <v>65.31818181818181</v>
+        <v>69</v>
       </c>
       <c r="AY5" t="n">
-        <v>1042954.545454545</v>
+        <v>2183333.333333333</v>
       </c>
       <c r="AZ5" t="n">
-        <v>69.13636363636364</v>
+        <v>74.125</v>
       </c>
       <c r="BA5" t="inlineStr"/>
       <c r="BB5" t="inlineStr"/>
@@ -1470,103 +1542,174 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>WlhYT07d</t>
+          <t>tYhtcc5C</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45508.65625</v>
-      </c>
-      <c r="C6" t="inlineStr"/>
+        <v>45522.64583333334</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">piccinini m 
+  ita </t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio partenio adriano lombardi
-  avellino </t>
+          <t xml:space="preserve">stadio nicola ceravolo
+  catanzaro </t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>26000</v>
-      </c>
-      <c r="F6" t="n">
-        <v>5050</v>
-      </c>
+        <v>14650</v>
+      </c>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H6" t="n">
         <v>1</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>A332L1f5</t>
+          <t>GnizyMB7</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>hKSfjtsQ</t>
+          <t>QDdvI0zl</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr"/>
-      <c r="T6" t="inlineStr"/>
-      <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr"/>
+      <c r="M6" t="n">
+        <v>49</v>
+      </c>
+      <c r="N6" t="n">
+        <v>51</v>
+      </c>
+      <c r="O6" t="n">
+        <v>9</v>
+      </c>
+      <c r="P6" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>4</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6</v>
+      </c>
+      <c r="S6" t="n">
+        <v>11</v>
+      </c>
+      <c r="T6" t="n">
+        <v>7</v>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>nsYMfLJM</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>bPHSQi9q</t>
+        </is>
+      </c>
       <c r="W6" t="n">
         <v>77</v>
       </c>
       <c r="X6" t="n">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="Y6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
         <v>20242025</v>
       </c>
-      <c r="AA6" t="inlineStr"/>
-      <c r="AB6" t="inlineStr"/>
-      <c r="AC6" t="inlineStr"/>
-      <c r="AD6" t="inlineStr"/>
-      <c r="AE6" t="inlineStr"/>
-      <c r="AF6" t="inlineStr"/>
-      <c r="AG6" t="inlineStr"/>
-      <c r="AH6" t="inlineStr"/>
-      <c r="AI6" t="inlineStr"/>
-      <c r="AJ6" t="inlineStr"/>
-      <c r="AK6" t="inlineStr"/>
-      <c r="AL6" t="inlineStr"/>
-      <c r="AM6" t="inlineStr"/>
-      <c r="AN6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>p84TeBhA</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>0M9xNN8N</t>
+        </is>
+      </c>
+      <c r="AC6" t="n">
+        <v>27.77777777777778</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>180.4444444444445</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>66.88888888888889</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>1030555.555555556</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>69.22222222222223</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>24.54545454545455</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>185.1818181818182</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>1.181818181818182</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>71.36363636363636</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>5297727.272727272</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>75.27272727272727</v>
+      </c>
       <c r="AO6" t="n">
-        <v>27.5</v>
+        <v>24.7</v>
       </c>
       <c r="AP6" t="n">
-        <v>182.8333333333333</v>
+        <v>182.3</v>
       </c>
       <c r="AQ6" t="n">
         <v>1</v>
       </c>
       <c r="AR6" t="n">
-        <v>67.16666666666667</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="AS6" t="n">
-        <v>1137500</v>
+        <v>985000</v>
       </c>
       <c r="AT6" t="n">
-        <v>69</v>
-      </c>
-      <c r="AU6" t="inlineStr"/>
-      <c r="AV6" t="inlineStr"/>
-      <c r="AW6" t="inlineStr"/>
-      <c r="AX6" t="inlineStr"/>
-      <c r="AY6" t="inlineStr"/>
-      <c r="AZ6" t="inlineStr"/>
+        <v>69.5</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>182.25</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>67.8</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>2540000</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>76.65000000000001</v>
+      </c>
       <c r="BA6" t="inlineStr"/>
       <c r="BB6" t="inlineStr"/>
       <c r="BC6" t="inlineStr"/>
@@ -1585,91 +1728,154 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>SzxylMbS</t>
+          <t>IXMN9zkI</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45508.64583333334</v>
-      </c>
-      <c r="C7" t="inlineStr"/>
+        <v>45522.64583333334</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">arena a 
+  ita </t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio dino manuzzi
-  cesena </t>
+          <t xml:space="preserve">mapei stadium – citta del tricolore
+  reggio emilia </t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>23860</v>
-      </c>
-      <c r="F7" t="n">
-        <v>4468</v>
-      </c>
+        <v>21525</v>
+      </c>
+      <c r="F7" t="inlineStr"/>
       <c r="G7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>xddf1qfh</t>
+          <t>6ulJbMCe</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2gUwEtrE</t>
+          <t>z7WK5Pwb</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr"/>
-      <c r="V7" t="inlineStr"/>
+      <c r="M7" t="n">
+        <v>30</v>
+      </c>
+      <c r="N7" t="n">
+        <v>70</v>
+      </c>
+      <c r="O7" t="n">
+        <v>12</v>
+      </c>
+      <c r="P7" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>6</v>
+      </c>
+      <c r="R7" t="n">
+        <v>4</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="n">
+        <v>25</v>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Gfur2NmR</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>hrkecaMB</t>
+        </is>
+      </c>
       <c r="W7" t="n">
         <v>77</v>
       </c>
       <c r="X7" t="n">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="Y7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
         <v>20242025</v>
       </c>
       <c r="AA7" t="inlineStr"/>
       <c r="AB7" t="inlineStr"/>
-      <c r="AC7" t="inlineStr"/>
-      <c r="AD7" t="inlineStr"/>
-      <c r="AE7" t="inlineStr"/>
-      <c r="AF7" t="inlineStr"/>
-      <c r="AG7" t="inlineStr"/>
-      <c r="AH7" t="inlineStr"/>
+      <c r="AC7" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>182.7</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>64.3</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>939000</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>68</v>
+      </c>
       <c r="AI7" t="inlineStr"/>
       <c r="AJ7" t="inlineStr"/>
       <c r="AK7" t="inlineStr"/>
       <c r="AL7" t="inlineStr"/>
       <c r="AM7" t="inlineStr"/>
       <c r="AN7" t="inlineStr"/>
-      <c r="AO7" t="inlineStr"/>
-      <c r="AP7" t="inlineStr"/>
-      <c r="AQ7" t="inlineStr"/>
-      <c r="AR7" t="inlineStr"/>
-      <c r="AS7" t="inlineStr"/>
-      <c r="AT7" t="inlineStr"/>
-      <c r="AU7" t="inlineStr"/>
-      <c r="AV7" t="inlineStr"/>
-      <c r="AW7" t="inlineStr"/>
-      <c r="AX7" t="inlineStr"/>
-      <c r="AY7" t="inlineStr"/>
-      <c r="AZ7" t="inlineStr"/>
+      <c r="AO7" t="n">
+        <v>26.84210526315789</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>182.8947368421053</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>65.26315789473684</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>1195000</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>69.36842105263158</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>29</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>181.6</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>70.2</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>1820000</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>70.2</v>
+      </c>
       <c r="BA7" t="inlineStr"/>
       <c r="BB7" t="inlineStr"/>
       <c r="BC7" t="inlineStr"/>
@@ -1688,114 +1894,173 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>bHLf4sq9</t>
+          <t>lvG7DIkg</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45507.64583333334</v>
-      </c>
-      <c r="C8" t="inlineStr"/>
+        <v>45522.64583333334</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">abisso r 
+  ita </t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">vanni sanna
-  sassari </t>
+          <t xml:space="preserve">stadio benito stirpe
+  frosinone </t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>12000</v>
-      </c>
-      <c r="F8" t="n">
-        <v>2955</v>
-      </c>
+        <v>16227</v>
+      </c>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H8" t="n">
         <v>2</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>UiGfvfvT</t>
+          <t>pfo9H1Wp</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>z7WK5Pwb</t>
+          <t>nJbCGx2U</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr"/>
-      <c r="T8" t="inlineStr"/>
-      <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr"/>
+      <c r="M8" t="n">
+        <v>45</v>
+      </c>
+      <c r="N8" t="n">
+        <v>55</v>
+      </c>
+      <c r="O8" t="n">
+        <v>20</v>
+      </c>
+      <c r="P8" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>12</v>
+      </c>
+      <c r="R8" t="n">
+        <v>4</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="n">
+        <v>13</v>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>dnLs0wVo</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>2kfSDavF</t>
+        </is>
+      </c>
       <c r="W8" t="n">
         <v>77</v>
       </c>
       <c r="X8" t="n">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="Y8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
         <v>20242025</v>
       </c>
-      <c r="AA8" t="inlineStr"/>
-      <c r="AB8" t="inlineStr"/>
-      <c r="AC8" t="inlineStr"/>
-      <c r="AD8" t="inlineStr"/>
-      <c r="AE8" t="inlineStr"/>
-      <c r="AF8" t="inlineStr"/>
-      <c r="AG8" t="inlineStr"/>
-      <c r="AH8" t="inlineStr"/>
-      <c r="AI8" t="inlineStr"/>
-      <c r="AJ8" t="inlineStr"/>
-      <c r="AK8" t="inlineStr"/>
-      <c r="AL8" t="inlineStr"/>
-      <c r="AM8" t="inlineStr"/>
-      <c r="AN8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>0M9xNN8N</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>d0PJxeie</t>
+        </is>
+      </c>
+      <c r="AC8" t="n">
+        <v>21.75</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>185.5</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>65.625</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>1646875</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>74.25</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>27</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>181.4444444444445</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>69.66666666666667</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>1680555.555555556</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>72.88888888888889</v>
+      </c>
       <c r="AO8" t="n">
-        <v>28</v>
+        <v>21.78260869565218</v>
       </c>
       <c r="AP8" t="n">
-        <v>176</v>
+        <v>184.304347826087</v>
       </c>
       <c r="AQ8" t="n">
         <v>1</v>
       </c>
       <c r="AR8" t="n">
-        <v>64</v>
+        <v>63.91304347826087</v>
       </c>
       <c r="AS8" t="n">
-        <v>587500</v>
+        <v>1310869.565217391</v>
       </c>
       <c r="AT8" t="n">
-        <v>64.5</v>
+        <v>74.04347826086956</v>
       </c>
       <c r="AU8" t="n">
-        <v>29</v>
+        <v>24.42857142857143</v>
       </c>
       <c r="AV8" t="n">
-        <v>181.6</v>
+        <v>183.4285714285714</v>
       </c>
       <c r="AW8" t="n">
-        <v>1</v>
+        <v>1.047619047619048</v>
       </c>
       <c r="AX8" t="n">
-        <v>70.2</v>
+        <v>67.76190476190476</v>
       </c>
       <c r="AY8" t="n">
-        <v>1820000</v>
+        <v>1782142.857142857</v>
       </c>
       <c r="AZ8" t="n">
-        <v>70.2</v>
+        <v>73.28571428571429</v>
       </c>
       <c r="BA8" t="inlineStr"/>
       <c r="BB8" t="inlineStr"/>
@@ -1815,110 +2080,199 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>f9bfyqFM</t>
+          <t>6RvR2hEi</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45507.54166666666</v>
-      </c>
-      <c r="C9" t="inlineStr"/>
+        <v>45522.5625</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">marchetti m 
+  ita </t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio dei marmi
-  carrara </t>
+          <t xml:space="preserve">stadio marc antonio bentegodi
+  verona </t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5280</v>
-      </c>
-      <c r="F9" t="n">
-        <v>1707</v>
-      </c>
+        <v>39211</v>
+      </c>
+      <c r="F9" t="inlineStr"/>
       <c r="G9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>hG4fg4z3</t>
+          <t>rJVAIaHo</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>4rwnnbnB</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr"/>
-      <c r="S9" t="inlineStr"/>
-      <c r="T9" t="inlineStr"/>
-      <c r="U9" t="inlineStr"/>
-      <c r="V9" t="inlineStr"/>
+          <t>69Dxbc61</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="M9" t="n">
+        <v>32</v>
+      </c>
+      <c r="N9" t="n">
+        <v>68</v>
+      </c>
+      <c r="O9" t="n">
+        <v>8</v>
+      </c>
+      <c r="P9" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>5</v>
+      </c>
+      <c r="R9" t="n">
+        <v>5</v>
+      </c>
+      <c r="S9" t="n">
+        <v>15</v>
+      </c>
+      <c r="T9" t="n">
+        <v>13</v>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>OW6PtuKn</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>23vSAc12</t>
+        </is>
+      </c>
       <c r="W9" t="n">
         <v>77</v>
       </c>
       <c r="X9" t="n">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="Y9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
         <v>20242025</v>
       </c>
-      <c r="AA9" t="inlineStr"/>
-      <c r="AB9" t="inlineStr"/>
-      <c r="AC9" t="inlineStr"/>
-      <c r="AD9" t="inlineStr"/>
-      <c r="AE9" t="inlineStr"/>
-      <c r="AF9" t="inlineStr"/>
-      <c r="AG9" t="inlineStr"/>
-      <c r="AH9" t="inlineStr"/>
-      <c r="AI9" t="inlineStr"/>
-      <c r="AJ9" t="inlineStr"/>
-      <c r="AK9" t="inlineStr"/>
-      <c r="AL9" t="inlineStr"/>
-      <c r="AM9" t="inlineStr"/>
-      <c r="AN9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>69Dxbc61</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>C06aJvIB</t>
+        </is>
+      </c>
+      <c r="AC9" t="n">
+        <v>25.875</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>185.375</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>73.75</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>5012500</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>76.625</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>182.2</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>80.7</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>31620000</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>81.5</v>
+      </c>
       <c r="AO9" t="n">
-        <v>21.4</v>
+        <v>23.95238095238095</v>
       </c>
       <c r="AP9" t="n">
-        <v>179.8</v>
+        <v>181</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1</v>
+        <v>1.047619047619048</v>
       </c>
       <c r="AR9" t="n">
-        <v>61.6</v>
+        <v>70.04761904761905</v>
       </c>
       <c r="AS9" t="n">
-        <v>775000</v>
+        <v>3560714.285714286</v>
       </c>
       <c r="AT9" t="n">
-        <v>70.8</v>
-      </c>
-      <c r="AU9" t="inlineStr"/>
-      <c r="AV9" t="inlineStr"/>
-      <c r="AW9" t="inlineStr"/>
-      <c r="AX9" t="inlineStr"/>
-      <c r="AY9" t="inlineStr"/>
-      <c r="AZ9" t="inlineStr"/>
-      <c r="BA9" t="inlineStr"/>
-      <c r="BB9" t="inlineStr"/>
-      <c r="BC9" t="inlineStr"/>
-      <c r="BD9" t="inlineStr"/>
-      <c r="BE9" t="inlineStr"/>
-      <c r="BF9" t="inlineStr"/>
-      <c r="BG9" t="inlineStr"/>
+        <v>75.61904761904762</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>24.41176470588235</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>182.1764705882353</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>1.411764705882353</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>76.05882352941177</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>16613235.29411765</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>79.58823529411765</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>23</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>186</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>1</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>66</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>1400000</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>72</v>
+      </c>
       <c r="BH9" t="inlineStr"/>
       <c r="BI9" t="inlineStr"/>
       <c r="BJ9" t="inlineStr"/>
@@ -1927,6 +2281,5346 @@
       <c r="BM9" t="inlineStr"/>
       <c r="BN9" t="inlineStr"/>
     </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>4xHh663n</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45522.5625</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">caputi m 
+  ita </t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio renato dall ara
+  bologna </t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>38279</v>
+      </c>
+      <c r="F10" t="n">
+        <v>26418</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>0M9xNN8N</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>rXw8YKDE</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="M10" t="n">
+        <v>74</v>
+      </c>
+      <c r="N10" t="n">
+        <v>26</v>
+      </c>
+      <c r="O10" t="n">
+        <v>22</v>
+      </c>
+      <c r="P10" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>7</v>
+      </c>
+      <c r="R10" t="n">
+        <v>2</v>
+      </c>
+      <c r="S10" t="n">
+        <v>15</v>
+      </c>
+      <c r="T10" t="n">
+        <v>13</v>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>tjY4uUem</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>ncu4OLs5</t>
+        </is>
+      </c>
+      <c r="W10" t="n">
+        <v>77</v>
+      </c>
+      <c r="X10" t="n">
+        <v>771</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>Q3A3IbXH</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>69Dxbc61</t>
+        </is>
+      </c>
+      <c r="AC10" t="n">
+        <v>25.27272727272727</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>186.1818181818182</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1.363636363636364</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>75.27272727272727</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>8381818.181818182</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>79.09090909090909</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>25.45454545454545</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>184.8181818181818</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>73.45454545454545</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>4663636.363636363</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>76.27272727272727</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>23.75</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>183.5</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>71.59999999999999</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>5271250</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>77.25</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>25.9375</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>181</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>1.0625</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>71.125</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>3143750</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>74.5625</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>185.2</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>5</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>353</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>37325000</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>393</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>25</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>187.5</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>149</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>20800000</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>0lGMiS5j</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45521.65625</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">maresca f 
+  ita </t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio giuseppe meazza  san siro 
+  milan </t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>80018</v>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="n">
+        <v>2</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>8Sa8HInO</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>MZFZnvX4</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="M11" t="n">
+        <v>56</v>
+      </c>
+      <c r="N11" t="n">
+        <v>44</v>
+      </c>
+      <c r="O11" t="n">
+        <v>20</v>
+      </c>
+      <c r="P11" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>6</v>
+      </c>
+      <c r="R11" t="n">
+        <v>3</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="n">
+        <v>7</v>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>KAwSWnoE</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>AB3WB3pA</t>
+        </is>
+      </c>
+      <c r="W11" t="n">
+        <v>77</v>
+      </c>
+      <c r="X11" t="n">
+        <v>771</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>Iw7eKK25</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>C06aJvIB</t>
+        </is>
+      </c>
+      <c r="AC11" t="n">
+        <v>24.72727272727273</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>182.8181818181818</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1.727272727272727</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>81.45454545454545</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>40727272.72727273</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>84.54545454545455</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>185.8</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>11290000</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>78.09999999999999</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>23.31578947368421</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>181.2631578947368</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>1.526315789473684</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>79</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>30031578.94736842</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>84.21052631578948</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>23.89473684210526</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>185.6315789473684</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>1.105263157894737</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>71.94736842105263</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>7406578.947368421</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>77.47368421052632</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>31</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>192</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>2</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>1</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>77</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>5500000</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>77</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>22.25</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>187.5</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>4</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>287</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>49600000</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>hKOA02XN</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45521.65625</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fabbri m 
+  ita </t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio carlo castellani
+  empoli </t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>16284</v>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>0ESCnI1H</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>4YSMlwj7</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="M12" t="n">
+        <v>39</v>
+      </c>
+      <c r="N12" t="n">
+        <v>61</v>
+      </c>
+      <c r="O12" t="n">
+        <v>9</v>
+      </c>
+      <c r="P12" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1</v>
+      </c>
+      <c r="S12" t="n">
+        <v>16</v>
+      </c>
+      <c r="T12" t="n">
+        <v>19</v>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>MBrKQFV7</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>CEv2hvmq</t>
+        </is>
+      </c>
+      <c r="W12" t="n">
+        <v>77</v>
+      </c>
+      <c r="X12" t="n">
+        <v>771</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>Q3A3IbXH</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>ttyLthOA</t>
+        </is>
+      </c>
+      <c r="AC12" t="n">
+        <v>23.72727272727273</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>184.8181818181818</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>70.81818181818181</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>3172727.272727273</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>76.63636363636364</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>25.09090909090909</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>183.1818181818182</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>1.454545454545455</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>71.45454545454545</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>4400000</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>76.90909090909091</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>24.25</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>181.75</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>68.91666666666667</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>2695416.666666667</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>75.20833333333333</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>26.47619047619047</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>181.8571428571429</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>72.47619047619048</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>5076190.476190476</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>75.80952380952381</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>187.4</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>5</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>347</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>11825000</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>363</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>27.66666666666667</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>182</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>224</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>19600000</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>EL1P0u6m</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45521.64583333334</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">collu g 
+  ita </t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio san nicola
+  bari </t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>58270</v>
+      </c>
+      <c r="F13" t="n">
+        <v>20957</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" t="n">
+        <v>3</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>xIkUr2vO</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>hKSfjtsQ</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="n">
+        <v>56</v>
+      </c>
+      <c r="N13" t="n">
+        <v>44</v>
+      </c>
+      <c r="O13" t="n">
+        <v>16</v>
+      </c>
+      <c r="P13" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>4</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6</v>
+      </c>
+      <c r="S13" t="n">
+        <v>20</v>
+      </c>
+      <c r="T13" t="n">
+        <v>14</v>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>nZ24J27c</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>tvh4IkLf</t>
+        </is>
+      </c>
+      <c r="W13" t="n">
+        <v>77</v>
+      </c>
+      <c r="X13" t="n">
+        <v>774</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>G8lYsMgU</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr"/>
+      <c r="AC13" t="n">
+        <v>27.33333333333333</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>181.5555555555555</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1.111111111111111</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>68.66666666666667</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>1541666.666666667</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>71.66666666666667</v>
+      </c>
+      <c r="AI13" t="inlineStr"/>
+      <c r="AJ13" t="inlineStr"/>
+      <c r="AK13" t="inlineStr"/>
+      <c r="AL13" t="inlineStr"/>
+      <c r="AM13" t="inlineStr"/>
+      <c r="AN13" t="inlineStr"/>
+      <c r="AO13" t="n">
+        <v>24.84</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>181.68</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>64.12</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>934600</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>68.36</v>
+      </c>
+      <c r="AU13" t="inlineStr"/>
+      <c r="AV13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr"/>
+      <c r="AX13" t="inlineStr"/>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr"/>
+      <c r="BA13" t="inlineStr"/>
+      <c r="BB13" t="inlineStr"/>
+      <c r="BC13" t="inlineStr"/>
+      <c r="BD13" t="inlineStr"/>
+      <c r="BE13" t="inlineStr"/>
+      <c r="BF13" t="inlineStr"/>
+      <c r="BG13" t="inlineStr"/>
+      <c r="BH13" t="inlineStr"/>
+      <c r="BI13" t="inlineStr"/>
+      <c r="BJ13" t="inlineStr"/>
+      <c r="BK13" t="inlineStr"/>
+      <c r="BL13" t="inlineStr"/>
+      <c r="BM13" t="inlineStr"/>
+      <c r="BN13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>M5TEBdK5</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45521.64583333334</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">manganiello g 
+  ita </t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">arena garibaldi   stadio romeo anconetani
+  pisa </t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>14869</v>
+      </c>
+      <c r="F14" t="n">
+        <v>8770</v>
+      </c>
+      <c r="G14" t="n">
+        <v>2</v>
+      </c>
+      <c r="H14" t="n">
+        <v>2</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>roasMsOT</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>re6VD39b</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="n">
+        <v>54</v>
+      </c>
+      <c r="N14" t="n">
+        <v>46</v>
+      </c>
+      <c r="O14" t="n">
+        <v>19</v>
+      </c>
+      <c r="P14" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>4</v>
+      </c>
+      <c r="R14" t="n">
+        <v>3</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="n">
+        <v>22</v>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>GfucctAF</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>O6SinSSs</t>
+        </is>
+      </c>
+      <c r="W14" t="n">
+        <v>77</v>
+      </c>
+      <c r="X14" t="n">
+        <v>774</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>Q3A3IbXH</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>d0PJxeie</t>
+        </is>
+      </c>
+      <c r="AC14" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>185.3</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>68.3</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>1697500</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>72.2</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>24.44444444444444</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>185.5555555555555</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>67.33333333333333</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>1563888.888888889</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>72.11111111111111</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>22.80952380952381</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>184.2380952380952</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>64.80952380952381</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>1483333.333333333</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>72.14285714285714</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>25.05882352941176</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>186.0588235294118</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>66.41176470588235</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>1320588.235294118</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>71.94117647058823</v>
+      </c>
+      <c r="BA14" t="inlineStr"/>
+      <c r="BB14" t="inlineStr"/>
+      <c r="BC14" t="inlineStr"/>
+      <c r="BD14" t="inlineStr"/>
+      <c r="BE14" t="inlineStr"/>
+      <c r="BF14" t="inlineStr"/>
+      <c r="BG14" t="inlineStr"/>
+      <c r="BH14" t="inlineStr"/>
+      <c r="BI14" t="inlineStr"/>
+      <c r="BJ14" t="inlineStr"/>
+      <c r="BK14" t="inlineStr"/>
+      <c r="BL14" t="inlineStr"/>
+      <c r="BM14" t="inlineStr"/>
+      <c r="BN14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>joLV7EJU</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45521.64583333334</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fourneau f 
+  ita </t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio arechi
+  salerno </t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>37800</v>
+      </c>
+      <c r="F15" t="n">
+        <v>12509</v>
+      </c>
+      <c r="G15" t="n">
+        <v>2</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Mq05g4BP</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>C0yUqo8c</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="n">
+        <v>70</v>
+      </c>
+      <c r="N15" t="n">
+        <v>30</v>
+      </c>
+      <c r="O15" t="n">
+        <v>15</v>
+      </c>
+      <c r="P15" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>7</v>
+      </c>
+      <c r="R15" t="n">
+        <v>3</v>
+      </c>
+      <c r="S15" t="n">
+        <v>23</v>
+      </c>
+      <c r="T15" t="n">
+        <v>12</v>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>OjWmexQb</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>8dDPzPa7</t>
+        </is>
+      </c>
+      <c r="W15" t="n">
+        <v>77</v>
+      </c>
+      <c r="X15" t="n">
+        <v>774</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>69Dxbc61</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>MkPmVv50</t>
+        </is>
+      </c>
+      <c r="AC15" t="n">
+        <v>25.11111111111111</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>183.7777777777778</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>69.44444444444444</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>2572222.222222222</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>74.88888888888889</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>24.375</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>181.5</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>65.125</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>1140000</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>70.75</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>22.72222222222222</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>178.0555555555555</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>66.22222222222223</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>1901388.888888889</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>74.61111111111111</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>26.84210526315789</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>182.7368421052632</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>65</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>844473.6842105263</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>68.47368421052632</v>
+      </c>
+      <c r="BA15" t="inlineStr"/>
+      <c r="BB15" t="inlineStr"/>
+      <c r="BC15" t="inlineStr"/>
+      <c r="BD15" t="inlineStr"/>
+      <c r="BE15" t="inlineStr"/>
+      <c r="BF15" t="inlineStr"/>
+      <c r="BG15" t="inlineStr"/>
+      <c r="BH15" t="inlineStr"/>
+      <c r="BI15" t="inlineStr"/>
+      <c r="BJ15" t="inlineStr"/>
+      <c r="BK15" t="inlineStr"/>
+      <c r="BL15" t="inlineStr"/>
+      <c r="BM15" t="inlineStr"/>
+      <c r="BN15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>WvwvCQVo</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45521.64583333334</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">perri m 
+  ita </t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio marco druso
+  bolzano </t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>5539</v>
+      </c>
+      <c r="F16" t="n">
+        <v>3512</v>
+      </c>
+      <c r="G16" t="n">
+        <v>2</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>W02MZDnp</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>MBn63swN</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="n">
+        <v>68</v>
+      </c>
+      <c r="N16" t="n">
+        <v>32</v>
+      </c>
+      <c r="O16" t="n">
+        <v>9</v>
+      </c>
+      <c r="P16" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>3</v>
+      </c>
+      <c r="R16" t="n">
+        <v>2</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="n">
+        <v>15</v>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>bmzifXwb</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>YTZ7S7pk</t>
+        </is>
+      </c>
+      <c r="W16" t="n">
+        <v>77</v>
+      </c>
+      <c r="X16" t="n">
+        <v>774</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>rXw8YKDE</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>0M9xNN8N</t>
+        </is>
+      </c>
+      <c r="AC16" t="n">
+        <v>30</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>182.8</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>67.90000000000001</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>951000</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>69.7</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>26.45454545454545</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>184.4545454545455</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>1.090909090909091</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>66.81818181818181</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>1190909.090909091</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>69.72727272727273</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>24.44444444444444</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>185.3888888888889</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>1.055555555555556</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>65.44444444444444</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>1131944.444444444</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>71.11111111111111</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>24.92307692307692</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>180.5384615384615</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>1.076923076923077</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>65.61538461538461</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>1168846.153846154</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>70.46153846153847</v>
+      </c>
+      <c r="BA16" t="inlineStr"/>
+      <c r="BB16" t="inlineStr"/>
+      <c r="BC16" t="inlineStr"/>
+      <c r="BD16" t="inlineStr"/>
+      <c r="BE16" t="inlineStr"/>
+      <c r="BF16" t="inlineStr"/>
+      <c r="BG16" t="inlineStr"/>
+      <c r="BH16" t="inlineStr"/>
+      <c r="BI16" t="inlineStr"/>
+      <c r="BJ16" t="inlineStr"/>
+      <c r="BK16" t="inlineStr"/>
+      <c r="BL16" t="inlineStr"/>
+      <c r="BM16" t="inlineStr"/>
+      <c r="BN16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>O2Fteteo</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45521.5625</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">feliciani e 
+  ita </t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio luigi ferraris
+  genoa </t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>36599</v>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H17" t="n">
+        <v>2</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>d0PJxeie</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Iw7eKK25</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="M17" t="n">
+        <v>32</v>
+      </c>
+      <c r="N17" t="n">
+        <v>68</v>
+      </c>
+      <c r="O17" t="n">
+        <v>10</v>
+      </c>
+      <c r="P17" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>6</v>
+      </c>
+      <c r="R17" t="n">
+        <v>9</v>
+      </c>
+      <c r="S17" t="n">
+        <v>15</v>
+      </c>
+      <c r="T17" t="n">
+        <v>14</v>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>tSiEeKvS</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>j32a3mqs</t>
+        </is>
+      </c>
+      <c r="W17" t="n">
+        <v>77</v>
+      </c>
+      <c r="X17" t="n">
+        <v>771</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>nJbCGx2U</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>8Sa8HInO</t>
+        </is>
+      </c>
+      <c r="AC17" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>184.9</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>73.59999999999999</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>5720000</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>78.2</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>28.36363636363636</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>182.8181818181818</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>2.454545454545455</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>83.36363636363636</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>43272727.27272727</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>85.36363636363636</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>26.70588235294118</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>184.4117647058823</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>1.352941176470588</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>70.64705882352941</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>3080882.352941176</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>73.70588235294117</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>25.82608695652174</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>182.7826086956522</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>1.782608695652174</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>78.95652173913044</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>26208695.65217391</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>82</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>22.25</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>188</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>258</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>4850000</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>295</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>28</v>
+      </c>
+      <c r="BI17" t="n">
+        <v>184</v>
+      </c>
+      <c r="BJ17" t="n">
+        <v>2.333333333333333</v>
+      </c>
+      <c r="BK17" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL17" t="n">
+        <v>236</v>
+      </c>
+      <c r="BM17" t="n">
+        <v>53800000</v>
+      </c>
+      <c r="BN17" t="n">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>Sf88FVcc</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45521.5625</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ayroldi g 
+  ita </t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio ennio tardini
+  parma </t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>27906</v>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="n">
+        <v>1</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>6DxlaxHN</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Q3A3IbXH</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="M18" t="n">
+        <v>39</v>
+      </c>
+      <c r="N18" t="n">
+        <v>61</v>
+      </c>
+      <c r="O18" t="n">
+        <v>13</v>
+      </c>
+      <c r="P18" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>5</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7</v>
+      </c>
+      <c r="S18" t="n">
+        <v>15</v>
+      </c>
+      <c r="T18" t="n">
+        <v>9</v>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>lQEaJ9QD</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>619UPLrb</t>
+        </is>
+      </c>
+      <c r="W18" t="n">
+        <v>77</v>
+      </c>
+      <c r="X18" t="n">
+        <v>771</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>0M9xNN8N</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>C06aJvIB</t>
+        </is>
+      </c>
+      <c r="AC18" t="n">
+        <v>22.44444444444444</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>184.7777777777778</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>69.55555555555556</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>3555555.555555556</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>77.33333333333333</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>185.7</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>76.09999999999999</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>13710000</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>80.3</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>22.73913043478261</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>180.5217391304348</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>1.130434782608696</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>66.73913043478261</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>2866956.52173913</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>74.26086956521739</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>22.68181818181818</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>180.4545454545455</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>1.409090909090909</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>73.13636363636364</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>11150000</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>80.77272727272727</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>187</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>5</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>355</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>15700000</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>373</v>
+      </c>
+      <c r="BH18" t="n">
+        <v>24</v>
+      </c>
+      <c r="BI18" t="n">
+        <v>187</v>
+      </c>
+      <c r="BJ18" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK18" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL18" t="n">
+        <v>72</v>
+      </c>
+      <c r="BM18" t="n">
+        <v>3200000</v>
+      </c>
+      <c r="BN18" t="n">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>8KfYbJz0</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45520.64583333334</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">aureliano g 
+  ita </t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio mario rigamonti
+  brescia </t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>19500</v>
+      </c>
+      <c r="F19" t="n">
+        <v>5317</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>jci0qO9B</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>n38Nktmn</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="n">
+        <v>37</v>
+      </c>
+      <c r="N19" t="n">
+        <v>63</v>
+      </c>
+      <c r="O19" t="n">
+        <v>18</v>
+      </c>
+      <c r="P19" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>6</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1</v>
+      </c>
+      <c r="S19" t="n">
+        <v>15</v>
+      </c>
+      <c r="T19" t="n">
+        <v>10</v>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>lb1XFX3n</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Wn0poKgt</t>
+        </is>
+      </c>
+      <c r="W19" t="n">
+        <v>77</v>
+      </c>
+      <c r="X19" t="n">
+        <v>774</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>8C9JjMXu</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>pfo9H1Wp</t>
+        </is>
+      </c>
+      <c r="AC19" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>184.7</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>66.40000000000001</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>1225000</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>70.09999999999999</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>181.5</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>70.7</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>3020000</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>23.21428571428572</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>181.2142857142857</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>64.71428571428571</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>1164285.714285714</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>72.28571428571429</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>24.375</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>183.8333333333333</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>1.041666666666667</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>69.66666666666667</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>2475000</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>75.41666666666667</v>
+      </c>
+      <c r="BA19" t="inlineStr"/>
+      <c r="BB19" t="inlineStr"/>
+      <c r="BC19" t="inlineStr"/>
+      <c r="BD19" t="inlineStr"/>
+      <c r="BE19" t="inlineStr"/>
+      <c r="BF19" t="inlineStr"/>
+      <c r="BG19" t="inlineStr"/>
+      <c r="BH19" t="inlineStr"/>
+      <c r="BI19" t="inlineStr"/>
+      <c r="BJ19" t="inlineStr"/>
+      <c r="BK19" t="inlineStr"/>
+      <c r="BL19" t="inlineStr"/>
+      <c r="BM19" t="inlineStr"/>
+      <c r="BN19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>8KIdPmPc</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>45516.67708333334</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pezzuto i 
+  ita </t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unipol domus
+  cagliari </t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>16416</v>
+      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="n">
+        <v>3</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>SCGVmKHb</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>hG4fg4z3</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="n">
+        <v>53</v>
+      </c>
+      <c r="N20" t="n">
+        <v>47</v>
+      </c>
+      <c r="O20" t="n">
+        <v>21</v>
+      </c>
+      <c r="P20" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>8</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1</v>
+      </c>
+      <c r="S20" t="n">
+        <v>15</v>
+      </c>
+      <c r="T20" t="n">
+        <v>11</v>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>MLVBCoYg</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>lSb6U6l0</t>
+        </is>
+      </c>
+      <c r="W20" t="n">
+        <v>77</v>
+      </c>
+      <c r="X20" t="n">
+        <v>773</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>69Dxbc61</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr"/>
+      <c r="AC20" t="n">
+        <v>26.27272727272727</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>185.2727272727273</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1.090909090909091</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>72</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>4015909.090909091</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>74.72727272727273</v>
+      </c>
+      <c r="AI20" t="inlineStr"/>
+      <c r="AJ20" t="inlineStr"/>
+      <c r="AK20" t="inlineStr"/>
+      <c r="AL20" t="inlineStr"/>
+      <c r="AM20" t="inlineStr"/>
+      <c r="AN20" t="inlineStr"/>
+      <c r="AO20" t="n">
+        <v>23.92307692307692</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>183.9230769230769</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>1.230769230769231</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>68.42307692307692</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>3002884.615384615</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>74.65384615384616</v>
+      </c>
+      <c r="AU20" t="inlineStr"/>
+      <c r="AV20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr"/>
+      <c r="AX20" t="inlineStr"/>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr"/>
+      <c r="BA20" t="inlineStr"/>
+      <c r="BB20" t="inlineStr"/>
+      <c r="BC20" t="inlineStr"/>
+      <c r="BD20" t="inlineStr"/>
+      <c r="BE20" t="inlineStr"/>
+      <c r="BF20" t="inlineStr"/>
+      <c r="BG20" t="inlineStr"/>
+      <c r="BH20" t="inlineStr"/>
+      <c r="BI20" t="inlineStr"/>
+      <c r="BJ20" t="inlineStr"/>
+      <c r="BK20" t="inlineStr"/>
+      <c r="BL20" t="inlineStr"/>
+      <c r="BM20" t="inlineStr"/>
+      <c r="BN20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>fNwTkrUF</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>45516.65625</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rutella d 
+  ita </t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio arechi
+  salerno </t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>37800</v>
+      </c>
+      <c r="F21" t="n">
+        <v>6905</v>
+      </c>
+      <c r="G21" t="n">
+        <v>4</v>
+      </c>
+      <c r="H21" t="n">
+        <v>3</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Mq05g4BP</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>re6VD39b</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="n">
+        <v>59</v>
+      </c>
+      <c r="N21" t="n">
+        <v>41</v>
+      </c>
+      <c r="O21" t="n">
+        <v>11</v>
+      </c>
+      <c r="P21" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>5</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7</v>
+      </c>
+      <c r="S21" t="n">
+        <v>13</v>
+      </c>
+      <c r="T21" t="n">
+        <v>17</v>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>OjWmexQb</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>O6SinSSs</t>
+        </is>
+      </c>
+      <c r="W21" t="n">
+        <v>77</v>
+      </c>
+      <c r="X21" t="n">
+        <v>773</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>69Dxbc61</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>d0PJxeie</t>
+        </is>
+      </c>
+      <c r="AC21" t="n">
+        <v>24.11111111111111</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>182</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>69.33333333333333</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>4894444.444444444</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>75.88888888888889</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>186.3</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>65.8</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>1295000</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>71.5</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>24.10526315789474</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>182.8421052631579</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>67.63157894736842</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>2236842.105263158</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>74.47368421052632</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>24.27777777777778</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>183.5555555555555</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>66.83333333333333</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>1538888.888888889</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>73.05555555555556</v>
+      </c>
+      <c r="BA21" t="inlineStr"/>
+      <c r="BB21" t="inlineStr"/>
+      <c r="BC21" t="inlineStr"/>
+      <c r="BD21" t="inlineStr"/>
+      <c r="BE21" t="inlineStr"/>
+      <c r="BF21" t="inlineStr"/>
+      <c r="BG21" t="inlineStr"/>
+      <c r="BH21" t="inlineStr"/>
+      <c r="BI21" t="inlineStr"/>
+      <c r="BJ21" t="inlineStr"/>
+      <c r="BK21" t="inlineStr"/>
+      <c r="BL21" t="inlineStr"/>
+      <c r="BM21" t="inlineStr"/>
+      <c r="BN21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>42SH31wI</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>45516.5625</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">perri m 
+  ita </t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio via del mare
+  lecce </t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>40670</v>
+      </c>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="n">
+        <v>2</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>G8lYsMgU</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>z7WK5Pwb</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="n">
+        <v>38</v>
+      </c>
+      <c r="N22" t="n">
+        <v>62</v>
+      </c>
+      <c r="O22" t="n">
+        <v>19</v>
+      </c>
+      <c r="P22" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>9</v>
+      </c>
+      <c r="R22" t="n">
+        <v>2</v>
+      </c>
+      <c r="S22" t="n">
+        <v>20</v>
+      </c>
+      <c r="T22" t="n">
+        <v>9</v>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>KtGrCa5d</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>hrkecaMB</t>
+        </is>
+      </c>
+      <c r="W22" t="n">
+        <v>77</v>
+      </c>
+      <c r="X22" t="n">
+        <v>773</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>xIkUr2vO</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr"/>
+      <c r="AC22" t="n">
+        <v>24</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>183.125</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>71.875</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>5475000</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>77.875</v>
+      </c>
+      <c r="AI22" t="inlineStr"/>
+      <c r="AJ22" t="inlineStr"/>
+      <c r="AK22" t="inlineStr"/>
+      <c r="AL22" t="inlineStr"/>
+      <c r="AM22" t="inlineStr"/>
+      <c r="AN22" t="inlineStr"/>
+      <c r="AO22" t="n">
+        <v>21.83333333333333</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>181.2777777777778</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>66.77777777777777</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>2694444.444444444</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>75.66666666666667</v>
+      </c>
+      <c r="AU22" t="inlineStr"/>
+      <c r="AV22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr"/>
+      <c r="AX22" t="inlineStr"/>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr"/>
+      <c r="BA22" t="inlineStr"/>
+      <c r="BB22" t="inlineStr"/>
+      <c r="BC22" t="inlineStr"/>
+      <c r="BD22" t="inlineStr"/>
+      <c r="BE22" t="inlineStr"/>
+      <c r="BF22" t="inlineStr"/>
+      <c r="BG22" t="inlineStr"/>
+      <c r="BH22" t="inlineStr"/>
+      <c r="BI22" t="inlineStr"/>
+      <c r="BJ22" t="inlineStr"/>
+      <c r="BK22" t="inlineStr"/>
+      <c r="BL22" t="inlineStr"/>
+      <c r="BM22" t="inlineStr"/>
+      <c r="BN22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>Aeu0r0Mk</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>45516.54166666666</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fourneau f 
+  ita </t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio benito stirpe
+  frosinone </t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>16227</v>
+      </c>
+      <c r="F23" t="n">
+        <v>9384</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" t="n">
+        <v>3</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>pfo9H1Wp</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>roasMsOT</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="n">
+        <v>59</v>
+      </c>
+      <c r="N23" t="n">
+        <v>41</v>
+      </c>
+      <c r="O23" t="n">
+        <v>5</v>
+      </c>
+      <c r="P23" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>2</v>
+      </c>
+      <c r="R23" t="n">
+        <v>4</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="n">
+        <v>19</v>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>dnLs0wVo</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>GfucctAF</t>
+        </is>
+      </c>
+      <c r="W23" t="n">
+        <v>77</v>
+      </c>
+      <c r="X23" t="n">
+        <v>773</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>0M9xNN8N</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>Q3A3IbXH</t>
+        </is>
+      </c>
+      <c r="AC23" t="n">
+        <v>22.22222222222222</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>186.1111111111111</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>65.77777777777777</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>1597222.222222222</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>74.55555555555556</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>185.3</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>68.3</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>1697500</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>72.2</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>20.66666666666667</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>185.5333333333333</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>61.86666666666667</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>980000</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>73.86666666666666</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>22.52</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>181.48</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>64.56</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>1611000</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>72.2</v>
+      </c>
+      <c r="BA23" t="inlineStr"/>
+      <c r="BB23" t="inlineStr"/>
+      <c r="BC23" t="inlineStr"/>
+      <c r="BD23" t="inlineStr"/>
+      <c r="BE23" t="inlineStr"/>
+      <c r="BF23" t="inlineStr"/>
+      <c r="BG23" t="inlineStr"/>
+      <c r="BH23" t="inlineStr"/>
+      <c r="BI23" t="inlineStr"/>
+      <c r="BJ23" t="inlineStr"/>
+      <c r="BK23" t="inlineStr"/>
+      <c r="BL23" t="inlineStr"/>
+      <c r="BM23" t="inlineStr"/>
+      <c r="BN23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>ALOjHNNj</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>45515.67708333334</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ghersini d 
+  ita </t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio olimpico di torino
+  turin </t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>28177</v>
+      </c>
+      <c r="F24" t="n">
+        <v>12035</v>
+      </c>
+      <c r="G24" t="n">
+        <v>2</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>MZFZnvX4</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>p84TeBhA</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="n">
+        <v>60</v>
+      </c>
+      <c r="N24" t="n">
+        <v>40</v>
+      </c>
+      <c r="O24" t="n">
+        <v>8</v>
+      </c>
+      <c r="P24" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>2</v>
+      </c>
+      <c r="R24" t="n">
+        <v>4</v>
+      </c>
+      <c r="S24" t="n">
+        <v>6</v>
+      </c>
+      <c r="T24" t="n">
+        <v>12</v>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>AB3WB3pA</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Yika9O16</t>
+        </is>
+      </c>
+      <c r="W24" t="n">
+        <v>77</v>
+      </c>
+      <c r="X24" t="n">
+        <v>773</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>C06aJvIB</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>GnizyMB7</t>
+        </is>
+      </c>
+      <c r="AC24" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>185.8</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>11290000</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>78.09999999999999</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>184.8</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>66.40000000000001</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>1167500</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>70.8</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>23.57894736842105</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>184.4736842105263</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>1.052631578947368</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>70.05263157894737</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>5423684.210526315</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>76.47368421052632</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>22.28571428571428</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>179.7142857142857</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>64.14285714285714</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>1171428.571428571</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>71.85714285714286</v>
+      </c>
+      <c r="BA24" t="inlineStr"/>
+      <c r="BB24" t="inlineStr"/>
+      <c r="BC24" t="inlineStr"/>
+      <c r="BD24" t="inlineStr"/>
+      <c r="BE24" t="inlineStr"/>
+      <c r="BF24" t="inlineStr"/>
+      <c r="BG24" t="inlineStr"/>
+      <c r="BH24" t="inlineStr"/>
+      <c r="BI24" t="inlineStr"/>
+      <c r="BJ24" t="inlineStr"/>
+      <c r="BK24" t="inlineStr"/>
+      <c r="BL24" t="inlineStr"/>
+      <c r="BM24" t="inlineStr"/>
+      <c r="BN24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>ILr8tvi2</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="n">
+        <v>45515.65625</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">collu g 
+  ita </t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio luigi ferraris
+  genoa </t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>36599</v>
+      </c>
+      <c r="F25" t="n">
+        <v>14196</v>
+      </c>
+      <c r="G25" t="n">
+        <v>2</v>
+      </c>
+      <c r="H25" t="n">
+        <v>1</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>nJbCGx2U</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>ttyLthOA</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="n">
+        <v>43</v>
+      </c>
+      <c r="N25" t="n">
+        <v>57</v>
+      </c>
+      <c r="O25" t="n">
+        <v>11</v>
+      </c>
+      <c r="P25" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>3</v>
+      </c>
+      <c r="R25" t="n">
+        <v>5</v>
+      </c>
+      <c r="S25" t="n">
+        <v>4</v>
+      </c>
+      <c r="T25" t="n">
+        <v>13</v>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>2kfSDavF</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>EZS2ir7i</t>
+        </is>
+      </c>
+      <c r="W25" t="n">
+        <v>77</v>
+      </c>
+      <c r="X25" t="n">
+        <v>773</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>d0PJxeie</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>4YSMlwj7</t>
+        </is>
+      </c>
+      <c r="AC25" t="n">
+        <v>27.66666666666667</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>181.7777777777778</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>1.111111111111111</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>70.33333333333333</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>2136111.111111111</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>73.44444444444444</v>
+      </c>
+      <c r="AI25" t="inlineStr"/>
+      <c r="AJ25" t="inlineStr"/>
+      <c r="AK25" t="inlineStr"/>
+      <c r="AL25" t="inlineStr"/>
+      <c r="AM25" t="inlineStr"/>
+      <c r="AN25" t="inlineStr"/>
+      <c r="AO25" t="n">
+        <v>25.25</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>181.85</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>67.55</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>1749750</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>72.45</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>28.04545454545455</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>183.8636363636364</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>1.363636363636364</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>70.59090909090909</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>3314318.181818182</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>71.68181818181819</v>
+      </c>
+      <c r="BA25" t="inlineStr"/>
+      <c r="BB25" t="inlineStr"/>
+      <c r="BC25" t="inlineStr"/>
+      <c r="BD25" t="inlineStr"/>
+      <c r="BE25" t="inlineStr"/>
+      <c r="BF25" t="inlineStr"/>
+      <c r="BG25" t="inlineStr"/>
+      <c r="BH25" t="inlineStr"/>
+      <c r="BI25" t="inlineStr"/>
+      <c r="BJ25" t="inlineStr"/>
+      <c r="BK25" t="inlineStr"/>
+      <c r="BL25" t="inlineStr"/>
+      <c r="BM25" t="inlineStr"/>
+      <c r="BN25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>bepKi4a3</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>45515.5625</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">perenzoni d 
+  ita </t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio ennio tardini
+  parma </t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>27906</v>
+      </c>
+      <c r="F26" t="n">
+        <v>5034</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" t="n">
+        <v>1</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>6DxlaxHN</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>n38Nktmn</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="n">
+        <v>47</v>
+      </c>
+      <c r="N26" t="n">
+        <v>53</v>
+      </c>
+      <c r="O26" t="n">
+        <v>17</v>
+      </c>
+      <c r="P26" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>4</v>
+      </c>
+      <c r="R26" t="n">
+        <v>4</v>
+      </c>
+      <c r="S26" t="n">
+        <v>7</v>
+      </c>
+      <c r="T26" t="n">
+        <v>12</v>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>lQEaJ9QD</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Wn0poKgt</t>
+        </is>
+      </c>
+      <c r="W26" t="n">
+        <v>77</v>
+      </c>
+      <c r="X26" t="n">
+        <v>773</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>0M9xNN8N</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>pfo9H1Wp</t>
+        </is>
+      </c>
+      <c r="AC26" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>185.3</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>69.59999999999999</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>2345000</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>74.2</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>181.5</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>70.7</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>3020000</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>22.95238095238095</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>183.1904761904762</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>1.047619047619048</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>67.04761904761905</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>2280476.19047619</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>74.66666666666667</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>24.82608695652174</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>183.9130434782609</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>69.26086956521739</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>2280434.782608696</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>74.26086956521739</v>
+      </c>
+      <c r="BA26" t="inlineStr"/>
+      <c r="BB26" t="inlineStr"/>
+      <c r="BC26" t="inlineStr"/>
+      <c r="BD26" t="inlineStr"/>
+      <c r="BE26" t="inlineStr"/>
+      <c r="BF26" t="inlineStr"/>
+      <c r="BG26" t="inlineStr"/>
+      <c r="BH26" t="inlineStr"/>
+      <c r="BI26" t="inlineStr"/>
+      <c r="BJ26" t="inlineStr"/>
+      <c r="BK26" t="inlineStr"/>
+      <c r="BL26" t="inlineStr"/>
+      <c r="BM26" t="inlineStr"/>
+      <c r="BN26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>6sP22LDL</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="n">
+        <v>45515.54166666666</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">caputi m 
+  ita </t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio mario rigamonti
+  brescia </t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>19500</v>
+      </c>
+      <c r="F27" t="n">
+        <v>4310</v>
+      </c>
+      <c r="G27" t="n">
+        <v>3</v>
+      </c>
+      <c r="H27" t="n">
+        <v>1</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>jci0qO9B</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>MkPmVv50</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="n">
+        <v>38</v>
+      </c>
+      <c r="N27" t="n">
+        <v>62</v>
+      </c>
+      <c r="O27" t="n">
+        <v>9</v>
+      </c>
+      <c r="P27" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>5</v>
+      </c>
+      <c r="R27" t="n">
+        <v>8</v>
+      </c>
+      <c r="S27" t="n">
+        <v>14</v>
+      </c>
+      <c r="T27" t="n">
+        <v>12</v>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>lb1XFX3n</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>n10g3KfJ</t>
+        </is>
+      </c>
+      <c r="W27" t="n">
+        <v>77</v>
+      </c>
+      <c r="X27" t="n">
+        <v>773</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>8C9JjMXu</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>rJVAIaHo</t>
+        </is>
+      </c>
+      <c r="AC27" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>184.7</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>66.40000000000001</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>1225000</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>70.09999999999999</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>26.88888888888889</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>183.8888888888889</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>1.111111111111111</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>69.66666666666667</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>1888888.888888889</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>72.33333333333333</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>22.77777777777778</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>181.6111111111111</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>64.33333333333333</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>1217777.777777778</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>72.66666666666667</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>23.47368421052632</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>184.2631578947368</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>1.052631578947368</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>66.78947368421052</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>1748421.052631579</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>73.42105263157895</v>
+      </c>
+      <c r="BA27" t="inlineStr"/>
+      <c r="BB27" t="inlineStr"/>
+      <c r="BC27" t="inlineStr"/>
+      <c r="BD27" t="inlineStr"/>
+      <c r="BE27" t="inlineStr"/>
+      <c r="BF27" t="inlineStr"/>
+      <c r="BG27" t="inlineStr"/>
+      <c r="BH27" t="inlineStr"/>
+      <c r="BI27" t="inlineStr"/>
+      <c r="BJ27" t="inlineStr"/>
+      <c r="BK27" t="inlineStr"/>
+      <c r="BL27" t="inlineStr"/>
+      <c r="BM27" t="inlineStr"/>
+      <c r="BN27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>dC3sew6e</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>45514.67708333334</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bonacina k 
+  ita </t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio diego armando maradona
+  naples </t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>54726</v>
+      </c>
+      <c r="F28" t="n">
+        <v>52000</v>
+      </c>
+      <c r="G28" t="n">
+        <v>1</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>69Dxbc61</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>MBn63swN</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="n">
+        <v>70</v>
+      </c>
+      <c r="N28" t="n">
+        <v>30</v>
+      </c>
+      <c r="O28" t="n">
+        <v>28</v>
+      </c>
+      <c r="P28" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>6</v>
+      </c>
+      <c r="R28" t="n">
+        <v>2</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="n">
+        <v>6</v>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>23vSAc12</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>YTZ7S7pk</t>
+        </is>
+      </c>
+      <c r="W28" t="n">
+        <v>77</v>
+      </c>
+      <c r="X28" t="n">
+        <v>773</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>C06aJvIB</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>0M9xNN8N</t>
+        </is>
+      </c>
+      <c r="AC28" t="n">
+        <v>26.72727272727273</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>182.0909090909091</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>1.727272727272727</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>80.72727272727273</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>32290909.09090909</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>82.36363636363636</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>184.6</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>67.8</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>1382500</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>70.7</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>25.15</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>182.65</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>75.2</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>9576250</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>77.95</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>23.78571428571428</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>181.1428571428571</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>63.85714285714285</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>1024642.857142857</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>69.64285714285714</v>
+      </c>
+      <c r="BA28" t="inlineStr"/>
+      <c r="BB28" t="inlineStr"/>
+      <c r="BC28" t="inlineStr"/>
+      <c r="BD28" t="inlineStr"/>
+      <c r="BE28" t="inlineStr"/>
+      <c r="BF28" t="inlineStr"/>
+      <c r="BG28" t="inlineStr"/>
+      <c r="BH28" t="inlineStr"/>
+      <c r="BI28" t="inlineStr"/>
+      <c r="BJ28" t="inlineStr"/>
+      <c r="BK28" t="inlineStr"/>
+      <c r="BL28" t="inlineStr"/>
+      <c r="BM28" t="inlineStr"/>
+      <c r="BN28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>Ob5Zdayq</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="n">
+        <v>45514.65625</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">arena a 
+  ita </t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio carlo castellani
+  empoli </t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>16284</v>
+      </c>
+      <c r="F29" t="n">
+        <v>1738</v>
+      </c>
+      <c r="G29" t="n">
+        <v>4</v>
+      </c>
+      <c r="H29" t="n">
+        <v>1</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>0ESCnI1H</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>GnizyMB7</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="n">
+        <v>57</v>
+      </c>
+      <c r="N29" t="n">
+        <v>43</v>
+      </c>
+      <c r="O29" t="n">
+        <v>22</v>
+      </c>
+      <c r="P29" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>8</v>
+      </c>
+      <c r="R29" t="n">
+        <v>3</v>
+      </c>
+      <c r="S29" t="n">
+        <v>9</v>
+      </c>
+      <c r="T29" t="n">
+        <v>10</v>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>MBrKQFV7</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>nsYMfLJM</t>
+        </is>
+      </c>
+      <c r="W29" t="n">
+        <v>77</v>
+      </c>
+      <c r="X29" t="n">
+        <v>773</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>Q3A3IbXH</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>p84TeBhA</t>
+        </is>
+      </c>
+      <c r="AC29" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>185</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>70.7</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>3150000</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>76.40000000000001</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>28.22222222222222</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>179.4444444444445</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>67.88888888888889</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>1133333.333333333</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>69.88888888888889</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>24.81818181818182</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>181.4090909090909</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>67.45454545454545</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>2088181.818181818</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>73.18181818181819</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>25</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>184.25</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>65.16666666666667</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>1014583.333333333</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>68.75</v>
+      </c>
+      <c r="BA29" t="inlineStr"/>
+      <c r="BB29" t="inlineStr"/>
+      <c r="BC29" t="inlineStr"/>
+      <c r="BD29" t="inlineStr"/>
+      <c r="BE29" t="inlineStr"/>
+      <c r="BF29" t="inlineStr"/>
+      <c r="BG29" t="inlineStr"/>
+      <c r="BH29" t="inlineStr"/>
+      <c r="BI29" t="inlineStr"/>
+      <c r="BJ29" t="inlineStr"/>
+      <c r="BK29" t="inlineStr"/>
+      <c r="BL29" t="inlineStr"/>
+      <c r="BM29" t="inlineStr"/>
+      <c r="BN29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>02s0k9od</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>45514.5625</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">crezzini v 
+  ita </t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio marc antonio bentegodi
+  verona </t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>39211</v>
+      </c>
+      <c r="F30" t="n">
+        <v>7048</v>
+      </c>
+      <c r="G30" t="n">
+        <v>1</v>
+      </c>
+      <c r="H30" t="n">
+        <v>2</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>rJVAIaHo</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>xddf1qfh</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="n">
+        <v>54</v>
+      </c>
+      <c r="N30" t="n">
+        <v>46</v>
+      </c>
+      <c r="O30" t="n">
+        <v>11</v>
+      </c>
+      <c r="P30" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>3</v>
+      </c>
+      <c r="R30" t="n">
+        <v>4</v>
+      </c>
+      <c r="S30" t="n">
+        <v>14</v>
+      </c>
+      <c r="T30" t="n">
+        <v>7</v>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>OW6PtuKn</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>vD8aDRIm</t>
+        </is>
+      </c>
+      <c r="W30" t="n">
+        <v>77</v>
+      </c>
+      <c r="X30" t="n">
+        <v>773</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>69Dxbc61</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr"/>
+      <c r="AC30" t="n">
+        <v>24.88888888888889</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>184.1111111111111</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>1.111111111111111</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>73.11111111111111</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>5011111.111111111</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>77.44444444444444</v>
+      </c>
+      <c r="AI30" t="inlineStr"/>
+      <c r="AJ30" t="inlineStr"/>
+      <c r="AK30" t="inlineStr"/>
+      <c r="AL30" t="inlineStr"/>
+      <c r="AM30" t="inlineStr"/>
+      <c r="AN30" t="inlineStr"/>
+      <c r="AO30" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>184.0555555555555</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>70.22222222222223</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>2776388.888888889</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>74.05555555555556</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>24.55555555555556</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>181.5555555555555</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>66.88888888888889</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>1650000</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>71</v>
+      </c>
+      <c r="BA30" t="inlineStr"/>
+      <c r="BB30" t="inlineStr"/>
+      <c r="BC30" t="inlineStr"/>
+      <c r="BD30" t="inlineStr"/>
+      <c r="BE30" t="inlineStr"/>
+      <c r="BF30" t="inlineStr"/>
+      <c r="BG30" t="inlineStr"/>
+      <c r="BH30" t="inlineStr"/>
+      <c r="BI30" t="inlineStr"/>
+      <c r="BJ30" t="inlineStr"/>
+      <c r="BK30" t="inlineStr"/>
+      <c r="BL30" t="inlineStr"/>
+      <c r="BM30" t="inlineStr"/>
+      <c r="BN30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>bs5ow5pA</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="n">
+        <v>45514.54166666666</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">galipo s 
+  ita </t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio giovanni zini
+  cremona </t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>20641</v>
+      </c>
+      <c r="F31" t="n">
+        <v>3724</v>
+      </c>
+      <c r="G31" t="n">
+        <v>2</v>
+      </c>
+      <c r="H31" t="n">
+        <v>1</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>KUzfp5N3</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>xIkUr2vO</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="n">
+        <v>58</v>
+      </c>
+      <c r="N31" t="n">
+        <v>42</v>
+      </c>
+      <c r="O31" t="n">
+        <v>13</v>
+      </c>
+      <c r="P31" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>3</v>
+      </c>
+      <c r="R31" t="n">
+        <v>4</v>
+      </c>
+      <c r="S31" t="n">
+        <v>15</v>
+      </c>
+      <c r="T31" t="n">
+        <v>12</v>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>YgLhKnOo</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>nZ24J27c</t>
+        </is>
+      </c>
+      <c r="W31" t="n">
+        <v>77</v>
+      </c>
+      <c r="X31" t="n">
+        <v>773</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>ttyLthOA</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>G8lYsMgU</t>
+        </is>
+      </c>
+      <c r="AC31" t="n">
+        <v>26.09090909090909</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>184.5454545454545</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>70.36363636363636</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>2154545.454545455</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>73.27272727272727</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>27.33333333333333</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>181.5555555555555</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>1.111111111111111</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>68.66666666666667</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>1541666.666666667</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>71.66666666666667</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>25.30434782608696</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>184.304347826087</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>1.130434782608696</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>69.08695652173913</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>2065217.391304348</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>74.04347826086956</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>24.66666666666667</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>182.2083333333333</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>1.041666666666667</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>64.29166666666667</v>
+      </c>
+      <c r="AY31" t="n">
+        <v>1022500</v>
+      </c>
+      <c r="AZ31" t="n">
+        <v>69.54166666666667</v>
+      </c>
+      <c r="BA31" t="inlineStr"/>
+      <c r="BB31" t="inlineStr"/>
+      <c r="BC31" t="inlineStr"/>
+      <c r="BD31" t="inlineStr"/>
+      <c r="BE31" t="inlineStr"/>
+      <c r="BF31" t="inlineStr"/>
+      <c r="BG31" t="inlineStr"/>
+      <c r="BH31" t="inlineStr"/>
+      <c r="BI31" t="inlineStr"/>
+      <c r="BJ31" t="inlineStr"/>
+      <c r="BK31" t="inlineStr"/>
+      <c r="BL31" t="inlineStr"/>
+      <c r="BM31" t="inlineStr"/>
+      <c r="BN31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>AZ3PVMxp</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="n">
+        <v>45513.67708333334</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cosso f 
+  ita </t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">brianteo
+  monza </t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>16917</v>
+      </c>
+      <c r="F32" t="n">
+        <v>7139</v>
+      </c>
+      <c r="G32" t="n">
+        <v>1</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>4YSMlwj7</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>W02MZDnp</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="n">
+        <v>57</v>
+      </c>
+      <c r="N32" t="n">
+        <v>43</v>
+      </c>
+      <c r="O32" t="n">
+        <v>10</v>
+      </c>
+      <c r="P32" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>4</v>
+      </c>
+      <c r="R32" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" t="n">
+        <v>15</v>
+      </c>
+      <c r="T32" t="n">
+        <v>9</v>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>CEv2hvmq</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>bmzifXwb</t>
+        </is>
+      </c>
+      <c r="W32" t="n">
+        <v>77</v>
+      </c>
+      <c r="X32" t="n">
+        <v>773</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>ttyLthOA</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>rXw8YKDE</t>
+        </is>
+      </c>
+      <c r="AC32" t="n">
+        <v>25.63636363636364</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>183.9090909090909</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>1.454545454545455</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>72.27272727272727</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>4727272.727272728</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>76.54545454545455</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>182.6</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>68</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>983500</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>70</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>26.29166666666667</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>180.875</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>72.29166666666667</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>5370833.333333333</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>75.375</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>23.57894736842105</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>185.3157894736842</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>65.26315789473684</v>
+      </c>
+      <c r="AY32" t="n">
+        <v>1278947.368421053</v>
+      </c>
+      <c r="AZ32" t="n">
+        <v>71.36842105263158</v>
+      </c>
+      <c r="BA32" t="inlineStr"/>
+      <c r="BB32" t="inlineStr"/>
+      <c r="BC32" t="inlineStr"/>
+      <c r="BD32" t="inlineStr"/>
+      <c r="BE32" t="inlineStr"/>
+      <c r="BF32" t="inlineStr"/>
+      <c r="BG32" t="inlineStr"/>
+      <c r="BH32" t="inlineStr"/>
+      <c r="BI32" t="inlineStr"/>
+      <c r="BJ32" t="inlineStr"/>
+      <c r="BK32" t="inlineStr"/>
+      <c r="BL32" t="inlineStr"/>
+      <c r="BM32" t="inlineStr"/>
+      <c r="BN32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>hvcjgHz8</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="n">
+        <v>45513.65625</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">di marco d 
+  ita </t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio luigi ferraris
+  genoa </t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>36599</v>
+      </c>
+      <c r="F33" t="n">
+        <v>22000</v>
+      </c>
+      <c r="G33" t="n">
+        <v>1</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>d0PJxeie</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>6ulJbMCe</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="n">
+        <v>54</v>
+      </c>
+      <c r="N33" t="n">
+        <v>46</v>
+      </c>
+      <c r="O33" t="n">
+        <v>19</v>
+      </c>
+      <c r="P33" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>13</v>
+      </c>
+      <c r="R33" t="n">
+        <v>5</v>
+      </c>
+      <c r="S33" t="n">
+        <v>16</v>
+      </c>
+      <c r="T33" t="n">
+        <v>11</v>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>tSiEeKvS</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Gfur2NmR</t>
+        </is>
+      </c>
+      <c r="W33" t="n">
+        <v>77</v>
+      </c>
+      <c r="X33" t="n">
+        <v>773</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>nJbCGx2U</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr"/>
+      <c r="AC33" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>183.9</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>72.3</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>4072500</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>75.8</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>26</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>183.875</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>63.375</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>781250</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>68.875</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>26.53333333333333</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>184.0666666666667</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>1.533333333333333</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>72.26666666666667</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>5316666.666666667</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>75.93333333333334</v>
+      </c>
+      <c r="AU33" t="n">
+        <v>25.4375</v>
+      </c>
+      <c r="AV33" t="n">
+        <v>179.875</v>
+      </c>
+      <c r="AW33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX33" t="n">
+        <v>62.1875</v>
+      </c>
+      <c r="AY33" t="n">
+        <v>718125</v>
+      </c>
+      <c r="AZ33" t="n">
+        <v>65.75</v>
+      </c>
+      <c r="BA33" t="inlineStr"/>
+      <c r="BB33" t="inlineStr"/>
+      <c r="BC33" t="inlineStr"/>
+      <c r="BD33" t="inlineStr"/>
+      <c r="BE33" t="inlineStr"/>
+      <c r="BF33" t="inlineStr"/>
+      <c r="BG33" t="inlineStr"/>
+      <c r="BH33" t="inlineStr"/>
+      <c r="BI33" t="inlineStr"/>
+      <c r="BJ33" t="inlineStr"/>
+      <c r="BK33" t="inlineStr"/>
+      <c r="BL33" t="inlineStr"/>
+      <c r="BM33" t="inlineStr"/>
+      <c r="BN33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>dnnqk0iD</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="n">
+        <v>45513.5625</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">scatena g 
+  ita </t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bluenergy stadium   stadio friuli
+  udine </t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>25144</v>
+      </c>
+      <c r="F34" t="n">
+        <v>5850</v>
+      </c>
+      <c r="G34" t="n">
+        <v>4</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>rXw8YKDE</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>A332L1f5</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="n">
+        <v>62</v>
+      </c>
+      <c r="N34" t="n">
+        <v>38</v>
+      </c>
+      <c r="O34" t="n">
+        <v>16</v>
+      </c>
+      <c r="P34" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>7</v>
+      </c>
+      <c r="R34" t="n">
+        <v>1</v>
+      </c>
+      <c r="S34" t="n">
+        <v>15</v>
+      </c>
+      <c r="T34" t="n">
+        <v>10</v>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>ncu4OLs5</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>WE57Jh0D</t>
+        </is>
+      </c>
+      <c r="W34" t="n">
+        <v>77</v>
+      </c>
+      <c r="X34" t="n">
+        <v>773</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>69Dxbc61</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr"/>
+      <c r="AC34" t="n">
+        <v>25.45454545454545</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>184.8181818181818</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>73.45454545454545</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>4663636.363636363</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>76.27272727272727</v>
+      </c>
+      <c r="AI34" t="inlineStr"/>
+      <c r="AJ34" t="inlineStr"/>
+      <c r="AK34" t="inlineStr"/>
+      <c r="AL34" t="inlineStr"/>
+      <c r="AM34" t="inlineStr"/>
+      <c r="AN34" t="inlineStr"/>
+      <c r="AO34" t="n">
+        <v>25.40909090909091</v>
+      </c>
+      <c r="AP34" t="n">
+        <v>183.8636363636364</v>
+      </c>
+      <c r="AQ34" t="n">
+        <v>1.045454545454545</v>
+      </c>
+      <c r="AR34" t="n">
+        <v>71.81818181818181</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>4140909.090909091</v>
+      </c>
+      <c r="AT34" t="n">
+        <v>75.90909090909091</v>
+      </c>
+      <c r="AU34" t="inlineStr"/>
+      <c r="AV34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr"/>
+      <c r="AX34" t="inlineStr"/>
+      <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr"/>
+      <c r="BA34" t="inlineStr"/>
+      <c r="BB34" t="inlineStr"/>
+      <c r="BC34" t="inlineStr"/>
+      <c r="BD34" t="inlineStr"/>
+      <c r="BE34" t="inlineStr"/>
+      <c r="BF34" t="inlineStr"/>
+      <c r="BG34" t="inlineStr"/>
+      <c r="BH34" t="inlineStr"/>
+      <c r="BI34" t="inlineStr"/>
+      <c r="BJ34" t="inlineStr"/>
+      <c r="BK34" t="inlineStr"/>
+      <c r="BL34" t="inlineStr"/>
+      <c r="BM34" t="inlineStr"/>
+      <c r="BN34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>QT6wuRFc</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="n">
+        <v>45513.54166666666</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">prontera a 
+  ita </t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mapei stadium – citta del tricolore
+  reggio emilia </t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>21525</v>
+      </c>
+      <c r="F35" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G35" t="n">
+        <v>2</v>
+      </c>
+      <c r="H35" t="n">
+        <v>1</v>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>QDdvI0zl</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>C0yUqo8c</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="n">
+        <v>49</v>
+      </c>
+      <c r="N35" t="n">
+        <v>51</v>
+      </c>
+      <c r="O35" t="n">
+        <v>15</v>
+      </c>
+      <c r="P35" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>9</v>
+      </c>
+      <c r="R35" t="n">
+        <v>2</v>
+      </c>
+      <c r="S35" t="n">
+        <v>15</v>
+      </c>
+      <c r="T35" t="n">
+        <v>9</v>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>bPHSQi9q</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>8dDPzPa7</t>
+        </is>
+      </c>
+      <c r="W35" t="n">
+        <v>77</v>
+      </c>
+      <c r="X35" t="n">
+        <v>773</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>0M9xNN8N</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>MkPmVv50</t>
+        </is>
+      </c>
+      <c r="AC35" t="n">
+        <v>24.54545454545455</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>185.1818181818182</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>1.181818181818182</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>71.36363636363636</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>5297727.272727272</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>75.27272727272727</v>
+      </c>
+      <c r="AI35" t="inlineStr"/>
+      <c r="AJ35" t="inlineStr"/>
+      <c r="AK35" t="inlineStr"/>
+      <c r="AL35" t="inlineStr"/>
+      <c r="AM35" t="inlineStr"/>
+      <c r="AN35" t="inlineStr"/>
+      <c r="AO35" t="n">
+        <v>21.60869565217391</v>
+      </c>
+      <c r="AP35" t="n">
+        <v>184.2608695652174</v>
+      </c>
+      <c r="AQ35" t="n">
+        <v>1.043478260869565</v>
+      </c>
+      <c r="AR35" t="n">
+        <v>68.08695652173913</v>
+      </c>
+      <c r="AS35" t="n">
+        <v>3495652.173913043</v>
+      </c>
+      <c r="AT35" t="n">
+        <v>78.26086956521739</v>
+      </c>
+      <c r="AU35" t="n">
+        <v>26.22727272727273</v>
+      </c>
+      <c r="AV35" t="n">
+        <v>184.7727272727273</v>
+      </c>
+      <c r="AW35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX35" t="n">
+        <v>65.31818181818181</v>
+      </c>
+      <c r="AY35" t="n">
+        <v>1042954.545454545</v>
+      </c>
+      <c r="AZ35" t="n">
+        <v>69.13636363636364</v>
+      </c>
+      <c r="BA35" t="inlineStr"/>
+      <c r="BB35" t="inlineStr"/>
+      <c r="BC35" t="inlineStr"/>
+      <c r="BD35" t="inlineStr"/>
+      <c r="BE35" t="inlineStr"/>
+      <c r="BF35" t="inlineStr"/>
+      <c r="BG35" t="inlineStr"/>
+      <c r="BH35" t="inlineStr"/>
+      <c r="BI35" t="inlineStr"/>
+      <c r="BJ35" t="inlineStr"/>
+      <c r="BK35" t="inlineStr"/>
+      <c r="BL35" t="inlineStr"/>
+      <c r="BM35" t="inlineStr"/>
+      <c r="BN35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>WlhYT07d</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="n">
+        <v>45508.65625</v>
+      </c>
+      <c r="C36" t="inlineStr"/>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio partenio adriano lombardi
+  avellino </t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>26000</v>
+      </c>
+      <c r="F36" t="n">
+        <v>5050</v>
+      </c>
+      <c r="G36" t="n">
+        <v>3</v>
+      </c>
+      <c r="H36" t="n">
+        <v>1</v>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>A332L1f5</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>hKSfjtsQ</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr"/>
+      <c r="Q36" t="inlineStr"/>
+      <c r="R36" t="inlineStr"/>
+      <c r="S36" t="inlineStr"/>
+      <c r="T36" t="inlineStr"/>
+      <c r="U36" t="inlineStr"/>
+      <c r="V36" t="inlineStr"/>
+      <c r="W36" t="n">
+        <v>77</v>
+      </c>
+      <c r="X36" t="n">
+        <v>773</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA36" t="inlineStr"/>
+      <c r="AB36" t="inlineStr"/>
+      <c r="AC36" t="inlineStr"/>
+      <c r="AD36" t="inlineStr"/>
+      <c r="AE36" t="inlineStr"/>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="inlineStr"/>
+      <c r="AH36" t="inlineStr"/>
+      <c r="AI36" t="inlineStr"/>
+      <c r="AJ36" t="inlineStr"/>
+      <c r="AK36" t="inlineStr"/>
+      <c r="AL36" t="inlineStr"/>
+      <c r="AM36" t="inlineStr"/>
+      <c r="AN36" t="inlineStr"/>
+      <c r="AO36" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="AP36" t="n">
+        <v>182.8333333333333</v>
+      </c>
+      <c r="AQ36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR36" t="n">
+        <v>67.16666666666667</v>
+      </c>
+      <c r="AS36" t="n">
+        <v>1137500</v>
+      </c>
+      <c r="AT36" t="n">
+        <v>69</v>
+      </c>
+      <c r="AU36" t="inlineStr"/>
+      <c r="AV36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr"/>
+      <c r="AX36" t="inlineStr"/>
+      <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr"/>
+      <c r="BA36" t="inlineStr"/>
+      <c r="BB36" t="inlineStr"/>
+      <c r="BC36" t="inlineStr"/>
+      <c r="BD36" t="inlineStr"/>
+      <c r="BE36" t="inlineStr"/>
+      <c r="BF36" t="inlineStr"/>
+      <c r="BG36" t="inlineStr"/>
+      <c r="BH36" t="inlineStr"/>
+      <c r="BI36" t="inlineStr"/>
+      <c r="BJ36" t="inlineStr"/>
+      <c r="BK36" t="inlineStr"/>
+      <c r="BL36" t="inlineStr"/>
+      <c r="BM36" t="inlineStr"/>
+      <c r="BN36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>SzxylMbS</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="n">
+        <v>45508.64583333334</v>
+      </c>
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio dino manuzzi
+  cesena </t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>23860</v>
+      </c>
+      <c r="F37" t="n">
+        <v>4468</v>
+      </c>
+      <c r="G37" t="n">
+        <v>3</v>
+      </c>
+      <c r="H37" t="n">
+        <v>1</v>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>xddf1qfh</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>2gUwEtrE</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" t="inlineStr"/>
+      <c r="Q37" t="inlineStr"/>
+      <c r="R37" t="inlineStr"/>
+      <c r="S37" t="inlineStr"/>
+      <c r="T37" t="inlineStr"/>
+      <c r="U37" t="inlineStr"/>
+      <c r="V37" t="inlineStr"/>
+      <c r="W37" t="n">
+        <v>77</v>
+      </c>
+      <c r="X37" t="n">
+        <v>773</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA37" t="inlineStr"/>
+      <c r="AB37" t="inlineStr"/>
+      <c r="AC37" t="inlineStr"/>
+      <c r="AD37" t="inlineStr"/>
+      <c r="AE37" t="inlineStr"/>
+      <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="inlineStr"/>
+      <c r="AH37" t="inlineStr"/>
+      <c r="AI37" t="inlineStr"/>
+      <c r="AJ37" t="inlineStr"/>
+      <c r="AK37" t="inlineStr"/>
+      <c r="AL37" t="inlineStr"/>
+      <c r="AM37" t="inlineStr"/>
+      <c r="AN37" t="inlineStr"/>
+      <c r="AO37" t="inlineStr"/>
+      <c r="AP37" t="inlineStr"/>
+      <c r="AQ37" t="inlineStr"/>
+      <c r="AR37" t="inlineStr"/>
+      <c r="AS37" t="inlineStr"/>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AU37" t="inlineStr"/>
+      <c r="AV37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr"/>
+      <c r="AX37" t="inlineStr"/>
+      <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr"/>
+      <c r="BA37" t="inlineStr"/>
+      <c r="BB37" t="inlineStr"/>
+      <c r="BC37" t="inlineStr"/>
+      <c r="BD37" t="inlineStr"/>
+      <c r="BE37" t="inlineStr"/>
+      <c r="BF37" t="inlineStr"/>
+      <c r="BG37" t="inlineStr"/>
+      <c r="BH37" t="inlineStr"/>
+      <c r="BI37" t="inlineStr"/>
+      <c r="BJ37" t="inlineStr"/>
+      <c r="BK37" t="inlineStr"/>
+      <c r="BL37" t="inlineStr"/>
+      <c r="BM37" t="inlineStr"/>
+      <c r="BN37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>bHLf4sq9</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="n">
+        <v>45507.64583333334</v>
+      </c>
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vanni sanna
+  sassari </t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>12000</v>
+      </c>
+      <c r="F38" t="n">
+        <v>2955</v>
+      </c>
+      <c r="G38" t="n">
+        <v>1</v>
+      </c>
+      <c r="H38" t="n">
+        <v>2</v>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>UiGfvfvT</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>z7WK5Pwb</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr"/>
+      <c r="P38" t="inlineStr"/>
+      <c r="Q38" t="inlineStr"/>
+      <c r="R38" t="inlineStr"/>
+      <c r="S38" t="inlineStr"/>
+      <c r="T38" t="inlineStr"/>
+      <c r="U38" t="inlineStr"/>
+      <c r="V38" t="inlineStr"/>
+      <c r="W38" t="n">
+        <v>77</v>
+      </c>
+      <c r="X38" t="n">
+        <v>773</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA38" t="inlineStr"/>
+      <c r="AB38" t="inlineStr"/>
+      <c r="AC38" t="inlineStr"/>
+      <c r="AD38" t="inlineStr"/>
+      <c r="AE38" t="inlineStr"/>
+      <c r="AF38" t="inlineStr"/>
+      <c r="AG38" t="inlineStr"/>
+      <c r="AH38" t="inlineStr"/>
+      <c r="AI38" t="inlineStr"/>
+      <c r="AJ38" t="inlineStr"/>
+      <c r="AK38" t="inlineStr"/>
+      <c r="AL38" t="inlineStr"/>
+      <c r="AM38" t="inlineStr"/>
+      <c r="AN38" t="inlineStr"/>
+      <c r="AO38" t="n">
+        <v>28</v>
+      </c>
+      <c r="AP38" t="n">
+        <v>176</v>
+      </c>
+      <c r="AQ38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR38" t="n">
+        <v>64</v>
+      </c>
+      <c r="AS38" t="n">
+        <v>587500</v>
+      </c>
+      <c r="AT38" t="n">
+        <v>64.5</v>
+      </c>
+      <c r="AU38" t="n">
+        <v>29</v>
+      </c>
+      <c r="AV38" t="n">
+        <v>181.6</v>
+      </c>
+      <c r="AW38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX38" t="n">
+        <v>70.2</v>
+      </c>
+      <c r="AY38" t="n">
+        <v>1820000</v>
+      </c>
+      <c r="AZ38" t="n">
+        <v>70.2</v>
+      </c>
+      <c r="BA38" t="inlineStr"/>
+      <c r="BB38" t="inlineStr"/>
+      <c r="BC38" t="inlineStr"/>
+      <c r="BD38" t="inlineStr"/>
+      <c r="BE38" t="inlineStr"/>
+      <c r="BF38" t="inlineStr"/>
+      <c r="BG38" t="inlineStr"/>
+      <c r="BH38" t="inlineStr"/>
+      <c r="BI38" t="inlineStr"/>
+      <c r="BJ38" t="inlineStr"/>
+      <c r="BK38" t="inlineStr"/>
+      <c r="BL38" t="inlineStr"/>
+      <c r="BM38" t="inlineStr"/>
+      <c r="BN38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>f9bfyqFM</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="n">
+        <v>45507.54166666666</v>
+      </c>
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio dei marmi
+  carrara </t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>5280</v>
+      </c>
+      <c r="F39" t="n">
+        <v>1707</v>
+      </c>
+      <c r="G39" t="n">
+        <v>2</v>
+      </c>
+      <c r="H39" t="n">
+        <v>1</v>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>hG4fg4z3</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>4rwnnbnB</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr"/>
+      <c r="P39" t="inlineStr"/>
+      <c r="Q39" t="inlineStr"/>
+      <c r="R39" t="inlineStr"/>
+      <c r="S39" t="inlineStr"/>
+      <c r="T39" t="inlineStr"/>
+      <c r="U39" t="inlineStr"/>
+      <c r="V39" t="inlineStr"/>
+      <c r="W39" t="n">
+        <v>77</v>
+      </c>
+      <c r="X39" t="n">
+        <v>773</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA39" t="inlineStr"/>
+      <c r="AB39" t="inlineStr"/>
+      <c r="AC39" t="inlineStr"/>
+      <c r="AD39" t="inlineStr"/>
+      <c r="AE39" t="inlineStr"/>
+      <c r="AF39" t="inlineStr"/>
+      <c r="AG39" t="inlineStr"/>
+      <c r="AH39" t="inlineStr"/>
+      <c r="AI39" t="inlineStr"/>
+      <c r="AJ39" t="inlineStr"/>
+      <c r="AK39" t="inlineStr"/>
+      <c r="AL39" t="inlineStr"/>
+      <c r="AM39" t="inlineStr"/>
+      <c r="AN39" t="inlineStr"/>
+      <c r="AO39" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="AP39" t="n">
+        <v>179.8</v>
+      </c>
+      <c r="AQ39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR39" t="n">
+        <v>61.6</v>
+      </c>
+      <c r="AS39" t="n">
+        <v>775000</v>
+      </c>
+      <c r="AT39" t="n">
+        <v>70.8</v>
+      </c>
+      <c r="AU39" t="inlineStr"/>
+      <c r="AV39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr"/>
+      <c r="AX39" t="inlineStr"/>
+      <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr"/>
+      <c r="BA39" t="inlineStr"/>
+      <c r="BB39" t="inlineStr"/>
+      <c r="BC39" t="inlineStr"/>
+      <c r="BD39" t="inlineStr"/>
+      <c r="BE39" t="inlineStr"/>
+      <c r="BF39" t="inlineStr"/>
+      <c r="BG39" t="inlineStr"/>
+      <c r="BH39" t="inlineStr"/>
+      <c r="BI39" t="inlineStr"/>
+      <c r="BJ39" t="inlineStr"/>
+      <c r="BK39" t="inlineStr"/>
+      <c r="BL39" t="inlineStr"/>
+      <c r="BM39" t="inlineStr"/>
+      <c r="BN39" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/italy/p6_deployment/data_preparation/construct_data/df_matches_to_construct_historic_values.xlsx
+++ b/data/italy/p6_deployment/data_preparation/construct_data/df_matches_to_construct_historic_values.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BN9"/>
+  <dimension ref="A1:BN41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -762,241 +762,275 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>AZ3PVMxp</t>
+          <t>EirZ0Wr4</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45513.67708333334</v>
+        <v>45523.65625</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">cosso f 
+          <t xml:space="preserve">marcenaro m 
   ita </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">brianteo
-  monza </t>
+          <t xml:space="preserve">allianz stadium
+  turin </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>16917</v>
-      </c>
-      <c r="F2" t="n">
-        <v>7139</v>
-      </c>
+        <v>41507</v>
+      </c>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>4YSMlwj7</t>
+          <t>C06aJvIB</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>W02MZDnp</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
+          <t>ttyLthOA</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.18</v>
+      </c>
       <c r="M2" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="N2" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="O2" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="P2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="T2" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>CEv2hvmq</t>
+          <t>bBhpZV2s</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>bmzifXwb</t>
+          <t>YXIDwoe5</t>
         </is>
       </c>
       <c r="W2" t="n">
         <v>77</v>
       </c>
       <c r="X2" t="n">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="Y2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
         <v>20242025</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>ttyLthOA</t>
+          <t>Iw7eKK25</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>rXw8YKDE</t>
+          <t>4YSMlwj7</t>
         </is>
       </c>
       <c r="AC2" t="n">
-        <v>25.63636363636364</v>
+        <v>24</v>
       </c>
       <c r="AD2" t="n">
-        <v>183.9090909090909</v>
+        <v>186.125</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.454545454545455</v>
+        <v>1.375</v>
       </c>
       <c r="AF2" t="n">
-        <v>72.27272727272727</v>
+        <v>78.75</v>
       </c>
       <c r="AG2" t="n">
-        <v>4727272.727272728</v>
+        <v>28437500</v>
       </c>
       <c r="AH2" t="n">
-        <v>76.54545454545455</v>
+        <v>83.125</v>
       </c>
       <c r="AI2" t="n">
-        <v>29.8</v>
+        <v>26.5</v>
       </c>
       <c r="AJ2" t="n">
-        <v>182.6</v>
+        <v>179.75</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.2</v>
+        <v>1.375</v>
       </c>
       <c r="AL2" t="n">
-        <v>68</v>
+        <v>72.375</v>
       </c>
       <c r="AM2" t="n">
-        <v>983500</v>
+        <v>5062500</v>
       </c>
       <c r="AN2" t="n">
-        <v>70</v>
+        <v>74.5</v>
       </c>
       <c r="AO2" t="n">
-        <v>26.29166666666667</v>
+        <v>25.125</v>
       </c>
       <c r="AP2" t="n">
-        <v>180.875</v>
+        <v>182.875</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="AR2" t="n">
-        <v>72.29166666666667</v>
+        <v>77</v>
       </c>
       <c r="AS2" t="n">
-        <v>5370833.333333333</v>
+        <v>18218750</v>
       </c>
       <c r="AT2" t="n">
-        <v>75.375</v>
+        <v>81.75</v>
       </c>
       <c r="AU2" t="n">
-        <v>23.57894736842105</v>
+        <v>27.15</v>
       </c>
       <c r="AV2" t="n">
-        <v>185.3157894736842</v>
+        <v>185</v>
       </c>
       <c r="AW2" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="AX2" t="n">
-        <v>65.26315789473684</v>
+        <v>71.15000000000001</v>
       </c>
       <c r="AY2" t="n">
-        <v>1278947.368421053</v>
+        <v>3786250</v>
       </c>
       <c r="AZ2" t="n">
-        <v>71.36842105263158</v>
-      </c>
-      <c r="BA2" t="inlineStr"/>
-      <c r="BB2" t="inlineStr"/>
-      <c r="BC2" t="inlineStr"/>
-      <c r="BD2" t="inlineStr"/>
-      <c r="BE2" t="inlineStr"/>
-      <c r="BF2" t="inlineStr"/>
-      <c r="BG2" t="inlineStr"/>
-      <c r="BH2" t="inlineStr"/>
-      <c r="BI2" t="inlineStr"/>
-      <c r="BJ2" t="inlineStr"/>
-      <c r="BK2" t="inlineStr"/>
-      <c r="BL2" t="inlineStr"/>
-      <c r="BM2" t="inlineStr"/>
-      <c r="BN2" t="inlineStr"/>
+        <v>72.45</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>27</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>185.25</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>321</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>103000000</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>334</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>27</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>187</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>73</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>3200000</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>73</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hvcjgHz8</t>
+          <t>t4ZkclrT</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45513.65625</v>
+        <v>45523.5625</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">di marco d 
+          <t xml:space="preserve">massa d 
   ita </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio luigi ferraris
-  genoa </t>
+          <t xml:space="preserve">stadio via del mare
+  lecce </t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>36599</v>
+        <v>40670</v>
       </c>
       <c r="F3" t="n">
-        <v>22000</v>
+        <v>28719</v>
       </c>
       <c r="G3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>d0PJxeie</t>
+          <t>G8lYsMgU</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>6ulJbMCe</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
+          <t>8C9JjMXu</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="L3" t="n">
+        <v>2.04</v>
+      </c>
       <c r="M3" t="n">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="N3" t="n">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="O3" t="n">
         <v>19</v>
@@ -1005,219 +1039,253 @@
         <v>10</v>
       </c>
       <c r="Q3" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="R3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S3" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="T3" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>tSiEeKvS</t>
+          <t>KtGrCa5d</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>Gfur2NmR</t>
+          <t>EJLKYOzb</t>
         </is>
       </c>
       <c r="W3" t="n">
         <v>77</v>
       </c>
       <c r="X3" t="n">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="Y3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
         <v>20242025</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>nJbCGx2U</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr"/>
+          <t>xIkUr2vO</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>8Sa8HInO</t>
+        </is>
+      </c>
       <c r="AC3" t="n">
-        <v>27.2</v>
+        <v>24</v>
       </c>
       <c r="AD3" t="n">
-        <v>183.9</v>
+        <v>183.125</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="AF3" t="n">
-        <v>72.3</v>
+        <v>71.875</v>
       </c>
       <c r="AG3" t="n">
-        <v>4072500</v>
+        <v>5475000</v>
       </c>
       <c r="AH3" t="n">
-        <v>75.8</v>
+        <v>77.875</v>
       </c>
       <c r="AI3" t="n">
-        <v>26</v>
+        <v>26.3</v>
       </c>
       <c r="AJ3" t="n">
-        <v>183.875</v>
+        <v>188</v>
       </c>
       <c r="AK3" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="AL3" t="n">
-        <v>63.375</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="AM3" t="n">
-        <v>781250</v>
+        <v>13650000</v>
       </c>
       <c r="AN3" t="n">
-        <v>68.875</v>
+        <v>80.2</v>
       </c>
       <c r="AO3" t="n">
-        <v>26.53333333333333</v>
+        <v>22.68421052631579</v>
       </c>
       <c r="AP3" t="n">
-        <v>184.0666666666667</v>
+        <v>181.6842105263158</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.533333333333333</v>
+        <v>1</v>
       </c>
       <c r="AR3" t="n">
-        <v>72.26666666666667</v>
+        <v>67.63157894736842</v>
       </c>
       <c r="AS3" t="n">
-        <v>5316666.666666667</v>
+        <v>2952631.578947369</v>
       </c>
       <c r="AT3" t="n">
-        <v>75.93333333333334</v>
+        <v>75.31578947368421</v>
       </c>
       <c r="AU3" t="n">
-        <v>25.4375</v>
+        <v>24</v>
       </c>
       <c r="AV3" t="n">
-        <v>179.875</v>
+        <v>185.7692307692308</v>
       </c>
       <c r="AW3" t="n">
-        <v>1</v>
+        <v>1.153846153846154</v>
       </c>
       <c r="AX3" t="n">
-        <v>62.1875</v>
+        <v>73.23076923076923</v>
       </c>
       <c r="AY3" t="n">
-        <v>718125</v>
+        <v>9996923.076923076</v>
       </c>
       <c r="AZ3" t="n">
-        <v>65.75</v>
-      </c>
-      <c r="BA3" t="inlineStr"/>
-      <c r="BB3" t="inlineStr"/>
-      <c r="BC3" t="inlineStr"/>
-      <c r="BD3" t="inlineStr"/>
-      <c r="BE3" t="inlineStr"/>
-      <c r="BF3" t="inlineStr"/>
-      <c r="BG3" t="inlineStr"/>
-      <c r="BH3" t="inlineStr"/>
-      <c r="BI3" t="inlineStr"/>
-      <c r="BJ3" t="inlineStr"/>
-      <c r="BK3" t="inlineStr"/>
-      <c r="BL3" t="inlineStr"/>
-      <c r="BM3" t="inlineStr"/>
-      <c r="BN3" t="inlineStr"/>
+        <v>78.76923076923077</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>24.33333333333333</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>182</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>3</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>215</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>11100000</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>232</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>26.25</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>189.25</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BK3" t="n">
+        <v>4</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>314</v>
+      </c>
+      <c r="BM3" t="n">
+        <v>74000000</v>
+      </c>
+      <c r="BN3" t="n">
+        <v>329</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>dnnqk0iD</t>
+          <t>YH892O2B</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45513.5625</v>
+        <v>45522.65625</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">scatena g 
+          <t xml:space="preserve">la penna f 
   ita </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">bluenergy stadium   stadio friuli
-  udine </t>
+          <t xml:space="preserve">unipol domus
+  cagliari </t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>25144</v>
-      </c>
-      <c r="F4" t="n">
-        <v>5850</v>
-      </c>
+        <v>16416</v>
+      </c>
+      <c r="F4" t="inlineStr"/>
       <c r="G4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>rXw8YKDE</t>
+          <t>SCGVmKHb</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>A332L1f5</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
+          <t>zVqqL0ma</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1.25</v>
+      </c>
       <c r="M4" t="n">
-        <v>62</v>
+        <v>43</v>
       </c>
       <c r="N4" t="n">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="O4" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="P4" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="Q4" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="R4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
       </c>
       <c r="T4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>ncu4OLs5</t>
+          <t>MLVBCoYg</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>WE57Jh0D</t>
+          <t>xjigzK81</t>
         </is>
       </c>
       <c r="W4" t="n">
         <v>77</v>
       </c>
       <c r="X4" t="n">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="Y4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
         <v>20242025</v>
@@ -1227,346 +1295,517 @@
           <t>69Dxbc61</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr"/>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>URcSl02h</t>
+        </is>
+      </c>
       <c r="AC4" t="n">
-        <v>25.45454545454545</v>
+        <v>24.90909090909091</v>
       </c>
       <c r="AD4" t="n">
-        <v>184.8181818181818</v>
+        <v>185</v>
       </c>
       <c r="AE4" t="n">
         <v>1</v>
       </c>
       <c r="AF4" t="n">
-        <v>73.45454545454545</v>
+        <v>72.27272727272727</v>
       </c>
       <c r="AG4" t="n">
-        <v>4663636.363636363</v>
+        <v>4581818.181818182</v>
       </c>
       <c r="AH4" t="n">
-        <v>76.27272727272727</v>
-      </c>
-      <c r="AI4" t="inlineStr"/>
-      <c r="AJ4" t="inlineStr"/>
-      <c r="AK4" t="inlineStr"/>
-      <c r="AL4" t="inlineStr"/>
-      <c r="AM4" t="inlineStr"/>
-      <c r="AN4" t="inlineStr"/>
+        <v>76.09090909090909</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>24.75</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>181.625</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>78</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>19037500</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>81</v>
+      </c>
       <c r="AO4" t="n">
-        <v>25.40909090909091</v>
+        <v>26.25</v>
       </c>
       <c r="AP4" t="n">
-        <v>183.8636363636364</v>
+        <v>184</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.045454545454545</v>
+        <v>1.4</v>
       </c>
       <c r="AR4" t="n">
-        <v>71.81818181818181</v>
+        <v>68.95</v>
       </c>
       <c r="AS4" t="n">
-        <v>4140909.090909091</v>
+        <v>2293750</v>
       </c>
       <c r="AT4" t="n">
-        <v>75.90909090909091</v>
-      </c>
-      <c r="AU4" t="inlineStr"/>
-      <c r="AV4" t="inlineStr"/>
-      <c r="AW4" t="inlineStr"/>
-      <c r="AX4" t="inlineStr"/>
-      <c r="AY4" t="inlineStr"/>
-      <c r="AZ4" t="inlineStr"/>
-      <c r="BA4" t="inlineStr"/>
-      <c r="BB4" t="inlineStr"/>
-      <c r="BC4" t="inlineStr"/>
-      <c r="BD4" t="inlineStr"/>
-      <c r="BE4" t="inlineStr"/>
-      <c r="BF4" t="inlineStr"/>
-      <c r="BG4" t="inlineStr"/>
-      <c r="BH4" t="inlineStr"/>
-      <c r="BI4" t="inlineStr"/>
-      <c r="BJ4" t="inlineStr"/>
-      <c r="BK4" t="inlineStr"/>
-      <c r="BL4" t="inlineStr"/>
-      <c r="BM4" t="inlineStr"/>
-      <c r="BN4" t="inlineStr"/>
+        <v>73.7</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>24.78947368421053</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>180.421052631579</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>1.894736842105263</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>77.21052631578948</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>24271052.63157895</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>82.21052631578948</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>28</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>183.5</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>288</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>12300000</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>292</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>29</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>180</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>78</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>13500000</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>78</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>QT6wuRFc</t>
+          <t>8jyraADG</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45513.54166666666</v>
+        <v>45522.65625</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">prontera a 
+          <t xml:space="preserve">tremolada p 
   ita </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapei stadium – citta del tricolore
-  reggio emilia </t>
+          <t xml:space="preserve">stadio olimpico
+  rome </t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>21525</v>
-      </c>
-      <c r="F5" t="n">
-        <v>2000</v>
-      </c>
+        <v>70634</v>
+      </c>
+      <c r="F5" t="inlineStr"/>
       <c r="G5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H5" t="n">
         <v>1</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>QDdvI0zl</t>
+          <t>URcSl02h</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>C0yUqo8c</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
+          <t>MkPmVv50</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.55</v>
+      </c>
       <c r="M5" t="n">
-        <v>49</v>
+        <v>67</v>
       </c>
       <c r="N5" t="n">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="O5" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="P5" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="Q5" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="R5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="T5" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>bPHSQi9q</t>
+          <t>S8Ygn9ME</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>8dDPzPa7</t>
+          <t>n10g3KfJ</t>
         </is>
       </c>
       <c r="W5" t="n">
         <v>77</v>
       </c>
       <c r="X5" t="n">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="Y5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
         <v>20242025</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0M9xNN8N</t>
+          <t>zVqqL0ma</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>MkPmVv50</t>
+          <t>rJVAIaHo</t>
         </is>
       </c>
       <c r="AC5" t="n">
-        <v>24.54545454545455</v>
+        <v>26.1</v>
       </c>
       <c r="AD5" t="n">
-        <v>185.1818181818182</v>
+        <v>182.4</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.181818181818182</v>
+        <v>1.6</v>
       </c>
       <c r="AF5" t="n">
-        <v>71.36363636363636</v>
+        <v>79</v>
       </c>
       <c r="AG5" t="n">
-        <v>5297727.272727272</v>
+        <v>20770000</v>
       </c>
       <c r="AH5" t="n">
-        <v>75.27272727272727</v>
-      </c>
-      <c r="AI5" t="inlineStr"/>
-      <c r="AJ5" t="inlineStr"/>
-      <c r="AK5" t="inlineStr"/>
-      <c r="AL5" t="inlineStr"/>
-      <c r="AM5" t="inlineStr"/>
-      <c r="AN5" t="inlineStr"/>
+        <v>81.5</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>26</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>183.5</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>69.90000000000001</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>2240000</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>74.2</v>
+      </c>
       <c r="AO5" t="n">
-        <v>21.60869565217391</v>
+        <v>24.70833333333333</v>
       </c>
       <c r="AP5" t="n">
-        <v>184.2608695652174</v>
+        <v>182.375</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.043478260869565</v>
+        <v>1.458333333333333</v>
       </c>
       <c r="AR5" t="n">
-        <v>68.08695652173913</v>
+        <v>74.45833333333333</v>
       </c>
       <c r="AS5" t="n">
-        <v>3495652.173913043</v>
+        <v>11406250</v>
       </c>
       <c r="AT5" t="n">
-        <v>78.26086956521739</v>
+        <v>79</v>
       </c>
       <c r="AU5" t="n">
-        <v>26.22727272727273</v>
+        <v>24.47619047619047</v>
       </c>
       <c r="AV5" t="n">
-        <v>184.7727272727273</v>
+        <v>181.7619047619048</v>
       </c>
       <c r="AW5" t="n">
         <v>1</v>
       </c>
       <c r="AX5" t="n">
-        <v>65.31818181818181</v>
+        <v>66.52380952380952</v>
       </c>
       <c r="AY5" t="n">
-        <v>1042954.545454545</v>
+        <v>1505714.285714286</v>
       </c>
       <c r="AZ5" t="n">
-        <v>69.13636363636364</v>
-      </c>
-      <c r="BA5" t="inlineStr"/>
-      <c r="BB5" t="inlineStr"/>
-      <c r="BC5" t="inlineStr"/>
-      <c r="BD5" t="inlineStr"/>
-      <c r="BE5" t="inlineStr"/>
-      <c r="BF5" t="inlineStr"/>
-      <c r="BG5" t="inlineStr"/>
-      <c r="BH5" t="inlineStr"/>
-      <c r="BI5" t="inlineStr"/>
-      <c r="BJ5" t="inlineStr"/>
-      <c r="BK5" t="inlineStr"/>
-      <c r="BL5" t="inlineStr"/>
-      <c r="BM5" t="inlineStr"/>
-      <c r="BN5" t="inlineStr"/>
+        <v>72.42857142857143</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>22</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>185</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>1</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>66</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>1200000</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>72</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>181.5</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>6</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>423</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>19125000</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>450</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>WlhYT07d</t>
+          <t>SORbFvLt</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45508.65625</v>
-      </c>
-      <c r="C6" t="inlineStr"/>
+        <v>45522.64583333334</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bonacina k 
+  ita </t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio partenio adriano lombardi
-  avellino </t>
+          <t xml:space="preserve">stadio san vito luigi marulla
+  cosenza </t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>26000</v>
+        <v>20987</v>
       </c>
       <c r="F6" t="n">
-        <v>5050</v>
+        <v>6840</v>
       </c>
       <c r="G6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>A332L1f5</t>
+          <t>p84TeBhA</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>hKSfjtsQ</t>
+          <t>KUzfp5N3</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr"/>
-      <c r="T6" t="inlineStr"/>
-      <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr"/>
+      <c r="M6" t="n">
+        <v>32</v>
+      </c>
+      <c r="N6" t="n">
+        <v>68</v>
+      </c>
+      <c r="O6" t="n">
+        <v>15</v>
+      </c>
+      <c r="P6" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>6</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1</v>
+      </c>
+      <c r="S6" t="n">
+        <v>11</v>
+      </c>
+      <c r="T6" t="n">
+        <v>16</v>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Yika9O16</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>YgLhKnOo</t>
+        </is>
+      </c>
       <c r="W6" t="n">
         <v>77</v>
       </c>
       <c r="X6" t="n">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="Y6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
         <v>20242025</v>
       </c>
-      <c r="AA6" t="inlineStr"/>
-      <c r="AB6" t="inlineStr"/>
-      <c r="AC6" t="inlineStr"/>
-      <c r="AD6" t="inlineStr"/>
-      <c r="AE6" t="inlineStr"/>
-      <c r="AF6" t="inlineStr"/>
-      <c r="AG6" t="inlineStr"/>
-      <c r="AH6" t="inlineStr"/>
-      <c r="AI6" t="inlineStr"/>
-      <c r="AJ6" t="inlineStr"/>
-      <c r="AK6" t="inlineStr"/>
-      <c r="AL6" t="inlineStr"/>
-      <c r="AM6" t="inlineStr"/>
-      <c r="AN6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>GnizyMB7</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>ttyLthOA</t>
+        </is>
+      </c>
+      <c r="AC6" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>184.7</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>65.7</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>1165000</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>71.59999999999999</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>25.81818181818182</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>186.0909090909091</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>69.45454545454545</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>1909090.909090909</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>73</v>
+      </c>
       <c r="AO6" t="n">
-        <v>27.5</v>
+        <v>22.25</v>
       </c>
       <c r="AP6" t="n">
-        <v>182.8333333333333</v>
+        <v>181.125</v>
       </c>
       <c r="AQ6" t="n">
         <v>1</v>
       </c>
       <c r="AR6" t="n">
-        <v>67.16666666666667</v>
+        <v>64.375</v>
       </c>
       <c r="AS6" t="n">
-        <v>1137500</v>
+        <v>1179687.5</v>
       </c>
       <c r="AT6" t="n">
+        <v>71.875</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>23.91666666666667</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>182.5</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX6" t="n">
         <v>69</v>
       </c>
-      <c r="AU6" t="inlineStr"/>
-      <c r="AV6" t="inlineStr"/>
-      <c r="AW6" t="inlineStr"/>
-      <c r="AX6" t="inlineStr"/>
-      <c r="AY6" t="inlineStr"/>
-      <c r="AZ6" t="inlineStr"/>
+      <c r="AY6" t="n">
+        <v>2183333.333333333</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>74.125</v>
+      </c>
       <c r="BA6" t="inlineStr"/>
       <c r="BB6" t="inlineStr"/>
       <c r="BC6" t="inlineStr"/>
@@ -1585,91 +1824,174 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>SzxylMbS</t>
+          <t>lvG7DIkg</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45508.64583333334</v>
-      </c>
-      <c r="C7" t="inlineStr"/>
+        <v>45522.64583333334</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">abisso r 
+  ita </t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio dino manuzzi
-  cesena </t>
+          <t xml:space="preserve">stadio benito stirpe
+  frosinone </t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>23860</v>
-      </c>
-      <c r="F7" t="n">
-        <v>4468</v>
-      </c>
+        <v>16227</v>
+      </c>
+      <c r="F7" t="inlineStr"/>
       <c r="G7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>xddf1qfh</t>
+          <t>pfo9H1Wp</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2gUwEtrE</t>
+          <t>nJbCGx2U</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr"/>
-      <c r="V7" t="inlineStr"/>
+      <c r="M7" t="n">
+        <v>45</v>
+      </c>
+      <c r="N7" t="n">
+        <v>55</v>
+      </c>
+      <c r="O7" t="n">
+        <v>20</v>
+      </c>
+      <c r="P7" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>12</v>
+      </c>
+      <c r="R7" t="n">
+        <v>4</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="n">
+        <v>13</v>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>dnLs0wVo</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>2kfSDavF</t>
+        </is>
+      </c>
       <c r="W7" t="n">
         <v>77</v>
       </c>
       <c r="X7" t="n">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="Y7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
         <v>20242025</v>
       </c>
-      <c r="AA7" t="inlineStr"/>
-      <c r="AB7" t="inlineStr"/>
-      <c r="AC7" t="inlineStr"/>
-      <c r="AD7" t="inlineStr"/>
-      <c r="AE7" t="inlineStr"/>
-      <c r="AF7" t="inlineStr"/>
-      <c r="AG7" t="inlineStr"/>
-      <c r="AH7" t="inlineStr"/>
-      <c r="AI7" t="inlineStr"/>
-      <c r="AJ7" t="inlineStr"/>
-      <c r="AK7" t="inlineStr"/>
-      <c r="AL7" t="inlineStr"/>
-      <c r="AM7" t="inlineStr"/>
-      <c r="AN7" t="inlineStr"/>
-      <c r="AO7" t="inlineStr"/>
-      <c r="AP7" t="inlineStr"/>
-      <c r="AQ7" t="inlineStr"/>
-      <c r="AR7" t="inlineStr"/>
-      <c r="AS7" t="inlineStr"/>
-      <c r="AT7" t="inlineStr"/>
-      <c r="AU7" t="inlineStr"/>
-      <c r="AV7" t="inlineStr"/>
-      <c r="AW7" t="inlineStr"/>
-      <c r="AX7" t="inlineStr"/>
-      <c r="AY7" t="inlineStr"/>
-      <c r="AZ7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>0M9xNN8N</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>d0PJxeie</t>
+        </is>
+      </c>
+      <c r="AC7" t="n">
+        <v>21.75</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>185.5</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>65.625</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>1646875</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>74.25</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>27</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>181.4444444444445</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>69.66666666666667</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>1680555.555555556</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>72.88888888888889</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>21.78260869565218</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>184.304347826087</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>63.91304347826087</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>1310869.565217391</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>74.04347826086956</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>24.42857142857143</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>183.4285714285714</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>1.047619047619048</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>67.76190476190476</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>1782142.857142857</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>73.28571428571429</v>
+      </c>
       <c r="BA7" t="inlineStr"/>
       <c r="BB7" t="inlineStr"/>
       <c r="BC7" t="inlineStr"/>
@@ -1688,34 +2010,37 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>bHLf4sq9</t>
+          <t>IXMN9zkI</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45507.64583333334</v>
-      </c>
-      <c r="C8" t="inlineStr"/>
+        <v>45522.64583333334</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">arena a 
+  ita </t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">vanni sanna
-  sassari </t>
+          <t xml:space="preserve">mapei stadium – citta del tricolore
+  reggio emilia </t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>12000</v>
-      </c>
-      <c r="F8" t="n">
-        <v>2955</v>
-      </c>
+        <v>21525</v>
+      </c>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H8" t="n">
         <v>2</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>UiGfvfvT</t>
+          <t>6ulJbMCe</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1725,36 +2050,72 @@
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr"/>
-      <c r="T8" t="inlineStr"/>
-      <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr"/>
+      <c r="M8" t="n">
+        <v>30</v>
+      </c>
+      <c r="N8" t="n">
+        <v>70</v>
+      </c>
+      <c r="O8" t="n">
+        <v>12</v>
+      </c>
+      <c r="P8" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>6</v>
+      </c>
+      <c r="R8" t="n">
+        <v>4</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="n">
+        <v>25</v>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Gfur2NmR</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>hrkecaMB</t>
+        </is>
+      </c>
       <c r="W8" t="n">
         <v>77</v>
       </c>
       <c r="X8" t="n">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="Y8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
         <v>20242025</v>
       </c>
       <c r="AA8" t="inlineStr"/>
       <c r="AB8" t="inlineStr"/>
-      <c r="AC8" t="inlineStr"/>
-      <c r="AD8" t="inlineStr"/>
-      <c r="AE8" t="inlineStr"/>
-      <c r="AF8" t="inlineStr"/>
-      <c r="AG8" t="inlineStr"/>
-      <c r="AH8" t="inlineStr"/>
+      <c r="AC8" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>182.7</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>64.3</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>939000</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>68</v>
+      </c>
       <c r="AI8" t="inlineStr"/>
       <c r="AJ8" t="inlineStr"/>
       <c r="AK8" t="inlineStr"/>
@@ -1762,22 +2123,22 @@
       <c r="AM8" t="inlineStr"/>
       <c r="AN8" t="inlineStr"/>
       <c r="AO8" t="n">
-        <v>28</v>
+        <v>26.84210526315789</v>
       </c>
       <c r="AP8" t="n">
-        <v>176</v>
+        <v>182.8947368421053</v>
       </c>
       <c r="AQ8" t="n">
         <v>1</v>
       </c>
       <c r="AR8" t="n">
-        <v>64</v>
+        <v>65.26315789473684</v>
       </c>
       <c r="AS8" t="n">
-        <v>587500</v>
+        <v>1195000</v>
       </c>
       <c r="AT8" t="n">
-        <v>64.5</v>
+        <v>69.36842105263158</v>
       </c>
       <c r="AU8" t="n">
         <v>29</v>
@@ -1815,103 +2176,174 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>f9bfyqFM</t>
+          <t>tYhtcc5C</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45507.54166666666</v>
-      </c>
-      <c r="C9" t="inlineStr"/>
+        <v>45522.64583333334</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">piccinini m 
+  ita </t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio dei marmi
-  carrara </t>
+          <t xml:space="preserve">stadio nicola ceravolo
+  catanzaro </t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5280</v>
-      </c>
-      <c r="F9" t="n">
-        <v>1707</v>
-      </c>
+        <v>14650</v>
+      </c>
+      <c r="F9" t="inlineStr"/>
       <c r="G9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H9" t="n">
         <v>1</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>hG4fg4z3</t>
+          <t>GnizyMB7</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>4rwnnbnB</t>
+          <t>QDdvI0zl</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr"/>
-      <c r="S9" t="inlineStr"/>
-      <c r="T9" t="inlineStr"/>
-      <c r="U9" t="inlineStr"/>
-      <c r="V9" t="inlineStr"/>
+      <c r="M9" t="n">
+        <v>49</v>
+      </c>
+      <c r="N9" t="n">
+        <v>51</v>
+      </c>
+      <c r="O9" t="n">
+        <v>9</v>
+      </c>
+      <c r="P9" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>4</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6</v>
+      </c>
+      <c r="S9" t="n">
+        <v>11</v>
+      </c>
+      <c r="T9" t="n">
+        <v>7</v>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>nsYMfLJM</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>bPHSQi9q</t>
+        </is>
+      </c>
       <c r="W9" t="n">
         <v>77</v>
       </c>
       <c r="X9" t="n">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="Y9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
         <v>20242025</v>
       </c>
-      <c r="AA9" t="inlineStr"/>
-      <c r="AB9" t="inlineStr"/>
-      <c r="AC9" t="inlineStr"/>
-      <c r="AD9" t="inlineStr"/>
-      <c r="AE9" t="inlineStr"/>
-      <c r="AF9" t="inlineStr"/>
-      <c r="AG9" t="inlineStr"/>
-      <c r="AH9" t="inlineStr"/>
-      <c r="AI9" t="inlineStr"/>
-      <c r="AJ9" t="inlineStr"/>
-      <c r="AK9" t="inlineStr"/>
-      <c r="AL9" t="inlineStr"/>
-      <c r="AM9" t="inlineStr"/>
-      <c r="AN9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>p84TeBhA</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>0M9xNN8N</t>
+        </is>
+      </c>
+      <c r="AC9" t="n">
+        <v>27.77777777777778</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>180.4444444444445</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>66.88888888888889</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>1030555.555555556</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>69.22222222222223</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>24.54545454545455</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>185.1818181818182</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>1.181818181818182</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>71.36363636363636</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>5297727.272727272</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>75.27272727272727</v>
+      </c>
       <c r="AO9" t="n">
-        <v>21.4</v>
+        <v>24.7</v>
       </c>
       <c r="AP9" t="n">
-        <v>179.8</v>
+        <v>182.3</v>
       </c>
       <c r="AQ9" t="n">
         <v>1</v>
       </c>
       <c r="AR9" t="n">
-        <v>61.6</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="AS9" t="n">
-        <v>775000</v>
+        <v>985000</v>
       </c>
       <c r="AT9" t="n">
-        <v>70.8</v>
-      </c>
-      <c r="AU9" t="inlineStr"/>
-      <c r="AV9" t="inlineStr"/>
-      <c r="AW9" t="inlineStr"/>
-      <c r="AX9" t="inlineStr"/>
-      <c r="AY9" t="inlineStr"/>
-      <c r="AZ9" t="inlineStr"/>
+        <v>69.5</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>182.25</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>67.8</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>2540000</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>76.65000000000001</v>
+      </c>
       <c r="BA9" t="inlineStr"/>
       <c r="BB9" t="inlineStr"/>
       <c r="BC9" t="inlineStr"/>
@@ -1927,6 +2359,5706 @@
       <c r="BM9" t="inlineStr"/>
       <c r="BN9" t="inlineStr"/>
     </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>x0nkeyzP</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45522.64583333334</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">prontera a 
+  ita </t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio dino manuzzi
+  cesena </t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>23860</v>
+      </c>
+      <c r="F10" t="n">
+        <v>11382</v>
+      </c>
+      <c r="G10" t="n">
+        <v>2</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>xddf1qfh</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>hG4fg4z3</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="n">
+        <v>42</v>
+      </c>
+      <c r="N10" t="n">
+        <v>58</v>
+      </c>
+      <c r="O10" t="n">
+        <v>14</v>
+      </c>
+      <c r="P10" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>8</v>
+      </c>
+      <c r="R10" t="n">
+        <v>4</v>
+      </c>
+      <c r="S10" t="n">
+        <v>13</v>
+      </c>
+      <c r="T10" t="n">
+        <v>14</v>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>vD8aDRIm</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>lSb6U6l0</t>
+        </is>
+      </c>
+      <c r="W10" t="n">
+        <v>77</v>
+      </c>
+      <c r="X10" t="n">
+        <v>774</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA10" t="inlineStr"/>
+      <c r="AB10" t="inlineStr"/>
+      <c r="AC10" t="inlineStr"/>
+      <c r="AD10" t="inlineStr"/>
+      <c r="AE10" t="inlineStr"/>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="inlineStr"/>
+      <c r="AH10" t="inlineStr"/>
+      <c r="AI10" t="inlineStr"/>
+      <c r="AJ10" t="inlineStr"/>
+      <c r="AK10" t="inlineStr"/>
+      <c r="AL10" t="inlineStr"/>
+      <c r="AM10" t="inlineStr"/>
+      <c r="AN10" t="inlineStr"/>
+      <c r="AO10" t="n">
+        <v>23.375</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>183.75</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>69.625</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>3056250</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>75.75</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>23.375</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>181.5</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>62.875</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>871875</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>70.25</v>
+      </c>
+      <c r="BA10" t="inlineStr"/>
+      <c r="BB10" t="inlineStr"/>
+      <c r="BC10" t="inlineStr"/>
+      <c r="BD10" t="inlineStr"/>
+      <c r="BE10" t="inlineStr"/>
+      <c r="BF10" t="inlineStr"/>
+      <c r="BG10" t="inlineStr"/>
+      <c r="BH10" t="inlineStr"/>
+      <c r="BI10" t="inlineStr"/>
+      <c r="BJ10" t="inlineStr"/>
+      <c r="BK10" t="inlineStr"/>
+      <c r="BL10" t="inlineStr"/>
+      <c r="BM10" t="inlineStr"/>
+      <c r="BN10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>4xHh663n</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45522.5625</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">caputi m 
+  ita </t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio renato dall ara
+  bologna </t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>38279</v>
+      </c>
+      <c r="F11" t="n">
+        <v>26418</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>0M9xNN8N</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>rXw8YKDE</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="M11" t="n">
+        <v>74</v>
+      </c>
+      <c r="N11" t="n">
+        <v>26</v>
+      </c>
+      <c r="O11" t="n">
+        <v>22</v>
+      </c>
+      <c r="P11" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>7</v>
+      </c>
+      <c r="R11" t="n">
+        <v>2</v>
+      </c>
+      <c r="S11" t="n">
+        <v>15</v>
+      </c>
+      <c r="T11" t="n">
+        <v>13</v>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>tjY4uUem</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>ncu4OLs5</t>
+        </is>
+      </c>
+      <c r="W11" t="n">
+        <v>77</v>
+      </c>
+      <c r="X11" t="n">
+        <v>771</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>Q3A3IbXH</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>69Dxbc61</t>
+        </is>
+      </c>
+      <c r="AC11" t="n">
+        <v>25.27272727272727</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>186.1818181818182</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1.363636363636364</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>75.27272727272727</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>8381818.181818182</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>79.09090909090909</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>25.45454545454545</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>184.8181818181818</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>73.45454545454545</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>4663636.363636363</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>76.27272727272727</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>23.75</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>183.5</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>71.59999999999999</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>5271250</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>77.25</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>25.9375</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>181</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>1.0625</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>71.125</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>3143750</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>74.5625</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>185.2</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>5</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>353</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>37325000</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>393</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>25</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>187.5</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>149</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>20800000</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>6RvR2hEi</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45522.5625</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">marchetti m 
+  ita </t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio marc antonio bentegodi
+  verona </t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>39211</v>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="n">
+        <v>3</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>rJVAIaHo</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>69Dxbc61</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="M12" t="n">
+        <v>32</v>
+      </c>
+      <c r="N12" t="n">
+        <v>68</v>
+      </c>
+      <c r="O12" t="n">
+        <v>8</v>
+      </c>
+      <c r="P12" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>5</v>
+      </c>
+      <c r="R12" t="n">
+        <v>5</v>
+      </c>
+      <c r="S12" t="n">
+        <v>15</v>
+      </c>
+      <c r="T12" t="n">
+        <v>13</v>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>OW6PtuKn</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>23vSAc12</t>
+        </is>
+      </c>
+      <c r="W12" t="n">
+        <v>77</v>
+      </c>
+      <c r="X12" t="n">
+        <v>771</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>69Dxbc61</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>C06aJvIB</t>
+        </is>
+      </c>
+      <c r="AC12" t="n">
+        <v>25.875</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>185.375</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>73.75</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>5012500</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>76.625</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>182.2</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>80.7</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>31620000</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>81.5</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>23.95238095238095</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>181</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>1.047619047619048</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>70.04761904761905</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>3560714.285714286</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>75.61904761904762</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>24.41176470588235</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>182.1764705882353</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>1.411764705882353</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>76.05882352941177</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>16613235.29411765</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>79.58823529411765</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>23</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>186</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>1</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>66</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>1400000</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>72</v>
+      </c>
+      <c r="BH12" t="inlineStr"/>
+      <c r="BI12" t="inlineStr"/>
+      <c r="BJ12" t="inlineStr"/>
+      <c r="BK12" t="inlineStr"/>
+      <c r="BL12" t="inlineStr"/>
+      <c r="BM12" t="inlineStr"/>
+      <c r="BN12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>hKOA02XN</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45521.65625</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fabbri m 
+  ita </t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio carlo castellani
+  empoli </t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>16284</v>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>0ESCnI1H</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>4YSMlwj7</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="M13" t="n">
+        <v>39</v>
+      </c>
+      <c r="N13" t="n">
+        <v>61</v>
+      </c>
+      <c r="O13" t="n">
+        <v>9</v>
+      </c>
+      <c r="P13" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1</v>
+      </c>
+      <c r="S13" t="n">
+        <v>16</v>
+      </c>
+      <c r="T13" t="n">
+        <v>19</v>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>MBrKQFV7</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>CEv2hvmq</t>
+        </is>
+      </c>
+      <c r="W13" t="n">
+        <v>77</v>
+      </c>
+      <c r="X13" t="n">
+        <v>771</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>Q3A3IbXH</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>ttyLthOA</t>
+        </is>
+      </c>
+      <c r="AC13" t="n">
+        <v>23.72727272727273</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>184.8181818181818</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>70.81818181818181</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>3172727.272727273</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>76.63636363636364</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>25.09090909090909</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>183.1818181818182</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>1.454545454545455</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>71.45454545454545</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>4400000</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>76.90909090909091</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>24.25</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>181.75</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>68.91666666666667</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>2695416.666666667</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>75.20833333333333</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>26.47619047619047</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>181.8571428571429</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>72.47619047619048</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>5076190.476190476</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>75.80952380952381</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>187.4</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>5</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>347</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>11825000</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>363</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>27.66666666666667</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>182</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>224</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>19600000</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>0lGMiS5j</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45521.65625</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">maresca f 
+  ita </t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio giuseppe meazza  san siro 
+  milan </t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>80018</v>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="n">
+        <v>2</v>
+      </c>
+      <c r="H14" t="n">
+        <v>2</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>8Sa8HInO</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>MZFZnvX4</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="M14" t="n">
+        <v>56</v>
+      </c>
+      <c r="N14" t="n">
+        <v>44</v>
+      </c>
+      <c r="O14" t="n">
+        <v>20</v>
+      </c>
+      <c r="P14" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>6</v>
+      </c>
+      <c r="R14" t="n">
+        <v>3</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="n">
+        <v>7</v>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>KAwSWnoE</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>AB3WB3pA</t>
+        </is>
+      </c>
+      <c r="W14" t="n">
+        <v>77</v>
+      </c>
+      <c r="X14" t="n">
+        <v>771</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>Iw7eKK25</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>C06aJvIB</t>
+        </is>
+      </c>
+      <c r="AC14" t="n">
+        <v>24.72727272727273</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>182.8181818181818</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1.727272727272727</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>81.45454545454545</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>40727272.72727273</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>84.54545454545455</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>185.8</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>11290000</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>78.09999999999999</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>23.31578947368421</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>181.2631578947368</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>1.526315789473684</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>79</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>30031578.94736842</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>84.21052631578948</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>23.89473684210526</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>185.6315789473684</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>1.105263157894737</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>71.94736842105263</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>7406578.947368421</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>77.47368421052632</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>31</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>192</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>2</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>1</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>77</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>5500000</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>77</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>22.25</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>187.5</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>4</v>
+      </c>
+      <c r="BL14" t="n">
+        <v>287</v>
+      </c>
+      <c r="BM14" t="n">
+        <v>49600000</v>
+      </c>
+      <c r="BN14" t="n">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>EL1P0u6m</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45521.64583333334</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">collu g 
+  ita </t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio san nicola
+  bari </t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>58270</v>
+      </c>
+      <c r="F15" t="n">
+        <v>20957</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" t="n">
+        <v>3</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>xIkUr2vO</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>hKSfjtsQ</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="n">
+        <v>56</v>
+      </c>
+      <c r="N15" t="n">
+        <v>44</v>
+      </c>
+      <c r="O15" t="n">
+        <v>16</v>
+      </c>
+      <c r="P15" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>4</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6</v>
+      </c>
+      <c r="S15" t="n">
+        <v>20</v>
+      </c>
+      <c r="T15" t="n">
+        <v>14</v>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>nZ24J27c</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>tvh4IkLf</t>
+        </is>
+      </c>
+      <c r="W15" t="n">
+        <v>77</v>
+      </c>
+      <c r="X15" t="n">
+        <v>774</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>G8lYsMgU</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr"/>
+      <c r="AC15" t="n">
+        <v>27.33333333333333</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>181.5555555555555</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.111111111111111</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>68.66666666666667</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>1541666.666666667</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>71.66666666666667</v>
+      </c>
+      <c r="AI15" t="inlineStr"/>
+      <c r="AJ15" t="inlineStr"/>
+      <c r="AK15" t="inlineStr"/>
+      <c r="AL15" t="inlineStr"/>
+      <c r="AM15" t="inlineStr"/>
+      <c r="AN15" t="inlineStr"/>
+      <c r="AO15" t="n">
+        <v>24.84</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>181.68</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>64.12</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>934600</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>68.36</v>
+      </c>
+      <c r="AU15" t="inlineStr"/>
+      <c r="AV15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr"/>
+      <c r="AX15" t="inlineStr"/>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr"/>
+      <c r="BA15" t="inlineStr"/>
+      <c r="BB15" t="inlineStr"/>
+      <c r="BC15" t="inlineStr"/>
+      <c r="BD15" t="inlineStr"/>
+      <c r="BE15" t="inlineStr"/>
+      <c r="BF15" t="inlineStr"/>
+      <c r="BG15" t="inlineStr"/>
+      <c r="BH15" t="inlineStr"/>
+      <c r="BI15" t="inlineStr"/>
+      <c r="BJ15" t="inlineStr"/>
+      <c r="BK15" t="inlineStr"/>
+      <c r="BL15" t="inlineStr"/>
+      <c r="BM15" t="inlineStr"/>
+      <c r="BN15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>M5TEBdK5</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45521.64583333334</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">manganiello g 
+  ita </t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">arena garibaldi   stadio romeo anconetani
+  pisa </t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>14869</v>
+      </c>
+      <c r="F16" t="n">
+        <v>8770</v>
+      </c>
+      <c r="G16" t="n">
+        <v>2</v>
+      </c>
+      <c r="H16" t="n">
+        <v>2</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>roasMsOT</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>re6VD39b</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="n">
+        <v>54</v>
+      </c>
+      <c r="N16" t="n">
+        <v>46</v>
+      </c>
+      <c r="O16" t="n">
+        <v>19</v>
+      </c>
+      <c r="P16" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>4</v>
+      </c>
+      <c r="R16" t="n">
+        <v>3</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="n">
+        <v>22</v>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>GfucctAF</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>O6SinSSs</t>
+        </is>
+      </c>
+      <c r="W16" t="n">
+        <v>77</v>
+      </c>
+      <c r="X16" t="n">
+        <v>774</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>Q3A3IbXH</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>d0PJxeie</t>
+        </is>
+      </c>
+      <c r="AC16" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>185.3</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>68.3</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>1697500</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>72.2</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>24.44444444444444</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>185.5555555555555</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>67.33333333333333</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>1563888.888888889</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>72.11111111111111</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>22.80952380952381</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>184.2380952380952</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>64.80952380952381</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>1483333.333333333</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>72.14285714285714</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>25.05882352941176</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>186.0588235294118</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>66.41176470588235</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>1320588.235294118</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>71.94117647058823</v>
+      </c>
+      <c r="BA16" t="inlineStr"/>
+      <c r="BB16" t="inlineStr"/>
+      <c r="BC16" t="inlineStr"/>
+      <c r="BD16" t="inlineStr"/>
+      <c r="BE16" t="inlineStr"/>
+      <c r="BF16" t="inlineStr"/>
+      <c r="BG16" t="inlineStr"/>
+      <c r="BH16" t="inlineStr"/>
+      <c r="BI16" t="inlineStr"/>
+      <c r="BJ16" t="inlineStr"/>
+      <c r="BK16" t="inlineStr"/>
+      <c r="BL16" t="inlineStr"/>
+      <c r="BM16" t="inlineStr"/>
+      <c r="BN16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>joLV7EJU</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45521.64583333334</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fourneau f 
+  ita </t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio arechi
+  salerno </t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>37800</v>
+      </c>
+      <c r="F17" t="n">
+        <v>12509</v>
+      </c>
+      <c r="G17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Mq05g4BP</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>C0yUqo8c</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="n">
+        <v>70</v>
+      </c>
+      <c r="N17" t="n">
+        <v>30</v>
+      </c>
+      <c r="O17" t="n">
+        <v>15</v>
+      </c>
+      <c r="P17" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>7</v>
+      </c>
+      <c r="R17" t="n">
+        <v>3</v>
+      </c>
+      <c r="S17" t="n">
+        <v>23</v>
+      </c>
+      <c r="T17" t="n">
+        <v>12</v>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>OjWmexQb</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>8dDPzPa7</t>
+        </is>
+      </c>
+      <c r="W17" t="n">
+        <v>77</v>
+      </c>
+      <c r="X17" t="n">
+        <v>774</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>69Dxbc61</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>MkPmVv50</t>
+        </is>
+      </c>
+      <c r="AC17" t="n">
+        <v>25.11111111111111</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>183.7777777777778</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>69.44444444444444</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>2572222.222222222</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>74.88888888888889</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>24.375</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>181.5</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>65.125</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>1140000</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>70.75</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>22.72222222222222</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>178.0555555555555</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>66.22222222222223</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>1901388.888888889</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>74.61111111111111</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>26.84210526315789</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>182.7368421052632</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>65</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>844473.6842105263</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>68.47368421052632</v>
+      </c>
+      <c r="BA17" t="inlineStr"/>
+      <c r="BB17" t="inlineStr"/>
+      <c r="BC17" t="inlineStr"/>
+      <c r="BD17" t="inlineStr"/>
+      <c r="BE17" t="inlineStr"/>
+      <c r="BF17" t="inlineStr"/>
+      <c r="BG17" t="inlineStr"/>
+      <c r="BH17" t="inlineStr"/>
+      <c r="BI17" t="inlineStr"/>
+      <c r="BJ17" t="inlineStr"/>
+      <c r="BK17" t="inlineStr"/>
+      <c r="BL17" t="inlineStr"/>
+      <c r="BM17" t="inlineStr"/>
+      <c r="BN17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>WvwvCQVo</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45521.64583333334</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">perri m 
+  ita </t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio marco druso
+  bolzano </t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>5539</v>
+      </c>
+      <c r="F18" t="n">
+        <v>3512</v>
+      </c>
+      <c r="G18" t="n">
+        <v>2</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>W02MZDnp</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>MBn63swN</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="n">
+        <v>68</v>
+      </c>
+      <c r="N18" t="n">
+        <v>32</v>
+      </c>
+      <c r="O18" t="n">
+        <v>9</v>
+      </c>
+      <c r="P18" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>3</v>
+      </c>
+      <c r="R18" t="n">
+        <v>2</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="n">
+        <v>15</v>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>bmzifXwb</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>YTZ7S7pk</t>
+        </is>
+      </c>
+      <c r="W18" t="n">
+        <v>77</v>
+      </c>
+      <c r="X18" t="n">
+        <v>774</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>rXw8YKDE</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>0M9xNN8N</t>
+        </is>
+      </c>
+      <c r="AC18" t="n">
+        <v>30</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>182.8</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>67.90000000000001</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>951000</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>69.7</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>26.45454545454545</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>184.4545454545455</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>1.090909090909091</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>66.81818181818181</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>1190909.090909091</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>69.72727272727273</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>24.44444444444444</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>185.3888888888889</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>1.055555555555556</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>65.44444444444444</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>1131944.444444444</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>71.11111111111111</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>24.92307692307692</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>180.5384615384615</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>1.076923076923077</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>65.61538461538461</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>1168846.153846154</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>70.46153846153847</v>
+      </c>
+      <c r="BA18" t="inlineStr"/>
+      <c r="BB18" t="inlineStr"/>
+      <c r="BC18" t="inlineStr"/>
+      <c r="BD18" t="inlineStr"/>
+      <c r="BE18" t="inlineStr"/>
+      <c r="BF18" t="inlineStr"/>
+      <c r="BG18" t="inlineStr"/>
+      <c r="BH18" t="inlineStr"/>
+      <c r="BI18" t="inlineStr"/>
+      <c r="BJ18" t="inlineStr"/>
+      <c r="BK18" t="inlineStr"/>
+      <c r="BL18" t="inlineStr"/>
+      <c r="BM18" t="inlineStr"/>
+      <c r="BN18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>O2Fteteo</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45521.5625</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">feliciani e 
+  ita </t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio luigi ferraris
+  genoa </t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>36599</v>
+      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="n">
+        <v>2</v>
+      </c>
+      <c r="H19" t="n">
+        <v>2</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>d0PJxeie</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Iw7eKK25</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="M19" t="n">
+        <v>32</v>
+      </c>
+      <c r="N19" t="n">
+        <v>68</v>
+      </c>
+      <c r="O19" t="n">
+        <v>10</v>
+      </c>
+      <c r="P19" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>6</v>
+      </c>
+      <c r="R19" t="n">
+        <v>9</v>
+      </c>
+      <c r="S19" t="n">
+        <v>15</v>
+      </c>
+      <c r="T19" t="n">
+        <v>14</v>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>tSiEeKvS</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>j32a3mqs</t>
+        </is>
+      </c>
+      <c r="W19" t="n">
+        <v>77</v>
+      </c>
+      <c r="X19" t="n">
+        <v>771</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>nJbCGx2U</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>8Sa8HInO</t>
+        </is>
+      </c>
+      <c r="AC19" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>184.9</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>73.59999999999999</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>5720000</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>78.2</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>28.36363636363636</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>182.8181818181818</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>2.454545454545455</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>83.36363636363636</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>43272727.27272727</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>85.36363636363636</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>26.70588235294118</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>184.4117647058823</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>1.352941176470588</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>70.64705882352941</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>3080882.352941176</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>73.70588235294117</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>25.82608695652174</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>182.7826086956522</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>1.782608695652174</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>78.95652173913044</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>26208695.65217391</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>82</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>22.25</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>188</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>258</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>4850000</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>295</v>
+      </c>
+      <c r="BH19" t="n">
+        <v>28</v>
+      </c>
+      <c r="BI19" t="n">
+        <v>184</v>
+      </c>
+      <c r="BJ19" t="n">
+        <v>2.333333333333333</v>
+      </c>
+      <c r="BK19" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL19" t="n">
+        <v>236</v>
+      </c>
+      <c r="BM19" t="n">
+        <v>53800000</v>
+      </c>
+      <c r="BN19" t="n">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>Sf88FVcc</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>45521.5625</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ayroldi g 
+  ita </t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio ennio tardini
+  parma </t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>27906</v>
+      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="n">
+        <v>1</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>6DxlaxHN</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Q3A3IbXH</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="M20" t="n">
+        <v>39</v>
+      </c>
+      <c r="N20" t="n">
+        <v>61</v>
+      </c>
+      <c r="O20" t="n">
+        <v>13</v>
+      </c>
+      <c r="P20" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>5</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7</v>
+      </c>
+      <c r="S20" t="n">
+        <v>15</v>
+      </c>
+      <c r="T20" t="n">
+        <v>9</v>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>lQEaJ9QD</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>619UPLrb</t>
+        </is>
+      </c>
+      <c r="W20" t="n">
+        <v>77</v>
+      </c>
+      <c r="X20" t="n">
+        <v>771</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>0M9xNN8N</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>C06aJvIB</t>
+        </is>
+      </c>
+      <c r="AC20" t="n">
+        <v>22.44444444444444</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>184.7777777777778</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>69.55555555555556</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>3555555.555555556</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>77.33333333333333</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>185.7</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>76.09999999999999</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>13710000</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>80.3</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>22.73913043478261</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>180.5217391304348</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>1.130434782608696</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>66.73913043478261</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>2866956.52173913</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>74.26086956521739</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>22.68181818181818</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>180.4545454545455</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>1.409090909090909</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>73.13636363636364</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>11150000</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>80.77272727272727</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>187</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>5</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>355</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>15700000</v>
+      </c>
+      <c r="BG20" t="n">
+        <v>373</v>
+      </c>
+      <c r="BH20" t="n">
+        <v>24</v>
+      </c>
+      <c r="BI20" t="n">
+        <v>187</v>
+      </c>
+      <c r="BJ20" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK20" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL20" t="n">
+        <v>72</v>
+      </c>
+      <c r="BM20" t="n">
+        <v>3200000</v>
+      </c>
+      <c r="BN20" t="n">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>8KfYbJz0</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>45520.64583333334</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">aureliano g 
+  ita </t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio mario rigamonti
+  brescia </t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>19500</v>
+      </c>
+      <c r="F21" t="n">
+        <v>5317</v>
+      </c>
+      <c r="G21" t="n">
+        <v>1</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>jci0qO9B</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>n38Nktmn</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="n">
+        <v>37</v>
+      </c>
+      <c r="N21" t="n">
+        <v>63</v>
+      </c>
+      <c r="O21" t="n">
+        <v>18</v>
+      </c>
+      <c r="P21" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>6</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1</v>
+      </c>
+      <c r="S21" t="n">
+        <v>15</v>
+      </c>
+      <c r="T21" t="n">
+        <v>10</v>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>lb1XFX3n</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Wn0poKgt</t>
+        </is>
+      </c>
+      <c r="W21" t="n">
+        <v>77</v>
+      </c>
+      <c r="X21" t="n">
+        <v>774</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>8C9JjMXu</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>pfo9H1Wp</t>
+        </is>
+      </c>
+      <c r="AC21" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>184.7</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>66.40000000000001</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>1225000</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>70.09999999999999</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>181.5</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>70.7</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>3020000</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>23.21428571428572</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>181.2142857142857</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>64.71428571428571</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>1164285.714285714</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>72.28571428571429</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>24.375</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>183.8333333333333</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>1.041666666666667</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>69.66666666666667</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>2475000</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>75.41666666666667</v>
+      </c>
+      <c r="BA21" t="inlineStr"/>
+      <c r="BB21" t="inlineStr"/>
+      <c r="BC21" t="inlineStr"/>
+      <c r="BD21" t="inlineStr"/>
+      <c r="BE21" t="inlineStr"/>
+      <c r="BF21" t="inlineStr"/>
+      <c r="BG21" t="inlineStr"/>
+      <c r="BH21" t="inlineStr"/>
+      <c r="BI21" t="inlineStr"/>
+      <c r="BJ21" t="inlineStr"/>
+      <c r="BK21" t="inlineStr"/>
+      <c r="BL21" t="inlineStr"/>
+      <c r="BM21" t="inlineStr"/>
+      <c r="BN21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>8KIdPmPc</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>45516.67708333334</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pezzuto i 
+  ita </t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unipol domus
+  cagliari </t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>16416</v>
+      </c>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="n">
+        <v>3</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>SCGVmKHb</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>hG4fg4z3</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="n">
+        <v>53</v>
+      </c>
+      <c r="N22" t="n">
+        <v>47</v>
+      </c>
+      <c r="O22" t="n">
+        <v>21</v>
+      </c>
+      <c r="P22" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>8</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1</v>
+      </c>
+      <c r="S22" t="n">
+        <v>15</v>
+      </c>
+      <c r="T22" t="n">
+        <v>11</v>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>MLVBCoYg</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>lSb6U6l0</t>
+        </is>
+      </c>
+      <c r="W22" t="n">
+        <v>77</v>
+      </c>
+      <c r="X22" t="n">
+        <v>773</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>69Dxbc61</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr"/>
+      <c r="AC22" t="n">
+        <v>26.27272727272727</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>185.2727272727273</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1.090909090909091</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>72</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>4015909.090909091</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>74.72727272727273</v>
+      </c>
+      <c r="AI22" t="inlineStr"/>
+      <c r="AJ22" t="inlineStr"/>
+      <c r="AK22" t="inlineStr"/>
+      <c r="AL22" t="inlineStr"/>
+      <c r="AM22" t="inlineStr"/>
+      <c r="AN22" t="inlineStr"/>
+      <c r="AO22" t="n">
+        <v>23.92307692307692</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>183.9230769230769</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>1.230769230769231</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>68.42307692307692</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>3002884.615384615</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>74.65384615384616</v>
+      </c>
+      <c r="AU22" t="inlineStr"/>
+      <c r="AV22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr"/>
+      <c r="AX22" t="inlineStr"/>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr"/>
+      <c r="BA22" t="inlineStr"/>
+      <c r="BB22" t="inlineStr"/>
+      <c r="BC22" t="inlineStr"/>
+      <c r="BD22" t="inlineStr"/>
+      <c r="BE22" t="inlineStr"/>
+      <c r="BF22" t="inlineStr"/>
+      <c r="BG22" t="inlineStr"/>
+      <c r="BH22" t="inlineStr"/>
+      <c r="BI22" t="inlineStr"/>
+      <c r="BJ22" t="inlineStr"/>
+      <c r="BK22" t="inlineStr"/>
+      <c r="BL22" t="inlineStr"/>
+      <c r="BM22" t="inlineStr"/>
+      <c r="BN22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>fNwTkrUF</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>45516.65625</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rutella d 
+  ita </t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio arechi
+  salerno </t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>37800</v>
+      </c>
+      <c r="F23" t="n">
+        <v>6905</v>
+      </c>
+      <c r="G23" t="n">
+        <v>4</v>
+      </c>
+      <c r="H23" t="n">
+        <v>3</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Mq05g4BP</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>re6VD39b</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="n">
+        <v>59</v>
+      </c>
+      <c r="N23" t="n">
+        <v>41</v>
+      </c>
+      <c r="O23" t="n">
+        <v>11</v>
+      </c>
+      <c r="P23" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>5</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7</v>
+      </c>
+      <c r="S23" t="n">
+        <v>13</v>
+      </c>
+      <c r="T23" t="n">
+        <v>17</v>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>OjWmexQb</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>O6SinSSs</t>
+        </is>
+      </c>
+      <c r="W23" t="n">
+        <v>77</v>
+      </c>
+      <c r="X23" t="n">
+        <v>773</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>69Dxbc61</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>d0PJxeie</t>
+        </is>
+      </c>
+      <c r="AC23" t="n">
+        <v>24.11111111111111</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>182</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>69.33333333333333</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>4894444.444444444</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>75.88888888888889</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>186.3</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>65.8</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>1295000</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>71.5</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>24.10526315789474</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>182.8421052631579</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>67.63157894736842</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>2236842.105263158</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>74.47368421052632</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>24.27777777777778</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>183.5555555555555</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>66.83333333333333</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>1538888.888888889</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>73.05555555555556</v>
+      </c>
+      <c r="BA23" t="inlineStr"/>
+      <c r="BB23" t="inlineStr"/>
+      <c r="BC23" t="inlineStr"/>
+      <c r="BD23" t="inlineStr"/>
+      <c r="BE23" t="inlineStr"/>
+      <c r="BF23" t="inlineStr"/>
+      <c r="BG23" t="inlineStr"/>
+      <c r="BH23" t="inlineStr"/>
+      <c r="BI23" t="inlineStr"/>
+      <c r="BJ23" t="inlineStr"/>
+      <c r="BK23" t="inlineStr"/>
+      <c r="BL23" t="inlineStr"/>
+      <c r="BM23" t="inlineStr"/>
+      <c r="BN23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>42SH31wI</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>45516.5625</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">perri m 
+  ita </t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio via del mare
+  lecce </t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>40670</v>
+      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="n">
+        <v>2</v>
+      </c>
+      <c r="H24" t="n">
+        <v>1</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>G8lYsMgU</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>z7WK5Pwb</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="n">
+        <v>38</v>
+      </c>
+      <c r="N24" t="n">
+        <v>62</v>
+      </c>
+      <c r="O24" t="n">
+        <v>19</v>
+      </c>
+      <c r="P24" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>9</v>
+      </c>
+      <c r="R24" t="n">
+        <v>2</v>
+      </c>
+      <c r="S24" t="n">
+        <v>20</v>
+      </c>
+      <c r="T24" t="n">
+        <v>9</v>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>KtGrCa5d</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>hrkecaMB</t>
+        </is>
+      </c>
+      <c r="W24" t="n">
+        <v>77</v>
+      </c>
+      <c r="X24" t="n">
+        <v>773</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>xIkUr2vO</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr"/>
+      <c r="AC24" t="n">
+        <v>24</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>183.125</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>71.875</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>5475000</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>77.875</v>
+      </c>
+      <c r="AI24" t="inlineStr"/>
+      <c r="AJ24" t="inlineStr"/>
+      <c r="AK24" t="inlineStr"/>
+      <c r="AL24" t="inlineStr"/>
+      <c r="AM24" t="inlineStr"/>
+      <c r="AN24" t="inlineStr"/>
+      <c r="AO24" t="n">
+        <v>21.83333333333333</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>181.2777777777778</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>66.77777777777777</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>2694444.444444444</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>75.66666666666667</v>
+      </c>
+      <c r="AU24" t="inlineStr"/>
+      <c r="AV24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr"/>
+      <c r="AX24" t="inlineStr"/>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr"/>
+      <c r="BA24" t="inlineStr"/>
+      <c r="BB24" t="inlineStr"/>
+      <c r="BC24" t="inlineStr"/>
+      <c r="BD24" t="inlineStr"/>
+      <c r="BE24" t="inlineStr"/>
+      <c r="BF24" t="inlineStr"/>
+      <c r="BG24" t="inlineStr"/>
+      <c r="BH24" t="inlineStr"/>
+      <c r="BI24" t="inlineStr"/>
+      <c r="BJ24" t="inlineStr"/>
+      <c r="BK24" t="inlineStr"/>
+      <c r="BL24" t="inlineStr"/>
+      <c r="BM24" t="inlineStr"/>
+      <c r="BN24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>Aeu0r0Mk</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="n">
+        <v>45516.54166666666</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fourneau f 
+  ita </t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio benito stirpe
+  frosinone </t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>16227</v>
+      </c>
+      <c r="F25" t="n">
+        <v>9384</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
+        <v>3</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>pfo9H1Wp</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>roasMsOT</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="n">
+        <v>59</v>
+      </c>
+      <c r="N25" t="n">
+        <v>41</v>
+      </c>
+      <c r="O25" t="n">
+        <v>5</v>
+      </c>
+      <c r="P25" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>2</v>
+      </c>
+      <c r="R25" t="n">
+        <v>4</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="n">
+        <v>19</v>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>dnLs0wVo</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>GfucctAF</t>
+        </is>
+      </c>
+      <c r="W25" t="n">
+        <v>77</v>
+      </c>
+      <c r="X25" t="n">
+        <v>773</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>0M9xNN8N</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>Q3A3IbXH</t>
+        </is>
+      </c>
+      <c r="AC25" t="n">
+        <v>22.22222222222222</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>186.1111111111111</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>65.77777777777777</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>1597222.222222222</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>74.55555555555556</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>185.3</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>68.3</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>1697500</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>72.2</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>20.66666666666667</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>185.5333333333333</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>61.86666666666667</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>980000</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>73.86666666666666</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>22.52</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>181.48</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>64.56</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>1611000</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>72.2</v>
+      </c>
+      <c r="BA25" t="inlineStr"/>
+      <c r="BB25" t="inlineStr"/>
+      <c r="BC25" t="inlineStr"/>
+      <c r="BD25" t="inlineStr"/>
+      <c r="BE25" t="inlineStr"/>
+      <c r="BF25" t="inlineStr"/>
+      <c r="BG25" t="inlineStr"/>
+      <c r="BH25" t="inlineStr"/>
+      <c r="BI25" t="inlineStr"/>
+      <c r="BJ25" t="inlineStr"/>
+      <c r="BK25" t="inlineStr"/>
+      <c r="BL25" t="inlineStr"/>
+      <c r="BM25" t="inlineStr"/>
+      <c r="BN25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>ALOjHNNj</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>45515.67708333334</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ghersini d 
+  ita </t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio olimpico di torino
+  turin </t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>28177</v>
+      </c>
+      <c r="F26" t="n">
+        <v>12035</v>
+      </c>
+      <c r="G26" t="n">
+        <v>2</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>MZFZnvX4</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>p84TeBhA</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="n">
+        <v>60</v>
+      </c>
+      <c r="N26" t="n">
+        <v>40</v>
+      </c>
+      <c r="O26" t="n">
+        <v>8</v>
+      </c>
+      <c r="P26" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>2</v>
+      </c>
+      <c r="R26" t="n">
+        <v>4</v>
+      </c>
+      <c r="S26" t="n">
+        <v>6</v>
+      </c>
+      <c r="T26" t="n">
+        <v>12</v>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>AB3WB3pA</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Yika9O16</t>
+        </is>
+      </c>
+      <c r="W26" t="n">
+        <v>77</v>
+      </c>
+      <c r="X26" t="n">
+        <v>773</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>C06aJvIB</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>GnizyMB7</t>
+        </is>
+      </c>
+      <c r="AC26" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>185.8</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>11290000</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>78.09999999999999</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>184.8</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>66.40000000000001</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>1167500</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>70.8</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>23.57894736842105</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>184.4736842105263</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>1.052631578947368</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>70.05263157894737</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>5423684.210526315</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>76.47368421052632</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>22.28571428571428</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>179.7142857142857</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>64.14285714285714</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>1171428.571428571</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>71.85714285714286</v>
+      </c>
+      <c r="BA26" t="inlineStr"/>
+      <c r="BB26" t="inlineStr"/>
+      <c r="BC26" t="inlineStr"/>
+      <c r="BD26" t="inlineStr"/>
+      <c r="BE26" t="inlineStr"/>
+      <c r="BF26" t="inlineStr"/>
+      <c r="BG26" t="inlineStr"/>
+      <c r="BH26" t="inlineStr"/>
+      <c r="BI26" t="inlineStr"/>
+      <c r="BJ26" t="inlineStr"/>
+      <c r="BK26" t="inlineStr"/>
+      <c r="BL26" t="inlineStr"/>
+      <c r="BM26" t="inlineStr"/>
+      <c r="BN26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>ILr8tvi2</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="n">
+        <v>45515.65625</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">collu g 
+  ita </t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio luigi ferraris
+  genoa </t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>36599</v>
+      </c>
+      <c r="F27" t="n">
+        <v>14196</v>
+      </c>
+      <c r="G27" t="n">
+        <v>2</v>
+      </c>
+      <c r="H27" t="n">
+        <v>1</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>nJbCGx2U</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>ttyLthOA</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="n">
+        <v>43</v>
+      </c>
+      <c r="N27" t="n">
+        <v>57</v>
+      </c>
+      <c r="O27" t="n">
+        <v>11</v>
+      </c>
+      <c r="P27" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>3</v>
+      </c>
+      <c r="R27" t="n">
+        <v>5</v>
+      </c>
+      <c r="S27" t="n">
+        <v>4</v>
+      </c>
+      <c r="T27" t="n">
+        <v>13</v>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>2kfSDavF</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>EZS2ir7i</t>
+        </is>
+      </c>
+      <c r="W27" t="n">
+        <v>77</v>
+      </c>
+      <c r="X27" t="n">
+        <v>773</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>d0PJxeie</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>4YSMlwj7</t>
+        </is>
+      </c>
+      <c r="AC27" t="n">
+        <v>27.66666666666667</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>181.7777777777778</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>1.111111111111111</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>70.33333333333333</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>2136111.111111111</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>73.44444444444444</v>
+      </c>
+      <c r="AI27" t="inlineStr"/>
+      <c r="AJ27" t="inlineStr"/>
+      <c r="AK27" t="inlineStr"/>
+      <c r="AL27" t="inlineStr"/>
+      <c r="AM27" t="inlineStr"/>
+      <c r="AN27" t="inlineStr"/>
+      <c r="AO27" t="n">
+        <v>25.25</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>181.85</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>67.55</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>1749750</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>72.45</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>28.04545454545455</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>183.8636363636364</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>1.363636363636364</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>70.59090909090909</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>3314318.181818182</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>71.68181818181819</v>
+      </c>
+      <c r="BA27" t="inlineStr"/>
+      <c r="BB27" t="inlineStr"/>
+      <c r="BC27" t="inlineStr"/>
+      <c r="BD27" t="inlineStr"/>
+      <c r="BE27" t="inlineStr"/>
+      <c r="BF27" t="inlineStr"/>
+      <c r="BG27" t="inlineStr"/>
+      <c r="BH27" t="inlineStr"/>
+      <c r="BI27" t="inlineStr"/>
+      <c r="BJ27" t="inlineStr"/>
+      <c r="BK27" t="inlineStr"/>
+      <c r="BL27" t="inlineStr"/>
+      <c r="BM27" t="inlineStr"/>
+      <c r="BN27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>bepKi4a3</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>45515.5625</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">perenzoni d 
+  ita </t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio ennio tardini
+  parma </t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>27906</v>
+      </c>
+      <c r="F28" t="n">
+        <v>5034</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" t="n">
+        <v>1</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>6DxlaxHN</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>n38Nktmn</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="n">
+        <v>47</v>
+      </c>
+      <c r="N28" t="n">
+        <v>53</v>
+      </c>
+      <c r="O28" t="n">
+        <v>17</v>
+      </c>
+      <c r="P28" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>4</v>
+      </c>
+      <c r="R28" t="n">
+        <v>4</v>
+      </c>
+      <c r="S28" t="n">
+        <v>7</v>
+      </c>
+      <c r="T28" t="n">
+        <v>12</v>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>lQEaJ9QD</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Wn0poKgt</t>
+        </is>
+      </c>
+      <c r="W28" t="n">
+        <v>77</v>
+      </c>
+      <c r="X28" t="n">
+        <v>773</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>0M9xNN8N</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>pfo9H1Wp</t>
+        </is>
+      </c>
+      <c r="AC28" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>185.3</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>69.59999999999999</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>2345000</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>74.2</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>181.5</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>70.7</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>3020000</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>22.95238095238095</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>183.1904761904762</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>1.047619047619048</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>67.04761904761905</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>2280476.19047619</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>74.66666666666667</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>24.82608695652174</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>183.9130434782609</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>69.26086956521739</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>2280434.782608696</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>74.26086956521739</v>
+      </c>
+      <c r="BA28" t="inlineStr"/>
+      <c r="BB28" t="inlineStr"/>
+      <c r="BC28" t="inlineStr"/>
+      <c r="BD28" t="inlineStr"/>
+      <c r="BE28" t="inlineStr"/>
+      <c r="BF28" t="inlineStr"/>
+      <c r="BG28" t="inlineStr"/>
+      <c r="BH28" t="inlineStr"/>
+      <c r="BI28" t="inlineStr"/>
+      <c r="BJ28" t="inlineStr"/>
+      <c r="BK28" t="inlineStr"/>
+      <c r="BL28" t="inlineStr"/>
+      <c r="BM28" t="inlineStr"/>
+      <c r="BN28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>6sP22LDL</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="n">
+        <v>45515.54166666666</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">caputi m 
+  ita </t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio mario rigamonti
+  brescia </t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>19500</v>
+      </c>
+      <c r="F29" t="n">
+        <v>4310</v>
+      </c>
+      <c r="G29" t="n">
+        <v>3</v>
+      </c>
+      <c r="H29" t="n">
+        <v>1</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>jci0qO9B</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>MkPmVv50</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="n">
+        <v>38</v>
+      </c>
+      <c r="N29" t="n">
+        <v>62</v>
+      </c>
+      <c r="O29" t="n">
+        <v>9</v>
+      </c>
+      <c r="P29" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>5</v>
+      </c>
+      <c r="R29" t="n">
+        <v>8</v>
+      </c>
+      <c r="S29" t="n">
+        <v>14</v>
+      </c>
+      <c r="T29" t="n">
+        <v>12</v>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>lb1XFX3n</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>n10g3KfJ</t>
+        </is>
+      </c>
+      <c r="W29" t="n">
+        <v>77</v>
+      </c>
+      <c r="X29" t="n">
+        <v>773</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>8C9JjMXu</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>rJVAIaHo</t>
+        </is>
+      </c>
+      <c r="AC29" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>184.7</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>66.40000000000001</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>1225000</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>70.09999999999999</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>26.88888888888889</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>183.8888888888889</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>1.111111111111111</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>69.66666666666667</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>1888888.888888889</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>72.33333333333333</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>22.77777777777778</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>181.6111111111111</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>64.33333333333333</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>1217777.777777778</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>72.66666666666667</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>23.47368421052632</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>184.2631578947368</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>1.052631578947368</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>66.78947368421052</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>1748421.052631579</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>73.42105263157895</v>
+      </c>
+      <c r="BA29" t="inlineStr"/>
+      <c r="BB29" t="inlineStr"/>
+      <c r="BC29" t="inlineStr"/>
+      <c r="BD29" t="inlineStr"/>
+      <c r="BE29" t="inlineStr"/>
+      <c r="BF29" t="inlineStr"/>
+      <c r="BG29" t="inlineStr"/>
+      <c r="BH29" t="inlineStr"/>
+      <c r="BI29" t="inlineStr"/>
+      <c r="BJ29" t="inlineStr"/>
+      <c r="BK29" t="inlineStr"/>
+      <c r="BL29" t="inlineStr"/>
+      <c r="BM29" t="inlineStr"/>
+      <c r="BN29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>dC3sew6e</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>45514.67708333334</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bonacina k 
+  ita </t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio diego armando maradona
+  naples </t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>54726</v>
+      </c>
+      <c r="F30" t="n">
+        <v>52000</v>
+      </c>
+      <c r="G30" t="n">
+        <v>1</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>69Dxbc61</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>MBn63swN</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="n">
+        <v>70</v>
+      </c>
+      <c r="N30" t="n">
+        <v>30</v>
+      </c>
+      <c r="O30" t="n">
+        <v>28</v>
+      </c>
+      <c r="P30" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>6</v>
+      </c>
+      <c r="R30" t="n">
+        <v>2</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="n">
+        <v>6</v>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>23vSAc12</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>YTZ7S7pk</t>
+        </is>
+      </c>
+      <c r="W30" t="n">
+        <v>77</v>
+      </c>
+      <c r="X30" t="n">
+        <v>773</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>C06aJvIB</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>0M9xNN8N</t>
+        </is>
+      </c>
+      <c r="AC30" t="n">
+        <v>26.72727272727273</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>182.0909090909091</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>1.727272727272727</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>80.72727272727273</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>32290909.09090909</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>82.36363636363636</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>184.6</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>67.8</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>1382500</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>70.7</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>25.15</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>182.65</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>75.2</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>9576250</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>77.95</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>23.78571428571428</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>181.1428571428571</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>63.85714285714285</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>1024642.857142857</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>69.64285714285714</v>
+      </c>
+      <c r="BA30" t="inlineStr"/>
+      <c r="BB30" t="inlineStr"/>
+      <c r="BC30" t="inlineStr"/>
+      <c r="BD30" t="inlineStr"/>
+      <c r="BE30" t="inlineStr"/>
+      <c r="BF30" t="inlineStr"/>
+      <c r="BG30" t="inlineStr"/>
+      <c r="BH30" t="inlineStr"/>
+      <c r="BI30" t="inlineStr"/>
+      <c r="BJ30" t="inlineStr"/>
+      <c r="BK30" t="inlineStr"/>
+      <c r="BL30" t="inlineStr"/>
+      <c r="BM30" t="inlineStr"/>
+      <c r="BN30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>Ob5Zdayq</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="n">
+        <v>45514.65625</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">arena a 
+  ita </t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio carlo castellani
+  empoli </t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>16284</v>
+      </c>
+      <c r="F31" t="n">
+        <v>1738</v>
+      </c>
+      <c r="G31" t="n">
+        <v>4</v>
+      </c>
+      <c r="H31" t="n">
+        <v>1</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>0ESCnI1H</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>GnizyMB7</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="n">
+        <v>57</v>
+      </c>
+      <c r="N31" t="n">
+        <v>43</v>
+      </c>
+      <c r="O31" t="n">
+        <v>22</v>
+      </c>
+      <c r="P31" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>8</v>
+      </c>
+      <c r="R31" t="n">
+        <v>3</v>
+      </c>
+      <c r="S31" t="n">
+        <v>9</v>
+      </c>
+      <c r="T31" t="n">
+        <v>10</v>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>MBrKQFV7</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>nsYMfLJM</t>
+        </is>
+      </c>
+      <c r="W31" t="n">
+        <v>77</v>
+      </c>
+      <c r="X31" t="n">
+        <v>773</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>Q3A3IbXH</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>p84TeBhA</t>
+        </is>
+      </c>
+      <c r="AC31" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>185</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>70.7</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>3150000</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>76.40000000000001</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>28.22222222222222</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>179.4444444444445</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>67.88888888888889</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>1133333.333333333</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>69.88888888888889</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>24.81818181818182</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>181.4090909090909</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>67.45454545454545</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>2088181.818181818</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>73.18181818181819</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>25</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>184.25</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>65.16666666666667</v>
+      </c>
+      <c r="AY31" t="n">
+        <v>1014583.333333333</v>
+      </c>
+      <c r="AZ31" t="n">
+        <v>68.75</v>
+      </c>
+      <c r="BA31" t="inlineStr"/>
+      <c r="BB31" t="inlineStr"/>
+      <c r="BC31" t="inlineStr"/>
+      <c r="BD31" t="inlineStr"/>
+      <c r="BE31" t="inlineStr"/>
+      <c r="BF31" t="inlineStr"/>
+      <c r="BG31" t="inlineStr"/>
+      <c r="BH31" t="inlineStr"/>
+      <c r="BI31" t="inlineStr"/>
+      <c r="BJ31" t="inlineStr"/>
+      <c r="BK31" t="inlineStr"/>
+      <c r="BL31" t="inlineStr"/>
+      <c r="BM31" t="inlineStr"/>
+      <c r="BN31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>02s0k9od</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="n">
+        <v>45514.5625</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">crezzini v 
+  ita </t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio marc antonio bentegodi
+  verona </t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>39211</v>
+      </c>
+      <c r="F32" t="n">
+        <v>7048</v>
+      </c>
+      <c r="G32" t="n">
+        <v>1</v>
+      </c>
+      <c r="H32" t="n">
+        <v>2</v>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>rJVAIaHo</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>xddf1qfh</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="n">
+        <v>54</v>
+      </c>
+      <c r="N32" t="n">
+        <v>46</v>
+      </c>
+      <c r="O32" t="n">
+        <v>11</v>
+      </c>
+      <c r="P32" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>3</v>
+      </c>
+      <c r="R32" t="n">
+        <v>4</v>
+      </c>
+      <c r="S32" t="n">
+        <v>14</v>
+      </c>
+      <c r="T32" t="n">
+        <v>7</v>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>OW6PtuKn</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>vD8aDRIm</t>
+        </is>
+      </c>
+      <c r="W32" t="n">
+        <v>77</v>
+      </c>
+      <c r="X32" t="n">
+        <v>773</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>69Dxbc61</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr"/>
+      <c r="AC32" t="n">
+        <v>24.88888888888889</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>184.1111111111111</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>1.111111111111111</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>73.11111111111111</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>5011111.111111111</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>77.44444444444444</v>
+      </c>
+      <c r="AI32" t="inlineStr"/>
+      <c r="AJ32" t="inlineStr"/>
+      <c r="AK32" t="inlineStr"/>
+      <c r="AL32" t="inlineStr"/>
+      <c r="AM32" t="inlineStr"/>
+      <c r="AN32" t="inlineStr"/>
+      <c r="AO32" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>184.0555555555555</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>70.22222222222223</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>2776388.888888889</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>74.05555555555556</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>24.55555555555556</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>181.5555555555555</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>66.88888888888889</v>
+      </c>
+      <c r="AY32" t="n">
+        <v>1650000</v>
+      </c>
+      <c r="AZ32" t="n">
+        <v>71</v>
+      </c>
+      <c r="BA32" t="inlineStr"/>
+      <c r="BB32" t="inlineStr"/>
+      <c r="BC32" t="inlineStr"/>
+      <c r="BD32" t="inlineStr"/>
+      <c r="BE32" t="inlineStr"/>
+      <c r="BF32" t="inlineStr"/>
+      <c r="BG32" t="inlineStr"/>
+      <c r="BH32" t="inlineStr"/>
+      <c r="BI32" t="inlineStr"/>
+      <c r="BJ32" t="inlineStr"/>
+      <c r="BK32" t="inlineStr"/>
+      <c r="BL32" t="inlineStr"/>
+      <c r="BM32" t="inlineStr"/>
+      <c r="BN32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>bs5ow5pA</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="n">
+        <v>45514.54166666666</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">galipo s 
+  ita </t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio giovanni zini
+  cremona </t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>20641</v>
+      </c>
+      <c r="F33" t="n">
+        <v>3724</v>
+      </c>
+      <c r="G33" t="n">
+        <v>2</v>
+      </c>
+      <c r="H33" t="n">
+        <v>1</v>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>KUzfp5N3</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>xIkUr2vO</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="n">
+        <v>58</v>
+      </c>
+      <c r="N33" t="n">
+        <v>42</v>
+      </c>
+      <c r="O33" t="n">
+        <v>13</v>
+      </c>
+      <c r="P33" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>3</v>
+      </c>
+      <c r="R33" t="n">
+        <v>4</v>
+      </c>
+      <c r="S33" t="n">
+        <v>15</v>
+      </c>
+      <c r="T33" t="n">
+        <v>12</v>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>YgLhKnOo</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>nZ24J27c</t>
+        </is>
+      </c>
+      <c r="W33" t="n">
+        <v>77</v>
+      </c>
+      <c r="X33" t="n">
+        <v>773</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>ttyLthOA</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>G8lYsMgU</t>
+        </is>
+      </c>
+      <c r="AC33" t="n">
+        <v>26.09090909090909</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>184.5454545454545</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>70.36363636363636</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>2154545.454545455</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>73.27272727272727</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>27.33333333333333</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>181.5555555555555</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>1.111111111111111</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>68.66666666666667</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>1541666.666666667</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>71.66666666666667</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>25.30434782608696</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>184.304347826087</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>1.130434782608696</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>69.08695652173913</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>2065217.391304348</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>74.04347826086956</v>
+      </c>
+      <c r="AU33" t="n">
+        <v>24.66666666666667</v>
+      </c>
+      <c r="AV33" t="n">
+        <v>182.2083333333333</v>
+      </c>
+      <c r="AW33" t="n">
+        <v>1.041666666666667</v>
+      </c>
+      <c r="AX33" t="n">
+        <v>64.29166666666667</v>
+      </c>
+      <c r="AY33" t="n">
+        <v>1022500</v>
+      </c>
+      <c r="AZ33" t="n">
+        <v>69.54166666666667</v>
+      </c>
+      <c r="BA33" t="inlineStr"/>
+      <c r="BB33" t="inlineStr"/>
+      <c r="BC33" t="inlineStr"/>
+      <c r="BD33" t="inlineStr"/>
+      <c r="BE33" t="inlineStr"/>
+      <c r="BF33" t="inlineStr"/>
+      <c r="BG33" t="inlineStr"/>
+      <c r="BH33" t="inlineStr"/>
+      <c r="BI33" t="inlineStr"/>
+      <c r="BJ33" t="inlineStr"/>
+      <c r="BK33" t="inlineStr"/>
+      <c r="BL33" t="inlineStr"/>
+      <c r="BM33" t="inlineStr"/>
+      <c r="BN33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>AZ3PVMxp</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="n">
+        <v>45513.67708333334</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cosso f 
+  ita </t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">brianteo
+  monza </t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>16917</v>
+      </c>
+      <c r="F34" t="n">
+        <v>7139</v>
+      </c>
+      <c r="G34" t="n">
+        <v>1</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>4YSMlwj7</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>W02MZDnp</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="n">
+        <v>57</v>
+      </c>
+      <c r="N34" t="n">
+        <v>43</v>
+      </c>
+      <c r="O34" t="n">
+        <v>10</v>
+      </c>
+      <c r="P34" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>4</v>
+      </c>
+      <c r="R34" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" t="n">
+        <v>15</v>
+      </c>
+      <c r="T34" t="n">
+        <v>9</v>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>CEv2hvmq</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>bmzifXwb</t>
+        </is>
+      </c>
+      <c r="W34" t="n">
+        <v>77</v>
+      </c>
+      <c r="X34" t="n">
+        <v>773</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>ttyLthOA</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>rXw8YKDE</t>
+        </is>
+      </c>
+      <c r="AC34" t="n">
+        <v>25.63636363636364</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>183.9090909090909</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>1.454545454545455</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>72.27272727272727</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>4727272.727272728</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>76.54545454545455</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>182.6</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>68</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>983500</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>70</v>
+      </c>
+      <c r="AO34" t="n">
+        <v>26.29166666666667</v>
+      </c>
+      <c r="AP34" t="n">
+        <v>180.875</v>
+      </c>
+      <c r="AQ34" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AR34" t="n">
+        <v>72.29166666666667</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>5370833.333333333</v>
+      </c>
+      <c r="AT34" t="n">
+        <v>75.375</v>
+      </c>
+      <c r="AU34" t="n">
+        <v>23.57894736842105</v>
+      </c>
+      <c r="AV34" t="n">
+        <v>185.3157894736842</v>
+      </c>
+      <c r="AW34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX34" t="n">
+        <v>65.26315789473684</v>
+      </c>
+      <c r="AY34" t="n">
+        <v>1278947.368421053</v>
+      </c>
+      <c r="AZ34" t="n">
+        <v>71.36842105263158</v>
+      </c>
+      <c r="BA34" t="inlineStr"/>
+      <c r="BB34" t="inlineStr"/>
+      <c r="BC34" t="inlineStr"/>
+      <c r="BD34" t="inlineStr"/>
+      <c r="BE34" t="inlineStr"/>
+      <c r="BF34" t="inlineStr"/>
+      <c r="BG34" t="inlineStr"/>
+      <c r="BH34" t="inlineStr"/>
+      <c r="BI34" t="inlineStr"/>
+      <c r="BJ34" t="inlineStr"/>
+      <c r="BK34" t="inlineStr"/>
+      <c r="BL34" t="inlineStr"/>
+      <c r="BM34" t="inlineStr"/>
+      <c r="BN34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>hvcjgHz8</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="n">
+        <v>45513.65625</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">di marco d 
+  ita </t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio luigi ferraris
+  genoa </t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>36599</v>
+      </c>
+      <c r="F35" t="n">
+        <v>22000</v>
+      </c>
+      <c r="G35" t="n">
+        <v>1</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>d0PJxeie</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>6ulJbMCe</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="n">
+        <v>54</v>
+      </c>
+      <c r="N35" t="n">
+        <v>46</v>
+      </c>
+      <c r="O35" t="n">
+        <v>19</v>
+      </c>
+      <c r="P35" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>13</v>
+      </c>
+      <c r="R35" t="n">
+        <v>5</v>
+      </c>
+      <c r="S35" t="n">
+        <v>16</v>
+      </c>
+      <c r="T35" t="n">
+        <v>11</v>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>tSiEeKvS</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Gfur2NmR</t>
+        </is>
+      </c>
+      <c r="W35" t="n">
+        <v>77</v>
+      </c>
+      <c r="X35" t="n">
+        <v>773</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>nJbCGx2U</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr"/>
+      <c r="AC35" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>183.9</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>72.3</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>4072500</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>75.8</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>26</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>183.875</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>63.375</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>781250</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>68.875</v>
+      </c>
+      <c r="AO35" t="n">
+        <v>26.53333333333333</v>
+      </c>
+      <c r="AP35" t="n">
+        <v>184.0666666666667</v>
+      </c>
+      <c r="AQ35" t="n">
+        <v>1.533333333333333</v>
+      </c>
+      <c r="AR35" t="n">
+        <v>72.26666666666667</v>
+      </c>
+      <c r="AS35" t="n">
+        <v>5316666.666666667</v>
+      </c>
+      <c r="AT35" t="n">
+        <v>75.93333333333334</v>
+      </c>
+      <c r="AU35" t="n">
+        <v>25.4375</v>
+      </c>
+      <c r="AV35" t="n">
+        <v>179.875</v>
+      </c>
+      <c r="AW35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX35" t="n">
+        <v>62.1875</v>
+      </c>
+      <c r="AY35" t="n">
+        <v>718125</v>
+      </c>
+      <c r="AZ35" t="n">
+        <v>65.75</v>
+      </c>
+      <c r="BA35" t="inlineStr"/>
+      <c r="BB35" t="inlineStr"/>
+      <c r="BC35" t="inlineStr"/>
+      <c r="BD35" t="inlineStr"/>
+      <c r="BE35" t="inlineStr"/>
+      <c r="BF35" t="inlineStr"/>
+      <c r="BG35" t="inlineStr"/>
+      <c r="BH35" t="inlineStr"/>
+      <c r="BI35" t="inlineStr"/>
+      <c r="BJ35" t="inlineStr"/>
+      <c r="BK35" t="inlineStr"/>
+      <c r="BL35" t="inlineStr"/>
+      <c r="BM35" t="inlineStr"/>
+      <c r="BN35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>dnnqk0iD</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="n">
+        <v>45513.5625</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">scatena g 
+  ita </t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bluenergy stadium   stadio friuli
+  udine </t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>25144</v>
+      </c>
+      <c r="F36" t="n">
+        <v>5850</v>
+      </c>
+      <c r="G36" t="n">
+        <v>4</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>rXw8YKDE</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>A332L1f5</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="n">
+        <v>62</v>
+      </c>
+      <c r="N36" t="n">
+        <v>38</v>
+      </c>
+      <c r="O36" t="n">
+        <v>16</v>
+      </c>
+      <c r="P36" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>7</v>
+      </c>
+      <c r="R36" t="n">
+        <v>1</v>
+      </c>
+      <c r="S36" t="n">
+        <v>15</v>
+      </c>
+      <c r="T36" t="n">
+        <v>10</v>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>ncu4OLs5</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>WE57Jh0D</t>
+        </is>
+      </c>
+      <c r="W36" t="n">
+        <v>77</v>
+      </c>
+      <c r="X36" t="n">
+        <v>773</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>69Dxbc61</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr"/>
+      <c r="AC36" t="n">
+        <v>25.45454545454545</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>184.8181818181818</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>73.45454545454545</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>4663636.363636363</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>76.27272727272727</v>
+      </c>
+      <c r="AI36" t="inlineStr"/>
+      <c r="AJ36" t="inlineStr"/>
+      <c r="AK36" t="inlineStr"/>
+      <c r="AL36" t="inlineStr"/>
+      <c r="AM36" t="inlineStr"/>
+      <c r="AN36" t="inlineStr"/>
+      <c r="AO36" t="n">
+        <v>25.40909090909091</v>
+      </c>
+      <c r="AP36" t="n">
+        <v>183.8636363636364</v>
+      </c>
+      <c r="AQ36" t="n">
+        <v>1.045454545454545</v>
+      </c>
+      <c r="AR36" t="n">
+        <v>71.81818181818181</v>
+      </c>
+      <c r="AS36" t="n">
+        <v>4140909.090909091</v>
+      </c>
+      <c r="AT36" t="n">
+        <v>75.90909090909091</v>
+      </c>
+      <c r="AU36" t="inlineStr"/>
+      <c r="AV36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr"/>
+      <c r="AX36" t="inlineStr"/>
+      <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr"/>
+      <c r="BA36" t="inlineStr"/>
+      <c r="BB36" t="inlineStr"/>
+      <c r="BC36" t="inlineStr"/>
+      <c r="BD36" t="inlineStr"/>
+      <c r="BE36" t="inlineStr"/>
+      <c r="BF36" t="inlineStr"/>
+      <c r="BG36" t="inlineStr"/>
+      <c r="BH36" t="inlineStr"/>
+      <c r="BI36" t="inlineStr"/>
+      <c r="BJ36" t="inlineStr"/>
+      <c r="BK36" t="inlineStr"/>
+      <c r="BL36" t="inlineStr"/>
+      <c r="BM36" t="inlineStr"/>
+      <c r="BN36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>QT6wuRFc</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="n">
+        <v>45513.54166666666</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">prontera a 
+  ita </t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mapei stadium – citta del tricolore
+  reggio emilia </t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>21525</v>
+      </c>
+      <c r="F37" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G37" t="n">
+        <v>2</v>
+      </c>
+      <c r="H37" t="n">
+        <v>1</v>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>QDdvI0zl</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>C0yUqo8c</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="n">
+        <v>49</v>
+      </c>
+      <c r="N37" t="n">
+        <v>51</v>
+      </c>
+      <c r="O37" t="n">
+        <v>15</v>
+      </c>
+      <c r="P37" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>9</v>
+      </c>
+      <c r="R37" t="n">
+        <v>2</v>
+      </c>
+      <c r="S37" t="n">
+        <v>15</v>
+      </c>
+      <c r="T37" t="n">
+        <v>9</v>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>bPHSQi9q</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>8dDPzPa7</t>
+        </is>
+      </c>
+      <c r="W37" t="n">
+        <v>77</v>
+      </c>
+      <c r="X37" t="n">
+        <v>773</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>0M9xNN8N</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>MkPmVv50</t>
+        </is>
+      </c>
+      <c r="AC37" t="n">
+        <v>24.54545454545455</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>185.1818181818182</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>1.181818181818182</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>71.36363636363636</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>5297727.272727272</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>75.27272727272727</v>
+      </c>
+      <c r="AI37" t="inlineStr"/>
+      <c r="AJ37" t="inlineStr"/>
+      <c r="AK37" t="inlineStr"/>
+      <c r="AL37" t="inlineStr"/>
+      <c r="AM37" t="inlineStr"/>
+      <c r="AN37" t="inlineStr"/>
+      <c r="AO37" t="n">
+        <v>21.60869565217391</v>
+      </c>
+      <c r="AP37" t="n">
+        <v>184.2608695652174</v>
+      </c>
+      <c r="AQ37" t="n">
+        <v>1.043478260869565</v>
+      </c>
+      <c r="AR37" t="n">
+        <v>68.08695652173913</v>
+      </c>
+      <c r="AS37" t="n">
+        <v>3495652.173913043</v>
+      </c>
+      <c r="AT37" t="n">
+        <v>78.26086956521739</v>
+      </c>
+      <c r="AU37" t="n">
+        <v>26.22727272727273</v>
+      </c>
+      <c r="AV37" t="n">
+        <v>184.7727272727273</v>
+      </c>
+      <c r="AW37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX37" t="n">
+        <v>65.31818181818181</v>
+      </c>
+      <c r="AY37" t="n">
+        <v>1042954.545454545</v>
+      </c>
+      <c r="AZ37" t="n">
+        <v>69.13636363636364</v>
+      </c>
+      <c r="BA37" t="inlineStr"/>
+      <c r="BB37" t="inlineStr"/>
+      <c r="BC37" t="inlineStr"/>
+      <c r="BD37" t="inlineStr"/>
+      <c r="BE37" t="inlineStr"/>
+      <c r="BF37" t="inlineStr"/>
+      <c r="BG37" t="inlineStr"/>
+      <c r="BH37" t="inlineStr"/>
+      <c r="BI37" t="inlineStr"/>
+      <c r="BJ37" t="inlineStr"/>
+      <c r="BK37" t="inlineStr"/>
+      <c r="BL37" t="inlineStr"/>
+      <c r="BM37" t="inlineStr"/>
+      <c r="BN37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>WlhYT07d</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="n">
+        <v>45508.65625</v>
+      </c>
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio partenio adriano lombardi
+  avellino </t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>26000</v>
+      </c>
+      <c r="F38" t="n">
+        <v>5050</v>
+      </c>
+      <c r="G38" t="n">
+        <v>3</v>
+      </c>
+      <c r="H38" t="n">
+        <v>1</v>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>A332L1f5</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>hKSfjtsQ</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr"/>
+      <c r="P38" t="inlineStr"/>
+      <c r="Q38" t="inlineStr"/>
+      <c r="R38" t="inlineStr"/>
+      <c r="S38" t="inlineStr"/>
+      <c r="T38" t="inlineStr"/>
+      <c r="U38" t="inlineStr"/>
+      <c r="V38" t="inlineStr"/>
+      <c r="W38" t="n">
+        <v>77</v>
+      </c>
+      <c r="X38" t="n">
+        <v>773</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA38" t="inlineStr"/>
+      <c r="AB38" t="inlineStr"/>
+      <c r="AC38" t="inlineStr"/>
+      <c r="AD38" t="inlineStr"/>
+      <c r="AE38" t="inlineStr"/>
+      <c r="AF38" t="inlineStr"/>
+      <c r="AG38" t="inlineStr"/>
+      <c r="AH38" t="inlineStr"/>
+      <c r="AI38" t="inlineStr"/>
+      <c r="AJ38" t="inlineStr"/>
+      <c r="AK38" t="inlineStr"/>
+      <c r="AL38" t="inlineStr"/>
+      <c r="AM38" t="inlineStr"/>
+      <c r="AN38" t="inlineStr"/>
+      <c r="AO38" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="AP38" t="n">
+        <v>182.8333333333333</v>
+      </c>
+      <c r="AQ38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR38" t="n">
+        <v>67.16666666666667</v>
+      </c>
+      <c r="AS38" t="n">
+        <v>1137500</v>
+      </c>
+      <c r="AT38" t="n">
+        <v>69</v>
+      </c>
+      <c r="AU38" t="inlineStr"/>
+      <c r="AV38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr"/>
+      <c r="AX38" t="inlineStr"/>
+      <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr"/>
+      <c r="BA38" t="inlineStr"/>
+      <c r="BB38" t="inlineStr"/>
+      <c r="BC38" t="inlineStr"/>
+      <c r="BD38" t="inlineStr"/>
+      <c r="BE38" t="inlineStr"/>
+      <c r="BF38" t="inlineStr"/>
+      <c r="BG38" t="inlineStr"/>
+      <c r="BH38" t="inlineStr"/>
+      <c r="BI38" t="inlineStr"/>
+      <c r="BJ38" t="inlineStr"/>
+      <c r="BK38" t="inlineStr"/>
+      <c r="BL38" t="inlineStr"/>
+      <c r="BM38" t="inlineStr"/>
+      <c r="BN38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>SzxylMbS</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="n">
+        <v>45508.64583333334</v>
+      </c>
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio dino manuzzi
+  cesena </t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>23860</v>
+      </c>
+      <c r="F39" t="n">
+        <v>4468</v>
+      </c>
+      <c r="G39" t="n">
+        <v>3</v>
+      </c>
+      <c r="H39" t="n">
+        <v>1</v>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>xddf1qfh</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>2gUwEtrE</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr"/>
+      <c r="P39" t="inlineStr"/>
+      <c r="Q39" t="inlineStr"/>
+      <c r="R39" t="inlineStr"/>
+      <c r="S39" t="inlineStr"/>
+      <c r="T39" t="inlineStr"/>
+      <c r="U39" t="inlineStr"/>
+      <c r="V39" t="inlineStr"/>
+      <c r="W39" t="n">
+        <v>77</v>
+      </c>
+      <c r="X39" t="n">
+        <v>773</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA39" t="inlineStr"/>
+      <c r="AB39" t="inlineStr"/>
+      <c r="AC39" t="inlineStr"/>
+      <c r="AD39" t="inlineStr"/>
+      <c r="AE39" t="inlineStr"/>
+      <c r="AF39" t="inlineStr"/>
+      <c r="AG39" t="inlineStr"/>
+      <c r="AH39" t="inlineStr"/>
+      <c r="AI39" t="inlineStr"/>
+      <c r="AJ39" t="inlineStr"/>
+      <c r="AK39" t="inlineStr"/>
+      <c r="AL39" t="inlineStr"/>
+      <c r="AM39" t="inlineStr"/>
+      <c r="AN39" t="inlineStr"/>
+      <c r="AO39" t="inlineStr"/>
+      <c r="AP39" t="inlineStr"/>
+      <c r="AQ39" t="inlineStr"/>
+      <c r="AR39" t="inlineStr"/>
+      <c r="AS39" t="inlineStr"/>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AU39" t="inlineStr"/>
+      <c r="AV39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr"/>
+      <c r="AX39" t="inlineStr"/>
+      <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr"/>
+      <c r="BA39" t="inlineStr"/>
+      <c r="BB39" t="inlineStr"/>
+      <c r="BC39" t="inlineStr"/>
+      <c r="BD39" t="inlineStr"/>
+      <c r="BE39" t="inlineStr"/>
+      <c r="BF39" t="inlineStr"/>
+      <c r="BG39" t="inlineStr"/>
+      <c r="BH39" t="inlineStr"/>
+      <c r="BI39" t="inlineStr"/>
+      <c r="BJ39" t="inlineStr"/>
+      <c r="BK39" t="inlineStr"/>
+      <c r="BL39" t="inlineStr"/>
+      <c r="BM39" t="inlineStr"/>
+      <c r="BN39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>bHLf4sq9</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="n">
+        <v>45507.64583333334</v>
+      </c>
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vanni sanna
+  sassari </t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>12000</v>
+      </c>
+      <c r="F40" t="n">
+        <v>2955</v>
+      </c>
+      <c r="G40" t="n">
+        <v>1</v>
+      </c>
+      <c r="H40" t="n">
+        <v>2</v>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>UiGfvfvT</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>z7WK5Pwb</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" t="inlineStr"/>
+      <c r="P40" t="inlineStr"/>
+      <c r="Q40" t="inlineStr"/>
+      <c r="R40" t="inlineStr"/>
+      <c r="S40" t="inlineStr"/>
+      <c r="T40" t="inlineStr"/>
+      <c r="U40" t="inlineStr"/>
+      <c r="V40" t="inlineStr"/>
+      <c r="W40" t="n">
+        <v>77</v>
+      </c>
+      <c r="X40" t="n">
+        <v>773</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA40" t="inlineStr"/>
+      <c r="AB40" t="inlineStr"/>
+      <c r="AC40" t="inlineStr"/>
+      <c r="AD40" t="inlineStr"/>
+      <c r="AE40" t="inlineStr"/>
+      <c r="AF40" t="inlineStr"/>
+      <c r="AG40" t="inlineStr"/>
+      <c r="AH40" t="inlineStr"/>
+      <c r="AI40" t="inlineStr"/>
+      <c r="AJ40" t="inlineStr"/>
+      <c r="AK40" t="inlineStr"/>
+      <c r="AL40" t="inlineStr"/>
+      <c r="AM40" t="inlineStr"/>
+      <c r="AN40" t="inlineStr"/>
+      <c r="AO40" t="n">
+        <v>28</v>
+      </c>
+      <c r="AP40" t="n">
+        <v>176</v>
+      </c>
+      <c r="AQ40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR40" t="n">
+        <v>64</v>
+      </c>
+      <c r="AS40" t="n">
+        <v>587500</v>
+      </c>
+      <c r="AT40" t="n">
+        <v>64.5</v>
+      </c>
+      <c r="AU40" t="n">
+        <v>29</v>
+      </c>
+      <c r="AV40" t="n">
+        <v>181.6</v>
+      </c>
+      <c r="AW40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX40" t="n">
+        <v>70.2</v>
+      </c>
+      <c r="AY40" t="n">
+        <v>1820000</v>
+      </c>
+      <c r="AZ40" t="n">
+        <v>70.2</v>
+      </c>
+      <c r="BA40" t="inlineStr"/>
+      <c r="BB40" t="inlineStr"/>
+      <c r="BC40" t="inlineStr"/>
+      <c r="BD40" t="inlineStr"/>
+      <c r="BE40" t="inlineStr"/>
+      <c r="BF40" t="inlineStr"/>
+      <c r="BG40" t="inlineStr"/>
+      <c r="BH40" t="inlineStr"/>
+      <c r="BI40" t="inlineStr"/>
+      <c r="BJ40" t="inlineStr"/>
+      <c r="BK40" t="inlineStr"/>
+      <c r="BL40" t="inlineStr"/>
+      <c r="BM40" t="inlineStr"/>
+      <c r="BN40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>f9bfyqFM</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="n">
+        <v>45507.54166666666</v>
+      </c>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio dei marmi
+  carrara </t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>5280</v>
+      </c>
+      <c r="F41" t="n">
+        <v>1707</v>
+      </c>
+      <c r="G41" t="n">
+        <v>2</v>
+      </c>
+      <c r="H41" t="n">
+        <v>1</v>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>hG4fg4z3</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>4rwnnbnB</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr"/>
+      <c r="P41" t="inlineStr"/>
+      <c r="Q41" t="inlineStr"/>
+      <c r="R41" t="inlineStr"/>
+      <c r="S41" t="inlineStr"/>
+      <c r="T41" t="inlineStr"/>
+      <c r="U41" t="inlineStr"/>
+      <c r="V41" t="inlineStr"/>
+      <c r="W41" t="n">
+        <v>77</v>
+      </c>
+      <c r="X41" t="n">
+        <v>773</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA41" t="inlineStr"/>
+      <c r="AB41" t="inlineStr"/>
+      <c r="AC41" t="inlineStr"/>
+      <c r="AD41" t="inlineStr"/>
+      <c r="AE41" t="inlineStr"/>
+      <c r="AF41" t="inlineStr"/>
+      <c r="AG41" t="inlineStr"/>
+      <c r="AH41" t="inlineStr"/>
+      <c r="AI41" t="inlineStr"/>
+      <c r="AJ41" t="inlineStr"/>
+      <c r="AK41" t="inlineStr"/>
+      <c r="AL41" t="inlineStr"/>
+      <c r="AM41" t="inlineStr"/>
+      <c r="AN41" t="inlineStr"/>
+      <c r="AO41" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="AP41" t="n">
+        <v>179.8</v>
+      </c>
+      <c r="AQ41" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR41" t="n">
+        <v>61.6</v>
+      </c>
+      <c r="AS41" t="n">
+        <v>775000</v>
+      </c>
+      <c r="AT41" t="n">
+        <v>70.8</v>
+      </c>
+      <c r="AU41" t="inlineStr"/>
+      <c r="AV41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr"/>
+      <c r="AX41" t="inlineStr"/>
+      <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr"/>
+      <c r="BA41" t="inlineStr"/>
+      <c r="BB41" t="inlineStr"/>
+      <c r="BC41" t="inlineStr"/>
+      <c r="BD41" t="inlineStr"/>
+      <c r="BE41" t="inlineStr"/>
+      <c r="BF41" t="inlineStr"/>
+      <c r="BG41" t="inlineStr"/>
+      <c r="BH41" t="inlineStr"/>
+      <c r="BI41" t="inlineStr"/>
+      <c r="BJ41" t="inlineStr"/>
+      <c r="BK41" t="inlineStr"/>
+      <c r="BL41" t="inlineStr"/>
+      <c r="BM41" t="inlineStr"/>
+      <c r="BN41" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/italy/p6_deployment/data_preparation/construct_data/df_matches_to_construct_historic_values.xlsx
+++ b/data/italy/p6_deployment/data_preparation/construct_data/df_matches_to_construct_historic_values.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BN82"/>
+  <dimension ref="A1:BN71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5132,7 +5132,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>v5l07LdU</t>
+          <t>jqIIP2Cb</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -5140,72 +5140,72 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t xml:space="preserve">perenzoni d 
+          <t xml:space="preserve">abisso r 
   ita </t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio nicola ceravolo
-  catanzaro </t>
+          <t xml:space="preserve">stadio danilo martelli
+  mantova </t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>14650</v>
+        <v>5423</v>
       </c>
       <c r="F24" t="n">
-        <v>9348</v>
+        <v>8651</v>
       </c>
       <c r="G24" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>GnizyMB7</t>
+          <t>z7WK5Pwb</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>hG4fg4z3</t>
+          <t>Mq05g4BP</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="N24" t="n">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="O24" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="P24" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Q24" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="R24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S24" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="T24" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>nsYMfLJM</t>
+          <t>hrkecaMB</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>lSb6U6l0</t>
+          <t>OjWmexQb</t>
         </is>
       </c>
       <c r="W24" t="n">
@@ -5220,30 +5220,18 @@
       <c r="Z24" t="n">
         <v>20242025</v>
       </c>
-      <c r="AA24" t="inlineStr">
-        <is>
-          <t>p84TeBhA</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr"/>
-      <c r="AC24" t="n">
-        <v>27.8</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>181</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>66.8</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>1057500</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>68.59999999999999</v>
-      </c>
+      <c r="AA24" t="inlineStr"/>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>69Dxbc61</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr"/>
+      <c r="AD24" t="inlineStr"/>
+      <c r="AE24" t="inlineStr"/>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="inlineStr"/>
+      <c r="AH24" t="inlineStr"/>
       <c r="AI24" t="inlineStr"/>
       <c r="AJ24" t="inlineStr"/>
       <c r="AK24" t="inlineStr"/>
@@ -5251,40 +5239,40 @@
       <c r="AM24" t="inlineStr"/>
       <c r="AN24" t="inlineStr"/>
       <c r="AO24" t="n">
-        <v>25.13636363636364</v>
+        <v>30.14285714285714</v>
       </c>
       <c r="AP24" t="n">
-        <v>183.6818181818182</v>
+        <v>183.4285714285714</v>
       </c>
       <c r="AQ24" t="n">
         <v>1</v>
       </c>
       <c r="AR24" t="n">
-        <v>66.59090909090909</v>
+        <v>68.14285714285714</v>
       </c>
       <c r="AS24" t="n">
-        <v>1270454.545454545</v>
+        <v>1157142.857142857</v>
       </c>
       <c r="AT24" t="n">
-        <v>71.13636363636364</v>
+        <v>68.14285714285714</v>
       </c>
       <c r="AU24" t="n">
-        <v>21.16666666666667</v>
+        <v>25.88888888888889</v>
       </c>
       <c r="AV24" t="n">
-        <v>181.0833333333333</v>
+        <v>182.7777777777778</v>
       </c>
       <c r="AW24" t="n">
         <v>1</v>
       </c>
       <c r="AX24" t="n">
-        <v>63.33333333333334</v>
+        <v>68.16666666666667</v>
       </c>
       <c r="AY24" t="n">
-        <v>1143750</v>
+        <v>1959722.222222222</v>
       </c>
       <c r="AZ24" t="n">
-        <v>74</v>
+        <v>72.94444444444444</v>
       </c>
       <c r="BA24" t="inlineStr"/>
       <c r="BB24" t="inlineStr"/>
@@ -5304,7 +5292,7 @@
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>fHO9ROsn</t>
+          <t>GUXb5YQq</t>
         </is>
       </c>
       <c r="B25" s="2" t="n">
@@ -5312,72 +5300,72 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t xml:space="preserve">bonacina k 
+          <t xml:space="preserve">massimi l 
   ita </t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio benito stirpe
-  frosinone </t>
+          <t xml:space="preserve">stadio renzo barbera
+  palermo </t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>16227</v>
+        <v>36349</v>
       </c>
       <c r="F25" t="n">
-        <v>10755</v>
+        <v>25787</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>pfo9H1Wp</t>
+          <t>n38Nktmn</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>hKSfjtsQ</t>
+          <t>p84TeBhA</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="N25" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="O25" t="n">
+        <v>22</v>
+      </c>
+      <c r="P25" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q25" t="n">
         <v>9</v>
-      </c>
-      <c r="P25" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>3</v>
       </c>
       <c r="R25" t="n">
         <v>3</v>
       </c>
       <c r="S25" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="T25" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>dnLs0wVo</t>
+          <t>Wn0poKgt</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>tvh4IkLf</t>
+          <t>Yika9O16</t>
         </is>
       </c>
       <c r="W25" t="n">
@@ -5394,69 +5382,85 @@
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>0M9xNN8N</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr"/>
+          <t>pfo9H1Wp</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>GnizyMB7</t>
+        </is>
+      </c>
       <c r="AC25" t="n">
-        <v>22.33333333333333</v>
+        <v>24.63636363636364</v>
       </c>
       <c r="AD25" t="n">
-        <v>184.7777777777778</v>
+        <v>182.4545454545455</v>
       </c>
       <c r="AE25" t="n">
         <v>1</v>
       </c>
       <c r="AF25" t="n">
-        <v>66.11111111111111</v>
+        <v>70.54545454545455</v>
       </c>
       <c r="AG25" t="n">
-        <v>1561111.111111111</v>
+        <v>3000000</v>
       </c>
       <c r="AH25" t="n">
-        <v>74</v>
-      </c>
-      <c r="AI25" t="inlineStr"/>
-      <c r="AJ25" t="inlineStr"/>
-      <c r="AK25" t="inlineStr"/>
-      <c r="AL25" t="inlineStr"/>
-      <c r="AM25" t="inlineStr"/>
-      <c r="AN25" t="inlineStr"/>
+        <v>76.18181818181819</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>185.3</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>65.90000000000001</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>1127500</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>71.8</v>
+      </c>
       <c r="AO25" t="n">
-        <v>23.22727272727273</v>
+        <v>24.375</v>
       </c>
       <c r="AP25" t="n">
-        <v>183.8181818181818</v>
+        <v>184.5833333333333</v>
       </c>
       <c r="AQ25" t="n">
         <v>1</v>
       </c>
       <c r="AR25" t="n">
-        <v>67.31818181818181</v>
+        <v>69.33333333333333</v>
       </c>
       <c r="AS25" t="n">
-        <v>1904545.454545455</v>
+        <v>2543750</v>
       </c>
       <c r="AT25" t="n">
-        <v>74.36363636363636</v>
+        <v>74.625</v>
       </c>
       <c r="AU25" t="n">
-        <v>21</v>
+        <v>24.36363636363636</v>
       </c>
       <c r="AV25" t="n">
-        <v>186.4</v>
+        <v>180.3636363636364</v>
       </c>
       <c r="AW25" t="n">
         <v>1</v>
       </c>
       <c r="AX25" t="n">
-        <v>63.2</v>
+        <v>66.22727272727273</v>
       </c>
       <c r="AY25" t="n">
-        <v>1040000</v>
+        <v>1332954.545454545</v>
       </c>
       <c r="AZ25" t="n">
-        <v>72</v>
+        <v>71.95454545454545</v>
       </c>
       <c r="BA25" t="inlineStr"/>
       <c r="BB25" t="inlineStr"/>
@@ -5476,7 +5480,7 @@
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>jqIIP2Cb</t>
+          <t>fHO9ROsn</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -5484,72 +5488,72 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t xml:space="preserve">abisso r 
+          <t xml:space="preserve">bonacina k 
   ita </t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio danilo martelli
-  mantova </t>
+          <t xml:space="preserve">stadio benito stirpe
+  frosinone </t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5423</v>
+        <v>16227</v>
       </c>
       <c r="F26" t="n">
-        <v>8651</v>
+        <v>10755</v>
       </c>
       <c r="G26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>z7WK5Pwb</t>
+          <t>pfo9H1Wp</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Mq05g4BP</t>
+          <t>hKSfjtsQ</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="n">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="N26" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="O26" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="P26" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S26" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="T26" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>hrkecaMB</t>
+          <t>dnLs0wVo</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>OjWmexQb</t>
+          <t>tvh4IkLf</t>
         </is>
       </c>
       <c r="W26" t="n">
@@ -5564,18 +5568,30 @@
       <c r="Z26" t="n">
         <v>20242025</v>
       </c>
-      <c r="AA26" t="inlineStr"/>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>69Dxbc61</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr"/>
-      <c r="AD26" t="inlineStr"/>
-      <c r="AE26" t="inlineStr"/>
-      <c r="AF26" t="inlineStr"/>
-      <c r="AG26" t="inlineStr"/>
-      <c r="AH26" t="inlineStr"/>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>0M9xNN8N</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr"/>
+      <c r="AC26" t="n">
+        <v>22.33333333333333</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>184.7777777777778</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>66.11111111111111</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>1561111.111111111</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>74</v>
+      </c>
       <c r="AI26" t="inlineStr"/>
       <c r="AJ26" t="inlineStr"/>
       <c r="AK26" t="inlineStr"/>
@@ -5583,40 +5599,40 @@
       <c r="AM26" t="inlineStr"/>
       <c r="AN26" t="inlineStr"/>
       <c r="AO26" t="n">
-        <v>30.14285714285714</v>
+        <v>23.22727272727273</v>
       </c>
       <c r="AP26" t="n">
-        <v>183.4285714285714</v>
+        <v>183.8181818181818</v>
       </c>
       <c r="AQ26" t="n">
         <v>1</v>
       </c>
       <c r="AR26" t="n">
-        <v>68.14285714285714</v>
+        <v>67.31818181818181</v>
       </c>
       <c r="AS26" t="n">
-        <v>1157142.857142857</v>
+        <v>1904545.454545455</v>
       </c>
       <c r="AT26" t="n">
-        <v>68.14285714285714</v>
+        <v>74.36363636363636</v>
       </c>
       <c r="AU26" t="n">
-        <v>25.88888888888889</v>
+        <v>21</v>
       </c>
       <c r="AV26" t="n">
-        <v>182.7777777777778</v>
+        <v>186.4</v>
       </c>
       <c r="AW26" t="n">
         <v>1</v>
       </c>
       <c r="AX26" t="n">
-        <v>68.16666666666667</v>
+        <v>63.2</v>
       </c>
       <c r="AY26" t="n">
-        <v>1959722.222222222</v>
+        <v>1040000</v>
       </c>
       <c r="AZ26" t="n">
-        <v>72.94444444444444</v>
+        <v>72</v>
       </c>
       <c r="BA26" t="inlineStr"/>
       <c r="BB26" t="inlineStr"/>
@@ -5636,7 +5652,7 @@
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>GUXb5YQq</t>
+          <t>v5l07LdU</t>
         </is>
       </c>
       <c r="B27" s="2" t="n">
@@ -5644,72 +5660,72 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t xml:space="preserve">massimi l 
+          <t xml:space="preserve">perenzoni d 
   ita </t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio renzo barbera
-  palermo </t>
+          <t xml:space="preserve">stadio nicola ceravolo
+  catanzaro </t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>36349</v>
+        <v>14650</v>
       </c>
       <c r="F27" t="n">
-        <v>25787</v>
+        <v>9348</v>
       </c>
       <c r="G27" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H27" t="n">
         <v>1</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>n38Nktmn</t>
+          <t>GnizyMB7</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>p84TeBhA</t>
+          <t>hG4fg4z3</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="n">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="N27" t="n">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="O27" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="P27" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="Q27" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="R27" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S27" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T27" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>Wn0poKgt</t>
+          <t>nsYMfLJM</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>Yika9O16</t>
+          <t>lSb6U6l0</t>
         </is>
       </c>
       <c r="W27" t="n">
@@ -5726,85 +5742,69 @@
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>pfo9H1Wp</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>GnizyMB7</t>
-        </is>
-      </c>
+          <t>p84TeBhA</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr"/>
       <c r="AC27" t="n">
-        <v>24.63636363636364</v>
+        <v>27.8</v>
       </c>
       <c r="AD27" t="n">
-        <v>182.4545454545455</v>
+        <v>181</v>
       </c>
       <c r="AE27" t="n">
         <v>1</v>
       </c>
       <c r="AF27" t="n">
-        <v>70.54545454545455</v>
+        <v>66.8</v>
       </c>
       <c r="AG27" t="n">
-        <v>3000000</v>
+        <v>1057500</v>
       </c>
       <c r="AH27" t="n">
-        <v>76.18181818181819</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>24.8</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>185.3</v>
-      </c>
-      <c r="AK27" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL27" t="n">
-        <v>65.90000000000001</v>
-      </c>
-      <c r="AM27" t="n">
-        <v>1127500</v>
-      </c>
-      <c r="AN27" t="n">
-        <v>71.8</v>
-      </c>
+        <v>68.59999999999999</v>
+      </c>
+      <c r="AI27" t="inlineStr"/>
+      <c r="AJ27" t="inlineStr"/>
+      <c r="AK27" t="inlineStr"/>
+      <c r="AL27" t="inlineStr"/>
+      <c r="AM27" t="inlineStr"/>
+      <c r="AN27" t="inlineStr"/>
       <c r="AO27" t="n">
-        <v>24.375</v>
+        <v>25.13636363636364</v>
       </c>
       <c r="AP27" t="n">
-        <v>184.5833333333333</v>
+        <v>183.6818181818182</v>
       </c>
       <c r="AQ27" t="n">
         <v>1</v>
       </c>
       <c r="AR27" t="n">
-        <v>69.33333333333333</v>
+        <v>66.59090909090909</v>
       </c>
       <c r="AS27" t="n">
-        <v>2543750</v>
+        <v>1270454.545454545</v>
       </c>
       <c r="AT27" t="n">
-        <v>74.625</v>
+        <v>71.13636363636364</v>
       </c>
       <c r="AU27" t="n">
-        <v>24.36363636363636</v>
+        <v>21.16666666666667</v>
       </c>
       <c r="AV27" t="n">
-        <v>180.3636363636364</v>
+        <v>181.0833333333333</v>
       </c>
       <c r="AW27" t="n">
         <v>1</v>
       </c>
       <c r="AX27" t="n">
-        <v>66.22727272727273</v>
+        <v>63.33333333333334</v>
       </c>
       <c r="AY27" t="n">
-        <v>1332954.545454545</v>
+        <v>1143750</v>
       </c>
       <c r="AZ27" t="n">
-        <v>71.95454545454545</v>
+        <v>74</v>
       </c>
       <c r="BA27" t="inlineStr"/>
       <c r="BB27" t="inlineStr"/>
@@ -5996,7 +5996,7 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>nZgYbEaC</t>
+          <t>r1mschUO</t>
         </is>
       </c>
       <c r="B29" s="2" t="n">
@@ -6004,76 +6004,76 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t xml:space="preserve">colombo a 
+          <t xml:space="preserve">ayroldi g 
   ita </t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio artemio franchi
-  florence </t>
+          <t xml:space="preserve">stadio luigi ferraris
+  genoa </t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>43147</v>
+        <v>36599</v>
       </c>
       <c r="F29" t="n">
-        <v>18376</v>
+        <v>30747</v>
       </c>
       <c r="G29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
         <v>2</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Q3A3IbXH</t>
+          <t>d0PJxeie</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>4YSMlwj7</t>
+          <t>rJVAIaHo</t>
         </is>
       </c>
       <c r="K29" t="n">
-        <v>1.31</v>
+        <v>1.59</v>
       </c>
       <c r="L29" t="n">
-        <v>0.21</v>
+        <v>1.72</v>
       </c>
       <c r="M29" t="n">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="N29" t="n">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="O29" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="P29" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="Q29" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="R29" t="n">
         <v>3</v>
       </c>
       <c r="S29" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T29" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>619UPLrb</t>
+          <t>tSiEeKvS</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>CEv2hvmq</t>
+          <t>OW6PtuKn</t>
         </is>
       </c>
       <c r="W29" t="n">
@@ -6090,133 +6090,133 @@
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>C06aJvIB</t>
+          <t>nJbCGx2U</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>ttyLthOA</t>
+          <t>69Dxbc61</t>
         </is>
       </c>
       <c r="AC29" t="n">
-        <v>25.6</v>
+        <v>26.18181818181818</v>
       </c>
       <c r="AD29" t="n">
-        <v>183.5</v>
+        <v>183.5454545454545</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.6</v>
+        <v>1.181818181818182</v>
       </c>
       <c r="AF29" t="n">
-        <v>75.5</v>
+        <v>73.45454545454545</v>
       </c>
       <c r="AG29" t="n">
-        <v>12180000</v>
+        <v>5572727.272727272</v>
       </c>
       <c r="AH29" t="n">
-        <v>79.7</v>
+        <v>78</v>
       </c>
       <c r="AI29" t="n">
-        <v>25</v>
+        <v>24.55555555555556</v>
       </c>
       <c r="AJ29" t="n">
-        <v>183.9</v>
+        <v>182.6666666666667</v>
       </c>
       <c r="AK29" t="n">
-        <v>1.4</v>
+        <v>1.111111111111111</v>
       </c>
       <c r="AL29" t="n">
-        <v>72.59999999999999</v>
+        <v>72.33333333333333</v>
       </c>
       <c r="AM29" t="n">
-        <v>5430000</v>
+        <v>4600000</v>
       </c>
       <c r="AN29" t="n">
-        <v>77.5</v>
+        <v>77.44444444444444</v>
       </c>
       <c r="AO29" t="n">
-        <v>23.26923076923077</v>
+        <v>27.42105263157895</v>
       </c>
       <c r="AP29" t="n">
-        <v>182.2307692307692</v>
+        <v>183.2105263157895</v>
       </c>
       <c r="AQ29" t="n">
-        <v>1.423076923076923</v>
+        <v>1.526315789473684</v>
       </c>
       <c r="AR29" t="n">
-        <v>74.38461538461539</v>
+        <v>71.21052631578948</v>
       </c>
       <c r="AS29" t="n">
-        <v>10907692.30769231</v>
+        <v>4819736.842105263</v>
       </c>
       <c r="AT29" t="n">
-        <v>80.53846153846153</v>
+        <v>73.21052631578948</v>
       </c>
       <c r="AU29" t="n">
-        <v>26.91666666666667</v>
+        <v>24.75</v>
       </c>
       <c r="AV29" t="n">
-        <v>183.3333333333333</v>
+        <v>184.0416666666667</v>
       </c>
       <c r="AW29" t="n">
-        <v>1.541666666666667</v>
+        <v>1.041666666666667</v>
       </c>
       <c r="AX29" t="n">
-        <v>71.91666666666667</v>
+        <v>71.125</v>
       </c>
       <c r="AY29" t="n">
-        <v>3630208.333333333</v>
+        <v>3532291.666666667</v>
       </c>
       <c r="AZ29" t="n">
-        <v>76.04166666666667</v>
+        <v>75.91666666666667</v>
       </c>
       <c r="BA29" t="n">
-        <v>26</v>
+        <v>21.33333333333333</v>
       </c>
       <c r="BB29" t="n">
-        <v>178</v>
+        <v>186.1666666666667</v>
       </c>
       <c r="BC29" t="n">
         <v>1</v>
       </c>
       <c r="BD29" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="BE29" t="n">
-        <v>79</v>
+        <v>410</v>
       </c>
       <c r="BF29" t="n">
-        <v>21000000</v>
+        <v>24650000</v>
       </c>
       <c r="BG29" t="n">
-        <v>80</v>
+        <v>474</v>
       </c>
       <c r="BH29" t="n">
-        <v>28.5</v>
+        <v>24.5</v>
       </c>
       <c r="BI29" t="n">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="BJ29" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="BK29" t="n">
         <v>2</v>
       </c>
       <c r="BL29" t="n">
-        <v>152</v>
+        <v>142</v>
       </c>
       <c r="BM29" t="n">
-        <v>16900000</v>
+        <v>10900000</v>
       </c>
       <c r="BN29" t="n">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>r1mschUO</t>
+          <t>nZgYbEaC</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -6224,76 +6224,76 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t xml:space="preserve">ayroldi g 
+          <t xml:space="preserve">colombo a 
   ita </t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio luigi ferraris
-  genoa </t>
+          <t xml:space="preserve">stadio artemio franchi
+  florence </t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>36599</v>
+        <v>43147</v>
       </c>
       <c r="F30" t="n">
-        <v>30747</v>
+        <v>18376</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H30" t="n">
         <v>2</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>d0PJxeie</t>
+          <t>Q3A3IbXH</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>rJVAIaHo</t>
+          <t>4YSMlwj7</t>
         </is>
       </c>
       <c r="K30" t="n">
-        <v>1.59</v>
+        <v>1.31</v>
       </c>
       <c r="L30" t="n">
-        <v>1.72</v>
+        <v>0.21</v>
       </c>
       <c r="M30" t="n">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="N30" t="n">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="O30" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="P30" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="Q30" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="R30" t="n">
         <v>3</v>
       </c>
       <c r="S30" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T30" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>tSiEeKvS</t>
+          <t>619UPLrb</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>OW6PtuKn</t>
+          <t>CEv2hvmq</t>
         </is>
       </c>
       <c r="W30" t="n">
@@ -6310,127 +6310,127 @@
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>nJbCGx2U</t>
+          <t>C06aJvIB</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>69Dxbc61</t>
+          <t>ttyLthOA</t>
         </is>
       </c>
       <c r="AC30" t="n">
-        <v>26.18181818181818</v>
+        <v>25.6</v>
       </c>
       <c r="AD30" t="n">
-        <v>183.5454545454545</v>
+        <v>183.5</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.181818181818182</v>
+        <v>1.6</v>
       </c>
       <c r="AF30" t="n">
-        <v>73.45454545454545</v>
+        <v>75.5</v>
       </c>
       <c r="AG30" t="n">
-        <v>5572727.272727272</v>
+        <v>12180000</v>
       </c>
       <c r="AH30" t="n">
-        <v>78</v>
+        <v>79.7</v>
       </c>
       <c r="AI30" t="n">
-        <v>24.55555555555556</v>
+        <v>25</v>
       </c>
       <c r="AJ30" t="n">
-        <v>182.6666666666667</v>
+        <v>183.9</v>
       </c>
       <c r="AK30" t="n">
-        <v>1.111111111111111</v>
+        <v>1.4</v>
       </c>
       <c r="AL30" t="n">
-        <v>72.33333333333333</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="AM30" t="n">
-        <v>4600000</v>
+        <v>5430000</v>
       </c>
       <c r="AN30" t="n">
-        <v>77.44444444444444</v>
+        <v>77.5</v>
       </c>
       <c r="AO30" t="n">
-        <v>27.42105263157895</v>
+        <v>23.26923076923077</v>
       </c>
       <c r="AP30" t="n">
-        <v>183.2105263157895</v>
+        <v>182.2307692307692</v>
       </c>
       <c r="AQ30" t="n">
-        <v>1.526315789473684</v>
+        <v>1.423076923076923</v>
       </c>
       <c r="AR30" t="n">
-        <v>71.21052631578948</v>
+        <v>74.38461538461539</v>
       </c>
       <c r="AS30" t="n">
-        <v>4819736.842105263</v>
+        <v>10907692.30769231</v>
       </c>
       <c r="AT30" t="n">
-        <v>73.21052631578948</v>
+        <v>80.53846153846153</v>
       </c>
       <c r="AU30" t="n">
-        <v>24.75</v>
+        <v>26.91666666666667</v>
       </c>
       <c r="AV30" t="n">
-        <v>184.0416666666667</v>
+        <v>183.3333333333333</v>
       </c>
       <c r="AW30" t="n">
-        <v>1.041666666666667</v>
+        <v>1.541666666666667</v>
       </c>
       <c r="AX30" t="n">
-        <v>71.125</v>
+        <v>71.91666666666667</v>
       </c>
       <c r="AY30" t="n">
-        <v>3532291.666666667</v>
+        <v>3630208.333333333</v>
       </c>
       <c r="AZ30" t="n">
-        <v>75.91666666666667</v>
+        <v>76.04166666666667</v>
       </c>
       <c r="BA30" t="n">
-        <v>21.33333333333333</v>
+        <v>26</v>
       </c>
       <c r="BB30" t="n">
-        <v>186.1666666666667</v>
+        <v>178</v>
       </c>
       <c r="BC30" t="n">
         <v>1</v>
       </c>
       <c r="BD30" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="BE30" t="n">
-        <v>410</v>
+        <v>79</v>
       </c>
       <c r="BF30" t="n">
-        <v>24650000</v>
+        <v>21000000</v>
       </c>
       <c r="BG30" t="n">
-        <v>474</v>
+        <v>80</v>
       </c>
       <c r="BH30" t="n">
-        <v>24.5</v>
+        <v>28.5</v>
       </c>
       <c r="BI30" t="n">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="BJ30" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="BK30" t="n">
         <v>2</v>
       </c>
       <c r="BL30" t="n">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="BM30" t="n">
-        <v>10900000</v>
+        <v>16900000</v>
       </c>
       <c r="BN30" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="31">
@@ -6862,7 +6862,7 @@
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>21OYHBAk</t>
+          <t>CGH1PgIF</t>
         </is>
       </c>
       <c r="B33" s="2" t="n">
@@ -6870,72 +6870,72 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t xml:space="preserve">rutella d 
+          <t xml:space="preserve">manganiello g 
   ita </t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio marco druso
-  bolzano </t>
+          <t xml:space="preserve">mapei stadium – citta del tricolore
+  reggio emilia </t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5539</v>
+        <v>21525</v>
       </c>
       <c r="F33" t="n">
-        <v>4065</v>
+        <v>4752</v>
       </c>
       <c r="G33" t="n">
         <v>1</v>
       </c>
       <c r="H33" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>W02MZDnp</t>
+          <t>QDdvI0zl</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>jci0qO9B</t>
+          <t>KUzfp5N3</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="n">
-        <v>67</v>
+        <v>50</v>
       </c>
       <c r="N33" t="n">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="O33" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="P33" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="Q33" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="R33" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="S33" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="T33" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>bmzifXwb</t>
+          <t>bPHSQi9q</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>lb1XFX3n</t>
+          <t>YgLhKnOo</t>
         </is>
       </c>
       <c r="W33" t="n">
@@ -6952,85 +6952,85 @@
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>rXw8YKDE</t>
+          <t>0M9xNN8N</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>8C9JjMXu</t>
+          <t>ttyLthOA</t>
         </is>
       </c>
       <c r="AC33" t="n">
-        <v>28.9</v>
+        <v>23</v>
       </c>
       <c r="AD33" t="n">
-        <v>183.5</v>
+        <v>185.7</v>
       </c>
       <c r="AE33" t="n">
         <v>1.1</v>
       </c>
       <c r="AF33" t="n">
-        <v>67.90000000000001</v>
+        <v>69.2</v>
       </c>
       <c r="AG33" t="n">
-        <v>1081000</v>
+        <v>3277500</v>
       </c>
       <c r="AH33" t="n">
-        <v>69.90000000000001</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="AI33" t="n">
-        <v>24.88888888888889</v>
+        <v>25.4</v>
       </c>
       <c r="AJ33" t="n">
-        <v>182.4444444444445</v>
+        <v>184.2</v>
       </c>
       <c r="AK33" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="AL33" t="n">
-        <v>67.11111111111111</v>
+        <v>69.7</v>
       </c>
       <c r="AM33" t="n">
-        <v>1408333.333333333</v>
+        <v>2210000</v>
       </c>
       <c r="AN33" t="n">
-        <v>71.88888888888889</v>
+        <v>74</v>
       </c>
       <c r="AO33" t="n">
-        <v>23.57142857142857</v>
+        <v>22.75</v>
       </c>
       <c r="AP33" t="n">
-        <v>184.7142857142857</v>
+        <v>182.25</v>
       </c>
       <c r="AQ33" t="n">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR33" t="n">
-        <v>65.33333333333333</v>
+        <v>67.3</v>
       </c>
       <c r="AS33" t="n">
-        <v>1263095.238095238</v>
+        <v>2145000</v>
       </c>
       <c r="AT33" t="n">
-        <v>71.04761904761905</v>
+        <v>74.5</v>
       </c>
       <c r="AU33" t="n">
-        <v>23.41176470588235</v>
+        <v>26.52173913043478</v>
       </c>
       <c r="AV33" t="n">
-        <v>181.7058823529412</v>
+        <v>182.9565217391304</v>
       </c>
       <c r="AW33" t="n">
-        <v>1</v>
+        <v>1.043478260869565</v>
       </c>
       <c r="AX33" t="n">
-        <v>64.17647058823529</v>
+        <v>69.73913043478261</v>
       </c>
       <c r="AY33" t="n">
-        <v>1038235.294117647</v>
+        <v>1930434.782608696</v>
       </c>
       <c r="AZ33" t="n">
-        <v>71.11764705882354</v>
+        <v>72.39130434782609</v>
       </c>
       <c r="BA33" t="inlineStr"/>
       <c r="BB33" t="inlineStr"/>
@@ -7050,7 +7050,7 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>CGH1PgIF</t>
+          <t>Ofy73Ced</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -7058,72 +7058,72 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t xml:space="preserve">manganiello g 
+          <t xml:space="preserve">galipo s 
   ita </t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapei stadium – citta del tricolore
-  reggio emilia </t>
+          <t xml:space="preserve">arena garibaldi   stadio romeo anconetani
+  pisa </t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>21525</v>
+        <v>14869</v>
       </c>
       <c r="F34" t="n">
-        <v>4752</v>
+        <v>8359</v>
       </c>
       <c r="G34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H34" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>QDdvI0zl</t>
+          <t>roasMsOT</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>KUzfp5N3</t>
+          <t>6ulJbMCe</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="n">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="N34" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="O34" t="n">
+        <v>15</v>
+      </c>
+      <c r="P34" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>5</v>
+      </c>
+      <c r="R34" t="n">
+        <v>5</v>
+      </c>
+      <c r="S34" t="n">
         <v>12</v>
       </c>
-      <c r="P34" t="n">
-        <v>11</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>4</v>
-      </c>
-      <c r="R34" t="n">
-        <v>6</v>
-      </c>
-      <c r="S34" t="n">
-        <v>15</v>
-      </c>
       <c r="T34" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>bPHSQi9q</t>
+          <t>GfucctAF</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>YgLhKnOo</t>
+          <t>Gfur2NmR</t>
         </is>
       </c>
       <c r="W34" t="n">
@@ -7140,85 +7140,81 @@
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>0M9xNN8N</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>ttyLthOA</t>
-        </is>
-      </c>
+          <t>Q3A3IbXH</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr"/>
       <c r="AC34" t="n">
-        <v>23</v>
+        <v>23.90909090909091</v>
       </c>
       <c r="AD34" t="n">
-        <v>185.7</v>
+        <v>185.3636363636364</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AF34" t="n">
-        <v>69.2</v>
+        <v>67</v>
       </c>
       <c r="AG34" t="n">
-        <v>3277500</v>
+        <v>1609090.909090909</v>
       </c>
       <c r="AH34" t="n">
-        <v>75.59999999999999</v>
+        <v>72.36363636363636</v>
       </c>
       <c r="AI34" t="n">
-        <v>25.4</v>
+        <v>25.5</v>
       </c>
       <c r="AJ34" t="n">
-        <v>184.2</v>
+        <v>182.9</v>
       </c>
       <c r="AK34" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AL34" t="n">
-        <v>69.7</v>
+        <v>64.5</v>
       </c>
       <c r="AM34" t="n">
-        <v>2210000</v>
+        <v>1119000</v>
       </c>
       <c r="AN34" t="n">
-        <v>74</v>
+        <v>68.8</v>
       </c>
       <c r="AO34" t="n">
-        <v>22.75</v>
+        <v>24.27272727272727</v>
       </c>
       <c r="AP34" t="n">
-        <v>182.25</v>
+        <v>182.9545454545455</v>
       </c>
       <c r="AQ34" t="n">
-        <v>1.15</v>
+        <v>1</v>
       </c>
       <c r="AR34" t="n">
-        <v>67.3</v>
+        <v>65.45454545454545</v>
       </c>
       <c r="AS34" t="n">
-        <v>2145000</v>
+        <v>1348863.636363636</v>
       </c>
       <c r="AT34" t="n">
-        <v>74.5</v>
+        <v>71.72727272727273</v>
       </c>
       <c r="AU34" t="n">
-        <v>26.52173913043478</v>
+        <v>25.31578947368421</v>
       </c>
       <c r="AV34" t="n">
-        <v>182.9565217391304</v>
+        <v>182.3684210526316</v>
       </c>
       <c r="AW34" t="n">
-        <v>1.043478260869565</v>
+        <v>1</v>
       </c>
       <c r="AX34" t="n">
-        <v>69.73913043478261</v>
+        <v>64.84210526315789</v>
       </c>
       <c r="AY34" t="n">
-        <v>1930434.782608696</v>
+        <v>1098157.894736842</v>
       </c>
       <c r="AZ34" t="n">
-        <v>72.39130434782609</v>
+        <v>69.05263157894737</v>
       </c>
       <c r="BA34" t="inlineStr"/>
       <c r="BB34" t="inlineStr"/>
@@ -7238,7 +7234,7 @@
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>Ofy73Ced</t>
+          <t>dtLQNtsB</t>
         </is>
       </c>
       <c r="B35" s="2" t="n">
@@ -7246,72 +7242,72 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t xml:space="preserve">galipo s 
+          <t xml:space="preserve">cosso f 
   ita </t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">arena garibaldi   stadio romeo anconetani
-  pisa </t>
+          <t xml:space="preserve">stadio alberto braglia
+  modena </t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>14869</v>
+        <v>21092</v>
       </c>
       <c r="F35" t="n">
-        <v>8359</v>
+        <v>8928</v>
       </c>
       <c r="G35" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
         <v>1</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>roasMsOT</t>
+          <t>MBn63swN</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>6ulJbMCe</t>
+          <t>C0yUqo8c</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="n">
-        <v>35</v>
+        <v>58</v>
       </c>
       <c r="N35" t="n">
-        <v>65</v>
+        <v>42</v>
       </c>
       <c r="O35" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="P35" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Q35" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R35" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S35" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="T35" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>GfucctAF</t>
+          <t>YTZ7S7pk</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>Gfur2NmR</t>
+          <t>8dDPzPa7</t>
         </is>
       </c>
       <c r="W35" t="n">
@@ -7328,81 +7324,85 @@
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>Q3A3IbXH</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr"/>
+          <t>0M9xNN8N</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>MkPmVv50</t>
+        </is>
+      </c>
       <c r="AC35" t="n">
-        <v>23.90909090909091</v>
+        <v>26.4</v>
       </c>
       <c r="AD35" t="n">
-        <v>185.3636363636364</v>
+        <v>183.8</v>
       </c>
       <c r="AE35" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="AF35" t="n">
-        <v>67</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="AG35" t="n">
-        <v>1609090.909090909</v>
+        <v>1467500</v>
       </c>
       <c r="AH35" t="n">
-        <v>72.36363636363636</v>
+        <v>71.3</v>
       </c>
       <c r="AI35" t="n">
-        <v>25.5</v>
+        <v>26.66666666666667</v>
       </c>
       <c r="AJ35" t="n">
-        <v>182.9</v>
+        <v>182.4444444444445</v>
       </c>
       <c r="AK35" t="n">
         <v>1</v>
       </c>
       <c r="AL35" t="n">
-        <v>64.5</v>
+        <v>66.77777777777777</v>
       </c>
       <c r="AM35" t="n">
-        <v>1119000</v>
+        <v>1100000</v>
       </c>
       <c r="AN35" t="n">
-        <v>68.8</v>
+        <v>69.66666666666667</v>
       </c>
       <c r="AO35" t="n">
-        <v>24.27272727272727</v>
+        <v>25.34782608695652</v>
       </c>
       <c r="AP35" t="n">
-        <v>182.9545454545455</v>
+        <v>182.2173913043478</v>
       </c>
       <c r="AQ35" t="n">
-        <v>1</v>
+        <v>1.217391304347826</v>
       </c>
       <c r="AR35" t="n">
-        <v>65.45454545454545</v>
+        <v>65.78260869565217</v>
       </c>
       <c r="AS35" t="n">
-        <v>1348863.636363636</v>
+        <v>1167391.304347826</v>
       </c>
       <c r="AT35" t="n">
-        <v>71.72727272727273</v>
+        <v>70.43478260869566</v>
       </c>
       <c r="AU35" t="n">
-        <v>25.31578947368421</v>
+        <v>24.72727272727273</v>
       </c>
       <c r="AV35" t="n">
-        <v>182.3684210526316</v>
+        <v>181.1818181818182</v>
       </c>
       <c r="AW35" t="n">
         <v>1</v>
       </c>
       <c r="AX35" t="n">
-        <v>64.84210526315789</v>
+        <v>64.81818181818181</v>
       </c>
       <c r="AY35" t="n">
-        <v>1098157.894736842</v>
+        <v>1029545.454545455</v>
       </c>
       <c r="AZ35" t="n">
-        <v>69.05263157894737</v>
+        <v>70.72727272727273</v>
       </c>
       <c r="BA35" t="inlineStr"/>
       <c r="BB35" t="inlineStr"/>
@@ -7422,7 +7422,7 @@
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>dtLQNtsB</t>
+          <t>21OYHBAk</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -7430,72 +7430,72 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t xml:space="preserve">cosso f 
+          <t xml:space="preserve">rutella d 
   ita </t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio alberto braglia
-  modena </t>
+          <t xml:space="preserve">stadio marco druso
+  bolzano </t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>21092</v>
+        <v>5539</v>
       </c>
       <c r="F36" t="n">
-        <v>8928</v>
+        <v>4065</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>MBn63swN</t>
+          <t>W02MZDnp</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>C0yUqo8c</t>
+          <t>jci0qO9B</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="n">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="N36" t="n">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="O36" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="P36" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Q36" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R36" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S36" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="T36" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>YTZ7S7pk</t>
+          <t>bmzifXwb</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>8dDPzPa7</t>
+          <t>lb1XFX3n</t>
         </is>
       </c>
       <c r="W36" t="n">
@@ -7512,34 +7512,34 @@
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>0M9xNN8N</t>
+          <t>rXw8YKDE</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>MkPmVv50</t>
+          <t>8C9JjMXu</t>
         </is>
       </c>
       <c r="AC36" t="n">
-        <v>26.4</v>
+        <v>28.9</v>
       </c>
       <c r="AD36" t="n">
-        <v>183.8</v>
+        <v>183.5</v>
       </c>
       <c r="AE36" t="n">
         <v>1.1</v>
       </c>
       <c r="AF36" t="n">
-        <v>68.09999999999999</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="AG36" t="n">
-        <v>1467500</v>
+        <v>1081000</v>
       </c>
       <c r="AH36" t="n">
-        <v>71.3</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="AI36" t="n">
-        <v>26.66666666666667</v>
+        <v>24.88888888888889</v>
       </c>
       <c r="AJ36" t="n">
         <v>182.4444444444445</v>
@@ -7548,49 +7548,49 @@
         <v>1</v>
       </c>
       <c r="AL36" t="n">
-        <v>66.77777777777777</v>
+        <v>67.11111111111111</v>
       </c>
       <c r="AM36" t="n">
-        <v>1100000</v>
+        <v>1408333.333333333</v>
       </c>
       <c r="AN36" t="n">
-        <v>69.66666666666667</v>
+        <v>71.88888888888889</v>
       </c>
       <c r="AO36" t="n">
-        <v>25.34782608695652</v>
+        <v>23.57142857142857</v>
       </c>
       <c r="AP36" t="n">
-        <v>182.2173913043478</v>
+        <v>184.7142857142857</v>
       </c>
       <c r="AQ36" t="n">
-        <v>1.217391304347826</v>
+        <v>1</v>
       </c>
       <c r="AR36" t="n">
-        <v>65.78260869565217</v>
+        <v>65.33333333333333</v>
       </c>
       <c r="AS36" t="n">
-        <v>1167391.304347826</v>
+        <v>1263095.238095238</v>
       </c>
       <c r="AT36" t="n">
-        <v>70.43478260869566</v>
+        <v>71.04761904761905</v>
       </c>
       <c r="AU36" t="n">
-        <v>24.72727272727273</v>
+        <v>23.41176470588235</v>
       </c>
       <c r="AV36" t="n">
-        <v>181.1818181818182</v>
+        <v>181.7058823529412</v>
       </c>
       <c r="AW36" t="n">
         <v>1</v>
       </c>
       <c r="AX36" t="n">
-        <v>64.81818181818181</v>
+        <v>64.17647058823529</v>
       </c>
       <c r="AY36" t="n">
-        <v>1029545.454545455</v>
+        <v>1038235.294117647</v>
       </c>
       <c r="AZ36" t="n">
-        <v>70.72727272727273</v>
+        <v>71.11764705882354</v>
       </c>
       <c r="BA36" t="inlineStr"/>
       <c r="BB36" t="inlineStr"/>
@@ -7610,7 +7610,7 @@
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>d4DGBiqI</t>
+          <t>ELeQ0zVa</t>
         </is>
       </c>
       <c r="B37" s="2" t="n">
@@ -7618,76 +7618,76 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t xml:space="preserve">fabbri m 
+          <t xml:space="preserve">marinelli l 
   ita </t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio via del mare
-  lecce </t>
+          <t xml:space="preserve">stadio renato dall ara
+  bologna </t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>40670</v>
+        <v>38279</v>
       </c>
       <c r="F37" t="n">
-        <v>26386</v>
+        <v>25960</v>
       </c>
       <c r="G37" t="n">
         <v>1</v>
       </c>
       <c r="H37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>G8lYsMgU</t>
+          <t>0M9xNN8N</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>SCGVmKHb</t>
+          <t>0ESCnI1H</t>
         </is>
       </c>
       <c r="K37" t="n">
-        <v>2.25</v>
+        <v>1.81</v>
       </c>
       <c r="L37" t="n">
-        <v>1.75</v>
+        <v>0.89</v>
       </c>
       <c r="M37" t="n">
-        <v>35</v>
+        <v>68</v>
       </c>
       <c r="N37" t="n">
-        <v>65</v>
+        <v>32</v>
       </c>
       <c r="O37" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="P37" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="Q37" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R37" t="n">
         <v>2</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T37" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>KtGrCa5d</t>
+          <t>tjY4uUem</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>MLVBCoYg</t>
+          <t>MBrKQFV7</t>
         </is>
       </c>
       <c r="W37" t="n">
@@ -7704,119 +7704,133 @@
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>xIkUr2vO</t>
+          <t>Q3A3IbXH</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>69Dxbc61</t>
+          <t>Q3A3IbXH</t>
         </is>
       </c>
       <c r="AC37" t="n">
-        <v>24.4</v>
+        <v>24.90909090909091</v>
       </c>
       <c r="AD37" t="n">
-        <v>182</v>
+        <v>184.4545454545455</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.1</v>
+        <v>1.454545454545455</v>
       </c>
       <c r="AF37" t="n">
-        <v>72</v>
+        <v>75.27272727272727</v>
       </c>
       <c r="AG37" t="n">
-        <v>5120000</v>
+        <v>10018181.81818182</v>
       </c>
       <c r="AH37" t="n">
-        <v>77.2</v>
+        <v>79.81818181818181</v>
       </c>
       <c r="AI37" t="n">
-        <v>25.09090909090909</v>
+        <v>24.09090909090909</v>
       </c>
       <c r="AJ37" t="n">
-        <v>185.7272727272727</v>
+        <v>184.8181818181818</v>
       </c>
       <c r="AK37" t="n">
-        <v>1.090909090909091</v>
+        <v>1</v>
       </c>
       <c r="AL37" t="n">
-        <v>72.72727272727273</v>
+        <v>69.72727272727273</v>
       </c>
       <c r="AM37" t="n">
-        <v>4990909.090909091</v>
+        <v>2990000</v>
       </c>
       <c r="AN37" t="n">
-        <v>76.36363636363636</v>
+        <v>75.36363636363636</v>
       </c>
       <c r="AO37" t="n">
-        <v>23.5</v>
+        <v>23.89285714285714</v>
       </c>
       <c r="AP37" t="n">
-        <v>184.45</v>
+        <v>185.5357142857143</v>
       </c>
       <c r="AQ37" t="n">
-        <v>1.05</v>
+        <v>1.178571428571429</v>
       </c>
       <c r="AR37" t="n">
-        <v>68.34999999999999</v>
+        <v>71.21428571428571</v>
       </c>
       <c r="AS37" t="n">
-        <v>2887500</v>
+        <v>5394642.857142857</v>
       </c>
       <c r="AT37" t="n">
-        <v>74.5</v>
+        <v>77.78571428571429</v>
       </c>
       <c r="AU37" t="n">
-        <v>27.5</v>
+        <v>22.8695652173913</v>
       </c>
       <c r="AV37" t="n">
-        <v>183.3214285714286</v>
+        <v>183.7826086956522</v>
       </c>
       <c r="AW37" t="n">
-        <v>1.357142857142857</v>
+        <v>1</v>
       </c>
       <c r="AX37" t="n">
-        <v>70.10714285714286</v>
+        <v>69.60869565217391</v>
       </c>
       <c r="AY37" t="n">
-        <v>2147321.428571429</v>
+        <v>3240217.391304348</v>
       </c>
       <c r="AZ37" t="n">
-        <v>73.42857142857143</v>
+        <v>75.91304347826087</v>
       </c>
       <c r="BA37" t="n">
-        <v>24.33333333333333</v>
+        <v>23.16666666666667</v>
       </c>
       <c r="BB37" t="n">
-        <v>182</v>
+        <v>184.8333333333333</v>
       </c>
       <c r="BC37" t="n">
-        <v>1.333333333333333</v>
+        <v>1</v>
       </c>
       <c r="BD37" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="BE37" t="n">
-        <v>213</v>
+        <v>442</v>
       </c>
       <c r="BF37" t="n">
-        <v>10300000</v>
+        <v>58400000</v>
       </c>
       <c r="BG37" t="n">
-        <v>230</v>
-      </c>
-      <c r="BH37" t="inlineStr"/>
-      <c r="BI37" t="inlineStr"/>
-      <c r="BJ37" t="inlineStr"/>
-      <c r="BK37" t="inlineStr"/>
-      <c r="BL37" t="inlineStr"/>
-      <c r="BM37" t="inlineStr"/>
-      <c r="BN37" t="inlineStr"/>
+        <v>476</v>
+      </c>
+      <c r="BH37" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="BI37" t="n">
+        <v>187.2</v>
+      </c>
+      <c r="BJ37" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BK37" t="n">
+        <v>5</v>
+      </c>
+      <c r="BL37" t="n">
+        <v>352</v>
+      </c>
+      <c r="BM37" t="n">
+        <v>16425000</v>
+      </c>
+      <c r="BN37" t="n">
+        <v>368</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>ELeQ0zVa</t>
+          <t>d4DGBiqI</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -7824,76 +7838,76 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t xml:space="preserve">marinelli l 
+          <t xml:space="preserve">fabbri m 
   ita </t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio renato dall ara
-  bologna </t>
+          <t xml:space="preserve">stadio via del mare
+  lecce </t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>38279</v>
+        <v>40670</v>
       </c>
       <c r="F38" t="n">
-        <v>25960</v>
+        <v>26386</v>
       </c>
       <c r="G38" t="n">
         <v>1</v>
       </c>
       <c r="H38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>0M9xNN8N</t>
+          <t>G8lYsMgU</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>0ESCnI1H</t>
+          <t>SCGVmKHb</t>
         </is>
       </c>
       <c r="K38" t="n">
-        <v>1.81</v>
+        <v>2.25</v>
       </c>
       <c r="L38" t="n">
-        <v>0.89</v>
+        <v>1.75</v>
       </c>
       <c r="M38" t="n">
-        <v>68</v>
+        <v>35</v>
       </c>
       <c r="N38" t="n">
-        <v>32</v>
+        <v>65</v>
       </c>
       <c r="O38" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="P38" t="n">
+        <v>21</v>
+      </c>
+      <c r="Q38" t="n">
         <v>4</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>3</v>
       </c>
       <c r="R38" t="n">
         <v>2</v>
       </c>
       <c r="S38" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T38" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>tjY4uUem</t>
+          <t>KtGrCa5d</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>MBrKQFV7</t>
+          <t>MLVBCoYg</t>
         </is>
       </c>
       <c r="W38" t="n">
@@ -7910,128 +7924,114 @@
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>Q3A3IbXH</t>
+          <t>xIkUr2vO</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>Q3A3IbXH</t>
+          <t>69Dxbc61</t>
         </is>
       </c>
       <c r="AC38" t="n">
-        <v>24.90909090909091</v>
+        <v>24.4</v>
       </c>
       <c r="AD38" t="n">
-        <v>184.4545454545455</v>
+        <v>182</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.454545454545455</v>
+        <v>1.1</v>
       </c>
       <c r="AF38" t="n">
-        <v>75.27272727272727</v>
+        <v>72</v>
       </c>
       <c r="AG38" t="n">
-        <v>10018181.81818182</v>
+        <v>5120000</v>
       </c>
       <c r="AH38" t="n">
-        <v>79.81818181818181</v>
+        <v>77.2</v>
       </c>
       <c r="AI38" t="n">
-        <v>24.09090909090909</v>
+        <v>25.09090909090909</v>
       </c>
       <c r="AJ38" t="n">
-        <v>184.8181818181818</v>
+        <v>185.7272727272727</v>
       </c>
       <c r="AK38" t="n">
-        <v>1</v>
+        <v>1.090909090909091</v>
       </c>
       <c r="AL38" t="n">
-        <v>69.72727272727273</v>
+        <v>72.72727272727273</v>
       </c>
       <c r="AM38" t="n">
-        <v>2990000</v>
+        <v>4990909.090909091</v>
       </c>
       <c r="AN38" t="n">
-        <v>75.36363636363636</v>
+        <v>76.36363636363636</v>
       </c>
       <c r="AO38" t="n">
-        <v>23.89285714285714</v>
+        <v>23.5</v>
       </c>
       <c r="AP38" t="n">
-        <v>185.5357142857143</v>
+        <v>184.45</v>
       </c>
       <c r="AQ38" t="n">
-        <v>1.178571428571429</v>
+        <v>1.05</v>
       </c>
       <c r="AR38" t="n">
-        <v>71.21428571428571</v>
+        <v>68.34999999999999</v>
       </c>
       <c r="AS38" t="n">
-        <v>5394642.857142857</v>
+        <v>2887500</v>
       </c>
       <c r="AT38" t="n">
-        <v>77.78571428571429</v>
+        <v>74.5</v>
       </c>
       <c r="AU38" t="n">
-        <v>22.8695652173913</v>
+        <v>27.5</v>
       </c>
       <c r="AV38" t="n">
-        <v>183.7826086956522</v>
+        <v>183.3214285714286</v>
       </c>
       <c r="AW38" t="n">
-        <v>1</v>
+        <v>1.357142857142857</v>
       </c>
       <c r="AX38" t="n">
-        <v>69.60869565217391</v>
+        <v>70.10714285714286</v>
       </c>
       <c r="AY38" t="n">
-        <v>3240217.391304348</v>
+        <v>2147321.428571429</v>
       </c>
       <c r="AZ38" t="n">
-        <v>75.91304347826087</v>
+        <v>73.42857142857143</v>
       </c>
       <c r="BA38" t="n">
-        <v>23.16666666666667</v>
+        <v>24.33333333333333</v>
       </c>
       <c r="BB38" t="n">
-        <v>184.8333333333333</v>
+        <v>182</v>
       </c>
       <c r="BC38" t="n">
-        <v>1</v>
+        <v>1.333333333333333</v>
       </c>
       <c r="BD38" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="BE38" t="n">
-        <v>442</v>
+        <v>213</v>
       </c>
       <c r="BF38" t="n">
-        <v>58400000</v>
+        <v>10300000</v>
       </c>
       <c r="BG38" t="n">
-        <v>476</v>
-      </c>
-      <c r="BH38" t="n">
-        <v>25.8</v>
-      </c>
-      <c r="BI38" t="n">
-        <v>187.2</v>
-      </c>
-      <c r="BJ38" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="BK38" t="n">
-        <v>5</v>
-      </c>
-      <c r="BL38" t="n">
-        <v>352</v>
-      </c>
-      <c r="BM38" t="n">
-        <v>16425000</v>
-      </c>
-      <c r="BN38" t="n">
-        <v>368</v>
-      </c>
+        <v>230</v>
+      </c>
+      <c r="BH38" t="inlineStr"/>
+      <c r="BI38" t="inlineStr"/>
+      <c r="BJ38" t="inlineStr"/>
+      <c r="BK38" t="inlineStr"/>
+      <c r="BL38" t="inlineStr"/>
+      <c r="BM38" t="inlineStr"/>
+      <c r="BN38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
@@ -8664,7 +8664,7 @@
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>zVpmZBZQ</t>
+          <t>SSPRRTR0</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -8672,72 +8672,72 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t xml:space="preserve">collu g 
+          <t xml:space="preserve">di marco d 
   ita </t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio dino manuzzi
-  cesena </t>
+          <t xml:space="preserve">stadio san vito luigi marulla
+  cosenza </t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>23860</v>
+        <v>20987</v>
       </c>
       <c r="F42" t="n">
-        <v>11870</v>
+        <v>8006</v>
       </c>
       <c r="G42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H42" t="n">
         <v>0</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>xddf1qfh</t>
+          <t>p84TeBhA</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>GnizyMB7</t>
+          <t>re6VD39b</t>
         </is>
       </c>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
       <c r="M42" t="n">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="N42" t="n">
-        <v>66</v>
+        <v>39</v>
       </c>
       <c r="O42" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="P42" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="Q42" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="R42" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T42" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>vD8aDRIm</t>
+          <t>Yika9O16</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>nsYMfLJM</t>
+          <t>O6SinSSs</t>
         </is>
       </c>
       <c r="W42" t="n">
@@ -8752,71 +8752,87 @@
       <c r="Z42" t="n">
         <v>20242025</v>
       </c>
-      <c r="AA42" t="inlineStr"/>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>GnizyMB7</t>
+        </is>
+      </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>p84TeBhA</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr"/>
-      <c r="AD42" t="inlineStr"/>
-      <c r="AE42" t="inlineStr"/>
-      <c r="AF42" t="inlineStr"/>
-      <c r="AG42" t="inlineStr"/>
-      <c r="AH42" t="inlineStr"/>
+          <t>d0PJxeie</t>
+        </is>
+      </c>
+      <c r="AC42" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>184.9</v>
+      </c>
+      <c r="AE42" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>66.90000000000001</v>
+      </c>
+      <c r="AG42" t="n">
+        <v>1215000</v>
+      </c>
+      <c r="AH42" t="n">
+        <v>70.90000000000001</v>
+      </c>
       <c r="AI42" t="n">
-        <v>25.88888888888889</v>
+        <v>23.8</v>
       </c>
       <c r="AJ42" t="n">
-        <v>182.2222222222222</v>
+        <v>185.9</v>
       </c>
       <c r="AK42" t="n">
         <v>1</v>
       </c>
       <c r="AL42" t="n">
-        <v>66.55555555555556</v>
+        <v>66.5</v>
       </c>
       <c r="AM42" t="n">
-        <v>1175000</v>
+        <v>1495000</v>
       </c>
       <c r="AN42" t="n">
-        <v>70.44444444444444</v>
+        <v>72.2</v>
       </c>
       <c r="AO42" t="n">
-        <v>24</v>
+        <v>22.66666666666667</v>
       </c>
       <c r="AP42" t="n">
-        <v>180.4444444444445</v>
+        <v>179.2222222222222</v>
       </c>
       <c r="AQ42" t="n">
         <v>1</v>
       </c>
       <c r="AR42" t="n">
-        <v>66.33333333333333</v>
+        <v>64.22222222222223</v>
       </c>
       <c r="AS42" t="n">
-        <v>1352777.777777778</v>
+        <v>1156944.444444444</v>
       </c>
       <c r="AT42" t="n">
-        <v>71.33333333333333</v>
+        <v>73</v>
       </c>
       <c r="AU42" t="n">
-        <v>25.4375</v>
+        <v>25.5</v>
       </c>
       <c r="AV42" t="n">
-        <v>183.1875</v>
+        <v>183.3</v>
       </c>
       <c r="AW42" t="n">
         <v>1</v>
       </c>
       <c r="AX42" t="n">
-        <v>66</v>
+        <v>65.95</v>
       </c>
       <c r="AY42" t="n">
-        <v>1154687.5</v>
+        <v>1251250</v>
       </c>
       <c r="AZ42" t="n">
-        <v>69.625</v>
+        <v>71.25</v>
       </c>
       <c r="BA42" t="inlineStr"/>
       <c r="BB42" t="inlineStr"/>
@@ -8836,7 +8852,7 @@
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>SSPRRTR0</t>
+          <t>zVpmZBZQ</t>
         </is>
       </c>
       <c r="B43" s="2" t="n">
@@ -8844,72 +8860,72 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t xml:space="preserve">di marco d 
+          <t xml:space="preserve">collu g 
   ita </t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio san vito luigi marulla
-  cosenza </t>
+          <t xml:space="preserve">stadio dino manuzzi
+  cesena </t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>20987</v>
+        <v>23860</v>
       </c>
       <c r="F43" t="n">
-        <v>8006</v>
+        <v>11870</v>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H43" t="n">
         <v>0</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>p84TeBhA</t>
+          <t>xddf1qfh</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>re6VD39b</t>
+          <t>GnizyMB7</t>
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
       <c r="M43" t="n">
-        <v>61</v>
+        <v>34</v>
       </c>
       <c r="N43" t="n">
-        <v>39</v>
+        <v>66</v>
       </c>
       <c r="O43" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="P43" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="Q43" t="n">
+        <v>5</v>
+      </c>
+      <c r="R43" t="n">
         <v>2</v>
       </c>
-      <c r="R43" t="n">
-        <v>4</v>
-      </c>
       <c r="S43" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T43" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>Yika9O16</t>
+          <t>vD8aDRIm</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>O6SinSSs</t>
+          <t>nsYMfLJM</t>
         </is>
       </c>
       <c r="W43" t="n">
@@ -8924,87 +8940,71 @@
       <c r="Z43" t="n">
         <v>20242025</v>
       </c>
-      <c r="AA43" t="inlineStr">
-        <is>
-          <t>GnizyMB7</t>
-        </is>
-      </c>
+      <c r="AA43" t="inlineStr"/>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>d0PJxeie</t>
-        </is>
-      </c>
-      <c r="AC43" t="n">
-        <v>25.3</v>
-      </c>
-      <c r="AD43" t="n">
-        <v>184.9</v>
-      </c>
-      <c r="AE43" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF43" t="n">
-        <v>66.90000000000001</v>
-      </c>
-      <c r="AG43" t="n">
-        <v>1215000</v>
-      </c>
-      <c r="AH43" t="n">
-        <v>70.90000000000001</v>
-      </c>
+          <t>p84TeBhA</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr"/>
+      <c r="AD43" t="inlineStr"/>
+      <c r="AE43" t="inlineStr"/>
+      <c r="AF43" t="inlineStr"/>
+      <c r="AG43" t="inlineStr"/>
+      <c r="AH43" t="inlineStr"/>
       <c r="AI43" t="n">
-        <v>23.8</v>
+        <v>25.88888888888889</v>
       </c>
       <c r="AJ43" t="n">
-        <v>185.9</v>
+        <v>182.2222222222222</v>
       </c>
       <c r="AK43" t="n">
         <v>1</v>
       </c>
       <c r="AL43" t="n">
-        <v>66.5</v>
+        <v>66.55555555555556</v>
       </c>
       <c r="AM43" t="n">
-        <v>1495000</v>
+        <v>1175000</v>
       </c>
       <c r="AN43" t="n">
-        <v>72.2</v>
+        <v>70.44444444444444</v>
       </c>
       <c r="AO43" t="n">
-        <v>22.66666666666667</v>
+        <v>24</v>
       </c>
       <c r="AP43" t="n">
-        <v>179.2222222222222</v>
+        <v>180.4444444444445</v>
       </c>
       <c r="AQ43" t="n">
         <v>1</v>
       </c>
       <c r="AR43" t="n">
-        <v>64.22222222222223</v>
+        <v>66.33333333333333</v>
       </c>
       <c r="AS43" t="n">
-        <v>1156944.444444444</v>
+        <v>1352777.777777778</v>
       </c>
       <c r="AT43" t="n">
-        <v>73</v>
+        <v>71.33333333333333</v>
       </c>
       <c r="AU43" t="n">
-        <v>25.5</v>
+        <v>25.4375</v>
       </c>
       <c r="AV43" t="n">
-        <v>183.3</v>
+        <v>183.1875</v>
       </c>
       <c r="AW43" t="n">
         <v>1</v>
       </c>
       <c r="AX43" t="n">
-        <v>65.95</v>
+        <v>66</v>
       </c>
       <c r="AY43" t="n">
-        <v>1251250</v>
+        <v>1154687.5</v>
       </c>
       <c r="AZ43" t="n">
-        <v>71.25</v>
+        <v>69.625</v>
       </c>
       <c r="BA43" t="inlineStr"/>
       <c r="BB43" t="inlineStr"/>
@@ -9168,7 +9168,7 @@
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>Eql9v7B6</t>
+          <t>W0WITkcl</t>
         </is>
       </c>
       <c r="B45" s="2" t="n">
@@ -9176,72 +9176,72 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t xml:space="preserve">feliciani e 
+          <t xml:space="preserve">arena a 
   ita </t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio arechi
-  salerno </t>
+          <t xml:space="preserve">stadio pier cesare tombolato
+  cittadella </t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>37800</v>
+        <v>7623</v>
       </c>
       <c r="F45" t="n">
-        <v>15683</v>
+        <v>3685</v>
       </c>
       <c r="G45" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H45" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Mq05g4BP</t>
+          <t>C0yUqo8c</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>nJbCGx2U</t>
+          <t>roasMsOT</t>
         </is>
       </c>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
       <c r="M45" t="n">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="N45" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="O45" t="n">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="P45" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="Q45" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="R45" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="S45" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="T45" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>OjWmexQb</t>
+          <t>8dDPzPa7</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>2kfSDavF</t>
+          <t>GfucctAF</t>
         </is>
       </c>
       <c r="W45" t="n">
@@ -9258,85 +9258,73 @@
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>69Dxbc61</t>
+          <t>MkPmVv50</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>d0PJxeie</t>
-        </is>
-      </c>
-      <c r="AC45" t="n">
-        <v>25.625</v>
-      </c>
-      <c r="AD45" t="n">
-        <v>182.25</v>
-      </c>
-      <c r="AE45" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF45" t="n">
-        <v>69.375</v>
-      </c>
-      <c r="AG45" t="n">
-        <v>2131250</v>
-      </c>
-      <c r="AH45" t="n">
-        <v>74.125</v>
-      </c>
+          <t>Q3A3IbXH</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr"/>
+      <c r="AD45" t="inlineStr"/>
+      <c r="AE45" t="inlineStr"/>
+      <c r="AF45" t="inlineStr"/>
+      <c r="AG45" t="inlineStr"/>
+      <c r="AH45" t="inlineStr"/>
       <c r="AI45" t="n">
-        <v>27.33333333333333</v>
+        <v>23.3</v>
       </c>
       <c r="AJ45" t="n">
-        <v>183.8888888888889</v>
+        <v>183.2</v>
       </c>
       <c r="AK45" t="n">
         <v>1</v>
       </c>
       <c r="AL45" t="n">
-        <v>70.55555555555556</v>
+        <v>65.8</v>
       </c>
       <c r="AM45" t="n">
-        <v>2000000</v>
+        <v>1690000</v>
       </c>
       <c r="AN45" t="n">
-        <v>73.33333333333333</v>
+        <v>73.2</v>
       </c>
       <c r="AO45" t="n">
-        <v>22.15384615384615</v>
+        <v>25.23809523809524</v>
       </c>
       <c r="AP45" t="n">
-        <v>178.3846153846154</v>
+        <v>181.952380952381</v>
       </c>
       <c r="AQ45" t="n">
         <v>1</v>
       </c>
       <c r="AR45" t="n">
-        <v>65.76923076923077</v>
+        <v>65.33333333333333</v>
       </c>
       <c r="AS45" t="n">
-        <v>1940384.615384615</v>
+        <v>1007142.857142857</v>
       </c>
       <c r="AT45" t="n">
-        <v>75.53846153846153</v>
+        <v>70.38095238095238</v>
       </c>
       <c r="AU45" t="n">
-        <v>25.125</v>
+        <v>24.29166666666667</v>
       </c>
       <c r="AV45" t="n">
-        <v>182.4583333333333</v>
+        <v>183.625</v>
       </c>
       <c r="AW45" t="n">
-        <v>1.125</v>
+        <v>1</v>
       </c>
       <c r="AX45" t="n">
-        <v>67.08333333333333</v>
+        <v>66.95833333333333</v>
       </c>
       <c r="AY45" t="n">
-        <v>1406041.666666667</v>
+        <v>1718750</v>
       </c>
       <c r="AZ45" t="n">
-        <v>71.875</v>
+        <v>71.5</v>
       </c>
       <c r="BA45" t="inlineStr"/>
       <c r="BB45" t="inlineStr"/>
@@ -9356,7 +9344,7 @@
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>v3ivyY4E</t>
+          <t>Y54hDUC7</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -9364,72 +9352,72 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t xml:space="preserve">monaldi m 
+          <t xml:space="preserve">la penna f 
   ita </t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t xml:space="preserve">arena garibaldi   stadio romeo anconetani
-  pisa </t>
+          <t xml:space="preserve">stadio san nicola
+  bari </t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>14869</v>
+        <v>58270</v>
       </c>
       <c r="F46" t="n">
-        <v>1987</v>
+        <v>15733</v>
       </c>
       <c r="G46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>hG4fg4z3</t>
+          <t>xIkUr2vO</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>W02MZDnp</t>
+          <t>QDdvI0zl</t>
         </is>
       </c>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr"/>
       <c r="M46" t="n">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="N46" t="n">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="O46" t="n">
+        <v>26</v>
+      </c>
+      <c r="P46" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>4</v>
+      </c>
+      <c r="R46" t="n">
+        <v>2</v>
+      </c>
+      <c r="S46" t="n">
+        <v>11</v>
+      </c>
+      <c r="T46" t="n">
         <v>12</v>
       </c>
-      <c r="P46" t="n">
-        <v>16</v>
-      </c>
-      <c r="Q46" t="n">
-        <v>3</v>
-      </c>
-      <c r="R46" t="n">
-        <v>4</v>
-      </c>
-      <c r="S46" t="n">
-        <v>16</v>
-      </c>
-      <c r="T46" t="n">
-        <v>13</v>
-      </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>lSb6U6l0</t>
+          <t>nZ24J27c</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>bmzifXwb</t>
+          <t>bPHSQi9q</t>
         </is>
       </c>
       <c r="W46" t="n">
@@ -9444,71 +9432,87 @@
       <c r="Z46" t="n">
         <v>20242025</v>
       </c>
-      <c r="AA46" t="inlineStr"/>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>G8lYsMgU</t>
+        </is>
+      </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>rXw8YKDE</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr"/>
-      <c r="AD46" t="inlineStr"/>
-      <c r="AE46" t="inlineStr"/>
-      <c r="AF46" t="inlineStr"/>
-      <c r="AG46" t="inlineStr"/>
-      <c r="AH46" t="inlineStr"/>
+          <t>0M9xNN8N</t>
+        </is>
+      </c>
+      <c r="AC46" t="n">
+        <v>27</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>183</v>
+      </c>
+      <c r="AE46" t="n">
+        <v>1.090909090909091</v>
+      </c>
+      <c r="AF46" t="n">
+        <v>68.45454545454545</v>
+      </c>
+      <c r="AG46" t="n">
+        <v>1509090.909090909</v>
+      </c>
+      <c r="AH46" t="n">
+        <v>71.09090909090909</v>
+      </c>
       <c r="AI46" t="n">
-        <v>27.3</v>
+        <v>22.9</v>
       </c>
       <c r="AJ46" t="n">
-        <v>184.6</v>
+        <v>186.4</v>
       </c>
       <c r="AK46" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="AL46" t="n">
-        <v>66.8</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="AM46" t="n">
-        <v>903500</v>
+        <v>3562500</v>
       </c>
       <c r="AN46" t="n">
-        <v>70.7</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="AO46" t="n">
-        <v>21.16666666666667</v>
+        <v>25.73913043478261</v>
       </c>
       <c r="AP46" t="n">
-        <v>180</v>
+        <v>177.9565217391304</v>
       </c>
       <c r="AQ46" t="n">
         <v>1</v>
       </c>
       <c r="AR46" t="n">
-        <v>62.16666666666666</v>
+        <v>64.52173913043478</v>
       </c>
       <c r="AS46" t="n">
-        <v>929166.6666666666</v>
+        <v>996304.3478260869</v>
       </c>
       <c r="AT46" t="n">
-        <v>72</v>
+        <v>69.1304347826087</v>
       </c>
       <c r="AU46" t="n">
-        <v>26.7</v>
+        <v>22.95238095238095</v>
       </c>
       <c r="AV46" t="n">
-        <v>181.9</v>
+        <v>184</v>
       </c>
       <c r="AW46" t="n">
-        <v>1</v>
+        <v>1.142857142857143</v>
       </c>
       <c r="AX46" t="n">
-        <v>67.05</v>
+        <v>67.19047619047619</v>
       </c>
       <c r="AY46" t="n">
-        <v>1346250</v>
+        <v>1971428.571428571</v>
       </c>
       <c r="AZ46" t="n">
-        <v>70.40000000000001</v>
+        <v>74.38095238095238</v>
       </c>
       <c r="BA46" t="inlineStr"/>
       <c r="BB46" t="inlineStr"/>
@@ -9528,7 +9532,7 @@
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>W0WITkcl</t>
+          <t>v3ivyY4E</t>
         </is>
       </c>
       <c r="B47" s="2" t="n">
@@ -9536,72 +9540,72 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t xml:space="preserve">arena a 
+          <t xml:space="preserve">monaldi m 
   ita </t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio pier cesare tombolato
-  cittadella </t>
+          <t xml:space="preserve">arena garibaldi   stadio romeo anconetani
+  pisa </t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>7623</v>
+        <v>14869</v>
       </c>
       <c r="F47" t="n">
-        <v>3685</v>
+        <v>1987</v>
       </c>
       <c r="G47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>C0yUqo8c</t>
+          <t>hG4fg4z3</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>roasMsOT</t>
+          <t>W02MZDnp</t>
         </is>
       </c>
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr"/>
       <c r="M47" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="N47" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="O47" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="P47" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="Q47" t="n">
+        <v>3</v>
+      </c>
+      <c r="R47" t="n">
         <v>4</v>
       </c>
-      <c r="R47" t="n">
-        <v>1</v>
-      </c>
       <c r="S47" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="T47" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>8dDPzPa7</t>
+          <t>lSb6U6l0</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>GfucctAF</t>
+          <t>bmzifXwb</t>
         </is>
       </c>
       <c r="W47" t="n">
@@ -9616,14 +9620,10 @@
       <c r="Z47" t="n">
         <v>20242025</v>
       </c>
-      <c r="AA47" t="inlineStr">
-        <is>
-          <t>MkPmVv50</t>
-        </is>
-      </c>
+      <c r="AA47" t="inlineStr"/>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>Q3A3IbXH</t>
+          <t>rXw8YKDE</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr"/>
@@ -9633,58 +9633,58 @@
       <c r="AG47" t="inlineStr"/>
       <c r="AH47" t="inlineStr"/>
       <c r="AI47" t="n">
-        <v>23.3</v>
+        <v>27.3</v>
       </c>
       <c r="AJ47" t="n">
-        <v>183.2</v>
+        <v>184.6</v>
       </c>
       <c r="AK47" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AL47" t="n">
-        <v>65.8</v>
+        <v>66.8</v>
       </c>
       <c r="AM47" t="n">
-        <v>1690000</v>
+        <v>903500</v>
       </c>
       <c r="AN47" t="n">
-        <v>73.2</v>
+        <v>70.7</v>
       </c>
       <c r="AO47" t="n">
-        <v>25.23809523809524</v>
+        <v>21.16666666666667</v>
       </c>
       <c r="AP47" t="n">
-        <v>181.952380952381</v>
+        <v>180</v>
       </c>
       <c r="AQ47" t="n">
         <v>1</v>
       </c>
       <c r="AR47" t="n">
-        <v>65.33333333333333</v>
+        <v>62.16666666666666</v>
       </c>
       <c r="AS47" t="n">
-        <v>1007142.857142857</v>
+        <v>929166.6666666666</v>
       </c>
       <c r="AT47" t="n">
-        <v>70.38095238095238</v>
+        <v>72</v>
       </c>
       <c r="AU47" t="n">
-        <v>24.29166666666667</v>
+        <v>26.7</v>
       </c>
       <c r="AV47" t="n">
-        <v>183.625</v>
+        <v>181.9</v>
       </c>
       <c r="AW47" t="n">
         <v>1</v>
       </c>
       <c r="AX47" t="n">
-        <v>66.95833333333333</v>
+        <v>67.05</v>
       </c>
       <c r="AY47" t="n">
-        <v>1718750</v>
+        <v>1346250</v>
       </c>
       <c r="AZ47" t="n">
-        <v>71.5</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="BA47" t="inlineStr"/>
       <c r="BB47" t="inlineStr"/>
@@ -9704,7 +9704,7 @@
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>tWk1tTtf</t>
+          <t>YPSZP7dD</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -9712,72 +9712,72 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t xml:space="preserve">sacchi j  l 
+          <t xml:space="preserve">fourneau f 
   ita </t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapei stadium – citta del tricolore
-  reggio emilia </t>
+          <t xml:space="preserve">stadio giovanni zini
+  cremona </t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>21525</v>
+        <v>20641</v>
       </c>
       <c r="F48" t="n">
-        <v>9252</v>
+        <v>9394</v>
       </c>
       <c r="G48" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>6ulJbMCe</t>
+          <t>KUzfp5N3</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>jci0qO9B</t>
+          <t>n38Nktmn</t>
         </is>
       </c>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
       <c r="M48" t="n">
-        <v>39</v>
+        <v>64</v>
       </c>
       <c r="N48" t="n">
-        <v>61</v>
+        <v>36</v>
       </c>
       <c r="O48" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="P48" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="Q48" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R48" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S48" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="T48" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>Gfur2NmR</t>
+          <t>YgLhKnOo</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>lb1XFX3n</t>
+          <t>Wn0poKgt</t>
         </is>
       </c>
       <c r="W48" t="n">
@@ -9792,83 +9792,87 @@
       <c r="Z48" t="n">
         <v>20242025</v>
       </c>
-      <c r="AA48" t="inlineStr"/>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>ttyLthOA</t>
+        </is>
+      </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>8C9JjMXu</t>
+          <t>pfo9H1Wp</t>
         </is>
       </c>
       <c r="AC48" t="n">
-        <v>26.33333333333333</v>
+        <v>26.2</v>
       </c>
       <c r="AD48" t="n">
-        <v>183.3333333333333</v>
+        <v>185.5</v>
       </c>
       <c r="AE48" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="AF48" t="n">
-        <v>66.11111111111111</v>
+        <v>70.7</v>
       </c>
       <c r="AG48" t="n">
-        <v>1063888.888888889</v>
+        <v>2380000</v>
       </c>
       <c r="AH48" t="n">
-        <v>69.22222222222223</v>
+        <v>74</v>
       </c>
       <c r="AI48" t="n">
-        <v>25.4</v>
+        <v>24.27272727272727</v>
       </c>
       <c r="AJ48" t="n">
-        <v>183.7</v>
+        <v>183.7272727272727</v>
       </c>
       <c r="AK48" t="n">
         <v>1</v>
       </c>
       <c r="AL48" t="n">
-        <v>66.3</v>
+        <v>70.27272727272727</v>
       </c>
       <c r="AM48" t="n">
-        <v>1205000</v>
+        <v>2818181.818181818</v>
       </c>
       <c r="AN48" t="n">
-        <v>70.2</v>
+        <v>76.18181818181819</v>
       </c>
       <c r="AO48" t="n">
-        <v>25.68421052631579</v>
+        <v>24.04</v>
       </c>
       <c r="AP48" t="n">
-        <v>181.7894736842105</v>
+        <v>183.12</v>
       </c>
       <c r="AQ48" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="AR48" t="n">
-        <v>63.89473684210526</v>
+        <v>68.44</v>
       </c>
       <c r="AS48" t="n">
-        <v>1174736.842105263</v>
+        <v>1972000</v>
       </c>
       <c r="AT48" t="n">
-        <v>68.42105263157895</v>
+        <v>74</v>
       </c>
       <c r="AU48" t="n">
-        <v>24.19047619047619</v>
+        <v>25.36363636363636</v>
       </c>
       <c r="AV48" t="n">
-        <v>182.7142857142857</v>
+        <v>181.5909090909091</v>
       </c>
       <c r="AW48" t="n">
-        <v>1</v>
+        <v>1.136363636363636</v>
       </c>
       <c r="AX48" t="n">
-        <v>64.76190476190476</v>
+        <v>69.59090909090909</v>
       </c>
       <c r="AY48" t="n">
-        <v>1086904.761904762</v>
+        <v>2509090.909090909</v>
       </c>
       <c r="AZ48" t="n">
-        <v>71.47619047619048</v>
+        <v>74.09090909090909</v>
       </c>
       <c r="BA48" t="inlineStr"/>
       <c r="BB48" t="inlineStr"/>
@@ -10076,7 +10080,7 @@
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>YPSZP7dD</t>
+          <t>tWk1tTtf</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -10084,72 +10088,72 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t xml:space="preserve">fourneau f 
+          <t xml:space="preserve">sacchi j  l 
   ita </t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio giovanni zini
-  cremona </t>
+          <t xml:space="preserve">mapei stadium – citta del tricolore
+  reggio emilia </t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>20641</v>
+        <v>21525</v>
       </c>
       <c r="F50" t="n">
-        <v>9394</v>
+        <v>9252</v>
       </c>
       <c r="G50" t="n">
+        <v>2</v>
+      </c>
+      <c r="H50" t="n">
         <v>0</v>
       </c>
-      <c r="H50" t="n">
-        <v>1</v>
-      </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>KUzfp5N3</t>
+          <t>6ulJbMCe</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>n38Nktmn</t>
+          <t>jci0qO9B</t>
         </is>
       </c>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
       <c r="M50" t="n">
-        <v>64</v>
+        <v>39</v>
       </c>
       <c r="N50" t="n">
-        <v>36</v>
+        <v>61</v>
       </c>
       <c r="O50" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="P50" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q50" t="n">
         <v>5</v>
       </c>
-      <c r="Q50" t="n">
+      <c r="R50" t="n">
         <v>4</v>
       </c>
-      <c r="R50" t="n">
-        <v>3</v>
-      </c>
       <c r="S50" t="n">
+        <v>16</v>
+      </c>
+      <c r="T50" t="n">
         <v>14</v>
       </c>
-      <c r="T50" t="n">
-        <v>21</v>
-      </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>YgLhKnOo</t>
+          <t>Gfur2NmR</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>Wn0poKgt</t>
+          <t>lb1XFX3n</t>
         </is>
       </c>
       <c r="W50" t="n">
@@ -10164,87 +10168,83 @@
       <c r="Z50" t="n">
         <v>20242025</v>
       </c>
-      <c r="AA50" t="inlineStr">
-        <is>
-          <t>ttyLthOA</t>
-        </is>
-      </c>
+      <c r="AA50" t="inlineStr"/>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>pfo9H1Wp</t>
+          <t>8C9JjMXu</t>
         </is>
       </c>
       <c r="AC50" t="n">
-        <v>26.2</v>
+        <v>26.33333333333333</v>
       </c>
       <c r="AD50" t="n">
-        <v>185.5</v>
+        <v>183.3333333333333</v>
       </c>
       <c r="AE50" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AF50" t="n">
-        <v>70.7</v>
+        <v>66.11111111111111</v>
       </c>
       <c r="AG50" t="n">
-        <v>2380000</v>
+        <v>1063888.888888889</v>
       </c>
       <c r="AH50" t="n">
-        <v>74</v>
+        <v>69.22222222222223</v>
       </c>
       <c r="AI50" t="n">
-        <v>24.27272727272727</v>
+        <v>25.4</v>
       </c>
       <c r="AJ50" t="n">
-        <v>183.7272727272727</v>
+        <v>183.7</v>
       </c>
       <c r="AK50" t="n">
         <v>1</v>
       </c>
       <c r="AL50" t="n">
-        <v>70.27272727272727</v>
+        <v>66.3</v>
       </c>
       <c r="AM50" t="n">
-        <v>2818181.818181818</v>
+        <v>1205000</v>
       </c>
       <c r="AN50" t="n">
-        <v>76.18181818181819</v>
+        <v>70.2</v>
       </c>
       <c r="AO50" t="n">
-        <v>24.04</v>
+        <v>25.68421052631579</v>
       </c>
       <c r="AP50" t="n">
-        <v>183.12</v>
+        <v>181.7894736842105</v>
       </c>
       <c r="AQ50" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="AR50" t="n">
-        <v>68.44</v>
+        <v>63.89473684210526</v>
       </c>
       <c r="AS50" t="n">
-        <v>1972000</v>
+        <v>1174736.842105263</v>
       </c>
       <c r="AT50" t="n">
-        <v>74</v>
+        <v>68.42105263157895</v>
       </c>
       <c r="AU50" t="n">
-        <v>25.36363636363636</v>
+        <v>24.19047619047619</v>
       </c>
       <c r="AV50" t="n">
-        <v>181.5909090909091</v>
+        <v>182.7142857142857</v>
       </c>
       <c r="AW50" t="n">
-        <v>1.136363636363636</v>
+        <v>1</v>
       </c>
       <c r="AX50" t="n">
-        <v>69.59090909090909</v>
+        <v>64.76190476190476</v>
       </c>
       <c r="AY50" t="n">
-        <v>2509090.909090909</v>
+        <v>1086904.761904762</v>
       </c>
       <c r="AZ50" t="n">
-        <v>74.09090909090909</v>
+        <v>71.47619047619048</v>
       </c>
       <c r="BA50" t="inlineStr"/>
       <c r="BB50" t="inlineStr"/>
@@ -10264,7 +10264,7 @@
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>Y54hDUC7</t>
+          <t>Eql9v7B6</t>
         </is>
       </c>
       <c r="B51" s="2" t="n">
@@ -10272,72 +10272,72 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t xml:space="preserve">la penna f 
+          <t xml:space="preserve">feliciani e 
   ita </t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio san nicola
-  bari </t>
+          <t xml:space="preserve">stadio arechi
+  salerno </t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>58270</v>
+        <v>37800</v>
       </c>
       <c r="F51" t="n">
-        <v>15733</v>
+        <v>15683</v>
       </c>
       <c r="G51" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H51" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>xIkUr2vO</t>
+          <t>Mq05g4BP</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>QDdvI0zl</t>
+          <t>nJbCGx2U</t>
         </is>
       </c>
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr"/>
       <c r="M51" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="N51" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="O51" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="P51" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q51" t="n">
         <v>8</v>
       </c>
-      <c r="Q51" t="n">
+      <c r="R51" t="n">
         <v>4</v>
       </c>
-      <c r="R51" t="n">
-        <v>2</v>
-      </c>
       <c r="S51" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="T51" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>nZ24J27c</t>
+          <t>OjWmexQb</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>bPHSQi9q</t>
+          <t>2kfSDavF</t>
         </is>
       </c>
       <c r="W51" t="n">
@@ -10354,85 +10354,85 @@
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>G8lYsMgU</t>
+          <t>69Dxbc61</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>0M9xNN8N</t>
+          <t>d0PJxeie</t>
         </is>
       </c>
       <c r="AC51" t="n">
-        <v>27</v>
+        <v>25.625</v>
       </c>
       <c r="AD51" t="n">
-        <v>183</v>
+        <v>182.25</v>
       </c>
       <c r="AE51" t="n">
-        <v>1.090909090909091</v>
+        <v>1</v>
       </c>
       <c r="AF51" t="n">
-        <v>68.45454545454545</v>
+        <v>69.375</v>
       </c>
       <c r="AG51" t="n">
-        <v>1509090.909090909</v>
+        <v>2131250</v>
       </c>
       <c r="AH51" t="n">
-        <v>71.09090909090909</v>
+        <v>74.125</v>
       </c>
       <c r="AI51" t="n">
-        <v>22.9</v>
+        <v>27.33333333333333</v>
       </c>
       <c r="AJ51" t="n">
-        <v>186.4</v>
+        <v>183.8888888888889</v>
       </c>
       <c r="AK51" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AL51" t="n">
-        <v>69.40000000000001</v>
+        <v>70.55555555555556</v>
       </c>
       <c r="AM51" t="n">
-        <v>3562500</v>
+        <v>2000000</v>
       </c>
       <c r="AN51" t="n">
-        <v>76.59999999999999</v>
+        <v>73.33333333333333</v>
       </c>
       <c r="AO51" t="n">
-        <v>25.73913043478261</v>
+        <v>22.15384615384615</v>
       </c>
       <c r="AP51" t="n">
-        <v>177.9565217391304</v>
+        <v>178.3846153846154</v>
       </c>
       <c r="AQ51" t="n">
         <v>1</v>
       </c>
       <c r="AR51" t="n">
-        <v>64.52173913043478</v>
+        <v>65.76923076923077</v>
       </c>
       <c r="AS51" t="n">
-        <v>996304.3478260869</v>
+        <v>1940384.615384615</v>
       </c>
       <c r="AT51" t="n">
-        <v>69.1304347826087</v>
+        <v>75.53846153846153</v>
       </c>
       <c r="AU51" t="n">
-        <v>22.95238095238095</v>
+        <v>25.125</v>
       </c>
       <c r="AV51" t="n">
-        <v>184</v>
+        <v>182.4583333333333</v>
       </c>
       <c r="AW51" t="n">
-        <v>1.142857142857143</v>
+        <v>1.125</v>
       </c>
       <c r="AX51" t="n">
-        <v>67.19047619047619</v>
+        <v>67.08333333333333</v>
       </c>
       <c r="AY51" t="n">
-        <v>1971428.571428571</v>
+        <v>1406041.666666667</v>
       </c>
       <c r="AZ51" t="n">
-        <v>74.38095238095238</v>
+        <v>71.875</v>
       </c>
       <c r="BA51" t="inlineStr"/>
       <c r="BB51" t="inlineStr"/>
@@ -10892,7 +10892,7 @@
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>UilLdutJ</t>
+          <t>2uc40Ntf</t>
         </is>
       </c>
       <c r="B54" s="2" t="n">
@@ -10900,76 +10900,76 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t xml:space="preserve">zufferli l 
+          <t xml:space="preserve">pairetto l 
   ita </t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio olimpico
-  rome </t>
+          <t xml:space="preserve">stadio diego armando maradona
+  naples </t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>70634</v>
+        <v>54726</v>
       </c>
       <c r="F54" t="n">
-        <v>67517</v>
+        <v>45000</v>
       </c>
       <c r="G54" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H54" t="n">
+        <v>0</v>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>69Dxbc61</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>0M9xNN8N</t>
+        </is>
+      </c>
+      <c r="K54" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="L54" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="M54" t="n">
+        <v>39</v>
+      </c>
+      <c r="N54" t="n">
+        <v>61</v>
+      </c>
+      <c r="O54" t="n">
+        <v>16</v>
+      </c>
+      <c r="P54" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>5</v>
+      </c>
+      <c r="R54" t="n">
         <v>2</v>
       </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>zVqqL0ma</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>0ESCnI1H</t>
-        </is>
-      </c>
-      <c r="K54" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="L54" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="M54" t="n">
-        <v>73</v>
-      </c>
-      <c r="N54" t="n">
-        <v>27</v>
-      </c>
-      <c r="O54" t="n">
-        <v>26</v>
-      </c>
-      <c r="P54" t="n">
-        <v>14</v>
-      </c>
-      <c r="Q54" t="n">
-        <v>7</v>
-      </c>
-      <c r="R54" t="n">
-        <v>4</v>
-      </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T54" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>xjigzK81</t>
+          <t>23vSAc12</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>MBrKQFV7</t>
+          <t>tjY4uUem</t>
         </is>
       </c>
       <c r="W54" t="n">
@@ -10986,7 +10986,7 @@
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>URcSl02h</t>
+          <t>C06aJvIB</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
@@ -10995,76 +10995,76 @@
         </is>
       </c>
       <c r="AC54" t="n">
-        <v>26.1</v>
+        <v>26.27272727272727</v>
       </c>
       <c r="AD54" t="n">
-        <v>182.8</v>
+        <v>181.9090909090909</v>
       </c>
       <c r="AE54" t="n">
-        <v>2</v>
+        <v>1.545454545454545</v>
       </c>
       <c r="AF54" t="n">
-        <v>79.2</v>
+        <v>80.45454545454545</v>
       </c>
       <c r="AG54" t="n">
-        <v>24780000</v>
+        <v>31700000</v>
       </c>
       <c r="AH54" t="n">
-        <v>81.2</v>
+        <v>82.18181818181819</v>
       </c>
       <c r="AI54" t="n">
-        <v>24.09090909090909</v>
+        <v>25.81818181818182</v>
       </c>
       <c r="AJ54" t="n">
-        <v>184.8181818181818</v>
+        <v>185.5454545454545</v>
       </c>
       <c r="AK54" t="n">
-        <v>1</v>
+        <v>1.363636363636364</v>
       </c>
       <c r="AL54" t="n">
-        <v>71.36363636363636</v>
+        <v>74.90909090909091</v>
       </c>
       <c r="AM54" t="n">
-        <v>3400000</v>
+        <v>8036363.636363637</v>
       </c>
       <c r="AN54" t="n">
-        <v>77.09090909090909</v>
+        <v>78.09090909090909</v>
       </c>
       <c r="AO54" t="n">
-        <v>23.81818181818182</v>
+        <v>25.875</v>
       </c>
       <c r="AP54" t="n">
-        <v>179.4090909090909</v>
+        <v>181.6875</v>
       </c>
       <c r="AQ54" t="n">
-        <v>1.545454545454545</v>
+        <v>1.6875</v>
       </c>
       <c r="AR54" t="n">
-        <v>75</v>
+        <v>75.3125</v>
       </c>
       <c r="AS54" t="n">
-        <v>13270454.54545454</v>
+        <v>10351562.5</v>
       </c>
       <c r="AT54" t="n">
-        <v>80.68181818181819</v>
+        <v>78.125</v>
       </c>
       <c r="AU54" t="n">
-        <v>22.66666666666667</v>
+        <v>23.3448275862069</v>
       </c>
       <c r="AV54" t="n">
-        <v>181.9583333333333</v>
+        <v>185.7241379310345</v>
       </c>
       <c r="AW54" t="n">
-        <v>1</v>
+        <v>1.172413793103448</v>
       </c>
       <c r="AX54" t="n">
-        <v>68</v>
+        <v>72.58620689655173</v>
       </c>
       <c r="AY54" t="n">
-        <v>2771458.333333333</v>
+        <v>7563793.103448275</v>
       </c>
       <c r="AZ54" t="n">
-        <v>75.04166666666667</v>
+        <v>78.89655172413794</v>
       </c>
       <c r="BA54" t="inlineStr"/>
       <c r="BB54" t="inlineStr"/>
@@ -11074,31 +11074,31 @@
       <c r="BF54" t="inlineStr"/>
       <c r="BG54" t="inlineStr"/>
       <c r="BH54" t="n">
-        <v>25.4</v>
+        <v>22.33333333333333</v>
       </c>
       <c r="BI54" t="n">
-        <v>187.4</v>
+        <v>181</v>
       </c>
       <c r="BJ54" t="n">
         <v>1</v>
       </c>
       <c r="BK54" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="BL54" t="n">
-        <v>347</v>
+        <v>216</v>
       </c>
       <c r="BM54" t="n">
-        <v>11825000</v>
+        <v>29400000</v>
       </c>
       <c r="BN54" t="n">
-        <v>363</v>
+        <v>237</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>2uc40Ntf</t>
+          <t>UilLdutJ</t>
         </is>
       </c>
       <c r="B55" s="2" t="n">
@@ -11106,76 +11106,76 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t xml:space="preserve">pairetto l 
+          <t xml:space="preserve">zufferli l 
   ita </t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio diego armando maradona
-  naples </t>
+          <t xml:space="preserve">stadio olimpico
+  rome </t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>54726</v>
+        <v>70634</v>
       </c>
       <c r="F55" t="n">
-        <v>45000</v>
+        <v>67517</v>
       </c>
       <c r="G55" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H55" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>69Dxbc61</t>
+          <t>zVqqL0ma</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>0M9xNN8N</t>
+          <t>0ESCnI1H</t>
         </is>
       </c>
       <c r="K55" t="n">
-        <v>1.92</v>
+        <v>2.98</v>
       </c>
       <c r="L55" t="n">
-        <v>0.46</v>
+        <v>2.87</v>
       </c>
       <c r="M55" t="n">
-        <v>39</v>
+        <v>73</v>
       </c>
       <c r="N55" t="n">
-        <v>61</v>
+        <v>27</v>
       </c>
       <c r="O55" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="P55" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="Q55" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="R55" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="n">
         <v>11</v>
       </c>
-      <c r="T55" t="n">
-        <v>17</v>
-      </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>23vSAc12</t>
+          <t>xjigzK81</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>tjY4uUem</t>
+          <t>MBrKQFV7</t>
         </is>
       </c>
       <c r="W55" t="n">
@@ -11192,7 +11192,7 @@
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>C06aJvIB</t>
+          <t>URcSl02h</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
@@ -11201,76 +11201,76 @@
         </is>
       </c>
       <c r="AC55" t="n">
-        <v>26.27272727272727</v>
+        <v>26.1</v>
       </c>
       <c r="AD55" t="n">
-        <v>181.9090909090909</v>
+        <v>182.8</v>
       </c>
       <c r="AE55" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF55" t="n">
+        <v>79.2</v>
+      </c>
+      <c r="AG55" t="n">
+        <v>24780000</v>
+      </c>
+      <c r="AH55" t="n">
+        <v>81.2</v>
+      </c>
+      <c r="AI55" t="n">
+        <v>24.09090909090909</v>
+      </c>
+      <c r="AJ55" t="n">
+        <v>184.8181818181818</v>
+      </c>
+      <c r="AK55" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL55" t="n">
+        <v>71.36363636363636</v>
+      </c>
+      <c r="AM55" t="n">
+        <v>3400000</v>
+      </c>
+      <c r="AN55" t="n">
+        <v>77.09090909090909</v>
+      </c>
+      <c r="AO55" t="n">
+        <v>23.81818181818182</v>
+      </c>
+      <c r="AP55" t="n">
+        <v>179.4090909090909</v>
+      </c>
+      <c r="AQ55" t="n">
         <v>1.545454545454545</v>
       </c>
-      <c r="AF55" t="n">
-        <v>80.45454545454545</v>
-      </c>
-      <c r="AG55" t="n">
-        <v>31700000</v>
-      </c>
-      <c r="AH55" t="n">
-        <v>82.18181818181819</v>
-      </c>
-      <c r="AI55" t="n">
-        <v>25.81818181818182</v>
-      </c>
-      <c r="AJ55" t="n">
-        <v>185.5454545454545</v>
-      </c>
-      <c r="AK55" t="n">
-        <v>1.363636363636364</v>
-      </c>
-      <c r="AL55" t="n">
-        <v>74.90909090909091</v>
-      </c>
-      <c r="AM55" t="n">
-        <v>8036363.636363637</v>
-      </c>
-      <c r="AN55" t="n">
-        <v>78.09090909090909</v>
-      </c>
-      <c r="AO55" t="n">
-        <v>25.875</v>
-      </c>
-      <c r="AP55" t="n">
-        <v>181.6875</v>
-      </c>
-      <c r="AQ55" t="n">
-        <v>1.6875</v>
-      </c>
       <c r="AR55" t="n">
-        <v>75.3125</v>
+        <v>75</v>
       </c>
       <c r="AS55" t="n">
-        <v>10351562.5</v>
+        <v>13270454.54545454</v>
       </c>
       <c r="AT55" t="n">
-        <v>78.125</v>
+        <v>80.68181818181819</v>
       </c>
       <c r="AU55" t="n">
-        <v>23.3448275862069</v>
+        <v>22.66666666666667</v>
       </c>
       <c r="AV55" t="n">
-        <v>185.7241379310345</v>
+        <v>181.9583333333333</v>
       </c>
       <c r="AW55" t="n">
-        <v>1.172413793103448</v>
+        <v>1</v>
       </c>
       <c r="AX55" t="n">
-        <v>72.58620689655173</v>
+        <v>68</v>
       </c>
       <c r="AY55" t="n">
-        <v>7563793.103448275</v>
+        <v>2771458.333333333</v>
       </c>
       <c r="AZ55" t="n">
-        <v>78.89655172413794</v>
+        <v>75.04166666666667</v>
       </c>
       <c r="BA55" t="inlineStr"/>
       <c r="BB55" t="inlineStr"/>
@@ -11280,25 +11280,25 @@
       <c r="BF55" t="inlineStr"/>
       <c r="BG55" t="inlineStr"/>
       <c r="BH55" t="n">
-        <v>22.33333333333333</v>
+        <v>25.4</v>
       </c>
       <c r="BI55" t="n">
-        <v>181</v>
+        <v>187.4</v>
       </c>
       <c r="BJ55" t="n">
         <v>1</v>
       </c>
       <c r="BK55" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BL55" t="n">
-        <v>216</v>
+        <v>347</v>
       </c>
       <c r="BM55" t="n">
-        <v>29400000</v>
+        <v>11825000</v>
       </c>
       <c r="BN55" t="n">
-        <v>237</v>
+        <v>363</v>
       </c>
     </row>
     <row r="56">
@@ -11636,7 +11636,7 @@
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>M7MVoOR0</t>
+          <t>dbt7KrYP</t>
         </is>
       </c>
       <c r="B58" s="2" t="n">
@@ -11644,76 +11644,76 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t xml:space="preserve">sozza s 
+          <t xml:space="preserve">rapuano a 
   ita </t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio artemio franchi
-  florence </t>
+          <t xml:space="preserve">stadio olimpico di torino
+  turin </t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>43147</v>
+        <v>28177</v>
       </c>
       <c r="F58" t="n">
-        <v>18915</v>
+        <v>20451</v>
       </c>
       <c r="G58" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Q3A3IbXH</t>
+          <t>MZFZnvX4</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>MkPmVv50</t>
+          <t>8C9JjMXu</t>
         </is>
       </c>
       <c r="K58" t="n">
-        <v>1.1</v>
+        <v>2.65</v>
       </c>
       <c r="L58" t="n">
-        <v>0.43</v>
+        <v>3.51</v>
       </c>
       <c r="M58" t="n">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="N58" t="n">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="O58" t="n">
+        <v>13</v>
+      </c>
+      <c r="P58" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>7</v>
+      </c>
+      <c r="R58" t="n">
+        <v>9</v>
+      </c>
+      <c r="S58" t="n">
+        <v>11</v>
+      </c>
+      <c r="T58" t="n">
         <v>14</v>
       </c>
-      <c r="P58" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q58" t="n">
-        <v>8</v>
-      </c>
-      <c r="R58" t="n">
-        <v>4</v>
-      </c>
-      <c r="S58" t="n">
-        <v>13</v>
-      </c>
-      <c r="T58" t="n">
-        <v>21</v>
-      </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>619UPLrb</t>
+          <t>AB3WB3pA</t>
         </is>
       </c>
       <c r="V58" t="inlineStr">
         <is>
-          <t>n10g3KfJ</t>
+          <t>EJLKYOzb</t>
         </is>
       </c>
       <c r="W58" t="n">
@@ -11735,128 +11735,128 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>rJVAIaHo</t>
+          <t>8Sa8HInO</t>
         </is>
       </c>
       <c r="AC58" t="n">
-        <v>25</v>
+        <v>26.8</v>
       </c>
       <c r="AD58" t="n">
-        <v>186.1</v>
+        <v>184.7</v>
       </c>
       <c r="AE58" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="AF58" t="n">
         <v>75.3</v>
       </c>
       <c r="AG58" t="n">
-        <v>12780000</v>
+        <v>10140000</v>
       </c>
       <c r="AH58" t="n">
-        <v>80.40000000000001</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="AI58" t="n">
-        <v>25.63636363636364</v>
+        <v>25.7</v>
       </c>
       <c r="AJ58" t="n">
-        <v>183.0909090909091</v>
+        <v>188.1</v>
       </c>
       <c r="AK58" t="n">
-        <v>1.090909090909091</v>
+        <v>1.4</v>
       </c>
       <c r="AL58" t="n">
-        <v>70</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="AM58" t="n">
-        <v>2300000</v>
+        <v>15600000</v>
       </c>
       <c r="AN58" t="n">
-        <v>74.63636363636364</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="AO58" t="n">
-        <v>23.5</v>
+        <v>23.66666666666667</v>
       </c>
       <c r="AP58" t="n">
-        <v>182.4583333333333</v>
+        <v>184</v>
       </c>
       <c r="AQ58" t="n">
+        <v>1.142857142857143</v>
+      </c>
+      <c r="AR58" t="n">
+        <v>71.66666666666667</v>
+      </c>
+      <c r="AS58" t="n">
+        <v>6963095.238095238</v>
+      </c>
+      <c r="AT58" t="n">
+        <v>76.42857142857143</v>
+      </c>
+      <c r="AU58" t="n">
+        <v>23.92307692307692</v>
+      </c>
+      <c r="AV58" t="n">
+        <v>188.1538461538462</v>
+      </c>
+      <c r="AW58" t="n">
+        <v>1.307692307692308</v>
+      </c>
+      <c r="AX58" t="n">
+        <v>74.76923076923077</v>
+      </c>
+      <c r="AY58" t="n">
+        <v>12796923.07692308</v>
+      </c>
+      <c r="AZ58" t="n">
+        <v>79.07692307692308</v>
+      </c>
+      <c r="BA58" t="n">
+        <v>22.33333333333333</v>
+      </c>
+      <c r="BB58" t="n">
+        <v>186.6666666666667</v>
+      </c>
+      <c r="BC58" t="n">
         <v>1.333333333333333</v>
       </c>
-      <c r="AR58" t="n">
-        <v>74.16666666666667</v>
-      </c>
-      <c r="AS58" t="n">
-        <v>11691666.66666667</v>
-      </c>
-      <c r="AT58" t="n">
-        <v>80.625</v>
-      </c>
-      <c r="AU58" t="n">
-        <v>23.52173913043478</v>
-      </c>
-      <c r="AV58" t="n">
-        <v>184.1304347826087</v>
-      </c>
-      <c r="AW58" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX58" t="n">
-        <v>66.47826086956522</v>
-      </c>
-      <c r="AY58" t="n">
-        <v>1631304.347826087</v>
-      </c>
-      <c r="AZ58" t="n">
-        <v>73.65217391304348</v>
-      </c>
-      <c r="BA58" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="BB58" t="n">
-        <v>185.5</v>
-      </c>
-      <c r="BC58" t="n">
-        <v>1</v>
-      </c>
       <c r="BD58" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BE58" t="n">
-        <v>155</v>
+        <v>220</v>
       </c>
       <c r="BF58" t="n">
-        <v>30500000</v>
+        <v>47500000</v>
       </c>
       <c r="BG58" t="n">
-        <v>160</v>
+        <v>244</v>
       </c>
       <c r="BH58" t="n">
-        <v>26.75</v>
+        <v>26.25</v>
       </c>
       <c r="BI58" t="n">
-        <v>178.75</v>
+        <v>189.25</v>
       </c>
       <c r="BJ58" t="n">
-        <v>1</v>
+        <v>1.75</v>
       </c>
       <c r="BK58" t="n">
         <v>4</v>
       </c>
       <c r="BL58" t="n">
-        <v>284</v>
+        <v>314</v>
       </c>
       <c r="BM58" t="n">
-        <v>14625000</v>
+        <v>74000000</v>
       </c>
       <c r="BN58" t="n">
-        <v>299</v>
+        <v>329</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>dbt7KrYP</t>
+          <t>M7MVoOR0</t>
         </is>
       </c>
       <c r="B59" s="2" t="n">
@@ -11864,76 +11864,76 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t xml:space="preserve">rapuano a 
+          <t xml:space="preserve">sozza s 
   ita </t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio olimpico di torino
-  turin </t>
+          <t xml:space="preserve">stadio artemio franchi
+  florence </t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>28177</v>
+        <v>43147</v>
       </c>
       <c r="F59" t="n">
-        <v>20451</v>
+        <v>18915</v>
       </c>
       <c r="G59" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>MZFZnvX4</t>
+          <t>Q3A3IbXH</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>8C9JjMXu</t>
+          <t>MkPmVv50</t>
         </is>
       </c>
       <c r="K59" t="n">
-        <v>2.65</v>
+        <v>1.1</v>
       </c>
       <c r="L59" t="n">
-        <v>3.51</v>
+        <v>0.43</v>
       </c>
       <c r="M59" t="n">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="N59" t="n">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="O59" t="n">
+        <v>14</v>
+      </c>
+      <c r="P59" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>8</v>
+      </c>
+      <c r="R59" t="n">
+        <v>4</v>
+      </c>
+      <c r="S59" t="n">
         <v>13</v>
       </c>
-      <c r="P59" t="n">
-        <v>25</v>
-      </c>
-      <c r="Q59" t="n">
-        <v>7</v>
-      </c>
-      <c r="R59" t="n">
-        <v>9</v>
-      </c>
-      <c r="S59" t="n">
-        <v>11</v>
-      </c>
       <c r="T59" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>AB3WB3pA</t>
+          <t>619UPLrb</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
         <is>
-          <t>EJLKYOzb</t>
+          <t>n10g3KfJ</t>
         </is>
       </c>
       <c r="W59" t="n">
@@ -11955,122 +11955,122 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>8Sa8HInO</t>
+          <t>rJVAIaHo</t>
         </is>
       </c>
       <c r="AC59" t="n">
-        <v>26.8</v>
+        <v>25</v>
       </c>
       <c r="AD59" t="n">
-        <v>184.7</v>
+        <v>186.1</v>
       </c>
       <c r="AE59" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AF59" t="n">
         <v>75.3</v>
       </c>
       <c r="AG59" t="n">
-        <v>10140000</v>
+        <v>12780000</v>
       </c>
       <c r="AH59" t="n">
-        <v>77.40000000000001</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="AI59" t="n">
-        <v>25.7</v>
+        <v>25.63636363636364</v>
       </c>
       <c r="AJ59" t="n">
-        <v>188.1</v>
+        <v>183.0909090909091</v>
       </c>
       <c r="AK59" t="n">
-        <v>1.4</v>
+        <v>1.090909090909091</v>
       </c>
       <c r="AL59" t="n">
-        <v>77.09999999999999</v>
+        <v>70</v>
       </c>
       <c r="AM59" t="n">
-        <v>15600000</v>
+        <v>2300000</v>
       </c>
       <c r="AN59" t="n">
-        <v>80.90000000000001</v>
+        <v>74.63636363636364</v>
       </c>
       <c r="AO59" t="n">
-        <v>23.66666666666667</v>
+        <v>23.5</v>
       </c>
       <c r="AP59" t="n">
-        <v>184</v>
+        <v>182.4583333333333</v>
       </c>
       <c r="AQ59" t="n">
-        <v>1.142857142857143</v>
+        <v>1.333333333333333</v>
       </c>
       <c r="AR59" t="n">
-        <v>71.66666666666667</v>
+        <v>74.16666666666667</v>
       </c>
       <c r="AS59" t="n">
-        <v>6963095.238095238</v>
+        <v>11691666.66666667</v>
       </c>
       <c r="AT59" t="n">
-        <v>76.42857142857143</v>
+        <v>80.625</v>
       </c>
       <c r="AU59" t="n">
-        <v>23.92307692307692</v>
+        <v>23.52173913043478</v>
       </c>
       <c r="AV59" t="n">
-        <v>188.1538461538462</v>
+        <v>184.1304347826087</v>
       </c>
       <c r="AW59" t="n">
-        <v>1.307692307692308</v>
+        <v>1</v>
       </c>
       <c r="AX59" t="n">
-        <v>74.76923076923077</v>
+        <v>66.47826086956522</v>
       </c>
       <c r="AY59" t="n">
-        <v>12796923.07692308</v>
+        <v>1631304.347826087</v>
       </c>
       <c r="AZ59" t="n">
-        <v>79.07692307692308</v>
+        <v>73.65217391304348</v>
       </c>
       <c r="BA59" t="n">
-        <v>22.33333333333333</v>
+        <v>25.5</v>
       </c>
       <c r="BB59" t="n">
-        <v>186.6666666666667</v>
+        <v>185.5</v>
       </c>
       <c r="BC59" t="n">
-        <v>1.333333333333333</v>
+        <v>1</v>
       </c>
       <c r="BD59" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BE59" t="n">
-        <v>220</v>
+        <v>155</v>
       </c>
       <c r="BF59" t="n">
-        <v>47500000</v>
+        <v>30500000</v>
       </c>
       <c r="BG59" t="n">
-        <v>244</v>
+        <v>160</v>
       </c>
       <c r="BH59" t="n">
-        <v>26.25</v>
+        <v>26.75</v>
       </c>
       <c r="BI59" t="n">
-        <v>189.25</v>
+        <v>178.75</v>
       </c>
       <c r="BJ59" t="n">
-        <v>1.75</v>
+        <v>1</v>
       </c>
       <c r="BK59" t="n">
         <v>4</v>
       </c>
       <c r="BL59" t="n">
-        <v>314</v>
+        <v>284</v>
       </c>
       <c r="BM59" t="n">
-        <v>74000000</v>
+        <v>14625000</v>
       </c>
       <c r="BN59" t="n">
-        <v>329</v>
+        <v>299</v>
       </c>
     </row>
     <row r="60">
@@ -12516,7 +12516,7 @@
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>CSXdOfL8</t>
+          <t>CxyB0iT1</t>
         </is>
       </c>
       <c r="B62" s="2" t="n">
@@ -12524,72 +12524,72 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t xml:space="preserve">cosso f 
+          <t xml:space="preserve">colombo a 
   ita </t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio luigi ferraris
-  genoa </t>
+          <t xml:space="preserve">arena garibaldi   stadio romeo anconetani
+  pisa </t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>36599</v>
+        <v>14869</v>
       </c>
       <c r="F62" t="n">
-        <v>23061</v>
+        <v>8811</v>
       </c>
       <c r="G62" t="n">
+        <v>2</v>
+      </c>
+      <c r="H62" t="n">
         <v>0</v>
       </c>
-      <c r="H62" t="n">
-        <v>1</v>
-      </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>nJbCGx2U</t>
+          <t>roasMsOT</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>6ulJbMCe</t>
+          <t>n38Nktmn</t>
         </is>
       </c>
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="n">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="N62" t="n">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="O62" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="P62" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="Q62" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="R62" t="n">
         <v>4</v>
       </c>
       <c r="S62" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T62" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>2kfSDavF</t>
+          <t>GfucctAF</t>
         </is>
       </c>
       <c r="V62" t="inlineStr">
         <is>
-          <t>Gfur2NmR</t>
+          <t>Wn0poKgt</t>
         </is>
       </c>
       <c r="W62" t="n">
@@ -12606,81 +12606,85 @@
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>d0PJxeie</t>
-        </is>
-      </c>
-      <c r="AB62" t="inlineStr"/>
+          <t>Q3A3IbXH</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>pfo9H1Wp</t>
+        </is>
+      </c>
       <c r="AC62" t="n">
-        <v>26.33333333333333</v>
+        <v>24.81818181818182</v>
       </c>
       <c r="AD62" t="n">
-        <v>181.5555555555555</v>
+        <v>186</v>
       </c>
       <c r="AE62" t="n">
         <v>1</v>
       </c>
       <c r="AF62" t="n">
-        <v>69</v>
+        <v>67.18181818181819</v>
       </c>
       <c r="AG62" t="n">
-        <v>1658333.333333333</v>
+        <v>1525000</v>
       </c>
       <c r="AH62" t="n">
-        <v>73.33333333333333</v>
+        <v>71.81818181818181</v>
       </c>
       <c r="AI62" t="n">
-        <v>25.5</v>
+        <v>25</v>
       </c>
       <c r="AJ62" t="n">
-        <v>182.9</v>
+        <v>182.6363636363636</v>
       </c>
       <c r="AK62" t="n">
         <v>1</v>
       </c>
       <c r="AL62" t="n">
-        <v>64.5</v>
+        <v>70.09090909090909</v>
       </c>
       <c r="AM62" t="n">
-        <v>1119000</v>
+        <v>2700000</v>
       </c>
       <c r="AN62" t="n">
-        <v>68.8</v>
+        <v>75.27272727272727</v>
       </c>
       <c r="AO62" t="n">
-        <v>24.15789473684211</v>
+        <v>23.09090909090909</v>
       </c>
       <c r="AP62" t="n">
-        <v>183.578947368421</v>
+        <v>182.1818181818182</v>
       </c>
       <c r="AQ62" t="n">
-        <v>1.052631578947368</v>
+        <v>1</v>
       </c>
       <c r="AR62" t="n">
-        <v>67.36842105263158</v>
+        <v>66.31818181818181</v>
       </c>
       <c r="AS62" t="n">
-        <v>1738157.894736842</v>
+        <v>1950000</v>
       </c>
       <c r="AT62" t="n">
-        <v>72.84210526315789</v>
+        <v>73.31818181818181</v>
       </c>
       <c r="AU62" t="n">
-        <v>27.8</v>
+        <v>23.82608695652174</v>
       </c>
       <c r="AV62" t="n">
-        <v>182.8</v>
+        <v>183.9130434782609</v>
       </c>
       <c r="AW62" t="n">
-        <v>1</v>
+        <v>1.043478260869565</v>
       </c>
       <c r="AX62" t="n">
-        <v>65.93333333333334</v>
+        <v>69.17391304347827</v>
       </c>
       <c r="AY62" t="n">
-        <v>1074333.333333333</v>
+        <v>2547826.086956522</v>
       </c>
       <c r="AZ62" t="n">
-        <v>69.2</v>
+        <v>75.78260869565217</v>
       </c>
       <c r="BA62" t="inlineStr"/>
       <c r="BB62" t="inlineStr"/>
@@ -12700,7 +12704,7 @@
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>4QCyHCDr</t>
+          <t>CSXdOfL8</t>
         </is>
       </c>
       <c r="B63" s="2" t="n">
@@ -12708,72 +12712,72 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t xml:space="preserve">pezzuto i 
+          <t xml:space="preserve">cosso f 
   ita </t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio alberto picco
-  la spezia </t>
+          <t xml:space="preserve">stadio luigi ferraris
+  genoa </t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>11466</v>
+        <v>36599</v>
       </c>
       <c r="F63" t="n">
-        <v>7821</v>
+        <v>23061</v>
       </c>
       <c r="G63" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H63" t="n">
         <v>1</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>re6VD39b</t>
+          <t>nJbCGx2U</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>pfo9H1Wp</t>
+          <t>6ulJbMCe</t>
         </is>
       </c>
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr"/>
       <c r="M63" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="N63" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="O63" t="n">
+        <v>9</v>
+      </c>
+      <c r="P63" t="n">
+        <v>19</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>1</v>
+      </c>
+      <c r="R63" t="n">
+        <v>4</v>
+      </c>
+      <c r="S63" t="n">
+        <v>11</v>
+      </c>
+      <c r="T63" t="n">
         <v>12</v>
       </c>
-      <c r="P63" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q63" t="n">
-        <v>6</v>
-      </c>
-      <c r="R63" t="n">
-        <v>3</v>
-      </c>
-      <c r="S63" t="n">
-        <v>19</v>
-      </c>
-      <c r="T63" t="n">
-        <v>18</v>
-      </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>O6SinSSs</t>
+          <t>2kfSDavF</t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
         <is>
-          <t>dnLs0wVo</t>
+          <t>Gfur2NmR</t>
         </is>
       </c>
       <c r="W63" t="n">
@@ -12793,82 +12797,78 @@
           <t>d0PJxeie</t>
         </is>
       </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>0M9xNN8N</t>
-        </is>
-      </c>
+      <c r="AB63" t="inlineStr"/>
       <c r="AC63" t="n">
-        <v>25.66666666666667</v>
+        <v>26.33333333333333</v>
       </c>
       <c r="AD63" t="n">
-        <v>184.8888888888889</v>
+        <v>181.5555555555555</v>
       </c>
       <c r="AE63" t="n">
         <v>1</v>
       </c>
       <c r="AF63" t="n">
-        <v>67.66666666666667</v>
+        <v>69</v>
       </c>
       <c r="AG63" t="n">
-        <v>1516666.666666667</v>
+        <v>1658333.333333333</v>
       </c>
       <c r="AH63" t="n">
-        <v>71.77777777777777</v>
+        <v>73.33333333333333</v>
       </c>
       <c r="AI63" t="n">
-        <v>22.44444444444444</v>
+        <v>25.5</v>
       </c>
       <c r="AJ63" t="n">
-        <v>185.1111111111111</v>
+        <v>182.9</v>
       </c>
       <c r="AK63" t="n">
         <v>1</v>
       </c>
       <c r="AL63" t="n">
-        <v>66.11111111111111</v>
+        <v>64.5</v>
       </c>
       <c r="AM63" t="n">
-        <v>1619444.444444444</v>
+        <v>1119000</v>
       </c>
       <c r="AN63" t="n">
-        <v>73.77777777777777</v>
+        <v>68.8</v>
       </c>
       <c r="AO63" t="n">
-        <v>23.77272727272727</v>
+        <v>24.15789473684211</v>
       </c>
       <c r="AP63" t="n">
-        <v>184.3181818181818</v>
+        <v>183.578947368421</v>
       </c>
       <c r="AQ63" t="n">
-        <v>1</v>
+        <v>1.052631578947368</v>
       </c>
       <c r="AR63" t="n">
-        <v>65.04545454545455</v>
+        <v>67.36842105263158</v>
       </c>
       <c r="AS63" t="n">
-        <v>1237500</v>
+        <v>1738157.894736842</v>
       </c>
       <c r="AT63" t="n">
-        <v>71.54545454545455</v>
+        <v>72.84210526315789</v>
       </c>
       <c r="AU63" t="n">
-        <v>22.23809523809524</v>
+        <v>27.8</v>
       </c>
       <c r="AV63" t="n">
-        <v>183.8571428571429</v>
+        <v>182.8</v>
       </c>
       <c r="AW63" t="n">
         <v>1</v>
       </c>
       <c r="AX63" t="n">
-        <v>64.47619047619048</v>
+        <v>65.93333333333334</v>
       </c>
       <c r="AY63" t="n">
-        <v>1373809.523809524</v>
+        <v>1074333.333333333</v>
       </c>
       <c r="AZ63" t="n">
-        <v>73.57142857142857</v>
+        <v>69.2</v>
       </c>
       <c r="BA63" t="inlineStr"/>
       <c r="BB63" t="inlineStr"/>
@@ -13064,7 +13064,7 @@
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>CEhO9e6F</t>
+          <t>4QCyHCDr</t>
         </is>
       </c>
       <c r="B65" s="2" t="n">
@@ -13072,72 +13072,72 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t xml:space="preserve">ghersini d 
+          <t xml:space="preserve">pezzuto i 
   ita </t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio giovanni zini
-  cremona </t>
+          <t xml:space="preserve">stadio alberto picco
+  la spezia </t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>20641</v>
+        <v>11466</v>
       </c>
       <c r="F65" t="n">
-        <v>8577</v>
+        <v>7821</v>
       </c>
       <c r="G65" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>KUzfp5N3</t>
+          <t>re6VD39b</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>hG4fg4z3</t>
+          <t>pfo9H1Wp</t>
         </is>
       </c>
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr"/>
       <c r="M65" t="n">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="N65" t="n">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="O65" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="P65" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Q65" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="R65" t="n">
         <v>3</v>
       </c>
       <c r="S65" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="T65" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>YgLhKnOo</t>
+          <t>O6SinSSs</t>
         </is>
       </c>
       <c r="V65" t="inlineStr">
         <is>
-          <t>lSb6U6l0</t>
+          <t>dnLs0wVo</t>
         </is>
       </c>
       <c r="W65" t="n">
@@ -13154,69 +13154,85 @@
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>ttyLthOA</t>
-        </is>
-      </c>
-      <c r="AB65" t="inlineStr"/>
+          <t>d0PJxeie</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>0M9xNN8N</t>
+        </is>
+      </c>
       <c r="AC65" t="n">
-        <v>26.18181818181818</v>
+        <v>25.66666666666667</v>
       </c>
       <c r="AD65" t="n">
-        <v>184.3636363636364</v>
+        <v>184.8888888888889</v>
       </c>
       <c r="AE65" t="n">
         <v>1</v>
       </c>
       <c r="AF65" t="n">
-        <v>69.54545454545455</v>
+        <v>67.66666666666667</v>
       </c>
       <c r="AG65" t="n">
-        <v>1772727.272727273</v>
+        <v>1516666.666666667</v>
       </c>
       <c r="AH65" t="n">
-        <v>72.63636363636364</v>
-      </c>
-      <c r="AI65" t="inlineStr"/>
-      <c r="AJ65" t="inlineStr"/>
-      <c r="AK65" t="inlineStr"/>
-      <c r="AL65" t="inlineStr"/>
-      <c r="AM65" t="inlineStr"/>
-      <c r="AN65" t="inlineStr"/>
+        <v>71.77777777777777</v>
+      </c>
+      <c r="AI65" t="n">
+        <v>22.44444444444444</v>
+      </c>
+      <c r="AJ65" t="n">
+        <v>185.1111111111111</v>
+      </c>
+      <c r="AK65" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL65" t="n">
+        <v>66.11111111111111</v>
+      </c>
+      <c r="AM65" t="n">
+        <v>1619444.444444444</v>
+      </c>
+      <c r="AN65" t="n">
+        <v>73.77777777777777</v>
+      </c>
       <c r="AO65" t="n">
-        <v>24.54166666666667</v>
+        <v>23.77272727272727</v>
       </c>
       <c r="AP65" t="n">
-        <v>183.3333333333333</v>
+        <v>184.3181818181818</v>
       </c>
       <c r="AQ65" t="n">
-        <v>1.125</v>
+        <v>1</v>
       </c>
       <c r="AR65" t="n">
-        <v>69.04166666666667</v>
+        <v>65.04545454545455</v>
       </c>
       <c r="AS65" t="n">
-        <v>2191666.666666667</v>
+        <v>1237500</v>
       </c>
       <c r="AT65" t="n">
-        <v>74.375</v>
+        <v>71.54545454545455</v>
       </c>
       <c r="AU65" t="n">
-        <v>21.8</v>
+        <v>22.23809523809524</v>
       </c>
       <c r="AV65" t="n">
-        <v>180.8</v>
+        <v>183.8571428571429</v>
       </c>
       <c r="AW65" t="n">
         <v>1</v>
       </c>
       <c r="AX65" t="n">
-        <v>64.40000000000001</v>
+        <v>64.47619047619048</v>
       </c>
       <c r="AY65" t="n">
-        <v>1350000</v>
+        <v>1373809.523809524</v>
       </c>
       <c r="AZ65" t="n">
-        <v>74.59999999999999</v>
+        <v>73.57142857142857</v>
       </c>
       <c r="BA65" t="inlineStr"/>
       <c r="BB65" t="inlineStr"/>
@@ -13236,7 +13252,7 @@
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>CxyB0iT1</t>
+          <t>CEhO9e6F</t>
         </is>
       </c>
       <c r="B66" s="2" t="n">
@@ -13244,72 +13260,72 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t xml:space="preserve">colombo a 
+          <t xml:space="preserve">ghersini d 
   ita </t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t xml:space="preserve">arena garibaldi   stadio romeo anconetani
-  pisa </t>
+          <t xml:space="preserve">stadio giovanni zini
+  cremona </t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>14869</v>
+        <v>20641</v>
       </c>
       <c r="F66" t="n">
-        <v>8811</v>
+        <v>8577</v>
       </c>
       <c r="G66" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H66" t="n">
         <v>0</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>roasMsOT</t>
+          <t>KUzfp5N3</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>n38Nktmn</t>
+          <t>hG4fg4z3</t>
         </is>
       </c>
       <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr"/>
       <c r="M66" t="n">
-        <v>34</v>
+        <v>63</v>
       </c>
       <c r="N66" t="n">
-        <v>66</v>
+        <v>37</v>
       </c>
       <c r="O66" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="P66" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="Q66" t="n">
         <v>4</v>
       </c>
       <c r="R66" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S66" t="n">
         <v>8</v>
       </c>
       <c r="T66" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>GfucctAF</t>
+          <t>YgLhKnOo</t>
         </is>
       </c>
       <c r="V66" t="inlineStr">
         <is>
-          <t>Wn0poKgt</t>
+          <t>lSb6U6l0</t>
         </is>
       </c>
       <c r="W66" t="n">
@@ -13326,85 +13342,69 @@
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>Q3A3IbXH</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>pfo9H1Wp</t>
-        </is>
-      </c>
+          <t>ttyLthOA</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr"/>
       <c r="AC66" t="n">
-        <v>24.81818181818182</v>
+        <v>26.18181818181818</v>
       </c>
       <c r="AD66" t="n">
-        <v>186</v>
+        <v>184.3636363636364</v>
       </c>
       <c r="AE66" t="n">
         <v>1</v>
       </c>
       <c r="AF66" t="n">
-        <v>67.18181818181819</v>
+        <v>69.54545454545455</v>
       </c>
       <c r="AG66" t="n">
-        <v>1525000</v>
+        <v>1772727.272727273</v>
       </c>
       <c r="AH66" t="n">
-        <v>71.81818181818181</v>
-      </c>
-      <c r="AI66" t="n">
-        <v>25</v>
-      </c>
-      <c r="AJ66" t="n">
-        <v>182.6363636363636</v>
-      </c>
-      <c r="AK66" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL66" t="n">
-        <v>70.09090909090909</v>
-      </c>
-      <c r="AM66" t="n">
-        <v>2700000</v>
-      </c>
-      <c r="AN66" t="n">
-        <v>75.27272727272727</v>
-      </c>
+        <v>72.63636363636364</v>
+      </c>
+      <c r="AI66" t="inlineStr"/>
+      <c r="AJ66" t="inlineStr"/>
+      <c r="AK66" t="inlineStr"/>
+      <c r="AL66" t="inlineStr"/>
+      <c r="AM66" t="inlineStr"/>
+      <c r="AN66" t="inlineStr"/>
       <c r="AO66" t="n">
-        <v>23.09090909090909</v>
+        <v>24.54166666666667</v>
       </c>
       <c r="AP66" t="n">
-        <v>182.1818181818182</v>
+        <v>183.3333333333333</v>
       </c>
       <c r="AQ66" t="n">
-        <v>1</v>
+        <v>1.125</v>
       </c>
       <c r="AR66" t="n">
-        <v>66.31818181818181</v>
+        <v>69.04166666666667</v>
       </c>
       <c r="AS66" t="n">
-        <v>1950000</v>
+        <v>2191666.666666667</v>
       </c>
       <c r="AT66" t="n">
-        <v>73.31818181818181</v>
+        <v>74.375</v>
       </c>
       <c r="AU66" t="n">
-        <v>23.82608695652174</v>
+        <v>21.8</v>
       </c>
       <c r="AV66" t="n">
-        <v>183.9130434782609</v>
+        <v>180.8</v>
       </c>
       <c r="AW66" t="n">
-        <v>1.043478260869565</v>
+        <v>1</v>
       </c>
       <c r="AX66" t="n">
-        <v>69.17391304347827</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="AY66" t="n">
-        <v>2547826.086956522</v>
+        <v>1350000</v>
       </c>
       <c r="AZ66" t="n">
-        <v>75.78260869565217</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="BA66" t="inlineStr"/>
       <c r="BB66" t="inlineStr"/>
@@ -14397,2200 +14397,6 @@
       <c r="BM71" t="inlineStr"/>
       <c r="BN71" t="inlineStr"/>
     </row>
-    <row r="72">
-      <c r="A72" s="1" t="inlineStr">
-        <is>
-          <t>EirZ0Wr4</t>
-        </is>
-      </c>
-      <c r="B72" s="2" t="n">
-        <v>45523.65625</v>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t xml:space="preserve">marcenaro m 
-  ita </t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t xml:space="preserve">allianz stadium
-  turin </t>
-        </is>
-      </c>
-      <c r="E72" t="n">
-        <v>41507</v>
-      </c>
-      <c r="F72" t="n">
-        <v>40696</v>
-      </c>
-      <c r="G72" t="n">
-        <v>3</v>
-      </c>
-      <c r="H72" t="n">
-        <v>0</v>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>C06aJvIB</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>ttyLthOA</t>
-        </is>
-      </c>
-      <c r="K72" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="L72" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="M72" t="n">
-        <v>58</v>
-      </c>
-      <c r="N72" t="n">
-        <v>42</v>
-      </c>
-      <c r="O72" t="n">
-        <v>12</v>
-      </c>
-      <c r="P72" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q72" t="n">
-        <v>9</v>
-      </c>
-      <c r="R72" t="n">
-        <v>1</v>
-      </c>
-      <c r="S72" t="n">
-        <v>11</v>
-      </c>
-      <c r="T72" t="n">
-        <v>12</v>
-      </c>
-      <c r="U72" t="inlineStr">
-        <is>
-          <t>bBhpZV2s</t>
-        </is>
-      </c>
-      <c r="V72" t="inlineStr">
-        <is>
-          <t>YXIDwoe5</t>
-        </is>
-      </c>
-      <c r="W72" t="n">
-        <v>77</v>
-      </c>
-      <c r="X72" t="n">
-        <v>771</v>
-      </c>
-      <c r="Y72" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z72" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="AA72" t="inlineStr">
-        <is>
-          <t>Iw7eKK25</t>
-        </is>
-      </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>4YSMlwj7</t>
-        </is>
-      </c>
-      <c r="AC72" t="n">
-        <v>23.77777777777778</v>
-      </c>
-      <c r="AD72" t="n">
-        <v>186.7777777777778</v>
-      </c>
-      <c r="AE72" t="n">
-        <v>1.444444444444444</v>
-      </c>
-      <c r="AF72" t="n">
-        <v>78.66666666666667</v>
-      </c>
-      <c r="AG72" t="n">
-        <v>27666666.66666667</v>
-      </c>
-      <c r="AH72" t="n">
-        <v>83.11111111111111</v>
-      </c>
-      <c r="AI72" t="n">
-        <v>28</v>
-      </c>
-      <c r="AJ72" t="n">
-        <v>180.8888888888889</v>
-      </c>
-      <c r="AK72" t="n">
-        <v>1.555555555555556</v>
-      </c>
-      <c r="AL72" t="n">
-        <v>72.77777777777777</v>
-      </c>
-      <c r="AM72" t="n">
-        <v>4591666.666666667</v>
-      </c>
-      <c r="AN72" t="n">
-        <v>74.66666666666667</v>
-      </c>
-      <c r="AO72" t="n">
-        <v>24.83333333333333</v>
-      </c>
-      <c r="AP72" t="n">
-        <v>182.0833333333333</v>
-      </c>
-      <c r="AQ72" t="n">
-        <v>1.666666666666667</v>
-      </c>
-      <c r="AR72" t="n">
-        <v>78.33333333333333</v>
-      </c>
-      <c r="AS72" t="n">
-        <v>23437500</v>
-      </c>
-      <c r="AT72" t="n">
-        <v>82.41666666666667</v>
-      </c>
-      <c r="AU72" t="n">
-        <v>26.47826086956522</v>
-      </c>
-      <c r="AV72" t="n">
-        <v>184.8695652173913</v>
-      </c>
-      <c r="AW72" t="n">
-        <v>1.260869565217391</v>
-      </c>
-      <c r="AX72" t="n">
-        <v>70.8695652173913</v>
-      </c>
-      <c r="AY72" t="n">
-        <v>3566304.347826087</v>
-      </c>
-      <c r="AZ72" t="n">
-        <v>72.78260869565217</v>
-      </c>
-      <c r="BA72" t="n">
-        <v>27</v>
-      </c>
-      <c r="BB72" t="n">
-        <v>185.25</v>
-      </c>
-      <c r="BC72" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="BD72" t="n">
-        <v>4</v>
-      </c>
-      <c r="BE72" t="n">
-        <v>321</v>
-      </c>
-      <c r="BF72" t="n">
-        <v>103000000</v>
-      </c>
-      <c r="BG72" t="n">
-        <v>334</v>
-      </c>
-      <c r="BH72" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="BI72" t="n">
-        <v>189</v>
-      </c>
-      <c r="BJ72" t="n">
-        <v>2</v>
-      </c>
-      <c r="BK72" t="n">
-        <v>2</v>
-      </c>
-      <c r="BL72" t="n">
-        <v>156</v>
-      </c>
-      <c r="BM72" t="n">
-        <v>33200000</v>
-      </c>
-      <c r="BN72" t="n">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="1" t="inlineStr">
-        <is>
-          <t>t4ZkclrT</t>
-        </is>
-      </c>
-      <c r="B73" s="2" t="n">
-        <v>45523.5625</v>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t xml:space="preserve">massa d 
-  ita </t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stadio via del mare
-  lecce </t>
-        </is>
-      </c>
-      <c r="E73" t="n">
-        <v>40670</v>
-      </c>
-      <c r="F73" t="n">
-        <v>28719</v>
-      </c>
-      <c r="G73" t="n">
-        <v>0</v>
-      </c>
-      <c r="H73" t="n">
-        <v>4</v>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>G8lYsMgU</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>8C9JjMXu</t>
-        </is>
-      </c>
-      <c r="K73" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="L73" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="M73" t="n">
-        <v>47</v>
-      </c>
-      <c r="N73" t="n">
-        <v>53</v>
-      </c>
-      <c r="O73" t="n">
-        <v>19</v>
-      </c>
-      <c r="P73" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q73" t="n">
-        <v>5</v>
-      </c>
-      <c r="R73" t="n">
-        <v>6</v>
-      </c>
-      <c r="S73" t="n">
-        <v>10</v>
-      </c>
-      <c r="T73" t="n">
-        <v>24</v>
-      </c>
-      <c r="U73" t="inlineStr">
-        <is>
-          <t>KtGrCa5d</t>
-        </is>
-      </c>
-      <c r="V73" t="inlineStr">
-        <is>
-          <t>EJLKYOzb</t>
-        </is>
-      </c>
-      <c r="W73" t="n">
-        <v>77</v>
-      </c>
-      <c r="X73" t="n">
-        <v>771</v>
-      </c>
-      <c r="Y73" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z73" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="AA73" t="inlineStr">
-        <is>
-          <t>xIkUr2vO</t>
-        </is>
-      </c>
-      <c r="AB73" t="inlineStr">
-        <is>
-          <t>8Sa8HInO</t>
-        </is>
-      </c>
-      <c r="AC73" t="n">
-        <v>23.88888888888889</v>
-      </c>
-      <c r="AD73" t="n">
-        <v>183.4444444444445</v>
-      </c>
-      <c r="AE73" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF73" t="n">
-        <v>71.22222222222223</v>
-      </c>
-      <c r="AG73" t="n">
-        <v>5044444.444444444</v>
-      </c>
-      <c r="AH73" t="n">
-        <v>77.33333333333333</v>
-      </c>
-      <c r="AI73" t="n">
-        <v>26.3</v>
-      </c>
-      <c r="AJ73" t="n">
-        <v>188.1</v>
-      </c>
-      <c r="AK73" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AL73" t="n">
-        <v>76.90000000000001</v>
-      </c>
-      <c r="AM73" t="n">
-        <v>13650000</v>
-      </c>
-      <c r="AN73" t="n">
-        <v>80.2</v>
-      </c>
-      <c r="AO73" t="n">
-        <v>22.71428571428572</v>
-      </c>
-      <c r="AP73" t="n">
-        <v>181.8571428571429</v>
-      </c>
-      <c r="AQ73" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR73" t="n">
-        <v>67.80952380952381</v>
-      </c>
-      <c r="AS73" t="n">
-        <v>2928571.428571429</v>
-      </c>
-      <c r="AT73" t="n">
-        <v>75.23809523809524</v>
-      </c>
-      <c r="AU73" t="n">
-        <v>24.1875</v>
-      </c>
-      <c r="AV73" t="n">
-        <v>185.3125</v>
-      </c>
-      <c r="AW73" t="n">
-        <v>1.3125</v>
-      </c>
-      <c r="AX73" t="n">
-        <v>73.375</v>
-      </c>
-      <c r="AY73" t="n">
-        <v>9003750</v>
-      </c>
-      <c r="AZ73" t="n">
-        <v>78.25</v>
-      </c>
-      <c r="BA73" t="n">
-        <v>24.33333333333333</v>
-      </c>
-      <c r="BB73" t="n">
-        <v>182</v>
-      </c>
-      <c r="BC73" t="n">
-        <v>1.333333333333333</v>
-      </c>
-      <c r="BD73" t="n">
-        <v>3</v>
-      </c>
-      <c r="BE73" t="n">
-        <v>213</v>
-      </c>
-      <c r="BF73" t="n">
-        <v>10300000</v>
-      </c>
-      <c r="BG73" t="n">
-        <v>230</v>
-      </c>
-      <c r="BH73" t="n">
-        <v>25.6</v>
-      </c>
-      <c r="BI73" t="n">
-        <v>189.4</v>
-      </c>
-      <c r="BJ73" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="BK73" t="n">
-        <v>5</v>
-      </c>
-      <c r="BL73" t="n">
-        <v>393</v>
-      </c>
-      <c r="BM73" t="n">
-        <v>95500000</v>
-      </c>
-      <c r="BN73" t="n">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="1" t="inlineStr">
-        <is>
-          <t>8jyraADG</t>
-        </is>
-      </c>
-      <c r="B74" s="2" t="n">
-        <v>45522.65625</v>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t xml:space="preserve">tremolada p 
-  ita </t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stadio olimpico
-  rome </t>
-        </is>
-      </c>
-      <c r="E74" t="n">
-        <v>70634</v>
-      </c>
-      <c r="F74" t="n">
-        <v>42000</v>
-      </c>
-      <c r="G74" t="n">
-        <v>3</v>
-      </c>
-      <c r="H74" t="n">
-        <v>1</v>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>URcSl02h</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>MkPmVv50</t>
-        </is>
-      </c>
-      <c r="K74" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="L74" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="M74" t="n">
-        <v>67</v>
-      </c>
-      <c r="N74" t="n">
-        <v>33</v>
-      </c>
-      <c r="O74" t="n">
-        <v>13</v>
-      </c>
-      <c r="P74" t="n">
-        <v>11</v>
-      </c>
-      <c r="Q74" t="n">
-        <v>6</v>
-      </c>
-      <c r="R74" t="n">
-        <v>3</v>
-      </c>
-      <c r="S74" t="n">
-        <v>14</v>
-      </c>
-      <c r="T74" t="n">
-        <v>11</v>
-      </c>
-      <c r="U74" t="inlineStr">
-        <is>
-          <t>S8Ygn9ME</t>
-        </is>
-      </c>
-      <c r="V74" t="inlineStr">
-        <is>
-          <t>n10g3KfJ</t>
-        </is>
-      </c>
-      <c r="W74" t="n">
-        <v>77</v>
-      </c>
-      <c r="X74" t="n">
-        <v>771</v>
-      </c>
-      <c r="Y74" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z74" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="AA74" t="inlineStr">
-        <is>
-          <t>zVqqL0ma</t>
-        </is>
-      </c>
-      <c r="AB74" t="inlineStr">
-        <is>
-          <t>rJVAIaHo</t>
-        </is>
-      </c>
-      <c r="AC74" t="n">
-        <v>26.1</v>
-      </c>
-      <c r="AD74" t="n">
-        <v>182.4</v>
-      </c>
-      <c r="AE74" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AF74" t="n">
-        <v>79</v>
-      </c>
-      <c r="AG74" t="n">
-        <v>20770000</v>
-      </c>
-      <c r="AH74" t="n">
-        <v>81.5</v>
-      </c>
-      <c r="AI74" t="n">
-        <v>26</v>
-      </c>
-      <c r="AJ74" t="n">
-        <v>183.5</v>
-      </c>
-      <c r="AK74" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AL74" t="n">
-        <v>69.90000000000001</v>
-      </c>
-      <c r="AM74" t="n">
-        <v>2240000</v>
-      </c>
-      <c r="AN74" t="n">
-        <v>74.2</v>
-      </c>
-      <c r="AO74" t="n">
-        <v>24.64</v>
-      </c>
-      <c r="AP74" t="n">
-        <v>182.4</v>
-      </c>
-      <c r="AQ74" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AR74" t="n">
-        <v>74.36</v>
-      </c>
-      <c r="AS74" t="n">
-        <v>11178000</v>
-      </c>
-      <c r="AT74" t="n">
-        <v>78.76000000000001</v>
-      </c>
-      <c r="AU74" t="n">
-        <v>24.47619047619047</v>
-      </c>
-      <c r="AV74" t="n">
-        <v>181.7619047619048</v>
-      </c>
-      <c r="AW74" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX74" t="n">
-        <v>66.52380952380952</v>
-      </c>
-      <c r="AY74" t="n">
-        <v>1505714.285714286</v>
-      </c>
-      <c r="AZ74" t="n">
-        <v>72.42857142857143</v>
-      </c>
-      <c r="BA74" t="n">
-        <v>22</v>
-      </c>
-      <c r="BB74" t="n">
-        <v>185</v>
-      </c>
-      <c r="BC74" t="n">
-        <v>1</v>
-      </c>
-      <c r="BD74" t="n">
-        <v>1</v>
-      </c>
-      <c r="BE74" t="n">
-        <v>66</v>
-      </c>
-      <c r="BF74" t="n">
-        <v>1200000</v>
-      </c>
-      <c r="BG74" t="n">
-        <v>72</v>
-      </c>
-      <c r="BH74" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="BI74" t="n">
-        <v>181.5</v>
-      </c>
-      <c r="BJ74" t="n">
-        <v>1</v>
-      </c>
-      <c r="BK74" t="n">
-        <v>6</v>
-      </c>
-      <c r="BL74" t="n">
-        <v>423</v>
-      </c>
-      <c r="BM74" t="n">
-        <v>19125000</v>
-      </c>
-      <c r="BN74" t="n">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="1" t="inlineStr">
-        <is>
-          <t>YH892O2B</t>
-        </is>
-      </c>
-      <c r="B75" s="2" t="n">
-        <v>45522.65625</v>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t xml:space="preserve">la penna f 
-  ita </t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t xml:space="preserve">unipol domus
-  cagliari </t>
-        </is>
-      </c>
-      <c r="E75" t="n">
-        <v>16416</v>
-      </c>
-      <c r="F75" t="n">
-        <v>16261</v>
-      </c>
-      <c r="G75" t="n">
-        <v>0</v>
-      </c>
-      <c r="H75" t="n">
-        <v>0</v>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>SCGVmKHb</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>zVqqL0ma</t>
-        </is>
-      </c>
-      <c r="K75" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="L75" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="M75" t="n">
-        <v>43</v>
-      </c>
-      <c r="N75" t="n">
-        <v>57</v>
-      </c>
-      <c r="O75" t="n">
-        <v>12</v>
-      </c>
-      <c r="P75" t="n">
-        <v>13</v>
-      </c>
-      <c r="Q75" t="n">
-        <v>2</v>
-      </c>
-      <c r="R75" t="n">
-        <v>3</v>
-      </c>
-      <c r="S75" t="n">
-        <v>15</v>
-      </c>
-      <c r="T75" t="n">
-        <v>7</v>
-      </c>
-      <c r="U75" t="inlineStr">
-        <is>
-          <t>MLVBCoYg</t>
-        </is>
-      </c>
-      <c r="V75" t="inlineStr">
-        <is>
-          <t>xjigzK81</t>
-        </is>
-      </c>
-      <c r="W75" t="n">
-        <v>77</v>
-      </c>
-      <c r="X75" t="n">
-        <v>771</v>
-      </c>
-      <c r="Y75" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z75" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="AA75" t="inlineStr">
-        <is>
-          <t>69Dxbc61</t>
-        </is>
-      </c>
-      <c r="AB75" t="inlineStr">
-        <is>
-          <t>URcSl02h</t>
-        </is>
-      </c>
-      <c r="AC75" t="n">
-        <v>24.90909090909091</v>
-      </c>
-      <c r="AD75" t="n">
-        <v>185</v>
-      </c>
-      <c r="AE75" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF75" t="n">
-        <v>72.36363636363636</v>
-      </c>
-      <c r="AG75" t="n">
-        <v>4636363.636363637</v>
-      </c>
-      <c r="AH75" t="n">
-        <v>76.18181818181819</v>
-      </c>
-      <c r="AI75" t="n">
-        <v>24.7</v>
-      </c>
-      <c r="AJ75" t="n">
-        <v>181.9</v>
-      </c>
-      <c r="AK75" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AL75" t="n">
-        <v>78.09999999999999</v>
-      </c>
-      <c r="AM75" t="n">
-        <v>19680000</v>
-      </c>
-      <c r="AN75" t="n">
-        <v>81.40000000000001</v>
-      </c>
-      <c r="AO75" t="n">
-        <v>26.25</v>
-      </c>
-      <c r="AP75" t="n">
-        <v>184</v>
-      </c>
-      <c r="AQ75" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AR75" t="n">
-        <v>68.95</v>
-      </c>
-      <c r="AS75" t="n">
-        <v>2293750</v>
-      </c>
-      <c r="AT75" t="n">
-        <v>73.7</v>
-      </c>
-      <c r="AU75" t="n">
-        <v>24.76190476190476</v>
-      </c>
-      <c r="AV75" t="n">
-        <v>180.6190476190476</v>
-      </c>
-      <c r="AW75" t="n">
-        <v>1.857142857142857</v>
-      </c>
-      <c r="AX75" t="n">
-        <v>77.33333333333333</v>
-      </c>
-      <c r="AY75" t="n">
-        <v>24078571.42857143</v>
-      </c>
-      <c r="AZ75" t="n">
-        <v>82.28571428571429</v>
-      </c>
-      <c r="BA75" t="n">
-        <v>28</v>
-      </c>
-      <c r="BB75" t="n">
-        <v>183.5</v>
-      </c>
-      <c r="BC75" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="BD75" t="n">
-        <v>4</v>
-      </c>
-      <c r="BE75" t="n">
-        <v>288</v>
-      </c>
-      <c r="BF75" t="n">
-        <v>12300000</v>
-      </c>
-      <c r="BG75" t="n">
-        <v>292</v>
-      </c>
-      <c r="BH75" t="n">
-        <v>29</v>
-      </c>
-      <c r="BI75" t="n">
-        <v>180</v>
-      </c>
-      <c r="BJ75" t="n">
-        <v>3</v>
-      </c>
-      <c r="BK75" t="n">
-        <v>1</v>
-      </c>
-      <c r="BL75" t="n">
-        <v>77</v>
-      </c>
-      <c r="BM75" t="n">
-        <v>10500000</v>
-      </c>
-      <c r="BN75" t="n">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="1" t="inlineStr">
-        <is>
-          <t>tYhtcc5C</t>
-        </is>
-      </c>
-      <c r="B76" s="2" t="n">
-        <v>45522.64583333334</v>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t xml:space="preserve">piccinini m 
-  ita </t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stadio nicola ceravolo
-  catanzaro </t>
-        </is>
-      </c>
-      <c r="E76" t="n">
-        <v>14650</v>
-      </c>
-      <c r="F76" t="n">
-        <v>12490</v>
-      </c>
-      <c r="G76" t="n">
-        <v>1</v>
-      </c>
-      <c r="H76" t="n">
-        <v>1</v>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>GnizyMB7</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>QDdvI0zl</t>
-        </is>
-      </c>
-      <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr"/>
-      <c r="M76" t="n">
-        <v>49</v>
-      </c>
-      <c r="N76" t="n">
-        <v>51</v>
-      </c>
-      <c r="O76" t="n">
-        <v>9</v>
-      </c>
-      <c r="P76" t="n">
-        <v>12</v>
-      </c>
-      <c r="Q76" t="n">
-        <v>4</v>
-      </c>
-      <c r="R76" t="n">
-        <v>6</v>
-      </c>
-      <c r="S76" t="n">
-        <v>11</v>
-      </c>
-      <c r="T76" t="n">
-        <v>7</v>
-      </c>
-      <c r="U76" t="inlineStr">
-        <is>
-          <t>nsYMfLJM</t>
-        </is>
-      </c>
-      <c r="V76" t="inlineStr">
-        <is>
-          <t>bPHSQi9q</t>
-        </is>
-      </c>
-      <c r="W76" t="n">
-        <v>77</v>
-      </c>
-      <c r="X76" t="n">
-        <v>774</v>
-      </c>
-      <c r="Y76" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z76" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="AA76" t="inlineStr">
-        <is>
-          <t>p84TeBhA</t>
-        </is>
-      </c>
-      <c r="AB76" t="inlineStr">
-        <is>
-          <t>0M9xNN8N</t>
-        </is>
-      </c>
-      <c r="AC76" t="n">
-        <v>27.77777777777778</v>
-      </c>
-      <c r="AD76" t="n">
-        <v>180.4444444444445</v>
-      </c>
-      <c r="AE76" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF76" t="n">
-        <v>66.88888888888889</v>
-      </c>
-      <c r="AG76" t="n">
-        <v>1030555.555555556</v>
-      </c>
-      <c r="AH76" t="n">
-        <v>69.22222222222223</v>
-      </c>
-      <c r="AI76" t="n">
-        <v>24.54545454545455</v>
-      </c>
-      <c r="AJ76" t="n">
-        <v>185.0909090909091</v>
-      </c>
-      <c r="AK76" t="n">
-        <v>1.181818181818182</v>
-      </c>
-      <c r="AL76" t="n">
-        <v>71.36363636363636</v>
-      </c>
-      <c r="AM76" t="n">
-        <v>5297727.272727272</v>
-      </c>
-      <c r="AN76" t="n">
-        <v>75.27272727272727</v>
-      </c>
-      <c r="AO76" t="n">
-        <v>24.7</v>
-      </c>
-      <c r="AP76" t="n">
-        <v>182.3</v>
-      </c>
-      <c r="AQ76" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR76" t="n">
-        <v>64.59999999999999</v>
-      </c>
-      <c r="AS76" t="n">
-        <v>940000</v>
-      </c>
-      <c r="AT76" t="n">
-        <v>69.2</v>
-      </c>
-      <c r="AU76" t="n">
-        <v>22.1</v>
-      </c>
-      <c r="AV76" t="n">
-        <v>182.35</v>
-      </c>
-      <c r="AW76" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AX76" t="n">
-        <v>67.8</v>
-      </c>
-      <c r="AY76" t="n">
-        <v>2540000</v>
-      </c>
-      <c r="AZ76" t="n">
-        <v>76.65000000000001</v>
-      </c>
-      <c r="BA76" t="inlineStr"/>
-      <c r="BB76" t="inlineStr"/>
-      <c r="BC76" t="inlineStr"/>
-      <c r="BD76" t="inlineStr"/>
-      <c r="BE76" t="inlineStr"/>
-      <c r="BF76" t="inlineStr"/>
-      <c r="BG76" t="inlineStr"/>
-      <c r="BH76" t="inlineStr"/>
-      <c r="BI76" t="inlineStr"/>
-      <c r="BJ76" t="inlineStr"/>
-      <c r="BK76" t="inlineStr"/>
-      <c r="BL76" t="inlineStr"/>
-      <c r="BM76" t="inlineStr"/>
-      <c r="BN76" t="inlineStr"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="1" t="inlineStr">
-        <is>
-          <t>x0nkeyzP</t>
-        </is>
-      </c>
-      <c r="B77" s="2" t="n">
-        <v>45522.64583333334</v>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t xml:space="preserve">prontera a 
-  ita </t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stadio dino manuzzi
-  cesena </t>
-        </is>
-      </c>
-      <c r="E77" t="n">
-        <v>23860</v>
-      </c>
-      <c r="F77" t="n">
-        <v>11382</v>
-      </c>
-      <c r="G77" t="n">
-        <v>2</v>
-      </c>
-      <c r="H77" t="n">
-        <v>1</v>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>xddf1qfh</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>hG4fg4z3</t>
-        </is>
-      </c>
-      <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr"/>
-      <c r="M77" t="n">
-        <v>42</v>
-      </c>
-      <c r="N77" t="n">
-        <v>58</v>
-      </c>
-      <c r="O77" t="n">
-        <v>14</v>
-      </c>
-      <c r="P77" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q77" t="n">
-        <v>8</v>
-      </c>
-      <c r="R77" t="n">
-        <v>4</v>
-      </c>
-      <c r="S77" t="n">
-        <v>13</v>
-      </c>
-      <c r="T77" t="n">
-        <v>14</v>
-      </c>
-      <c r="U77" t="inlineStr">
-        <is>
-          <t>vD8aDRIm</t>
-        </is>
-      </c>
-      <c r="V77" t="inlineStr">
-        <is>
-          <t>lSb6U6l0</t>
-        </is>
-      </c>
-      <c r="W77" t="n">
-        <v>77</v>
-      </c>
-      <c r="X77" t="n">
-        <v>774</v>
-      </c>
-      <c r="Y77" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z77" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="AA77" t="inlineStr"/>
-      <c r="AB77" t="inlineStr"/>
-      <c r="AC77" t="inlineStr"/>
-      <c r="AD77" t="inlineStr"/>
-      <c r="AE77" t="inlineStr"/>
-      <c r="AF77" t="inlineStr"/>
-      <c r="AG77" t="inlineStr"/>
-      <c r="AH77" t="inlineStr"/>
-      <c r="AI77" t="inlineStr"/>
-      <c r="AJ77" t="inlineStr"/>
-      <c r="AK77" t="inlineStr"/>
-      <c r="AL77" t="inlineStr"/>
-      <c r="AM77" t="inlineStr"/>
-      <c r="AN77" t="inlineStr"/>
-      <c r="AO77" t="n">
-        <v>23.66666666666667</v>
-      </c>
-      <c r="AP77" t="n">
-        <v>184.8888888888889</v>
-      </c>
-      <c r="AQ77" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR77" t="n">
-        <v>69</v>
-      </c>
-      <c r="AS77" t="n">
-        <v>2786111.111111111</v>
-      </c>
-      <c r="AT77" t="n">
-        <v>74.88888888888889</v>
-      </c>
-      <c r="AU77" t="n">
-        <v>23.375</v>
-      </c>
-      <c r="AV77" t="n">
-        <v>181.5</v>
-      </c>
-      <c r="AW77" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX77" t="n">
-        <v>62.875</v>
-      </c>
-      <c r="AY77" t="n">
-        <v>871875</v>
-      </c>
-      <c r="AZ77" t="n">
-        <v>70.25</v>
-      </c>
-      <c r="BA77" t="inlineStr"/>
-      <c r="BB77" t="inlineStr"/>
-      <c r="BC77" t="inlineStr"/>
-      <c r="BD77" t="inlineStr"/>
-      <c r="BE77" t="inlineStr"/>
-      <c r="BF77" t="inlineStr"/>
-      <c r="BG77" t="inlineStr"/>
-      <c r="BH77" t="inlineStr"/>
-      <c r="BI77" t="inlineStr"/>
-      <c r="BJ77" t="inlineStr"/>
-      <c r="BK77" t="inlineStr"/>
-      <c r="BL77" t="inlineStr"/>
-      <c r="BM77" t="inlineStr"/>
-      <c r="BN77" t="inlineStr"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="1" t="inlineStr">
-        <is>
-          <t>SORbFvLt</t>
-        </is>
-      </c>
-      <c r="B78" s="2" t="n">
-        <v>45522.64583333334</v>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t xml:space="preserve">bonacina k 
-  ita </t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stadio san vito luigi marulla
-  cosenza </t>
-        </is>
-      </c>
-      <c r="E78" t="n">
-        <v>20987</v>
-      </c>
-      <c r="F78" t="n">
-        <v>6840</v>
-      </c>
-      <c r="G78" t="n">
-        <v>1</v>
-      </c>
-      <c r="H78" t="n">
-        <v>0</v>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>p84TeBhA</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>KUzfp5N3</t>
-        </is>
-      </c>
-      <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr"/>
-      <c r="M78" t="n">
-        <v>32</v>
-      </c>
-      <c r="N78" t="n">
-        <v>68</v>
-      </c>
-      <c r="O78" t="n">
-        <v>15</v>
-      </c>
-      <c r="P78" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q78" t="n">
-        <v>6</v>
-      </c>
-      <c r="R78" t="n">
-        <v>1</v>
-      </c>
-      <c r="S78" t="n">
-        <v>11</v>
-      </c>
-      <c r="T78" t="n">
-        <v>16</v>
-      </c>
-      <c r="U78" t="inlineStr">
-        <is>
-          <t>Yika9O16</t>
-        </is>
-      </c>
-      <c r="V78" t="inlineStr">
-        <is>
-          <t>YgLhKnOo</t>
-        </is>
-      </c>
-      <c r="W78" t="n">
-        <v>77</v>
-      </c>
-      <c r="X78" t="n">
-        <v>774</v>
-      </c>
-      <c r="Y78" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z78" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="AA78" t="inlineStr">
-        <is>
-          <t>GnizyMB7</t>
-        </is>
-      </c>
-      <c r="AB78" t="inlineStr">
-        <is>
-          <t>ttyLthOA</t>
-        </is>
-      </c>
-      <c r="AC78" t="n">
-        <v>24.3</v>
-      </c>
-      <c r="AD78" t="n">
-        <v>184.7</v>
-      </c>
-      <c r="AE78" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF78" t="n">
-        <v>65.7</v>
-      </c>
-      <c r="AG78" t="n">
-        <v>1165000</v>
-      </c>
-      <c r="AH78" t="n">
-        <v>71.59999999999999</v>
-      </c>
-      <c r="AI78" t="n">
-        <v>25.81818181818182</v>
-      </c>
-      <c r="AJ78" t="n">
-        <v>186.0909090909091</v>
-      </c>
-      <c r="AK78" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL78" t="n">
-        <v>69.45454545454545</v>
-      </c>
-      <c r="AM78" t="n">
-        <v>1909090.909090909</v>
-      </c>
-      <c r="AN78" t="n">
-        <v>73</v>
-      </c>
-      <c r="AO78" t="n">
-        <v>23</v>
-      </c>
-      <c r="AP78" t="n">
-        <v>179.2105263157895</v>
-      </c>
-      <c r="AQ78" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR78" t="n">
-        <v>64.63157894736842</v>
-      </c>
-      <c r="AS78" t="n">
-        <v>1147368.421052632</v>
-      </c>
-      <c r="AT78" t="n">
-        <v>71.10526315789474</v>
-      </c>
-      <c r="AU78" t="n">
-        <v>23.91666666666667</v>
-      </c>
-      <c r="AV78" t="n">
-        <v>182.5</v>
-      </c>
-      <c r="AW78" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX78" t="n">
-        <v>69</v>
-      </c>
-      <c r="AY78" t="n">
-        <v>2183333.333333333</v>
-      </c>
-      <c r="AZ78" t="n">
-        <v>74.125</v>
-      </c>
-      <c r="BA78" t="inlineStr"/>
-      <c r="BB78" t="inlineStr"/>
-      <c r="BC78" t="inlineStr"/>
-      <c r="BD78" t="inlineStr"/>
-      <c r="BE78" t="inlineStr"/>
-      <c r="BF78" t="inlineStr"/>
-      <c r="BG78" t="inlineStr"/>
-      <c r="BH78" t="inlineStr"/>
-      <c r="BI78" t="inlineStr"/>
-      <c r="BJ78" t="inlineStr"/>
-      <c r="BK78" t="inlineStr"/>
-      <c r="BL78" t="inlineStr"/>
-      <c r="BM78" t="inlineStr"/>
-      <c r="BN78" t="inlineStr"/>
-    </row>
-    <row r="79">
-      <c r="A79" s="1" t="inlineStr">
-        <is>
-          <t>lvG7DIkg</t>
-        </is>
-      </c>
-      <c r="B79" s="2" t="n">
-        <v>45522.64583333334</v>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t xml:space="preserve">abisso r 
-  ita </t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stadio benito stirpe
-  frosinone </t>
-        </is>
-      </c>
-      <c r="E79" t="n">
-        <v>16227</v>
-      </c>
-      <c r="F79" t="n">
-        <v>10855</v>
-      </c>
-      <c r="G79" t="n">
-        <v>2</v>
-      </c>
-      <c r="H79" t="n">
-        <v>2</v>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>pfo9H1Wp</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>nJbCGx2U</t>
-        </is>
-      </c>
-      <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr"/>
-      <c r="M79" t="n">
-        <v>45</v>
-      </c>
-      <c r="N79" t="n">
-        <v>55</v>
-      </c>
-      <c r="O79" t="n">
-        <v>20</v>
-      </c>
-      <c r="P79" t="n">
-        <v>17</v>
-      </c>
-      <c r="Q79" t="n">
-        <v>12</v>
-      </c>
-      <c r="R79" t="n">
-        <v>4</v>
-      </c>
-      <c r="S79" t="n">
-        <v>10</v>
-      </c>
-      <c r="T79" t="n">
-        <v>13</v>
-      </c>
-      <c r="U79" t="inlineStr">
-        <is>
-          <t>dnLs0wVo</t>
-        </is>
-      </c>
-      <c r="V79" t="inlineStr">
-        <is>
-          <t>2kfSDavF</t>
-        </is>
-      </c>
-      <c r="W79" t="n">
-        <v>77</v>
-      </c>
-      <c r="X79" t="n">
-        <v>774</v>
-      </c>
-      <c r="Y79" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z79" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="AA79" t="inlineStr">
-        <is>
-          <t>0M9xNN8N</t>
-        </is>
-      </c>
-      <c r="AB79" t="inlineStr">
-        <is>
-          <t>d0PJxeie</t>
-        </is>
-      </c>
-      <c r="AC79" t="n">
-        <v>21.75</v>
-      </c>
-      <c r="AD79" t="n">
-        <v>185.5</v>
-      </c>
-      <c r="AE79" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF79" t="n">
-        <v>65.625</v>
-      </c>
-      <c r="AG79" t="n">
-        <v>1646875</v>
-      </c>
-      <c r="AH79" t="n">
-        <v>74.25</v>
-      </c>
-      <c r="AI79" t="n">
-        <v>27</v>
-      </c>
-      <c r="AJ79" t="n">
-        <v>181.4444444444445</v>
-      </c>
-      <c r="AK79" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL79" t="n">
-        <v>69.66666666666667</v>
-      </c>
-      <c r="AM79" t="n">
-        <v>1680555.555555556</v>
-      </c>
-      <c r="AN79" t="n">
-        <v>72.88888888888889</v>
-      </c>
-      <c r="AO79" t="n">
-        <v>21.78260869565218</v>
-      </c>
-      <c r="AP79" t="n">
-        <v>184.304347826087</v>
-      </c>
-      <c r="AQ79" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR79" t="n">
-        <v>63.91304347826087</v>
-      </c>
-      <c r="AS79" t="n">
-        <v>1310869.565217391</v>
-      </c>
-      <c r="AT79" t="n">
-        <v>74.04347826086956</v>
-      </c>
-      <c r="AU79" t="n">
-        <v>24.42857142857143</v>
-      </c>
-      <c r="AV79" t="n">
-        <v>183.4761904761905</v>
-      </c>
-      <c r="AW79" t="n">
-        <v>1.047619047619048</v>
-      </c>
-      <c r="AX79" t="n">
-        <v>67.76190476190476</v>
-      </c>
-      <c r="AY79" t="n">
-        <v>1782142.857142857</v>
-      </c>
-      <c r="AZ79" t="n">
-        <v>73.28571428571429</v>
-      </c>
-      <c r="BA79" t="inlineStr"/>
-      <c r="BB79" t="inlineStr"/>
-      <c r="BC79" t="inlineStr"/>
-      <c r="BD79" t="inlineStr"/>
-      <c r="BE79" t="inlineStr"/>
-      <c r="BF79" t="inlineStr"/>
-      <c r="BG79" t="inlineStr"/>
-      <c r="BH79" t="inlineStr"/>
-      <c r="BI79" t="inlineStr"/>
-      <c r="BJ79" t="inlineStr"/>
-      <c r="BK79" t="inlineStr"/>
-      <c r="BL79" t="inlineStr"/>
-      <c r="BM79" t="inlineStr"/>
-      <c r="BN79" t="inlineStr"/>
-    </row>
-    <row r="80">
-      <c r="A80" s="1" t="inlineStr">
-        <is>
-          <t>IXMN9zkI</t>
-        </is>
-      </c>
-      <c r="B80" s="2" t="n">
-        <v>45522.64583333334</v>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t xml:space="preserve">arena a 
-  ita </t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mapei stadium – citta del tricolore
-  reggio emilia </t>
-        </is>
-      </c>
-      <c r="E80" t="n">
-        <v>21525</v>
-      </c>
-      <c r="F80" t="n">
-        <v>10255</v>
-      </c>
-      <c r="G80" t="n">
-        <v>2</v>
-      </c>
-      <c r="H80" t="n">
-        <v>2</v>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>6ulJbMCe</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>z7WK5Pwb</t>
-        </is>
-      </c>
-      <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
-      <c r="M80" t="n">
-        <v>30</v>
-      </c>
-      <c r="N80" t="n">
-        <v>70</v>
-      </c>
-      <c r="O80" t="n">
-        <v>12</v>
-      </c>
-      <c r="P80" t="n">
-        <v>13</v>
-      </c>
-      <c r="Q80" t="n">
-        <v>6</v>
-      </c>
-      <c r="R80" t="n">
-        <v>4</v>
-      </c>
-      <c r="S80" t="n">
-        <v>10</v>
-      </c>
-      <c r="T80" t="n">
-        <v>25</v>
-      </c>
-      <c r="U80" t="inlineStr">
-        <is>
-          <t>Gfur2NmR</t>
-        </is>
-      </c>
-      <c r="V80" t="inlineStr">
-        <is>
-          <t>hrkecaMB</t>
-        </is>
-      </c>
-      <c r="W80" t="n">
-        <v>77</v>
-      </c>
-      <c r="X80" t="n">
-        <v>774</v>
-      </c>
-      <c r="Y80" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z80" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="AA80" t="inlineStr"/>
-      <c r="AB80" t="inlineStr"/>
-      <c r="AC80" t="n">
-        <v>25.7</v>
-      </c>
-      <c r="AD80" t="n">
-        <v>182.7</v>
-      </c>
-      <c r="AE80" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF80" t="n">
-        <v>64.3</v>
-      </c>
-      <c r="AG80" t="n">
-        <v>939000</v>
-      </c>
-      <c r="AH80" t="n">
-        <v>68</v>
-      </c>
-      <c r="AI80" t="inlineStr"/>
-      <c r="AJ80" t="inlineStr"/>
-      <c r="AK80" t="inlineStr"/>
-      <c r="AL80" t="inlineStr"/>
-      <c r="AM80" t="inlineStr"/>
-      <c r="AN80" t="inlineStr"/>
-      <c r="AO80" t="n">
-        <v>26.84210526315789</v>
-      </c>
-      <c r="AP80" t="n">
-        <v>182.8947368421053</v>
-      </c>
-      <c r="AQ80" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR80" t="n">
-        <v>65.26315789473684</v>
-      </c>
-      <c r="AS80" t="n">
-        <v>1195000</v>
-      </c>
-      <c r="AT80" t="n">
-        <v>69.36842105263158</v>
-      </c>
-      <c r="AU80" t="n">
-        <v>29</v>
-      </c>
-      <c r="AV80" t="n">
-        <v>181.6</v>
-      </c>
-      <c r="AW80" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX80" t="n">
-        <v>70.2</v>
-      </c>
-      <c r="AY80" t="n">
-        <v>1820000</v>
-      </c>
-      <c r="AZ80" t="n">
-        <v>70.2</v>
-      </c>
-      <c r="BA80" t="inlineStr"/>
-      <c r="BB80" t="inlineStr"/>
-      <c r="BC80" t="inlineStr"/>
-      <c r="BD80" t="inlineStr"/>
-      <c r="BE80" t="inlineStr"/>
-      <c r="BF80" t="inlineStr"/>
-      <c r="BG80" t="inlineStr"/>
-      <c r="BH80" t="inlineStr"/>
-      <c r="BI80" t="inlineStr"/>
-      <c r="BJ80" t="inlineStr"/>
-      <c r="BK80" t="inlineStr"/>
-      <c r="BL80" t="inlineStr"/>
-      <c r="BM80" t="inlineStr"/>
-      <c r="BN80" t="inlineStr"/>
-    </row>
-    <row r="81">
-      <c r="A81" s="1" t="inlineStr">
-        <is>
-          <t>6RvR2hEi</t>
-        </is>
-      </c>
-      <c r="B81" s="2" t="n">
-        <v>45522.5625</v>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t xml:space="preserve">marchetti m 
-  ita </t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stadio marc antonio bentegodi
-  verona </t>
-        </is>
-      </c>
-      <c r="E81" t="n">
-        <v>39211</v>
-      </c>
-      <c r="F81" t="n">
-        <v>20027</v>
-      </c>
-      <c r="G81" t="n">
-        <v>3</v>
-      </c>
-      <c r="H81" t="n">
-        <v>0</v>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>rJVAIaHo</t>
-        </is>
-      </c>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t>69Dxbc61</t>
-        </is>
-      </c>
-      <c r="K81" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="L81" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="M81" t="n">
-        <v>32</v>
-      </c>
-      <c r="N81" t="n">
-        <v>68</v>
-      </c>
-      <c r="O81" t="n">
-        <v>8</v>
-      </c>
-      <c r="P81" t="n">
-        <v>15</v>
-      </c>
-      <c r="Q81" t="n">
-        <v>5</v>
-      </c>
-      <c r="R81" t="n">
-        <v>5</v>
-      </c>
-      <c r="S81" t="n">
-        <v>15</v>
-      </c>
-      <c r="T81" t="n">
-        <v>13</v>
-      </c>
-      <c r="U81" t="inlineStr">
-        <is>
-          <t>OW6PtuKn</t>
-        </is>
-      </c>
-      <c r="V81" t="inlineStr">
-        <is>
-          <t>23vSAc12</t>
-        </is>
-      </c>
-      <c r="W81" t="n">
-        <v>77</v>
-      </c>
-      <c r="X81" t="n">
-        <v>771</v>
-      </c>
-      <c r="Y81" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z81" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="AA81" t="inlineStr">
-        <is>
-          <t>69Dxbc61</t>
-        </is>
-      </c>
-      <c r="AB81" t="inlineStr">
-        <is>
-          <t>C06aJvIB</t>
-        </is>
-      </c>
-      <c r="AC81" t="n">
-        <v>25.875</v>
-      </c>
-      <c r="AD81" t="n">
-        <v>185.375</v>
-      </c>
-      <c r="AE81" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AF81" t="n">
-        <v>73.875</v>
-      </c>
-      <c r="AG81" t="n">
-        <v>5387500</v>
-      </c>
-      <c r="AH81" t="n">
-        <v>77</v>
-      </c>
-      <c r="AI81" t="n">
-        <v>27.4</v>
-      </c>
-      <c r="AJ81" t="n">
-        <v>182</v>
-      </c>
-      <c r="AK81" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AL81" t="n">
-        <v>80.7</v>
-      </c>
-      <c r="AM81" t="n">
-        <v>31620000</v>
-      </c>
-      <c r="AN81" t="n">
-        <v>81.5</v>
-      </c>
-      <c r="AO81" t="n">
-        <v>23.77272727272727</v>
-      </c>
-      <c r="AP81" t="n">
-        <v>181.3636363636364</v>
-      </c>
-      <c r="AQ81" t="n">
-        <v>1.045454545454545</v>
-      </c>
-      <c r="AR81" t="n">
-        <v>69.77272727272727</v>
-      </c>
-      <c r="AS81" t="n">
-        <v>3589772.727272727</v>
-      </c>
-      <c r="AT81" t="n">
-        <v>76.31818181818181</v>
-      </c>
-      <c r="AU81" t="n">
-        <v>24.22222222222222</v>
-      </c>
-      <c r="AV81" t="n">
-        <v>182.2222222222222</v>
-      </c>
-      <c r="AW81" t="n">
-        <v>1.388888888888889</v>
-      </c>
-      <c r="AX81" t="n">
-        <v>75.77777777777777</v>
-      </c>
-      <c r="AY81" t="n">
-        <v>15906944.44444444</v>
-      </c>
-      <c r="AZ81" t="n">
-        <v>79.72222222222223</v>
-      </c>
-      <c r="BA81" t="n">
-        <v>23</v>
-      </c>
-      <c r="BB81" t="n">
-        <v>184</v>
-      </c>
-      <c r="BC81" t="n">
-        <v>1</v>
-      </c>
-      <c r="BD81" t="n">
-        <v>1</v>
-      </c>
-      <c r="BE81" t="n">
-        <v>66</v>
-      </c>
-      <c r="BF81" t="n">
-        <v>1400000</v>
-      </c>
-      <c r="BG81" t="n">
-        <v>72</v>
-      </c>
-      <c r="BH81" t="inlineStr"/>
-      <c r="BI81" t="inlineStr"/>
-      <c r="BJ81" t="inlineStr"/>
-      <c r="BK81" t="inlineStr"/>
-      <c r="BL81" t="inlineStr"/>
-      <c r="BM81" t="inlineStr"/>
-      <c r="BN81" t="inlineStr"/>
-    </row>
-    <row r="82">
-      <c r="A82" s="1" t="inlineStr">
-        <is>
-          <t>4xHh663n</t>
-        </is>
-      </c>
-      <c r="B82" s="2" t="n">
-        <v>45522.5625</v>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t xml:space="preserve">caputi m 
-  ita </t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stadio renato dall ara
-  bologna </t>
-        </is>
-      </c>
-      <c r="E82" t="n">
-        <v>38279</v>
-      </c>
-      <c r="F82" t="n">
-        <v>26418</v>
-      </c>
-      <c r="G82" t="n">
-        <v>1</v>
-      </c>
-      <c r="H82" t="n">
-        <v>1</v>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>0M9xNN8N</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>rXw8YKDE</t>
-        </is>
-      </c>
-      <c r="K82" t="n">
-        <v>3.11</v>
-      </c>
-      <c r="L82" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="M82" t="n">
-        <v>74</v>
-      </c>
-      <c r="N82" t="n">
-        <v>26</v>
-      </c>
-      <c r="O82" t="n">
-        <v>22</v>
-      </c>
-      <c r="P82" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q82" t="n">
-        <v>7</v>
-      </c>
-      <c r="R82" t="n">
-        <v>2</v>
-      </c>
-      <c r="S82" t="n">
-        <v>15</v>
-      </c>
-      <c r="T82" t="n">
-        <v>13</v>
-      </c>
-      <c r="U82" t="inlineStr">
-        <is>
-          <t>tjY4uUem</t>
-        </is>
-      </c>
-      <c r="V82" t="inlineStr">
-        <is>
-          <t>ncu4OLs5</t>
-        </is>
-      </c>
-      <c r="W82" t="n">
-        <v>77</v>
-      </c>
-      <c r="X82" t="n">
-        <v>771</v>
-      </c>
-      <c r="Y82" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z82" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="AA82" t="inlineStr">
-        <is>
-          <t>Q3A3IbXH</t>
-        </is>
-      </c>
-      <c r="AB82" t="inlineStr">
-        <is>
-          <t>69Dxbc61</t>
-        </is>
-      </c>
-      <c r="AC82" t="n">
-        <v>25.27272727272727</v>
-      </c>
-      <c r="AD82" t="n">
-        <v>185.8181818181818</v>
-      </c>
-      <c r="AE82" t="n">
-        <v>1.363636363636364</v>
-      </c>
-      <c r="AF82" t="n">
-        <v>74.63636363636364</v>
-      </c>
-      <c r="AG82" t="n">
-        <v>7945454.545454546</v>
-      </c>
-      <c r="AH82" t="n">
-        <v>78.72727272727273</v>
-      </c>
-      <c r="AI82" t="n">
-        <v>25.45454545454545</v>
-      </c>
-      <c r="AJ82" t="n">
-        <v>184.6363636363636</v>
-      </c>
-      <c r="AK82" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL82" t="n">
-        <v>73.45454545454545</v>
-      </c>
-      <c r="AM82" t="n">
-        <v>4818181.818181818</v>
-      </c>
-      <c r="AN82" t="n">
-        <v>76.63636363636364</v>
-      </c>
-      <c r="AO82" t="n">
-        <v>23.46153846153846</v>
-      </c>
-      <c r="AP82" t="n">
-        <v>184.2692307692308</v>
-      </c>
-      <c r="AQ82" t="n">
-        <v>1.115384615384615</v>
-      </c>
-      <c r="AR82" t="n">
-        <v>72.5</v>
-      </c>
-      <c r="AS82" t="n">
-        <v>7831730.769230769</v>
-      </c>
-      <c r="AT82" t="n">
-        <v>78.69230769230769</v>
-      </c>
-      <c r="AU82" t="n">
-        <v>25.47058823529412</v>
-      </c>
-      <c r="AV82" t="n">
-        <v>181.1176470588235</v>
-      </c>
-      <c r="AW82" t="n">
-        <v>1.058823529411765</v>
-      </c>
-      <c r="AX82" t="n">
-        <v>70.82352941176471</v>
-      </c>
-      <c r="AY82" t="n">
-        <v>3123529.411764706</v>
-      </c>
-      <c r="AZ82" t="n">
-        <v>75.35294117647059</v>
-      </c>
-      <c r="BA82" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="BB82" t="n">
-        <v>185.2</v>
-      </c>
-      <c r="BC82" t="n">
-        <v>1</v>
-      </c>
-      <c r="BD82" t="n">
-        <v>5</v>
-      </c>
-      <c r="BE82" t="n">
-        <v>353</v>
-      </c>
-      <c r="BF82" t="n">
-        <v>37325000</v>
-      </c>
-      <c r="BG82" t="n">
-        <v>393</v>
-      </c>
-      <c r="BH82" t="n">
-        <v>25</v>
-      </c>
-      <c r="BI82" t="n">
-        <v>187.5</v>
-      </c>
-      <c r="BJ82" t="n">
-        <v>2</v>
-      </c>
-      <c r="BK82" t="n">
-        <v>2</v>
-      </c>
-      <c r="BL82" t="n">
-        <v>149</v>
-      </c>
-      <c r="BM82" t="n">
-        <v>20800000</v>
-      </c>
-      <c r="BN82" t="n">
-        <v>160</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
